--- a/Data Files/Backoffce/IndexacaoFG/IndexacaoFG_SANTANDER.xlsx
+++ b/Data Files/Backoffce/IndexacaoFG/IndexacaoFG_SANTANDER.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Public\RPA_ALLIANZ\Data Files\Backoffce\IndexacaoFG\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{25C83EC4-1C12-45CD-8A6D-9E0F80170936}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4E6A9ABF-0632-4B50-81C2-434A980A9BC9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7" uniqueCount="7">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="125" uniqueCount="33">
   <si>
     <t xml:space="preserve">status </t>
   </si>
@@ -49,6 +49,84 @@
   </si>
   <si>
     <t>Processar</t>
+  </si>
+  <si>
+    <t>1070</t>
+  </si>
+  <si>
+    <t>Relatório de Recusas - 15 e 16/08/2025</t>
+  </si>
+  <si>
+    <t>133813872</t>
+  </si>
+  <si>
+    <t>133820120</t>
+  </si>
+  <si>
+    <t>133830073</t>
+  </si>
+  <si>
+    <t>133822007</t>
+  </si>
+  <si>
+    <t>133830806</t>
+  </si>
+  <si>
+    <t>133882674</t>
+  </si>
+  <si>
+    <t>133913617</t>
+  </si>
+  <si>
+    <t>133922035</t>
+  </si>
+  <si>
+    <t>133757851</t>
+  </si>
+  <si>
+    <t>133825443</t>
+  </si>
+  <si>
+    <t>133814333</t>
+  </si>
+  <si>
+    <t>133816407</t>
+  </si>
+  <si>
+    <t>133816965</t>
+  </si>
+  <si>
+    <t>133817939</t>
+  </si>
+  <si>
+    <t>133820507</t>
+  </si>
+  <si>
+    <t>133824279</t>
+  </si>
+  <si>
+    <t>133824311</t>
+  </si>
+  <si>
+    <t>133824973</t>
+  </si>
+  <si>
+    <t>133826007</t>
+  </si>
+  <si>
+    <t>133786822</t>
+  </si>
+  <si>
+    <t>133786999</t>
+  </si>
+  <si>
+    <t>133788351</t>
+  </si>
+  <si>
+    <t>133787120</t>
+  </si>
+  <si>
+    <t>Relatório de Recusas  11.08.2025 a 17.08.2025</t>
   </si>
 </sst>
 </file>
@@ -484,97 +562,453 @@
       </c>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A2" s="6"/>
+      <c r="A2" s="6">
+        <v>133745121</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C2" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D2" s="2" t="s">
+        <v>32</v>
+      </c>
       <c r="E2" s="2" t="s">
         <v>6</v>
       </c>
       <c r="F2"/>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A3" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C3" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D3" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="E3" s="2" t="s">
+        <v>6</v>
+      </c>
       <c r="F3"/>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A4" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="B4" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C4" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D4" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="E4" s="2" t="s">
+        <v>6</v>
+      </c>
       <c r="F4"/>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A5" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="B5" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C5" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D5" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="E5" s="2" t="s">
+        <v>6</v>
+      </c>
       <c r="F5"/>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A6" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="B6" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C6" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D6" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="E6" s="2" t="s">
+        <v>6</v>
+      </c>
       <c r="F6"/>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A7" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="B7" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C7" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D7" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="E7" s="2" t="s">
+        <v>6</v>
+      </c>
       <c r="F7"/>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A8" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="B8" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C8" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D8" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="E8" s="2" t="s">
+        <v>6</v>
+      </c>
       <c r="F8"/>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A9" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="B9" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C9" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D9" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="E9" s="2" t="s">
+        <v>6</v>
+      </c>
       <c r="F9"/>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A10" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="B10" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C10" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D10" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="E10" s="2" t="s">
+        <v>6</v>
+      </c>
       <c r="F10"/>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A11" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="B11" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C11" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D11" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="E11" s="2" t="s">
+        <v>6</v>
+      </c>
       <c r="F11"/>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A12" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="B12" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C12" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D12" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="E12" s="2" t="s">
+        <v>6</v>
+      </c>
       <c r="F12"/>
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A13" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="B13" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C13" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D13" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="E13" s="2" t="s">
+        <v>6</v>
+      </c>
       <c r="F13"/>
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A14" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="B14" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C14" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D14" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="E14" s="2" t="s">
+        <v>6</v>
+      </c>
       <c r="F14"/>
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A15" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="B15" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C15" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D15" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="E15" s="2" t="s">
+        <v>6</v>
+      </c>
       <c r="F15"/>
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A16" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="B16" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C16" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D16" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="E16" s="2" t="s">
+        <v>6</v>
+      </c>
       <c r="F16"/>
     </row>
-    <row r="17" spans="6:6" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A17" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="B17" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C17" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D17" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="E17" s="2" t="s">
+        <v>6</v>
+      </c>
       <c r="F17"/>
     </row>
-    <row r="18" spans="6:6" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A18" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="B18" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C18" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D18" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="E18" s="2" t="s">
+        <v>6</v>
+      </c>
       <c r="F18"/>
     </row>
-    <row r="19" spans="6:6" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A19" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="B19" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C19" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D19" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="E19" s="2" t="s">
+        <v>6</v>
+      </c>
       <c r="F19"/>
     </row>
-    <row r="20" spans="6:6" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A20" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="B20" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C20" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D20" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="E20" s="2" t="s">
+        <v>6</v>
+      </c>
       <c r="F20"/>
     </row>
-    <row r="21" spans="6:6" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A21" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="B21" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C21" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D21" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="E21" s="2" t="s">
+        <v>6</v>
+      </c>
       <c r="F21"/>
     </row>
-    <row r="22" spans="6:6" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A22" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="B22" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C22" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D22" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="E22" s="2" t="s">
+        <v>6</v>
+      </c>
       <c r="F22"/>
     </row>
-    <row r="23" spans="6:6" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A23" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="B23" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C23" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D23" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="E23" s="2" t="s">
+        <v>6</v>
+      </c>
       <c r="F23"/>
     </row>
-    <row r="24" spans="6:6" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A24" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="B24" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C24" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D24" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="E24" s="2" t="s">
+        <v>6</v>
+      </c>
       <c r="F24"/>
     </row>
-    <row r="25" spans="6:6" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A25" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="B25" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C25" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D25" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="E25" s="2" t="s">
+        <v>6</v>
+      </c>
       <c r="F25"/>
     </row>
-    <row r="26" spans="6:6" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:6" x14ac:dyDescent="0.25">
       <c r="F26"/>
     </row>
-    <row r="27" spans="6:6" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:6" x14ac:dyDescent="0.25">
       <c r="F27"/>
     </row>
-    <row r="28" spans="6:6" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:6" x14ac:dyDescent="0.25">
       <c r="F28"/>
     </row>
-    <row r="29" spans="6:6" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:6" x14ac:dyDescent="0.25">
       <c r="F29"/>
     </row>
-    <row r="30" spans="6:6" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:6" x14ac:dyDescent="0.25">
       <c r="F30"/>
     </row>
-    <row r="31" spans="6:6" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:6" x14ac:dyDescent="0.25">
       <c r="F31"/>
     </row>
   </sheetData>

--- a/Data Files/Backoffce/IndexacaoFG/IndexacaoFG_SANTANDER.xlsx
+++ b/Data Files/Backoffce/IndexacaoFG/IndexacaoFG_SANTANDER.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Public\RPA_ALLIANZ\Data Files\Backoffce\IndexacaoFG\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Public\RPA_ALLIANZ_TREINAMENTO\Data Files\Backoffce\IndexacaoFG\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4E6A9ABF-0632-4B50-81C2-434A980A9BC9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7E90323A-1F47-40A6-BB99-AF701012AC4A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="125" uniqueCount="33">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="145" uniqueCount="37">
   <si>
     <t xml:space="preserve">status </t>
   </si>
@@ -54,79 +54,91 @@
     <t>1070</t>
   </si>
   <si>
-    <t>Relatório de Recusas - 15 e 16/08/2025</t>
-  </si>
-  <si>
-    <t>133813872</t>
-  </si>
-  <si>
-    <t>133820120</t>
-  </si>
-  <si>
-    <t>133830073</t>
-  </si>
-  <si>
-    <t>133822007</t>
-  </si>
-  <si>
-    <t>133830806</t>
-  </si>
-  <si>
-    <t>133882674</t>
-  </si>
-  <si>
-    <t>133913617</t>
-  </si>
-  <si>
-    <t>133922035</t>
-  </si>
-  <si>
-    <t>133757851</t>
-  </si>
-  <si>
-    <t>133825443</t>
-  </si>
-  <si>
-    <t>133814333</t>
-  </si>
-  <si>
-    <t>133816407</t>
-  </si>
-  <si>
-    <t>133816965</t>
-  </si>
-  <si>
-    <t>133817939</t>
-  </si>
-  <si>
-    <t>133820507</t>
-  </si>
-  <si>
-    <t>133824279</t>
-  </si>
-  <si>
-    <t>133824311</t>
-  </si>
-  <si>
-    <t>133824973</t>
-  </si>
-  <si>
-    <t>133826007</t>
-  </si>
-  <si>
-    <t>133786822</t>
-  </si>
-  <si>
-    <t>133786999</t>
-  </si>
-  <si>
-    <t>133788351</t>
-  </si>
-  <si>
-    <t>133787120</t>
-  </si>
-  <si>
-    <t>Relatório de Recusas  11.08.2025 a 17.08.2025</t>
+    <t>Relatório de Recusas - 18/08/2025</t>
+  </si>
+  <si>
+    <t>133788586</t>
+  </si>
+  <si>
+    <t>133775956</t>
+  </si>
+  <si>
+    <t>133778612</t>
+  </si>
+  <si>
+    <t>133843546</t>
+  </si>
+  <si>
+    <t>133844880</t>
+  </si>
+  <si>
+    <t>133852150</t>
+  </si>
+  <si>
+    <t>133847302</t>
+  </si>
+  <si>
+    <t>133845796</t>
+  </si>
+  <si>
+    <t>133845334</t>
+  </si>
+  <si>
+    <t>133836999</t>
+  </si>
+  <si>
+    <t>133858333</t>
+  </si>
+  <si>
+    <t>133884806</t>
+  </si>
+  <si>
+    <t>133927823</t>
+  </si>
+  <si>
+    <t>133853753</t>
+  </si>
+  <si>
+    <t>133964393</t>
+  </si>
+  <si>
+    <t>133804555</t>
+  </si>
+  <si>
+    <t>133884367</t>
+  </si>
+  <si>
+    <t>133836968</t>
+  </si>
+  <si>
+    <t>133845051</t>
+  </si>
+  <si>
+    <t>133853915</t>
+  </si>
+  <si>
+    <t>133779013</t>
+  </si>
+  <si>
+    <t>133839597</t>
+  </si>
+  <si>
+    <t>133844566</t>
+  </si>
+  <si>
+    <t>133848977</t>
+  </si>
+  <si>
+    <t>133853183</t>
+  </si>
+  <si>
+    <t>133854342</t>
+  </si>
+  <si>
+    <t>133787871</t>
+  </si>
+  <si>
+    <t>Relatório de Recusas  18.08.2025 a 24.08.2025</t>
   </si>
 </sst>
 </file>
@@ -563,7 +575,7 @@
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A2" s="6">
-        <v>133745121</v>
+        <v>133775905</v>
       </c>
       <c r="B2" s="1" t="s">
         <v>7</v>
@@ -572,7 +584,7 @@
         <v>8</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="E2" s="2" t="s">
         <v>6</v>
@@ -590,7 +602,7 @@
         <v>8</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="E3" s="2" t="s">
         <v>6</v>
@@ -608,7 +620,7 @@
         <v>8</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="E4" s="2" t="s">
         <v>6</v>
@@ -626,7 +638,7 @@
         <v>8</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="E5" s="2" t="s">
         <v>6</v>
@@ -644,7 +656,7 @@
         <v>8</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="E6" s="2" t="s">
         <v>6</v>
@@ -662,7 +674,7 @@
         <v>8</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="E7" s="2" t="s">
         <v>6</v>
@@ -680,7 +692,7 @@
         <v>8</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="E8" s="2" t="s">
         <v>6</v>
@@ -698,7 +710,7 @@
         <v>8</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="E9" s="2" t="s">
         <v>6</v>
@@ -716,7 +728,7 @@
         <v>8</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="E10" s="2" t="s">
         <v>6</v>
@@ -734,7 +746,7 @@
         <v>8</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="E11" s="2" t="s">
         <v>6</v>
@@ -752,7 +764,7 @@
         <v>8</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="E12" s="2" t="s">
         <v>6</v>
@@ -770,7 +782,7 @@
         <v>8</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="E13" s="2" t="s">
         <v>6</v>
@@ -788,7 +800,7 @@
         <v>8</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="E14" s="2" t="s">
         <v>6</v>
@@ -806,7 +818,7 @@
         <v>8</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="E15" s="2" t="s">
         <v>6</v>
@@ -824,7 +836,7 @@
         <v>8</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="E16" s="2" t="s">
         <v>6</v>
@@ -842,7 +854,7 @@
         <v>8</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="E17" s="2" t="s">
         <v>6</v>
@@ -860,7 +872,7 @@
         <v>8</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="E18" s="2" t="s">
         <v>6</v>
@@ -878,7 +890,7 @@
         <v>8</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="E19" s="2" t="s">
         <v>6</v>
@@ -896,7 +908,7 @@
         <v>8</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="E20" s="2" t="s">
         <v>6</v>
@@ -914,7 +926,7 @@
         <v>8</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="E21" s="2" t="s">
         <v>6</v>
@@ -932,7 +944,7 @@
         <v>8</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="E22" s="2" t="s">
         <v>6</v>
@@ -950,7 +962,7 @@
         <v>8</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="E23" s="2" t="s">
         <v>6</v>
@@ -968,7 +980,7 @@
         <v>8</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="E24" s="2" t="s">
         <v>6</v>
@@ -986,23 +998,83 @@
         <v>8</v>
       </c>
       <c r="D25" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="E25" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="F25"/>
+    </row>
+    <row r="26" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A26" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="E25" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="F25"/>
-    </row>
-    <row r="26" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="B26" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C26" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D26" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="E26" s="2" t="s">
+        <v>6</v>
+      </c>
       <c r="F26"/>
     </row>
     <row r="27" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A27" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="B27" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C27" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D27" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="E27" s="2" t="s">
+        <v>6</v>
+      </c>
       <c r="F27"/>
     </row>
     <row r="28" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A28" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="B28" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C28" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D28" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="E28" s="2" t="s">
+        <v>6</v>
+      </c>
       <c r="F28"/>
     </row>
     <row r="29" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A29" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="B29" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C29" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D29" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="E29" s="2" t="s">
+        <v>6</v>
+      </c>
       <c r="F29"/>
     </row>
     <row r="30" spans="1:6" x14ac:dyDescent="0.25">

--- a/Data Files/Backoffce/IndexacaoFG/IndexacaoFG_SANTANDER.xlsx
+++ b/Data Files/Backoffce/IndexacaoFG/IndexacaoFG_SANTANDER.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Public\RPA_ALLIANZ_TREINAMENTO\Data Files\Backoffce\IndexacaoFG\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7E90323A-1F47-40A6-BB99-AF701012AC4A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{89BADC9F-F2F9-4CFD-AE46-52BAE801AEE0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="145" uniqueCount="37">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="155" uniqueCount="39">
   <si>
     <t xml:space="preserve">status </t>
   </si>
@@ -54,91 +54,97 @@
     <t>1070</t>
   </si>
   <si>
-    <t>Relatório de Recusas - 18/08/2025</t>
-  </si>
-  <si>
-    <t>133788586</t>
-  </si>
-  <si>
-    <t>133775956</t>
-  </si>
-  <si>
-    <t>133778612</t>
-  </si>
-  <si>
-    <t>133843546</t>
-  </si>
-  <si>
-    <t>133844880</t>
-  </si>
-  <si>
-    <t>133852150</t>
-  </si>
-  <si>
-    <t>133847302</t>
-  </si>
-  <si>
-    <t>133845796</t>
-  </si>
-  <si>
-    <t>133845334</t>
-  </si>
-  <si>
-    <t>133836999</t>
-  </si>
-  <si>
-    <t>133858333</t>
-  </si>
-  <si>
-    <t>133884806</t>
-  </si>
-  <si>
-    <t>133927823</t>
-  </si>
-  <si>
-    <t>133853753</t>
-  </si>
-  <si>
-    <t>133964393</t>
-  </si>
-  <si>
-    <t>133804555</t>
-  </si>
-  <si>
-    <t>133884367</t>
-  </si>
-  <si>
-    <t>133836968</t>
-  </si>
-  <si>
-    <t>133845051</t>
-  </si>
-  <si>
-    <t>133853915</t>
-  </si>
-  <si>
-    <t>133779013</t>
-  </si>
-  <si>
-    <t>133839597</t>
-  </si>
-  <si>
-    <t>133844566</t>
-  </si>
-  <si>
-    <t>133848977</t>
-  </si>
-  <si>
-    <t>133853183</t>
-  </si>
-  <si>
-    <t>133854342</t>
-  </si>
-  <si>
-    <t>133787871</t>
-  </si>
-  <si>
     <t>Relatório de Recusas  18.08.2025 a 24.08.2025</t>
+  </si>
+  <si>
+    <t>Relatório de Recusas - 19/08/2025</t>
+  </si>
+  <si>
+    <t>133803315</t>
+  </si>
+  <si>
+    <t>133861062</t>
+  </si>
+  <si>
+    <t>133868104</t>
+  </si>
+  <si>
+    <t>133875420</t>
+  </si>
+  <si>
+    <t>133877557</t>
+  </si>
+  <si>
+    <t>133876760</t>
+  </si>
+  <si>
+    <t>133879524</t>
+  </si>
+  <si>
+    <t>133872254</t>
+  </si>
+  <si>
+    <t>133870244</t>
+  </si>
+  <si>
+    <t>133880078</t>
+  </si>
+  <si>
+    <t>133922650</t>
+  </si>
+  <si>
+    <t>133911512</t>
+  </si>
+  <si>
+    <t>133905990</t>
+  </si>
+  <si>
+    <t>133911050</t>
+  </si>
+  <si>
+    <t>133935279</t>
+  </si>
+  <si>
+    <t>133932051</t>
+  </si>
+  <si>
+    <t>133946707</t>
+  </si>
+  <si>
+    <t>133876306</t>
+  </si>
+  <si>
+    <t>133932144</t>
+  </si>
+  <si>
+    <t>133869524</t>
+  </si>
+  <si>
+    <t>133867026</t>
+  </si>
+  <si>
+    <t>133867535</t>
+  </si>
+  <si>
+    <t>133873348</t>
+  </si>
+  <si>
+    <t>133874234</t>
+  </si>
+  <si>
+    <t>133876009</t>
+  </si>
+  <si>
+    <t>133911850</t>
+  </si>
+  <si>
+    <t>133800340</t>
+  </si>
+  <si>
+    <t>133915274</t>
+  </si>
+  <si>
+    <t>133771620</t>
   </si>
 </sst>
 </file>
@@ -575,16 +581,16 @@
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A2" s="6">
-        <v>133775905</v>
+        <v>133808844</v>
       </c>
       <c r="B2" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>36</v>
+        <v>8</v>
       </c>
       <c r="E2" s="2" t="s">
         <v>6</v>
@@ -593,16 +599,16 @@
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B3" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>36</v>
+        <v>8</v>
       </c>
       <c r="E3" s="2" t="s">
         <v>6</v>
@@ -611,16 +617,16 @@
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B4" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>36</v>
+        <v>8</v>
       </c>
       <c r="E4" s="2" t="s">
         <v>6</v>
@@ -629,16 +635,16 @@
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B5" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>36</v>
+        <v>8</v>
       </c>
       <c r="E5" s="2" t="s">
         <v>6</v>
@@ -647,16 +653,16 @@
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" s="1" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B6" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>36</v>
+        <v>8</v>
       </c>
       <c r="E6" s="2" t="s">
         <v>6</v>
@@ -665,16 +671,16 @@
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" s="1" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B7" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>36</v>
+        <v>8</v>
       </c>
       <c r="E7" s="2" t="s">
         <v>6</v>
@@ -683,16 +689,16 @@
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" s="1" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="B8" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>36</v>
+        <v>8</v>
       </c>
       <c r="E8" s="2" t="s">
         <v>6</v>
@@ -701,16 +707,16 @@
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B9" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>36</v>
+        <v>8</v>
       </c>
       <c r="E9" s="2" t="s">
         <v>6</v>
@@ -719,16 +725,16 @@
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A10" s="1" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="B10" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>36</v>
+        <v>8</v>
       </c>
       <c r="E10" s="2" t="s">
         <v>6</v>
@@ -737,16 +743,16 @@
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A11" s="1" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="B11" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>36</v>
+        <v>8</v>
       </c>
       <c r="E11" s="2" t="s">
         <v>6</v>
@@ -755,16 +761,16 @@
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A12" s="1" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B12" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>36</v>
+        <v>8</v>
       </c>
       <c r="E12" s="2" t="s">
         <v>6</v>
@@ -773,16 +779,16 @@
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A13" s="1" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B13" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>36</v>
+        <v>8</v>
       </c>
       <c r="E13" s="2" t="s">
         <v>6</v>
@@ -791,16 +797,16 @@
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A14" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B14" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>36</v>
+        <v>8</v>
       </c>
       <c r="E14" s="2" t="s">
         <v>6</v>
@@ -809,16 +815,16 @@
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A15" s="1" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="B15" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>36</v>
+        <v>8</v>
       </c>
       <c r="E15" s="2" t="s">
         <v>6</v>
@@ -827,16 +833,16 @@
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A16" s="1" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B16" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>36</v>
+        <v>8</v>
       </c>
       <c r="E16" s="2" t="s">
         <v>6</v>
@@ -845,16 +851,16 @@
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A17" s="1" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="B17" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>36</v>
+        <v>8</v>
       </c>
       <c r="E17" s="2" t="s">
         <v>6</v>
@@ -863,16 +869,16 @@
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A18" s="1" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="B18" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>36</v>
+        <v>8</v>
       </c>
       <c r="E18" s="2" t="s">
         <v>6</v>
@@ -881,16 +887,16 @@
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A19" s="1" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="B19" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>36</v>
+        <v>8</v>
       </c>
       <c r="E19" s="2" t="s">
         <v>6</v>
@@ -899,16 +905,16 @@
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A20" s="1" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="B20" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>36</v>
+        <v>8</v>
       </c>
       <c r="E20" s="2" t="s">
         <v>6</v>
@@ -917,16 +923,16 @@
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A21" s="1" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="B21" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>36</v>
+        <v>8</v>
       </c>
       <c r="E21" s="2" t="s">
         <v>6</v>
@@ -935,16 +941,16 @@
     </row>
     <row r="22" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A22" s="1" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="B22" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>36</v>
+        <v>8</v>
       </c>
       <c r="E22" s="2" t="s">
         <v>6</v>
@@ -953,16 +959,16 @@
     </row>
     <row r="23" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A23" s="1" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B23" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>36</v>
+        <v>8</v>
       </c>
       <c r="E23" s="2" t="s">
         <v>6</v>
@@ -971,16 +977,16 @@
     </row>
     <row r="24" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A24" s="1" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B24" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C24" s="2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>36</v>
+        <v>8</v>
       </c>
       <c r="E24" s="2" t="s">
         <v>6</v>
@@ -989,16 +995,16 @@
     </row>
     <row r="25" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A25" s="1" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="B25" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C25" s="2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D25" s="2" t="s">
-        <v>36</v>
+        <v>8</v>
       </c>
       <c r="E25" s="2" t="s">
         <v>6</v>
@@ -1007,16 +1013,16 @@
     </row>
     <row r="26" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A26" s="1" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="B26" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C26" s="2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D26" s="2" t="s">
-        <v>36</v>
+        <v>8</v>
       </c>
       <c r="E26" s="2" t="s">
         <v>6</v>
@@ -1025,16 +1031,16 @@
     </row>
     <row r="27" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A27" s="1" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B27" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C27" s="2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D27" s="2" t="s">
-        <v>36</v>
+        <v>8</v>
       </c>
       <c r="E27" s="2" t="s">
         <v>6</v>
@@ -1043,16 +1049,16 @@
     </row>
     <row r="28" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A28" s="1" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="B28" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C28" s="2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D28" s="2" t="s">
-        <v>36</v>
+        <v>8</v>
       </c>
       <c r="E28" s="2" t="s">
         <v>6</v>
@@ -1061,16 +1067,16 @@
     </row>
     <row r="29" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A29" s="1" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="B29" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C29" s="2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D29" s="2" t="s">
-        <v>36</v>
+        <v>8</v>
       </c>
       <c r="E29" s="2" t="s">
         <v>6</v>
@@ -1078,9 +1084,39 @@
       <c r="F29"/>
     </row>
     <row r="30" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A30" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="B30" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C30" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D30" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E30" s="2" t="s">
+        <v>6</v>
+      </c>
       <c r="F30"/>
     </row>
     <row r="31" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A31" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="B31" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C31" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D31" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E31" s="2" t="s">
+        <v>6</v>
+      </c>
       <c r="F31"/>
     </row>
   </sheetData>

--- a/Data Files/Backoffce/IndexacaoFG/IndexacaoFG_SANTANDER.xlsx
+++ b/Data Files/Backoffce/IndexacaoFG/IndexacaoFG_SANTANDER.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Public\RPA_ALLIANZ_TREINAMENTO\Data Files\Backoffce\IndexacaoFG\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{89BADC9F-F2F9-4CFD-AE46-52BAE801AEE0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4C139DA7-F925-4ABD-B344-00E2ED994044}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="155" uniqueCount="39">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="165" uniqueCount="41">
   <si>
     <t xml:space="preserve">status </t>
   </si>
@@ -57,94 +57,100 @@
     <t>Relatório de Recusas  18.08.2025 a 24.08.2025</t>
   </si>
   <si>
-    <t>Relatório de Recusas - 19/08/2025</t>
-  </si>
-  <si>
-    <t>133803315</t>
-  </si>
-  <si>
-    <t>133861062</t>
-  </si>
-  <si>
-    <t>133868104</t>
-  </si>
-  <si>
-    <t>133875420</t>
-  </si>
-  <si>
-    <t>133877557</t>
-  </si>
-  <si>
-    <t>133876760</t>
-  </si>
-  <si>
-    <t>133879524</t>
-  </si>
-  <si>
-    <t>133872254</t>
-  </si>
-  <si>
-    <t>133870244</t>
-  </si>
-  <si>
-    <t>133880078</t>
-  </si>
-  <si>
-    <t>133922650</t>
-  </si>
-  <si>
-    <t>133911512</t>
-  </si>
-  <si>
-    <t>133905990</t>
-  </si>
-  <si>
-    <t>133911050</t>
-  </si>
-  <si>
-    <t>133935279</t>
-  </si>
-  <si>
-    <t>133932051</t>
-  </si>
-  <si>
-    <t>133946707</t>
-  </si>
-  <si>
-    <t>133876306</t>
-  </si>
-  <si>
-    <t>133932144</t>
-  </si>
-  <si>
-    <t>133869524</t>
-  </si>
-  <si>
-    <t>133867026</t>
-  </si>
-  <si>
-    <t>133867535</t>
-  </si>
-  <si>
-    <t>133873348</t>
-  </si>
-  <si>
-    <t>133874234</t>
-  </si>
-  <si>
-    <t>133876009</t>
-  </si>
-  <si>
-    <t>133911850</t>
-  </si>
-  <si>
-    <t>133800340</t>
-  </si>
-  <si>
-    <t>133915274</t>
-  </si>
-  <si>
-    <t>133771620</t>
+    <t>Relatório de Recusas Santander - 20/08/2025</t>
+  </si>
+  <si>
+    <t>133900643</t>
+  </si>
+  <si>
+    <t>133899667</t>
+  </si>
+  <si>
+    <t>133886492</t>
+  </si>
+  <si>
+    <t>133883689</t>
+  </si>
+  <si>
+    <t>133888951</t>
+  </si>
+  <si>
+    <t>133900517</t>
+  </si>
+  <si>
+    <t>133905982</t>
+  </si>
+  <si>
+    <t>133935397</t>
+  </si>
+  <si>
+    <t>133955878</t>
+  </si>
+  <si>
+    <t>133831480</t>
+  </si>
+  <si>
+    <t>133991674</t>
+  </si>
+  <si>
+    <t>133825672</t>
+  </si>
+  <si>
+    <t>133821785</t>
+  </si>
+  <si>
+    <t>133891318</t>
+  </si>
+  <si>
+    <t>133886466</t>
+  </si>
+  <si>
+    <t>133884071</t>
+  </si>
+  <si>
+    <t>133882691</t>
+  </si>
+  <si>
+    <t>133884174</t>
+  </si>
+  <si>
+    <t>133884764</t>
+  </si>
+  <si>
+    <t>133885292</t>
+  </si>
+  <si>
+    <t>133886200</t>
+  </si>
+  <si>
+    <t>133887225</t>
+  </si>
+  <si>
+    <t>133888000</t>
+  </si>
+  <si>
+    <t>133889763</t>
+  </si>
+  <si>
+    <t>133891148</t>
+  </si>
+  <si>
+    <t>133893013</t>
+  </si>
+  <si>
+    <t>133895953</t>
+  </si>
+  <si>
+    <t>133899379</t>
+  </si>
+  <si>
+    <t>133900805</t>
+  </si>
+  <si>
+    <t>133842513</t>
+  </si>
+  <si>
+    <t>133921749</t>
   </si>
 </sst>
 </file>
@@ -549,7 +555,7 @@
   <sheetPr>
     <pageSetUpPr autoPageBreaks="0"/>
   </sheetPr>
-  <dimension ref="A1:F31"/>
+  <dimension ref="A1:F33"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="2" width="16.7109375" style="1" customWidth="1" collapsed="1"/>
@@ -581,7 +587,7 @@
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A2" s="6">
-        <v>133808844</v>
+        <v>133826900</v>
       </c>
       <c r="B2" s="1" t="s">
         <v>7</v>
@@ -1118,6 +1124,40 @@
         <v>6</v>
       </c>
       <c r="F31"/>
+    </row>
+    <row r="32" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A32" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="B32" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C32" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D32" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E32" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="33" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A33" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="B33" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C33" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D33" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E33" s="2" t="s">
+        <v>6</v>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:F1" xr:uid="{00000000-0001-0000-0000-000000000000}"/>

--- a/Data Files/Backoffce/IndexacaoFG/IndexacaoFG_SANTANDER.xlsx
+++ b/Data Files/Backoffce/IndexacaoFG/IndexacaoFG_SANTANDER.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Public\RPA_ALLIANZ_TREINAMENTO\Data Files\Backoffce\IndexacaoFG\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4C139DA7-F925-4ABD-B344-00E2ED994044}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5D64454E-BBBC-4B53-8618-8798F73E6D5B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="165" uniqueCount="41">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="120" uniqueCount="32">
   <si>
     <t xml:space="preserve">status </t>
   </si>
@@ -54,103 +54,76 @@
     <t>1070</t>
   </si>
   <si>
-    <t>Relatório de Recusas  18.08.2025 a 24.08.2025</t>
-  </si>
-  <si>
-    <t>Relatório de Recusas Santander - 20/08/2025</t>
-  </si>
-  <si>
-    <t>133900643</t>
-  </si>
-  <si>
-    <t>133899667</t>
-  </si>
-  <si>
-    <t>133886492</t>
-  </si>
-  <si>
-    <t>133883689</t>
-  </si>
-  <si>
-    <t>133888951</t>
-  </si>
-  <si>
-    <t>133900517</t>
-  </si>
-  <si>
-    <t>133905982</t>
-  </si>
-  <si>
-    <t>133935397</t>
-  </si>
-  <si>
-    <t>133955878</t>
-  </si>
-  <si>
-    <t>133831480</t>
-  </si>
-  <si>
-    <t>133991674</t>
-  </si>
-  <si>
-    <t>133825672</t>
-  </si>
-  <si>
-    <t>133821785</t>
-  </si>
-  <si>
-    <t>133891318</t>
-  </si>
-  <si>
-    <t>133886466</t>
-  </si>
-  <si>
-    <t>133884071</t>
-  </si>
-  <si>
-    <t>133882691</t>
-  </si>
-  <si>
-    <t>133884174</t>
-  </si>
-  <si>
-    <t>133884764</t>
-  </si>
-  <si>
-    <t>133885292</t>
-  </si>
-  <si>
-    <t>133886200</t>
-  </si>
-  <si>
-    <t>133887225</t>
-  </si>
-  <si>
-    <t>133888000</t>
-  </si>
-  <si>
-    <t>133889763</t>
-  </si>
-  <si>
-    <t>133891148</t>
-  </si>
-  <si>
-    <t>133893013</t>
-  </si>
-  <si>
-    <t>133895953</t>
-  </si>
-  <si>
-    <t>133899379</t>
-  </si>
-  <si>
-    <t>133900805</t>
-  </si>
-  <si>
-    <t>133842513</t>
-  </si>
-  <si>
-    <t>133921749</t>
+    <t>Relatório de Recusas  18.08.2025 a 24.08.2025 (2)</t>
+  </si>
+  <si>
+    <t>Relatório de Recusas Santander - 21/08/2025</t>
+  </si>
+  <si>
+    <t>133923062</t>
+  </si>
+  <si>
+    <t>133922170</t>
+  </si>
+  <si>
+    <t>133905503</t>
+  </si>
+  <si>
+    <t>133911420</t>
+  </si>
+  <si>
+    <t>133933085</t>
+  </si>
+  <si>
+    <t>133985114</t>
+  </si>
+  <si>
+    <t>134005144</t>
+  </si>
+  <si>
+    <t>134014878</t>
+  </si>
+  <si>
+    <t>134000835</t>
+  </si>
+  <si>
+    <t>133919464</t>
+  </si>
+  <si>
+    <t>133912813</t>
+  </si>
+  <si>
+    <t>133846121</t>
+  </si>
+  <si>
+    <t>133908635</t>
+  </si>
+  <si>
+    <t>133914655</t>
+  </si>
+  <si>
+    <t>133912574</t>
+  </si>
+  <si>
+    <t>133884538</t>
+  </si>
+  <si>
+    <t>133916595</t>
+  </si>
+  <si>
+    <t>133918760</t>
+  </si>
+  <si>
+    <t>133919246</t>
+  </si>
+  <si>
+    <t>133920065</t>
+  </si>
+  <si>
+    <t>133924364</t>
+  </si>
+  <si>
+    <t>133986355</t>
   </si>
 </sst>
 </file>
@@ -555,7 +528,7 @@
   <sheetPr>
     <pageSetUpPr autoPageBreaks="0"/>
   </sheetPr>
-  <dimension ref="A1:F33"/>
+  <dimension ref="A1:F31"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="2" width="16.7109375" style="1" customWidth="1" collapsed="1"/>
@@ -587,7 +560,7 @@
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A2" s="6">
-        <v>133826900</v>
+        <v>133856610</v>
       </c>
       <c r="B2" s="1" t="s">
         <v>7</v>
@@ -1000,164 +973,25 @@
       <c r="F24"/>
     </row>
     <row r="25" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A25" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="B25" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C25" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D25" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="E25" s="2" t="s">
-        <v>6</v>
-      </c>
       <c r="F25"/>
     </row>
     <row r="26" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A26" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="B26" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C26" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D26" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="E26" s="2" t="s">
-        <v>6</v>
-      </c>
       <c r="F26"/>
     </row>
     <row r="27" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A27" s="1" t="s">
-        <v>34</v>
-      </c>
-      <c r="B27" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C27" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D27" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="E27" s="2" t="s">
-        <v>6</v>
-      </c>
       <c r="F27"/>
     </row>
     <row r="28" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A28" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="B28" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C28" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D28" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="E28" s="2" t="s">
-        <v>6</v>
-      </c>
       <c r="F28"/>
     </row>
     <row r="29" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A29" s="1" t="s">
-        <v>36</v>
-      </c>
-      <c r="B29" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C29" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D29" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="E29" s="2" t="s">
-        <v>6</v>
-      </c>
       <c r="F29"/>
     </row>
     <row r="30" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A30" s="1" t="s">
-        <v>37</v>
-      </c>
-      <c r="B30" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C30" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D30" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="E30" s="2" t="s">
-        <v>6</v>
-      </c>
       <c r="F30"/>
     </row>
     <row r="31" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A31" s="1" t="s">
-        <v>38</v>
-      </c>
-      <c r="B31" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C31" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D31" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="E31" s="2" t="s">
-        <v>6</v>
-      </c>
       <c r="F31"/>
-    </row>
-    <row r="32" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A32" s="1" t="s">
-        <v>39</v>
-      </c>
-      <c r="B32" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C32" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D32" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="E32" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="33" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A33" s="1" t="s">
-        <v>40</v>
-      </c>
-      <c r="B33" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C33" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D33" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="E33" s="2" t="s">
-        <v>6</v>
-      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:F1" xr:uid="{00000000-0001-0000-0000-000000000000}"/>

--- a/Data Files/Backoffce/IndexacaoFG/IndexacaoFG_SANTANDER.xlsx
+++ b/Data Files/Backoffce/IndexacaoFG/IndexacaoFG_SANTANDER.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Public\RPA_ALLIANZ_TREINAMENTO\Data Files\Backoffce\IndexacaoFG\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5D64454E-BBBC-4B53-8618-8798F73E6D5B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B6AFB659-12A1-4C2B-A6DC-7EEA2D941A39}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="120" uniqueCount="32">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="190" uniqueCount="46">
   <si>
     <t xml:space="preserve">status </t>
   </si>
@@ -54,76 +54,118 @@
     <t>1070</t>
   </si>
   <si>
-    <t>Relatório de Recusas  18.08.2025 a 24.08.2025 (2)</t>
-  </si>
-  <si>
-    <t>Relatório de Recusas Santander - 21/08/2025</t>
-  </si>
-  <si>
-    <t>133923062</t>
-  </si>
-  <si>
-    <t>133922170</t>
-  </si>
-  <si>
-    <t>133905503</t>
-  </si>
-  <si>
-    <t>133911420</t>
-  </si>
-  <si>
-    <t>133933085</t>
-  </si>
-  <si>
-    <t>133985114</t>
-  </si>
-  <si>
-    <t>134005144</t>
-  </si>
-  <si>
-    <t>134014878</t>
-  </si>
-  <si>
-    <t>134000835</t>
-  </si>
-  <si>
-    <t>133919464</t>
-  </si>
-  <si>
-    <t>133912813</t>
-  </si>
-  <si>
-    <t>133846121</t>
-  </si>
-  <si>
-    <t>133908635</t>
-  </si>
-  <si>
-    <t>133914655</t>
-  </si>
-  <si>
-    <t>133912574</t>
-  </si>
-  <si>
-    <t>133884538</t>
-  </si>
-  <si>
-    <t>133916595</t>
-  </si>
-  <si>
-    <t>133918760</t>
-  </si>
-  <si>
-    <t>133919246</t>
-  </si>
-  <si>
-    <t>133920065</t>
-  </si>
-  <si>
-    <t>133924364</t>
-  </si>
-  <si>
-    <t>133986355</t>
+    <t>Relatório de Recusas Santander - 22 e 23/08/2025</t>
+  </si>
+  <si>
+    <t>133945181</t>
+  </si>
+  <si>
+    <t>133941672</t>
+  </si>
+  <si>
+    <t>133944838</t>
+  </si>
+  <si>
+    <t>133943216</t>
+  </si>
+  <si>
+    <t>133945919</t>
+  </si>
+  <si>
+    <t>133946502</t>
+  </si>
+  <si>
+    <t>133950757</t>
+  </si>
+  <si>
+    <t>133957142</t>
+  </si>
+  <si>
+    <t>133955314</t>
+  </si>
+  <si>
+    <t>133965171</t>
+  </si>
+  <si>
+    <t>133988082</t>
+  </si>
+  <si>
+    <t>133938526</t>
+  </si>
+  <si>
+    <t>133998849</t>
+  </si>
+  <si>
+    <t>134003321</t>
+  </si>
+  <si>
+    <t>134013696</t>
+  </si>
+  <si>
+    <t>133940676</t>
+  </si>
+  <si>
+    <t>134028714</t>
+  </si>
+  <si>
+    <t>133944288</t>
+  </si>
+  <si>
+    <t>133945536</t>
+  </si>
+  <si>
+    <t>133867375</t>
+  </si>
+  <si>
+    <t>133867440</t>
+  </si>
+  <si>
+    <t>133933745</t>
+  </si>
+  <si>
+    <t>133934159</t>
+  </si>
+  <si>
+    <t>133937435</t>
+  </si>
+  <si>
+    <t>133937572</t>
+  </si>
+  <si>
+    <t>133938063</t>
+  </si>
+  <si>
+    <t>133945619</t>
+  </si>
+  <si>
+    <t>133940538</t>
+  </si>
+  <si>
+    <t>133941656</t>
+  </si>
+  <si>
+    <t>133943853</t>
+  </si>
+  <si>
+    <t>133944333</t>
+  </si>
+  <si>
+    <t>133944732</t>
+  </si>
+  <si>
+    <t>133945826</t>
+  </si>
+  <si>
+    <t>133946111</t>
+  </si>
+  <si>
+    <t>133947348</t>
+  </si>
+  <si>
+    <t>133899410</t>
+  </si>
+  <si>
+    <t>Relatório de Recusas  18.08.2025 a 24.08.2025</t>
   </si>
 </sst>
 </file>
@@ -528,7 +570,7 @@
   <sheetPr>
     <pageSetUpPr autoPageBreaks="0"/>
   </sheetPr>
-  <dimension ref="A1:F31"/>
+  <dimension ref="A1:F38"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="2" width="16.7109375" style="1" customWidth="1" collapsed="1"/>
@@ -560,16 +602,16 @@
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A2" s="6">
-        <v>133856610</v>
+        <v>133946662</v>
       </c>
       <c r="B2" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>8</v>
+        <v>45</v>
       </c>
       <c r="E2" s="2" t="s">
         <v>6</v>
@@ -578,16 +620,16 @@
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B3" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>8</v>
+        <v>45</v>
       </c>
       <c r="E3" s="2" t="s">
         <v>6</v>
@@ -596,16 +638,16 @@
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B4" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>8</v>
+        <v>45</v>
       </c>
       <c r="E4" s="2" t="s">
         <v>6</v>
@@ -614,16 +656,16 @@
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B5" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>8</v>
+        <v>45</v>
       </c>
       <c r="E5" s="2" t="s">
         <v>6</v>
@@ -632,16 +674,16 @@
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" s="1" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B6" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>8</v>
+        <v>45</v>
       </c>
       <c r="E6" s="2" t="s">
         <v>6</v>
@@ -650,16 +692,16 @@
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" s="1" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B7" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>8</v>
+        <v>45</v>
       </c>
       <c r="E7" s="2" t="s">
         <v>6</v>
@@ -668,16 +710,16 @@
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" s="1" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B8" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>8</v>
+        <v>45</v>
       </c>
       <c r="E8" s="2" t="s">
         <v>6</v>
@@ -686,16 +728,16 @@
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" s="1" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B9" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>8</v>
+        <v>45</v>
       </c>
       <c r="E9" s="2" t="s">
         <v>6</v>
@@ -704,16 +746,16 @@
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A10" s="1" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B10" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>8</v>
+        <v>45</v>
       </c>
       <c r="E10" s="2" t="s">
         <v>6</v>
@@ -722,16 +764,16 @@
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A11" s="1" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B11" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>8</v>
+        <v>45</v>
       </c>
       <c r="E11" s="2" t="s">
         <v>6</v>
@@ -740,16 +782,16 @@
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A12" s="1" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B12" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>8</v>
+        <v>45</v>
       </c>
       <c r="E12" s="2" t="s">
         <v>6</v>
@@ -758,16 +800,16 @@
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A13" s="1" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B13" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>8</v>
+        <v>45</v>
       </c>
       <c r="E13" s="2" t="s">
         <v>6</v>
@@ -776,16 +818,16 @@
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A14" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="B14" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>8</v>
+        <v>45</v>
       </c>
       <c r="E14" s="2" t="s">
         <v>6</v>
@@ -794,16 +836,16 @@
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A15" s="1" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B15" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>8</v>
+        <v>45</v>
       </c>
       <c r="E15" s="2" t="s">
         <v>6</v>
@@ -812,16 +854,16 @@
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A16" s="1" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B16" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>8</v>
+        <v>45</v>
       </c>
       <c r="E16" s="2" t="s">
         <v>6</v>
@@ -830,16 +872,16 @@
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A17" s="1" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B17" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>8</v>
+        <v>45</v>
       </c>
       <c r="E17" s="2" t="s">
         <v>6</v>
@@ -848,16 +890,16 @@
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A18" s="1" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B18" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>8</v>
+        <v>45</v>
       </c>
       <c r="E18" s="2" t="s">
         <v>6</v>
@@ -866,16 +908,16 @@
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A19" s="1" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B19" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>8</v>
+        <v>45</v>
       </c>
       <c r="E19" s="2" t="s">
         <v>6</v>
@@ -884,16 +926,16 @@
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A20" s="1" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="B20" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>8</v>
+        <v>45</v>
       </c>
       <c r="E20" s="2" t="s">
         <v>6</v>
@@ -902,16 +944,16 @@
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A21" s="1" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="B21" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>8</v>
+        <v>45</v>
       </c>
       <c r="E21" s="2" t="s">
         <v>6</v>
@@ -920,16 +962,16 @@
     </row>
     <row r="22" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A22" s="1" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="B22" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>8</v>
+        <v>45</v>
       </c>
       <c r="E22" s="2" t="s">
         <v>6</v>
@@ -938,16 +980,16 @@
     </row>
     <row r="23" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A23" s="1" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B23" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>8</v>
+        <v>45</v>
       </c>
       <c r="E23" s="2" t="s">
         <v>6</v>
@@ -956,42 +998,266 @@
     </row>
     <row r="24" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A24" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="B24" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C24" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D24" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="E24" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="F24"/>
+    </row>
+    <row r="25" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A25" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="B24" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C24" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D24" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="E24" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="F24"/>
-    </row>
-    <row r="25" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="B25" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C25" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D25" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="E25" s="2" t="s">
+        <v>6</v>
+      </c>
       <c r="F25"/>
     </row>
     <row r="26" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A26" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="B26" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C26" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D26" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="E26" s="2" t="s">
+        <v>6</v>
+      </c>
       <c r="F26"/>
     </row>
     <row r="27" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A27" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="B27" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C27" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D27" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="E27" s="2" t="s">
+        <v>6</v>
+      </c>
       <c r="F27"/>
     </row>
     <row r="28" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A28" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="B28" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C28" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D28" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="E28" s="2" t="s">
+        <v>6</v>
+      </c>
       <c r="F28"/>
     </row>
     <row r="29" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A29" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="B29" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C29" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D29" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="E29" s="2" t="s">
+        <v>6</v>
+      </c>
       <c r="F29"/>
     </row>
     <row r="30" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A30" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="B30" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C30" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D30" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="E30" s="2" t="s">
+        <v>6</v>
+      </c>
       <c r="F30"/>
     </row>
     <row r="31" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A31" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="B31" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C31" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D31" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="E31" s="2" t="s">
+        <v>6</v>
+      </c>
       <c r="F31"/>
+    </row>
+    <row r="32" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A32" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="B32" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C32" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D32" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="E32" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="33" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A33" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="B33" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C33" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D33" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="E33" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="34" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A34" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="B34" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C34" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D34" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="E34" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="35" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A35" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="B35" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C35" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D35" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="E35" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="36" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A36" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="B36" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C36" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D36" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="E36" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="37" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A37" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="B37" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C37" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D37" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="E37" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="38" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A38" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="B38" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C38" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D38" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="E38" s="2" t="s">
+        <v>6</v>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:F1" xr:uid="{00000000-0001-0000-0000-000000000000}"/>

--- a/Data Files/Backoffce/IndexacaoFG/IndexacaoFG_SANTANDER.xlsx
+++ b/Data Files/Backoffce/IndexacaoFG/IndexacaoFG_SANTANDER.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Public\RPA_ALLIANZ_TREINAMENTO\Data Files\Backoffce\IndexacaoFG\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B6AFB659-12A1-4C2B-A6DC-7EEA2D941A39}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{38586527-F0B2-4EE9-959A-712D31B160C2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="190" uniqueCount="46">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="190" uniqueCount="80">
   <si>
     <t xml:space="preserve">status </t>
   </si>
@@ -54,118 +54,220 @@
     <t>1070</t>
   </si>
   <si>
-    <t>Relatório de Recusas Santander - 22 e 23/08/2025</t>
-  </si>
-  <si>
-    <t>133945181</t>
-  </si>
-  <si>
-    <t>133941672</t>
-  </si>
-  <si>
-    <t>133944838</t>
-  </si>
-  <si>
-    <t>133943216</t>
-  </si>
-  <si>
-    <t>133945919</t>
-  </si>
-  <si>
-    <t>133946502</t>
-  </si>
-  <si>
-    <t>133950757</t>
-  </si>
-  <si>
-    <t>133957142</t>
-  </si>
-  <si>
-    <t>133955314</t>
-  </si>
-  <si>
-    <t>133965171</t>
-  </si>
-  <si>
-    <t>133988082</t>
-  </si>
-  <si>
-    <t>133938526</t>
-  </si>
-  <si>
-    <t>133998849</t>
-  </si>
-  <si>
-    <t>134003321</t>
-  </si>
-  <si>
-    <t>134013696</t>
-  </si>
-  <si>
-    <t>133940676</t>
-  </si>
-  <si>
-    <t>134028714</t>
-  </si>
-  <si>
-    <t>133944288</t>
-  </si>
-  <si>
-    <t>133945536</t>
-  </si>
-  <si>
-    <t>133867375</t>
-  </si>
-  <si>
-    <t>133867440</t>
-  </si>
-  <si>
-    <t>133933745</t>
-  </si>
-  <si>
-    <t>133934159</t>
-  </si>
-  <si>
-    <t>133937435</t>
-  </si>
-  <si>
-    <t>133937572</t>
-  </si>
-  <si>
-    <t>133938063</t>
-  </si>
-  <si>
-    <t>133945619</t>
-  </si>
-  <si>
-    <t>133940538</t>
-  </si>
-  <si>
-    <t>133941656</t>
-  </si>
-  <si>
-    <t>133943853</t>
-  </si>
-  <si>
-    <t>133944333</t>
-  </si>
-  <si>
-    <t>133944732</t>
-  </si>
-  <si>
-    <t>133945826</t>
-  </si>
-  <si>
-    <t>133946111</t>
-  </si>
-  <si>
-    <t>133947348</t>
-  </si>
-  <si>
-    <t>133899410</t>
-  </si>
-  <si>
-    <t>Relatório de Recusas  18.08.2025 a 24.08.2025</t>
+    <t>Relatório de Recusas  25.08.2025 a 31.08.2025</t>
+  </si>
+  <si>
+    <t>Relatório de Recusas  25.08.2025 a 31.08.2026</t>
+  </si>
+  <si>
+    <t>Relatório de Recusas  25.08.2025 a 31.08.2027</t>
+  </si>
+  <si>
+    <t>Relatório de Recusas  25.08.2025 a 31.08.2028</t>
+  </si>
+  <si>
+    <t>Relatório de Recusas  25.08.2025 a 31.08.2029</t>
+  </si>
+  <si>
+    <t>Relatório de Recusas  25.08.2025 a 31.08.2030</t>
+  </si>
+  <si>
+    <t>Relatório de Recusas  25.08.2025 a 31.08.2031</t>
+  </si>
+  <si>
+    <t>Relatório de Recusas  25.08.2025 a 31.08.2032</t>
+  </si>
+  <si>
+    <t>Relatório de Recusas  25.08.2025 a 31.08.2033</t>
+  </si>
+  <si>
+    <t>Relatório de Recusas  25.08.2025 a 31.08.2034</t>
+  </si>
+  <si>
+    <t>Relatório de Recusas  25.08.2025 a 31.08.2035</t>
+  </si>
+  <si>
+    <t>Relatório de Recusas  25.08.2025 a 31.08.2036</t>
+  </si>
+  <si>
+    <t>Relatório de Recusas  25.08.2025 a 31.08.2037</t>
+  </si>
+  <si>
+    <t>Relatório de Recusas  25.08.2025 a 31.08.2038</t>
+  </si>
+  <si>
+    <t>Relatório de Recusas  25.08.2025 a 31.08.2039</t>
+  </si>
+  <si>
+    <t>Relatório de Recusas  25.08.2025 a 31.08.2040</t>
+  </si>
+  <si>
+    <t>Relatório de Recusas  25.08.2025 a 31.08.2041</t>
+  </si>
+  <si>
+    <t>Relatório de Recusas  25.08.2025 a 31.08.2042</t>
+  </si>
+  <si>
+    <t>Relatório de Recusas  25.08.2025 a 31.08.2043</t>
+  </si>
+  <si>
+    <t>Relatório de Recusas  25.08.2025 a 31.08.2044</t>
+  </si>
+  <si>
+    <t>Relatório de Recusas  25.08.2025 a 31.08.2045</t>
+  </si>
+  <si>
+    <t>Relatório de Recusas  25.08.2025 a 31.08.2046</t>
+  </si>
+  <si>
+    <t>Relatório de Recusas  25.08.2025 a 31.08.2047</t>
+  </si>
+  <si>
+    <t>Relatório de Recusas  25.08.2025 a 31.08.2048</t>
+  </si>
+  <si>
+    <t>Relatório de Recusas  25.08.2025 a 31.08.2049</t>
+  </si>
+  <si>
+    <t>Relatório de Recusas  25.08.2025 a 31.08.2050</t>
+  </si>
+  <si>
+    <t>Relatório de Recusas  25.08.2025 a 31.08.2051</t>
+  </si>
+  <si>
+    <t>Relatório de Recusas  25.08.2025 a 31.08.2052</t>
+  </si>
+  <si>
+    <t>Relatório de Recusas  25.08.2025 a 31.08.2053</t>
+  </si>
+  <si>
+    <t>Relatório de Recusas  25.08.2025 a 31.08.2054</t>
+  </si>
+  <si>
+    <t>Relatório de Recusas  25.08.2025 a 31.08.2055</t>
+  </si>
+  <si>
+    <t>Relatório de Recusas  25.08.2025 a 31.08.2056</t>
+  </si>
+  <si>
+    <t>Relatório de Recusas  25.08.2025 a 31.08.2057</t>
+  </si>
+  <si>
+    <t>Relatório de Recusas  25.08.2025 a 31.08.2058</t>
+  </si>
+  <si>
+    <t>Relatório de Recusas  25.08.2025 a 31.08.2059</t>
+  </si>
+  <si>
+    <t>Relatório de Recusas Santander - 25/08/2025</t>
+  </si>
+  <si>
+    <t>133968006</t>
+  </si>
+  <si>
+    <t>133967991</t>
+  </si>
+  <si>
+    <t>133951481</t>
+  </si>
+  <si>
+    <t>133967394</t>
+  </si>
+  <si>
+    <t>133949785</t>
+  </si>
+  <si>
+    <t>134013450</t>
+  </si>
+  <si>
+    <t>134014769</t>
+  </si>
+  <si>
+    <t>134005066</t>
+  </si>
+  <si>
+    <t>134002756</t>
+  </si>
+  <si>
+    <t>134011554</t>
+  </si>
+  <si>
+    <t>134032061</t>
+  </si>
+  <si>
+    <t>133961746</t>
+  </si>
+  <si>
+    <t>134051881</t>
+  </si>
+  <si>
+    <t>134072663</t>
+  </si>
+  <si>
+    <t>134072098</t>
+  </si>
+  <si>
+    <t>133997089</t>
+  </si>
+  <si>
+    <t>133888532</t>
+  </si>
+  <si>
+    <t>133921740</t>
+  </si>
+  <si>
+    <t>133962059</t>
+  </si>
+  <si>
+    <t>133958216</t>
+  </si>
+  <si>
+    <t>133951650</t>
+  </si>
+  <si>
+    <t>133989708</t>
+  </si>
+  <si>
+    <t>133954717</t>
+  </si>
+  <si>
+    <t>133952751</t>
+  </si>
+  <si>
+    <t>133954071</t>
+  </si>
+  <si>
+    <t>133954202</t>
+  </si>
+  <si>
+    <t>133954629</t>
+  </si>
+  <si>
+    <t>133956387</t>
+  </si>
+  <si>
+    <t>133959303</t>
+  </si>
+  <si>
+    <t>133960867</t>
+  </si>
+  <si>
+    <t>133980197</t>
+  </si>
+  <si>
+    <t>133963543</t>
+  </si>
+  <si>
+    <t>133963790</t>
+  </si>
+  <si>
+    <t>133975706</t>
+  </si>
+  <si>
+    <t>133964091</t>
+  </si>
+  <si>
+    <t>134012322</t>
   </si>
 </sst>
 </file>
@@ -602,16 +704,16 @@
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A2" s="6">
-        <v>133946662</v>
+        <v>133951577</v>
       </c>
       <c r="B2" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C2" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="D2" s="2" t="s">
         <v>8</v>
-      </c>
-      <c r="D2" s="2" t="s">
-        <v>45</v>
       </c>
       <c r="E2" s="2" t="s">
         <v>6</v>
@@ -620,16 +722,16 @@
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
-        <v>9</v>
+        <v>44</v>
       </c>
       <c r="B3" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C3" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="D3" s="2" t="s">
         <v>8</v>
-      </c>
-      <c r="D3" s="2" t="s">
-        <v>45</v>
       </c>
       <c r="E3" s="2" t="s">
         <v>6</v>
@@ -638,16 +740,16 @@
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
-        <v>10</v>
+        <v>45</v>
       </c>
       <c r="B4" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C4" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="D4" s="2" t="s">
         <v>8</v>
-      </c>
-      <c r="D4" s="2" t="s">
-        <v>45</v>
       </c>
       <c r="E4" s="2" t="s">
         <v>6</v>
@@ -656,16 +758,16 @@
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
-        <v>11</v>
+        <v>46</v>
       </c>
       <c r="B5" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>8</v>
+        <v>43</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>45</v>
+        <v>9</v>
       </c>
       <c r="E5" s="2" t="s">
         <v>6</v>
@@ -674,16 +776,16 @@
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" s="1" t="s">
-        <v>12</v>
+        <v>47</v>
       </c>
       <c r="B6" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>8</v>
+        <v>43</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>45</v>
+        <v>10</v>
       </c>
       <c r="E6" s="2" t="s">
         <v>6</v>
@@ -692,16 +794,16 @@
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" s="1" t="s">
-        <v>13</v>
+        <v>48</v>
       </c>
       <c r="B7" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>8</v>
+        <v>43</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>45</v>
+        <v>11</v>
       </c>
       <c r="E7" s="2" t="s">
         <v>6</v>
@@ -710,16 +812,16 @@
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" s="1" t="s">
-        <v>14</v>
+        <v>49</v>
       </c>
       <c r="B8" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>8</v>
+        <v>43</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>45</v>
+        <v>12</v>
       </c>
       <c r="E8" s="2" t="s">
         <v>6</v>
@@ -728,16 +830,16 @@
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" s="1" t="s">
-        <v>15</v>
+        <v>50</v>
       </c>
       <c r="B9" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>8</v>
+        <v>43</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>45</v>
+        <v>13</v>
       </c>
       <c r="E9" s="2" t="s">
         <v>6</v>
@@ -746,16 +848,16 @@
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A10" s="1" t="s">
-        <v>16</v>
+        <v>51</v>
       </c>
       <c r="B10" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>8</v>
+        <v>43</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>45</v>
+        <v>14</v>
       </c>
       <c r="E10" s="2" t="s">
         <v>6</v>
@@ -764,16 +866,16 @@
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A11" s="1" t="s">
-        <v>17</v>
+        <v>52</v>
       </c>
       <c r="B11" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>8</v>
+        <v>43</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>45</v>
+        <v>15</v>
       </c>
       <c r="E11" s="2" t="s">
         <v>6</v>
@@ -782,16 +884,16 @@
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A12" s="1" t="s">
-        <v>18</v>
+        <v>53</v>
       </c>
       <c r="B12" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>8</v>
+        <v>43</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>45</v>
+        <v>16</v>
       </c>
       <c r="E12" s="2" t="s">
         <v>6</v>
@@ -800,16 +902,16 @@
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A13" s="1" t="s">
-        <v>19</v>
+        <v>54</v>
       </c>
       <c r="B13" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>8</v>
+        <v>43</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>45</v>
+        <v>17</v>
       </c>
       <c r="E13" s="2" t="s">
         <v>6</v>
@@ -818,16 +920,16 @@
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A14" s="1" t="s">
-        <v>20</v>
+        <v>55</v>
       </c>
       <c r="B14" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>8</v>
+        <v>43</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>45</v>
+        <v>18</v>
       </c>
       <c r="E14" s="2" t="s">
         <v>6</v>
@@ -836,16 +938,16 @@
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A15" s="1" t="s">
-        <v>21</v>
+        <v>56</v>
       </c>
       <c r="B15" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>8</v>
+        <v>43</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>45</v>
+        <v>19</v>
       </c>
       <c r="E15" s="2" t="s">
         <v>6</v>
@@ -854,16 +956,16 @@
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A16" s="1" t="s">
-        <v>22</v>
+        <v>57</v>
       </c>
       <c r="B16" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>8</v>
+        <v>43</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>45</v>
+        <v>20</v>
       </c>
       <c r="E16" s="2" t="s">
         <v>6</v>
@@ -872,16 +974,16 @@
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A17" s="1" t="s">
-        <v>23</v>
+        <v>58</v>
       </c>
       <c r="B17" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>8</v>
+        <v>43</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>45</v>
+        <v>21</v>
       </c>
       <c r="E17" s="2" t="s">
         <v>6</v>
@@ -890,16 +992,16 @@
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A18" s="1" t="s">
-        <v>24</v>
+        <v>59</v>
       </c>
       <c r="B18" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>8</v>
+        <v>43</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>45</v>
+        <v>22</v>
       </c>
       <c r="E18" s="2" t="s">
         <v>6</v>
@@ -908,16 +1010,16 @@
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A19" s="1" t="s">
-        <v>25</v>
+        <v>60</v>
       </c>
       <c r="B19" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>8</v>
+        <v>43</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>45</v>
+        <v>23</v>
       </c>
       <c r="E19" s="2" t="s">
         <v>6</v>
@@ -926,16 +1028,16 @@
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A20" s="1" t="s">
-        <v>26</v>
+        <v>61</v>
       </c>
       <c r="B20" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>8</v>
+        <v>43</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>45</v>
+        <v>24</v>
       </c>
       <c r="E20" s="2" t="s">
         <v>6</v>
@@ -944,16 +1046,16 @@
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A21" s="1" t="s">
-        <v>27</v>
+        <v>62</v>
       </c>
       <c r="B21" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>8</v>
+        <v>43</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>45</v>
+        <v>25</v>
       </c>
       <c r="E21" s="2" t="s">
         <v>6</v>
@@ -962,16 +1064,16 @@
     </row>
     <row r="22" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A22" s="1" t="s">
-        <v>28</v>
+        <v>63</v>
       </c>
       <c r="B22" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>8</v>
+        <v>43</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>45</v>
+        <v>26</v>
       </c>
       <c r="E22" s="2" t="s">
         <v>6</v>
@@ -980,16 +1082,16 @@
     </row>
     <row r="23" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A23" s="1" t="s">
-        <v>29</v>
+        <v>64</v>
       </c>
       <c r="B23" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>8</v>
+        <v>43</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>45</v>
+        <v>27</v>
       </c>
       <c r="E23" s="2" t="s">
         <v>6</v>
@@ -998,16 +1100,16 @@
     </row>
     <row r="24" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A24" s="1" t="s">
-        <v>30</v>
+        <v>65</v>
       </c>
       <c r="B24" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C24" s="2" t="s">
-        <v>8</v>
+        <v>43</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>45</v>
+        <v>28</v>
       </c>
       <c r="E24" s="2" t="s">
         <v>6</v>
@@ -1016,16 +1118,16 @@
     </row>
     <row r="25" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A25" s="1" t="s">
-        <v>31</v>
+        <v>66</v>
       </c>
       <c r="B25" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C25" s="2" t="s">
-        <v>8</v>
+        <v>43</v>
       </c>
       <c r="D25" s="2" t="s">
-        <v>45</v>
+        <v>29</v>
       </c>
       <c r="E25" s="2" t="s">
         <v>6</v>
@@ -1034,16 +1136,16 @@
     </row>
     <row r="26" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A26" s="1" t="s">
-        <v>32</v>
+        <v>67</v>
       </c>
       <c r="B26" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C26" s="2" t="s">
-        <v>8</v>
+        <v>43</v>
       </c>
       <c r="D26" s="2" t="s">
-        <v>45</v>
+        <v>30</v>
       </c>
       <c r="E26" s="2" t="s">
         <v>6</v>
@@ -1052,16 +1154,16 @@
     </row>
     <row r="27" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A27" s="1" t="s">
-        <v>33</v>
+        <v>68</v>
       </c>
       <c r="B27" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C27" s="2" t="s">
-        <v>8</v>
+        <v>43</v>
       </c>
       <c r="D27" s="2" t="s">
-        <v>45</v>
+        <v>31</v>
       </c>
       <c r="E27" s="2" t="s">
         <v>6</v>
@@ -1070,16 +1172,16 @@
     </row>
     <row r="28" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A28" s="1" t="s">
-        <v>34</v>
+        <v>69</v>
       </c>
       <c r="B28" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C28" s="2" t="s">
-        <v>8</v>
+        <v>43</v>
       </c>
       <c r="D28" s="2" t="s">
-        <v>45</v>
+        <v>32</v>
       </c>
       <c r="E28" s="2" t="s">
         <v>6</v>
@@ -1088,16 +1190,16 @@
     </row>
     <row r="29" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A29" s="1" t="s">
-        <v>35</v>
+        <v>70</v>
       </c>
       <c r="B29" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C29" s="2" t="s">
-        <v>8</v>
+        <v>43</v>
       </c>
       <c r="D29" s="2" t="s">
-        <v>45</v>
+        <v>33</v>
       </c>
       <c r="E29" s="2" t="s">
         <v>6</v>
@@ -1106,16 +1208,16 @@
     </row>
     <row r="30" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A30" s="1" t="s">
-        <v>36</v>
+        <v>71</v>
       </c>
       <c r="B30" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C30" s="2" t="s">
-        <v>8</v>
+        <v>43</v>
       </c>
       <c r="D30" s="2" t="s">
-        <v>45</v>
+        <v>34</v>
       </c>
       <c r="E30" s="2" t="s">
         <v>6</v>
@@ -1124,16 +1226,16 @@
     </row>
     <row r="31" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A31" s="1" t="s">
-        <v>37</v>
+        <v>72</v>
       </c>
       <c r="B31" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C31" s="2" t="s">
-        <v>8</v>
+        <v>43</v>
       </c>
       <c r="D31" s="2" t="s">
-        <v>45</v>
+        <v>35</v>
       </c>
       <c r="E31" s="2" t="s">
         <v>6</v>
@@ -1142,16 +1244,16 @@
     </row>
     <row r="32" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A32" s="1" t="s">
-        <v>38</v>
+        <v>73</v>
       </c>
       <c r="B32" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C32" s="2" t="s">
-        <v>8</v>
+        <v>43</v>
       </c>
       <c r="D32" s="2" t="s">
-        <v>45</v>
+        <v>36</v>
       </c>
       <c r="E32" s="2" t="s">
         <v>6</v>
@@ -1159,16 +1261,16 @@
     </row>
     <row r="33" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A33" s="1" t="s">
-        <v>39</v>
+        <v>74</v>
       </c>
       <c r="B33" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C33" s="2" t="s">
-        <v>8</v>
+        <v>43</v>
       </c>
       <c r="D33" s="2" t="s">
-        <v>45</v>
+        <v>37</v>
       </c>
       <c r="E33" s="2" t="s">
         <v>6</v>
@@ -1176,16 +1278,16 @@
     </row>
     <row r="34" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A34" s="1" t="s">
-        <v>40</v>
+        <v>75</v>
       </c>
       <c r="B34" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C34" s="2" t="s">
-        <v>8</v>
+        <v>43</v>
       </c>
       <c r="D34" s="2" t="s">
-        <v>45</v>
+        <v>38</v>
       </c>
       <c r="E34" s="2" t="s">
         <v>6</v>
@@ -1193,16 +1295,16 @@
     </row>
     <row r="35" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A35" s="1" t="s">
-        <v>41</v>
+        <v>76</v>
       </c>
       <c r="B35" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C35" s="2" t="s">
-        <v>8</v>
+        <v>43</v>
       </c>
       <c r="D35" s="2" t="s">
-        <v>45</v>
+        <v>39</v>
       </c>
       <c r="E35" s="2" t="s">
         <v>6</v>
@@ -1210,16 +1312,16 @@
     </row>
     <row r="36" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A36" s="1" t="s">
-        <v>42</v>
+        <v>77</v>
       </c>
       <c r="B36" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C36" s="2" t="s">
-        <v>8</v>
+        <v>43</v>
       </c>
       <c r="D36" s="2" t="s">
-        <v>45</v>
+        <v>40</v>
       </c>
       <c r="E36" s="2" t="s">
         <v>6</v>
@@ -1227,16 +1329,16 @@
     </row>
     <row r="37" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A37" s="1" t="s">
-        <v>43</v>
+        <v>78</v>
       </c>
       <c r="B37" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C37" s="2" t="s">
-        <v>8</v>
+        <v>43</v>
       </c>
       <c r="D37" s="2" t="s">
-        <v>45</v>
+        <v>41</v>
       </c>
       <c r="E37" s="2" t="s">
         <v>6</v>
@@ -1244,16 +1346,16 @@
     </row>
     <row r="38" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A38" s="1" t="s">
-        <v>44</v>
+        <v>79</v>
       </c>
       <c r="B38" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C38" s="2" t="s">
-        <v>8</v>
+        <v>43</v>
       </c>
       <c r="D38" s="2" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="E38" s="2" t="s">
         <v>6</v>

--- a/Data Files/Backoffce/IndexacaoFG/IndexacaoFG_SANTANDER.xlsx
+++ b/Data Files/Backoffce/IndexacaoFG/IndexacaoFG_SANTANDER.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Public\RPA_ALLIANZ_TREINAMENTO\Data Files\Backoffce\IndexacaoFG\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{38586527-F0B2-4EE9-959A-712D31B160C2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B4D4EC2F-FFE4-48D1-8F93-D5EECA3CC2B2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="190" uniqueCount="80">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="190" uniqueCount="47">
   <si>
     <t xml:space="preserve">status </t>
   </si>
@@ -58,105 +58,6 @@
   </si>
   <si>
     <t>Relatório de Recusas  25.08.2025 a 31.08.2026</t>
-  </si>
-  <si>
-    <t>Relatório de Recusas  25.08.2025 a 31.08.2027</t>
-  </si>
-  <si>
-    <t>Relatório de Recusas  25.08.2025 a 31.08.2028</t>
-  </si>
-  <si>
-    <t>Relatório de Recusas  25.08.2025 a 31.08.2029</t>
-  </si>
-  <si>
-    <t>Relatório de Recusas  25.08.2025 a 31.08.2030</t>
-  </si>
-  <si>
-    <t>Relatório de Recusas  25.08.2025 a 31.08.2031</t>
-  </si>
-  <si>
-    <t>Relatório de Recusas  25.08.2025 a 31.08.2032</t>
-  </si>
-  <si>
-    <t>Relatório de Recusas  25.08.2025 a 31.08.2033</t>
-  </si>
-  <si>
-    <t>Relatório de Recusas  25.08.2025 a 31.08.2034</t>
-  </si>
-  <si>
-    <t>Relatório de Recusas  25.08.2025 a 31.08.2035</t>
-  </si>
-  <si>
-    <t>Relatório de Recusas  25.08.2025 a 31.08.2036</t>
-  </si>
-  <si>
-    <t>Relatório de Recusas  25.08.2025 a 31.08.2037</t>
-  </si>
-  <si>
-    <t>Relatório de Recusas  25.08.2025 a 31.08.2038</t>
-  </si>
-  <si>
-    <t>Relatório de Recusas  25.08.2025 a 31.08.2039</t>
-  </si>
-  <si>
-    <t>Relatório de Recusas  25.08.2025 a 31.08.2040</t>
-  </si>
-  <si>
-    <t>Relatório de Recusas  25.08.2025 a 31.08.2041</t>
-  </si>
-  <si>
-    <t>Relatório de Recusas  25.08.2025 a 31.08.2042</t>
-  </si>
-  <si>
-    <t>Relatório de Recusas  25.08.2025 a 31.08.2043</t>
-  </si>
-  <si>
-    <t>Relatório de Recusas  25.08.2025 a 31.08.2044</t>
-  </si>
-  <si>
-    <t>Relatório de Recusas  25.08.2025 a 31.08.2045</t>
-  </si>
-  <si>
-    <t>Relatório de Recusas  25.08.2025 a 31.08.2046</t>
-  </si>
-  <si>
-    <t>Relatório de Recusas  25.08.2025 a 31.08.2047</t>
-  </si>
-  <si>
-    <t>Relatório de Recusas  25.08.2025 a 31.08.2048</t>
-  </si>
-  <si>
-    <t>Relatório de Recusas  25.08.2025 a 31.08.2049</t>
-  </si>
-  <si>
-    <t>Relatório de Recusas  25.08.2025 a 31.08.2050</t>
-  </si>
-  <si>
-    <t>Relatório de Recusas  25.08.2025 a 31.08.2051</t>
-  </si>
-  <si>
-    <t>Relatório de Recusas  25.08.2025 a 31.08.2052</t>
-  </si>
-  <si>
-    <t>Relatório de Recusas  25.08.2025 a 31.08.2053</t>
-  </si>
-  <si>
-    <t>Relatório de Recusas  25.08.2025 a 31.08.2054</t>
-  </si>
-  <si>
-    <t>Relatório de Recusas  25.08.2025 a 31.08.2055</t>
-  </si>
-  <si>
-    <t>Relatório de Recusas  25.08.2025 a 31.08.2056</t>
-  </si>
-  <si>
-    <t>Relatório de Recusas  25.08.2025 a 31.08.2057</t>
-  </si>
-  <si>
-    <t>Relatório de Recusas  25.08.2025 a 31.08.2058</t>
-  </si>
-  <si>
-    <t>Relatório de Recusas  25.08.2025 a 31.08.2059</t>
   </si>
   <si>
     <t>Relatório de Recusas Santander - 25/08/2025</t>
@@ -710,7 +611,7 @@
         <v>7</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>43</v>
+        <v>10</v>
       </c>
       <c r="D2" s="2" t="s">
         <v>8</v>
@@ -722,13 +623,13 @@
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
-        <v>44</v>
+        <v>11</v>
       </c>
       <c r="B3" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>43</v>
+        <v>10</v>
       </c>
       <c r="D3" s="2" t="s">
         <v>8</v>
@@ -740,13 +641,13 @@
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
-        <v>45</v>
+        <v>12</v>
       </c>
       <c r="B4" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>43</v>
+        <v>10</v>
       </c>
       <c r="D4" s="2" t="s">
         <v>8</v>
@@ -758,16 +659,16 @@
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
-        <v>46</v>
+        <v>13</v>
       </c>
       <c r="B5" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>43</v>
+        <v>10</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E5" s="2" t="s">
         <v>6</v>
@@ -776,16 +677,16 @@
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" s="1" t="s">
-        <v>47</v>
+        <v>14</v>
       </c>
       <c r="B6" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>43</v>
+        <v>10</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="E6" s="2" t="s">
         <v>6</v>
@@ -794,16 +695,16 @@
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" s="1" t="s">
-        <v>48</v>
+        <v>15</v>
       </c>
       <c r="B7" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>43</v>
+        <v>10</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="E7" s="2" t="s">
         <v>6</v>
@@ -812,16 +713,16 @@
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" s="1" t="s">
-        <v>49</v>
+        <v>16</v>
       </c>
       <c r="B8" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>43</v>
+        <v>10</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="E8" s="2" t="s">
         <v>6</v>
@@ -830,16 +731,16 @@
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" s="1" t="s">
-        <v>50</v>
+        <v>17</v>
       </c>
       <c r="B9" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>43</v>
+        <v>10</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="E9" s="2" t="s">
         <v>6</v>
@@ -848,16 +749,16 @@
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A10" s="1" t="s">
-        <v>51</v>
+        <v>18</v>
       </c>
       <c r="B10" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>43</v>
+        <v>10</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="E10" s="2" t="s">
         <v>6</v>
@@ -866,16 +767,16 @@
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A11" s="1" t="s">
-        <v>52</v>
+        <v>19</v>
       </c>
       <c r="B11" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>43</v>
+        <v>10</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="E11" s="2" t="s">
         <v>6</v>
@@ -884,16 +785,16 @@
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A12" s="1" t="s">
-        <v>53</v>
+        <v>20</v>
       </c>
       <c r="B12" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>43</v>
+        <v>10</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>16</v>
+        <v>8</v>
       </c>
       <c r="E12" s="2" t="s">
         <v>6</v>
@@ -902,16 +803,16 @@
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A13" s="1" t="s">
-        <v>54</v>
+        <v>21</v>
       </c>
       <c r="B13" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>43</v>
+        <v>10</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>17</v>
+        <v>8</v>
       </c>
       <c r="E13" s="2" t="s">
         <v>6</v>
@@ -920,16 +821,16 @@
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A14" s="1" t="s">
-        <v>55</v>
+        <v>22</v>
       </c>
       <c r="B14" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>43</v>
+        <v>10</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>18</v>
+        <v>8</v>
       </c>
       <c r="E14" s="2" t="s">
         <v>6</v>
@@ -938,16 +839,16 @@
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A15" s="1" t="s">
-        <v>56</v>
+        <v>23</v>
       </c>
       <c r="B15" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>43</v>
+        <v>10</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>19</v>
+        <v>8</v>
       </c>
       <c r="E15" s="2" t="s">
         <v>6</v>
@@ -956,16 +857,16 @@
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A16" s="1" t="s">
-        <v>57</v>
+        <v>24</v>
       </c>
       <c r="B16" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>43</v>
+        <v>10</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>20</v>
+        <v>8</v>
       </c>
       <c r="E16" s="2" t="s">
         <v>6</v>
@@ -974,16 +875,16 @@
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A17" s="1" t="s">
-        <v>58</v>
+        <v>25</v>
       </c>
       <c r="B17" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>43</v>
+        <v>10</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>21</v>
+        <v>8</v>
       </c>
       <c r="E17" s="2" t="s">
         <v>6</v>
@@ -992,16 +893,16 @@
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A18" s="1" t="s">
-        <v>59</v>
+        <v>26</v>
       </c>
       <c r="B18" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>43</v>
+        <v>10</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>22</v>
+        <v>8</v>
       </c>
       <c r="E18" s="2" t="s">
         <v>6</v>
@@ -1010,16 +911,16 @@
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A19" s="1" t="s">
-        <v>60</v>
+        <v>27</v>
       </c>
       <c r="B19" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>43</v>
+        <v>10</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>23</v>
+        <v>8</v>
       </c>
       <c r="E19" s="2" t="s">
         <v>6</v>
@@ -1028,16 +929,16 @@
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A20" s="1" t="s">
-        <v>61</v>
+        <v>28</v>
       </c>
       <c r="B20" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>43</v>
+        <v>10</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>24</v>
+        <v>8</v>
       </c>
       <c r="E20" s="2" t="s">
         <v>6</v>
@@ -1046,16 +947,16 @@
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A21" s="1" t="s">
-        <v>62</v>
+        <v>29</v>
       </c>
       <c r="B21" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>43</v>
+        <v>10</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>25</v>
+        <v>8</v>
       </c>
       <c r="E21" s="2" t="s">
         <v>6</v>
@@ -1064,16 +965,16 @@
     </row>
     <row r="22" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A22" s="1" t="s">
-        <v>63</v>
+        <v>30</v>
       </c>
       <c r="B22" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>43</v>
+        <v>10</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>26</v>
+        <v>8</v>
       </c>
       <c r="E22" s="2" t="s">
         <v>6</v>
@@ -1082,16 +983,16 @@
     </row>
     <row r="23" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A23" s="1" t="s">
-        <v>64</v>
+        <v>31</v>
       </c>
       <c r="B23" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>43</v>
+        <v>10</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>27</v>
+        <v>8</v>
       </c>
       <c r="E23" s="2" t="s">
         <v>6</v>
@@ -1100,16 +1001,16 @@
     </row>
     <row r="24" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A24" s="1" t="s">
-        <v>65</v>
+        <v>32</v>
       </c>
       <c r="B24" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C24" s="2" t="s">
-        <v>43</v>
+        <v>10</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>28</v>
+        <v>8</v>
       </c>
       <c r="E24" s="2" t="s">
         <v>6</v>
@@ -1118,16 +1019,16 @@
     </row>
     <row r="25" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A25" s="1" t="s">
-        <v>66</v>
+        <v>33</v>
       </c>
       <c r="B25" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C25" s="2" t="s">
-        <v>43</v>
+        <v>10</v>
       </c>
       <c r="D25" s="2" t="s">
-        <v>29</v>
+        <v>8</v>
       </c>
       <c r="E25" s="2" t="s">
         <v>6</v>
@@ -1136,16 +1037,16 @@
     </row>
     <row r="26" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A26" s="1" t="s">
-        <v>67</v>
+        <v>34</v>
       </c>
       <c r="B26" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C26" s="2" t="s">
-        <v>43</v>
+        <v>10</v>
       </c>
       <c r="D26" s="2" t="s">
-        <v>30</v>
+        <v>8</v>
       </c>
       <c r="E26" s="2" t="s">
         <v>6</v>
@@ -1154,16 +1055,16 @@
     </row>
     <row r="27" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A27" s="1" t="s">
-        <v>68</v>
+        <v>35</v>
       </c>
       <c r="B27" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C27" s="2" t="s">
-        <v>43</v>
+        <v>10</v>
       </c>
       <c r="D27" s="2" t="s">
-        <v>31</v>
+        <v>8</v>
       </c>
       <c r="E27" s="2" t="s">
         <v>6</v>
@@ -1172,16 +1073,16 @@
     </row>
     <row r="28" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A28" s="1" t="s">
-        <v>69</v>
+        <v>36</v>
       </c>
       <c r="B28" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C28" s="2" t="s">
-        <v>43</v>
+        <v>10</v>
       </c>
       <c r="D28" s="2" t="s">
-        <v>32</v>
+        <v>8</v>
       </c>
       <c r="E28" s="2" t="s">
         <v>6</v>
@@ -1190,16 +1091,16 @@
     </row>
     <row r="29" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A29" s="1" t="s">
-        <v>70</v>
+        <v>37</v>
       </c>
       <c r="B29" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C29" s="2" t="s">
-        <v>43</v>
+        <v>10</v>
       </c>
       <c r="D29" s="2" t="s">
-        <v>33</v>
+        <v>8</v>
       </c>
       <c r="E29" s="2" t="s">
         <v>6</v>
@@ -1208,16 +1109,16 @@
     </row>
     <row r="30" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A30" s="1" t="s">
-        <v>71</v>
+        <v>38</v>
       </c>
       <c r="B30" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C30" s="2" t="s">
-        <v>43</v>
+        <v>10</v>
       </c>
       <c r="D30" s="2" t="s">
-        <v>34</v>
+        <v>9</v>
       </c>
       <c r="E30" s="2" t="s">
         <v>6</v>
@@ -1226,16 +1127,16 @@
     </row>
     <row r="31" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A31" s="1" t="s">
-        <v>72</v>
+        <v>39</v>
       </c>
       <c r="B31" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C31" s="2" t="s">
-        <v>43</v>
+        <v>10</v>
       </c>
       <c r="D31" s="2" t="s">
-        <v>35</v>
+        <v>8</v>
       </c>
       <c r="E31" s="2" t="s">
         <v>6</v>
@@ -1244,16 +1145,16 @@
     </row>
     <row r="32" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A32" s="1" t="s">
-        <v>73</v>
+        <v>40</v>
       </c>
       <c r="B32" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C32" s="2" t="s">
-        <v>43</v>
+        <v>10</v>
       </c>
       <c r="D32" s="2" t="s">
-        <v>36</v>
+        <v>8</v>
       </c>
       <c r="E32" s="2" t="s">
         <v>6</v>
@@ -1261,16 +1162,16 @@
     </row>
     <row r="33" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A33" s="1" t="s">
-        <v>74</v>
+        <v>41</v>
       </c>
       <c r="B33" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C33" s="2" t="s">
-        <v>43</v>
+        <v>10</v>
       </c>
       <c r="D33" s="2" t="s">
-        <v>37</v>
+        <v>8</v>
       </c>
       <c r="E33" s="2" t="s">
         <v>6</v>
@@ -1278,16 +1179,16 @@
     </row>
     <row r="34" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A34" s="1" t="s">
-        <v>75</v>
+        <v>42</v>
       </c>
       <c r="B34" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C34" s="2" t="s">
-        <v>43</v>
+        <v>10</v>
       </c>
       <c r="D34" s="2" t="s">
-        <v>38</v>
+        <v>8</v>
       </c>
       <c r="E34" s="2" t="s">
         <v>6</v>
@@ -1295,16 +1196,16 @@
     </row>
     <row r="35" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A35" s="1" t="s">
-        <v>76</v>
+        <v>43</v>
       </c>
       <c r="B35" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C35" s="2" t="s">
-        <v>43</v>
+        <v>10</v>
       </c>
       <c r="D35" s="2" t="s">
-        <v>39</v>
+        <v>9</v>
       </c>
       <c r="E35" s="2" t="s">
         <v>6</v>
@@ -1312,16 +1213,16 @@
     </row>
     <row r="36" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A36" s="1" t="s">
-        <v>77</v>
+        <v>44</v>
       </c>
       <c r="B36" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C36" s="2" t="s">
-        <v>43</v>
+        <v>10</v>
       </c>
       <c r="D36" s="2" t="s">
-        <v>40</v>
+        <v>8</v>
       </c>
       <c r="E36" s="2" t="s">
         <v>6</v>
@@ -1329,16 +1230,16 @@
     </row>
     <row r="37" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A37" s="1" t="s">
-        <v>78</v>
+        <v>45</v>
       </c>
       <c r="B37" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C37" s="2" t="s">
-        <v>43</v>
+        <v>10</v>
       </c>
       <c r="D37" s="2" t="s">
-        <v>41</v>
+        <v>9</v>
       </c>
       <c r="E37" s="2" t="s">
         <v>6</v>
@@ -1346,16 +1247,16 @@
     </row>
     <row r="38" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A38" s="1" t="s">
-        <v>79</v>
+        <v>46</v>
       </c>
       <c r="B38" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C38" s="2" t="s">
-        <v>43</v>
+        <v>10</v>
       </c>
       <c r="D38" s="2" t="s">
-        <v>42</v>
+        <v>8</v>
       </c>
       <c r="E38" s="2" t="s">
         <v>6</v>

--- a/Data Files/Backoffce/IndexacaoFG/IndexacaoFG_SANTANDER.xlsx
+++ b/Data Files/Backoffce/IndexacaoFG/IndexacaoFG_SANTANDER.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Public\RPA_ALLIANZ_TREINAMENTO\Data Files\Backoffce\IndexacaoFG\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B4D4EC2F-FFE4-48D1-8F93-D5EECA3CC2B2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{779A10D1-103A-4028-9BB8-5677165F4D47}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1515" yWindow="1515" windowWidth="15375" windowHeight="7875" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="IndexacaoFG" sheetId="2" r:id="rId1"/>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="190" uniqueCount="47">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="160" uniqueCount="40">
   <si>
     <t xml:space="preserve">status </t>
   </si>
@@ -57,118 +57,97 @@
     <t>Relatório de Recusas  25.08.2025 a 31.08.2025</t>
   </si>
   <si>
-    <t>Relatório de Recusas  25.08.2025 a 31.08.2026</t>
-  </si>
-  <si>
-    <t>Relatório de Recusas Santander - 25/08/2025</t>
-  </si>
-  <si>
-    <t>133968006</t>
-  </si>
-  <si>
-    <t>133967991</t>
-  </si>
-  <si>
-    <t>133951481</t>
-  </si>
-  <si>
-    <t>133967394</t>
-  </si>
-  <si>
-    <t>133949785</t>
-  </si>
-  <si>
-    <t>134013450</t>
-  </si>
-  <si>
-    <t>134014769</t>
-  </si>
-  <si>
-    <t>134005066</t>
-  </si>
-  <si>
-    <t>134002756</t>
-  </si>
-  <si>
-    <t>134011554</t>
-  </si>
-  <si>
-    <t>134032061</t>
-  </si>
-  <si>
-    <t>133961746</t>
-  </si>
-  <si>
-    <t>134051881</t>
-  </si>
-  <si>
-    <t>134072663</t>
-  </si>
-  <si>
-    <t>134072098</t>
-  </si>
-  <si>
-    <t>133997089</t>
-  </si>
-  <si>
-    <t>133888532</t>
-  </si>
-  <si>
-    <t>133921740</t>
-  </si>
-  <si>
-    <t>133962059</t>
-  </si>
-  <si>
-    <t>133958216</t>
-  </si>
-  <si>
-    <t>133951650</t>
-  </si>
-  <si>
-    <t>133989708</t>
-  </si>
-  <si>
-    <t>133954717</t>
-  </si>
-  <si>
-    <t>133952751</t>
-  </si>
-  <si>
-    <t>133954071</t>
-  </si>
-  <si>
-    <t>133954202</t>
-  </si>
-  <si>
-    <t>133954629</t>
-  </si>
-  <si>
-    <t>133956387</t>
-  </si>
-  <si>
-    <t>133959303</t>
-  </si>
-  <si>
-    <t>133960867</t>
-  </si>
-  <si>
-    <t>133980197</t>
-  </si>
-  <si>
-    <t>133963543</t>
-  </si>
-  <si>
-    <t>133963790</t>
-  </si>
-  <si>
-    <t>133975706</t>
-  </si>
-  <si>
-    <t>133964091</t>
-  </si>
-  <si>
-    <t>134012322</t>
+    <t>Relatório de Recusas Santander - 26/08/2025</t>
+  </si>
+  <si>
+    <t>133981283</t>
+  </si>
+  <si>
+    <t>133985758</t>
+  </si>
+  <si>
+    <t>133980027</t>
+  </si>
+  <si>
+    <t>134028037</t>
+  </si>
+  <si>
+    <t>134062392</t>
+  </si>
+  <si>
+    <t>133976697</t>
+  </si>
+  <si>
+    <t>134069140</t>
+  </si>
+  <si>
+    <t>134071914</t>
+  </si>
+  <si>
+    <t>134032849</t>
+  </si>
+  <si>
+    <t>134075165</t>
+  </si>
+  <si>
+    <t>133991881</t>
+  </si>
+  <si>
+    <t>134080037</t>
+  </si>
+  <si>
+    <t>134082173</t>
+  </si>
+  <si>
+    <t>134097930</t>
+  </si>
+  <si>
+    <t>133980373</t>
+  </si>
+  <si>
+    <t>134034881</t>
+  </si>
+  <si>
+    <t>133997076</t>
+  </si>
+  <si>
+    <t>133922899</t>
+  </si>
+  <si>
+    <t>133982224</t>
+  </si>
+  <si>
+    <t>133974816</t>
+  </si>
+  <si>
+    <t>133978116</t>
+  </si>
+  <si>
+    <t>133980382</t>
+  </si>
+  <si>
+    <t>133981246</t>
+  </si>
+  <si>
+    <t>133981548</t>
+  </si>
+  <si>
+    <t>133982313</t>
+  </si>
+  <si>
+    <t>133987942</t>
+  </si>
+  <si>
+    <t>133988895</t>
+  </si>
+  <si>
+    <t>133989544</t>
+  </si>
+  <si>
+    <t>133990516</t>
+  </si>
+  <si>
+    <t>133990572</t>
   </si>
 </sst>
 </file>
@@ -573,7 +552,7 @@
   <sheetPr>
     <pageSetUpPr autoPageBreaks="0"/>
   </sheetPr>
-  <dimension ref="A1:F38"/>
+  <dimension ref="A1:F32"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="2" width="16.7109375" style="1" customWidth="1" collapsed="1"/>
@@ -605,13 +584,13 @@
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A2" s="6">
-        <v>133951577</v>
+        <v>133978332</v>
       </c>
       <c r="B2" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D2" s="2" t="s">
         <v>8</v>
@@ -623,13 +602,13 @@
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B3" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D3" s="2" t="s">
         <v>8</v>
@@ -641,13 +620,13 @@
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B4" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D4" s="2" t="s">
         <v>8</v>
@@ -659,13 +638,13 @@
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B5" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D5" s="2" t="s">
         <v>8</v>
@@ -677,13 +656,13 @@
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" s="1" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B6" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D6" s="2" t="s">
         <v>8</v>
@@ -695,13 +674,13 @@
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" s="1" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B7" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D7" s="2" t="s">
         <v>8</v>
@@ -713,13 +692,13 @@
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" s="1" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B8" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D8" s="2" t="s">
         <v>8</v>
@@ -731,13 +710,13 @@
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" s="1" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B9" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D9" s="2" t="s">
         <v>8</v>
@@ -749,13 +728,13 @@
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A10" s="1" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B10" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D10" s="2" t="s">
         <v>8</v>
@@ -767,13 +746,13 @@
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A11" s="1" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B11" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D11" s="2" t="s">
         <v>8</v>
@@ -785,13 +764,13 @@
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A12" s="1" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B12" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D12" s="2" t="s">
         <v>8</v>
@@ -803,13 +782,13 @@
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A13" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="B13" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D13" s="2" t="s">
         <v>8</v>
@@ -821,13 +800,13 @@
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A14" s="1" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B14" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D14" s="2" t="s">
         <v>8</v>
@@ -839,13 +818,13 @@
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A15" s="1" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B15" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D15" s="2" t="s">
         <v>8</v>
@@ -857,13 +836,13 @@
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A16" s="1" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B16" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D16" s="2" t="s">
         <v>8</v>
@@ -875,13 +854,13 @@
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A17" s="1" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B17" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D17" s="2" t="s">
         <v>8</v>
@@ -893,13 +872,13 @@
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A18" s="1" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B18" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D18" s="2" t="s">
         <v>8</v>
@@ -911,13 +890,13 @@
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A19" s="1" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="B19" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D19" s="2" t="s">
         <v>8</v>
@@ -929,13 +908,13 @@
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A20" s="1" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="B20" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D20" s="2" t="s">
         <v>8</v>
@@ -947,13 +926,13 @@
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A21" s="1" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="B21" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D21" s="2" t="s">
         <v>8</v>
@@ -965,13 +944,13 @@
     </row>
     <row r="22" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A22" s="1" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B22" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D22" s="2" t="s">
         <v>8</v>
@@ -983,13 +962,13 @@
     </row>
     <row r="23" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A23" s="1" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="B23" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D23" s="2" t="s">
         <v>8</v>
@@ -1001,13 +980,13 @@
     </row>
     <row r="24" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A24" s="1" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="B24" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C24" s="2" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D24" s="2" t="s">
         <v>8</v>
@@ -1019,13 +998,13 @@
     </row>
     <row r="25" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A25" s="1" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B25" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C25" s="2" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D25" s="2" t="s">
         <v>8</v>
@@ -1037,13 +1016,13 @@
     </row>
     <row r="26" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A26" s="1" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B26" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C26" s="2" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D26" s="2" t="s">
         <v>8</v>
@@ -1055,13 +1034,13 @@
     </row>
     <row r="27" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A27" s="1" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="B27" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C27" s="2" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D27" s="2" t="s">
         <v>8</v>
@@ -1073,13 +1052,13 @@
     </row>
     <row r="28" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A28" s="1" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="B28" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C28" s="2" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D28" s="2" t="s">
         <v>8</v>
@@ -1091,13 +1070,13 @@
     </row>
     <row r="29" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A29" s="1" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="B29" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C29" s="2" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D29" s="2" t="s">
         <v>8</v>
@@ -1109,16 +1088,16 @@
     </row>
     <row r="30" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A30" s="1" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B30" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C30" s="2" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D30" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E30" s="2" t="s">
         <v>6</v>
@@ -1127,13 +1106,13 @@
     </row>
     <row r="31" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A31" s="1" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B31" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C31" s="2" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D31" s="2" t="s">
         <v>8</v>
@@ -1145,120 +1124,18 @@
     </row>
     <row r="32" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A32" s="1" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B32" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C32" s="2" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D32" s="2" t="s">
         <v>8</v>
       </c>
       <c r="E32" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="33" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A33" s="1" t="s">
-        <v>41</v>
-      </c>
-      <c r="B33" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C33" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="D33" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="E33" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="34" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A34" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="B34" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C34" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="D34" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="E34" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="35" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A35" s="1" t="s">
-        <v>43</v>
-      </c>
-      <c r="B35" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C35" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="D35" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="E35" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="36" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A36" s="1" t="s">
-        <v>44</v>
-      </c>
-      <c r="B36" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C36" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="D36" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="E36" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="37" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A37" s="1" t="s">
-        <v>45</v>
-      </c>
-      <c r="B37" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C37" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="D37" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="E37" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="38" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A38" s="1" t="s">
-        <v>46</v>
-      </c>
-      <c r="B38" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C38" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="D38" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="E38" s="2" t="s">
         <v>6</v>
       </c>
     </row>

--- a/Data Files/Backoffce/IndexacaoFG/IndexacaoFG_SANTANDER.xlsx
+++ b/Data Files/Backoffce/IndexacaoFG/IndexacaoFG_SANTANDER.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Public\RPA_ALLIANZ_TREINAMENTO\Data Files\Backoffce\IndexacaoFG\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{779A10D1-103A-4028-9BB8-5677165F4D47}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{818D5C31-632C-4EA0-8BCB-325B367D02AD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1515" yWindow="1515" windowWidth="15375" windowHeight="7875" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="3150" yWindow="2955" windowWidth="15375" windowHeight="7875" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="IndexacaoFG" sheetId="2" r:id="rId1"/>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="160" uniqueCount="40">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="130" uniqueCount="34">
   <si>
     <t xml:space="preserve">status </t>
   </si>
@@ -57,97 +57,79 @@
     <t>Relatório de Recusas  25.08.2025 a 31.08.2025</t>
   </si>
   <si>
-    <t>Relatório de Recusas Santander - 26/08/2025</t>
-  </si>
-  <si>
-    <t>133981283</t>
-  </si>
-  <si>
-    <t>133985758</t>
-  </si>
-  <si>
-    <t>133980027</t>
-  </si>
-  <si>
-    <t>134028037</t>
-  </si>
-  <si>
-    <t>134062392</t>
-  </si>
-  <si>
-    <t>133976697</t>
-  </si>
-  <si>
-    <t>134069140</t>
-  </si>
-  <si>
-    <t>134071914</t>
-  </si>
-  <si>
-    <t>134032849</t>
-  </si>
-  <si>
-    <t>134075165</t>
-  </si>
-  <si>
-    <t>133991881</t>
-  </si>
-  <si>
-    <t>134080037</t>
-  </si>
-  <si>
-    <t>134082173</t>
-  </si>
-  <si>
-    <t>134097930</t>
-  </si>
-  <si>
-    <t>133980373</t>
-  </si>
-  <si>
-    <t>134034881</t>
-  </si>
-  <si>
-    <t>133997076</t>
-  </si>
-  <si>
-    <t>133922899</t>
-  </si>
-  <si>
-    <t>133982224</t>
-  </si>
-  <si>
-    <t>133974816</t>
-  </si>
-  <si>
-    <t>133978116</t>
-  </si>
-  <si>
-    <t>133980382</t>
-  </si>
-  <si>
-    <t>133981246</t>
-  </si>
-  <si>
-    <t>133981548</t>
-  </si>
-  <si>
-    <t>133982313</t>
-  </si>
-  <si>
-    <t>133987942</t>
-  </si>
-  <si>
-    <t>133988895</t>
-  </si>
-  <si>
-    <t>133989544</t>
-  </si>
-  <si>
-    <t>133990516</t>
-  </si>
-  <si>
-    <t>133990572</t>
+    <t>Relatório de Recusas Santander - 27/08/2025</t>
+  </si>
+  <si>
+    <t>134002781</t>
+  </si>
+  <si>
+    <t>134011293</t>
+  </si>
+  <si>
+    <t>134015104</t>
+  </si>
+  <si>
+    <t>134003094</t>
+  </si>
+  <si>
+    <t>134009970</t>
+  </si>
+  <si>
+    <t>134023812</t>
+  </si>
+  <si>
+    <t>134009993</t>
+  </si>
+  <si>
+    <t>134015383</t>
+  </si>
+  <si>
+    <t>134094458</t>
+  </si>
+  <si>
+    <t>134095206</t>
+  </si>
+  <si>
+    <t>134111744</t>
+  </si>
+  <si>
+    <t>134106242</t>
+  </si>
+  <si>
+    <t>134131120</t>
+  </si>
+  <si>
+    <t>134012774</t>
+  </si>
+  <si>
+    <t>134003887</t>
+  </si>
+  <si>
+    <t>133996064</t>
+  </si>
+  <si>
+    <t>134005385</t>
+  </si>
+  <si>
+    <t>134007219</t>
+  </si>
+  <si>
+    <t>134008340</t>
+  </si>
+  <si>
+    <t>134009089</t>
+  </si>
+  <si>
+    <t>134010861</t>
+  </si>
+  <si>
+    <t>134011991</t>
+  </si>
+  <si>
+    <t>134012545</t>
+  </si>
+  <si>
+    <t>134015859</t>
   </si>
 </sst>
 </file>
@@ -552,7 +534,7 @@
   <sheetPr>
     <pageSetUpPr autoPageBreaks="0"/>
   </sheetPr>
-  <dimension ref="A1:F32"/>
+  <dimension ref="A1:F31"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="2" width="16.7109375" style="1" customWidth="1" collapsed="1"/>
@@ -584,7 +566,7 @@
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A2" s="6">
-        <v>133978332</v>
+        <v>133931478</v>
       </c>
       <c r="B2" s="1" t="s">
         <v>7</v>
@@ -1033,111 +1015,19 @@
       <c r="F26"/>
     </row>
     <row r="27" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A27" s="1" t="s">
-        <v>34</v>
-      </c>
-      <c r="B27" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C27" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D27" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="E27" s="2" t="s">
-        <v>6</v>
-      </c>
       <c r="F27"/>
     </row>
     <row r="28" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A28" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="B28" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C28" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D28" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="E28" s="2" t="s">
-        <v>6</v>
-      </c>
       <c r="F28"/>
     </row>
     <row r="29" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A29" s="1" t="s">
-        <v>36</v>
-      </c>
-      <c r="B29" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C29" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D29" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="E29" s="2" t="s">
-        <v>6</v>
-      </c>
       <c r="F29"/>
     </row>
     <row r="30" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A30" s="1" t="s">
-        <v>37</v>
-      </c>
-      <c r="B30" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C30" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D30" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="E30" s="2" t="s">
-        <v>6</v>
-      </c>
       <c r="F30"/>
     </row>
     <row r="31" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A31" s="1" t="s">
-        <v>38</v>
-      </c>
-      <c r="B31" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C31" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D31" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="E31" s="2" t="s">
-        <v>6</v>
-      </c>
       <c r="F31"/>
-    </row>
-    <row r="32" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A32" s="1" t="s">
-        <v>39</v>
-      </c>
-      <c r="B32" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C32" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D32" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="E32" s="2" t="s">
-        <v>6</v>
-      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:F1" xr:uid="{00000000-0001-0000-0000-000000000000}"/>

--- a/Data Files/Backoffce/IndexacaoFG/IndexacaoFG_SANTANDER.xlsx
+++ b/Data Files/Backoffce/IndexacaoFG/IndexacaoFG_SANTANDER.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Public\RPA_ALLIANZ_TREINAMENTO\Data Files\Backoffce\IndexacaoFG\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{818D5C31-632C-4EA0-8BCB-325B367D02AD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{49083378-A8C0-492F-8998-45BB426951CB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3150" yWindow="2955" windowWidth="15375" windowHeight="7875" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="IndexacaoFG" sheetId="2" r:id="rId1"/>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="130" uniqueCount="34">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="140" uniqueCount="36">
   <si>
     <t xml:space="preserve">status </t>
   </si>
@@ -51,85 +51,91 @@
     <t>Processar</t>
   </si>
   <si>
+    <t>Relatório de Recusas  25.08.2025 a 31.08.2025</t>
+  </si>
+  <si>
     <t>1070</t>
   </si>
   <si>
-    <t>Relatório de Recusas  25.08.2025 a 31.08.2025</t>
-  </si>
-  <si>
-    <t>Relatório de Recusas Santander - 27/08/2025</t>
-  </si>
-  <si>
-    <t>134002781</t>
-  </si>
-  <si>
-    <t>134011293</t>
-  </si>
-  <si>
-    <t>134015104</t>
-  </si>
-  <si>
-    <t>134003094</t>
-  </si>
-  <si>
-    <t>134009970</t>
-  </si>
-  <si>
-    <t>134023812</t>
-  </si>
-  <si>
-    <t>134009993</t>
-  </si>
-  <si>
-    <t>134015383</t>
-  </si>
-  <si>
-    <t>134094458</t>
-  </si>
-  <si>
-    <t>134095206</t>
-  </si>
-  <si>
-    <t>134111744</t>
-  </si>
-  <si>
-    <t>134106242</t>
-  </si>
-  <si>
-    <t>134131120</t>
-  </si>
-  <si>
-    <t>134012774</t>
-  </si>
-  <si>
-    <t>134003887</t>
-  </si>
-  <si>
-    <t>133996064</t>
-  </si>
-  <si>
-    <t>134005385</t>
-  </si>
-  <si>
-    <t>134007219</t>
-  </si>
-  <si>
-    <t>134008340</t>
-  </si>
-  <si>
-    <t>134009089</t>
-  </si>
-  <si>
-    <t>134010861</t>
-  </si>
-  <si>
-    <t>134011991</t>
-  </si>
-  <si>
-    <t>134012545</t>
-  </si>
-  <si>
-    <t>134015859</t>
+    <t>Relatório de Recusas Santander - 28/08/2025</t>
+  </si>
+  <si>
+    <t>134030410</t>
+  </si>
+  <si>
+    <t>134085449</t>
+  </si>
+  <si>
+    <t>134081882</t>
+  </si>
+  <si>
+    <t>134120327</t>
+  </si>
+  <si>
+    <t>134123005</t>
+  </si>
+  <si>
+    <t>134151226</t>
+  </si>
+  <si>
+    <t>134156211</t>
+  </si>
+  <si>
+    <t>133953737</t>
+  </si>
+  <si>
+    <t>133956942</t>
+  </si>
+  <si>
+    <t>133957208</t>
+  </si>
+  <si>
+    <t>133969078</t>
+  </si>
+  <si>
+    <t>133968156</t>
+  </si>
+  <si>
+    <t>134028341</t>
+  </si>
+  <si>
+    <t>133980074</t>
+  </si>
+  <si>
+    <t>134046643</t>
+  </si>
+  <si>
+    <t>134021045</t>
+  </si>
+  <si>
+    <t>134028122</t>
+  </si>
+  <si>
+    <t>133961625</t>
+  </si>
+  <si>
+    <t>134026947</t>
+  </si>
+  <si>
+    <t>134027915</t>
+  </si>
+  <si>
+    <t>134027953</t>
+  </si>
+  <si>
+    <t>134029327</t>
+  </si>
+  <si>
+    <t>134033569</t>
+  </si>
+  <si>
+    <t>134033796</t>
+  </si>
+  <si>
+    <t>134037774</t>
+  </si>
+  <si>
+    <t>134075647</t>
   </si>
 </sst>
 </file>
@@ -566,16 +572,16 @@
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A2" s="6">
-        <v>133931478</v>
+        <v>134037866</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C2" s="2" t="s">
         <v>9</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E2" s="2" t="s">
         <v>6</v>
@@ -587,13 +593,13 @@
         <v>10</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C3" s="2" t="s">
         <v>9</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E3" s="2" t="s">
         <v>6</v>
@@ -605,13 +611,13 @@
         <v>11</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C4" s="2" t="s">
         <v>9</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E4" s="2" t="s">
         <v>6</v>
@@ -623,13 +629,13 @@
         <v>12</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C5" s="2" t="s">
         <v>9</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E5" s="2" t="s">
         <v>6</v>
@@ -641,13 +647,13 @@
         <v>13</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C6" s="2" t="s">
         <v>9</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E6" s="2" t="s">
         <v>6</v>
@@ -659,13 +665,13 @@
         <v>14</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C7" s="2" t="s">
         <v>9</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E7" s="2" t="s">
         <v>6</v>
@@ -677,13 +683,13 @@
         <v>15</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C8" s="2" t="s">
         <v>9</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E8" s="2" t="s">
         <v>6</v>
@@ -695,13 +701,13 @@
         <v>16</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C9" s="2" t="s">
         <v>9</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E9" s="2" t="s">
         <v>6</v>
@@ -713,13 +719,13 @@
         <v>17</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C10" s="2" t="s">
         <v>9</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E10" s="2" t="s">
         <v>6</v>
@@ -731,13 +737,13 @@
         <v>18</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C11" s="2" t="s">
         <v>9</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E11" s="2" t="s">
         <v>6</v>
@@ -749,13 +755,13 @@
         <v>19</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C12" s="2" t="s">
         <v>9</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E12" s="2" t="s">
         <v>6</v>
@@ -767,13 +773,13 @@
         <v>20</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C13" s="2" t="s">
         <v>9</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E13" s="2" t="s">
         <v>6</v>
@@ -785,13 +791,13 @@
         <v>21</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C14" s="2" t="s">
         <v>9</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E14" s="2" t="s">
         <v>6</v>
@@ -803,13 +809,13 @@
         <v>22</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C15" s="2" t="s">
         <v>9</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E15" s="2" t="s">
         <v>6</v>
@@ -821,13 +827,13 @@
         <v>23</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C16" s="2" t="s">
         <v>9</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E16" s="2" t="s">
         <v>6</v>
@@ -839,13 +845,13 @@
         <v>24</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C17" s="2" t="s">
         <v>9</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E17" s="2" t="s">
         <v>6</v>
@@ -857,13 +863,13 @@
         <v>25</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C18" s="2" t="s">
         <v>9</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E18" s="2" t="s">
         <v>6</v>
@@ -875,13 +881,13 @@
         <v>26</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C19" s="2" t="s">
         <v>9</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E19" s="2" t="s">
         <v>6</v>
@@ -893,13 +899,13 @@
         <v>27</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C20" s="2" t="s">
         <v>9</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E20" s="2" t="s">
         <v>6</v>
@@ -911,13 +917,13 @@
         <v>28</v>
       </c>
       <c r="B21" s="1" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C21" s="2" t="s">
         <v>9</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E21" s="2" t="s">
         <v>6</v>
@@ -929,13 +935,13 @@
         <v>29</v>
       </c>
       <c r="B22" s="1" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C22" s="2" t="s">
         <v>9</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E22" s="2" t="s">
         <v>6</v>
@@ -947,13 +953,13 @@
         <v>30</v>
       </c>
       <c r="B23" s="1" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C23" s="2" t="s">
         <v>9</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E23" s="2" t="s">
         <v>6</v>
@@ -965,13 +971,13 @@
         <v>31</v>
       </c>
       <c r="B24" s="1" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C24" s="2" t="s">
         <v>9</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E24" s="2" t="s">
         <v>6</v>
@@ -983,13 +989,13 @@
         <v>32</v>
       </c>
       <c r="B25" s="1" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C25" s="2" t="s">
         <v>9</v>
       </c>
       <c r="D25" s="2" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E25" s="2" t="s">
         <v>6</v>
@@ -1001,13 +1007,13 @@
         <v>33</v>
       </c>
       <c r="B26" s="1" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C26" s="2" t="s">
         <v>9</v>
       </c>
       <c r="D26" s="2" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E26" s="2" t="s">
         <v>6</v>
@@ -1015,9 +1021,39 @@
       <c r="F26"/>
     </row>
     <row r="27" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A27" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="B27" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C27" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D27" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="E27" s="2" t="s">
+        <v>6</v>
+      </c>
       <c r="F27"/>
     </row>
     <row r="28" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A28" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="B28" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C28" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D28" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="E28" s="2" t="s">
+        <v>6</v>
+      </c>
       <c r="F28"/>
     </row>
     <row r="29" spans="1:6" x14ac:dyDescent="0.25">

--- a/Data Files/Backoffce/IndexacaoFG/IndexacaoFG_SANTANDER.xlsx
+++ b/Data Files/Backoffce/IndexacaoFG/IndexacaoFG_SANTANDER.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Public\RPA_ALLIANZ_TREINAMENTO\Data Files\Backoffce\IndexacaoFG\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{49083378-A8C0-492F-8998-45BB426951CB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DB130924-2914-43D6-81AE-C96A8DF65B67}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="140" uniqueCount="36">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="130" uniqueCount="34">
   <si>
     <t xml:space="preserve">status </t>
   </si>
@@ -57,85 +57,79 @@
     <t>1070</t>
   </si>
   <si>
-    <t>Relatório de Recusas Santander - 28/08/2025</t>
-  </si>
-  <si>
-    <t>134030410</t>
-  </si>
-  <si>
-    <t>134085449</t>
-  </si>
-  <si>
-    <t>134081882</t>
-  </si>
-  <si>
-    <t>134120327</t>
-  </si>
-  <si>
-    <t>134123005</t>
-  </si>
-  <si>
-    <t>134151226</t>
-  </si>
-  <si>
-    <t>134156211</t>
-  </si>
-  <si>
-    <t>133953737</t>
-  </si>
-  <si>
-    <t>133956942</t>
-  </si>
-  <si>
-    <t>133957208</t>
-  </si>
-  <si>
-    <t>133969078</t>
-  </si>
-  <si>
-    <t>133968156</t>
-  </si>
-  <si>
-    <t>134028341</t>
-  </si>
-  <si>
-    <t>133980074</t>
-  </si>
-  <si>
-    <t>134046643</t>
-  </si>
-  <si>
-    <t>134021045</t>
-  </si>
-  <si>
-    <t>134028122</t>
-  </si>
-  <si>
-    <t>133961625</t>
-  </si>
-  <si>
-    <t>134026947</t>
-  </si>
-  <si>
-    <t>134027915</t>
-  </si>
-  <si>
-    <t>134027953</t>
-  </si>
-  <si>
-    <t>134029327</t>
-  </si>
-  <si>
-    <t>134033569</t>
-  </si>
-  <si>
-    <t>134033796</t>
-  </si>
-  <si>
-    <t>134037774</t>
-  </si>
-  <si>
-    <t>134075647</t>
+    <t>Relatório de Recusas Santander - 29 e 30/08/2025</t>
+  </si>
+  <si>
+    <t>133979133</t>
+  </si>
+  <si>
+    <t>134050897</t>
+  </si>
+  <si>
+    <t>134058118</t>
+  </si>
+  <si>
+    <t>134057758</t>
+  </si>
+  <si>
+    <t>134049809</t>
+  </si>
+  <si>
+    <t>134140085</t>
+  </si>
+  <si>
+    <t>134157687</t>
+  </si>
+  <si>
+    <t>134150333</t>
+  </si>
+  <si>
+    <t>134147149</t>
+  </si>
+  <si>
+    <t>133976007</t>
+  </si>
+  <si>
+    <t>133955750</t>
+  </si>
+  <si>
+    <t>133990957</t>
+  </si>
+  <si>
+    <t>134073293</t>
+  </si>
+  <si>
+    <t>134048206</t>
+  </si>
+  <si>
+    <t>134048620</t>
+  </si>
+  <si>
+    <t>134050664</t>
+  </si>
+  <si>
+    <t>134053988</t>
+  </si>
+  <si>
+    <t>134009983</t>
+  </si>
+  <si>
+    <t>134078495</t>
+  </si>
+  <si>
+    <t>134078694</t>
+  </si>
+  <si>
+    <t>134195138</t>
+  </si>
+  <si>
+    <t>133981227</t>
+  </si>
+  <si>
+    <t>134080559</t>
+  </si>
+  <si>
+    <t>134067107</t>
   </si>
 </sst>
 </file>
@@ -572,7 +566,7 @@
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A2" s="6">
-        <v>134037866</v>
+        <v>134048500</v>
       </c>
       <c r="B2" s="1" t="s">
         <v>8</v>
@@ -1021,39 +1015,9 @@
       <c r="F26"/>
     </row>
     <row r="27" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A27" s="1" t="s">
-        <v>34</v>
-      </c>
-      <c r="B27" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="C27" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D27" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="E27" s="2" t="s">
-        <v>6</v>
-      </c>
       <c r="F27"/>
     </row>
     <row r="28" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A28" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="B28" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="C28" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D28" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="E28" s="2" t="s">
-        <v>6</v>
-      </c>
       <c r="F28"/>
     </row>
     <row r="29" spans="1:6" x14ac:dyDescent="0.25">

--- a/Data Files/Backoffce/IndexacaoFG/IndexacaoFG_SANTANDER.xlsx
+++ b/Data Files/Backoffce/IndexacaoFG/IndexacaoFG_SANTANDER.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Public\RPA_ALLIANZ_TREINAMENTO\Data Files\Backoffce\IndexacaoFG\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DB130924-2914-43D6-81AE-C96A8DF65B67}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D57BE537-BD82-4EA6-A924-A4FFB7EFE940}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="130" uniqueCount="34">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="90" uniqueCount="26">
   <si>
     <t xml:space="preserve">status </t>
   </si>
@@ -51,85 +51,61 @@
     <t>Processar</t>
   </si>
   <si>
-    <t>Relatório de Recusas  25.08.2025 a 31.08.2025</t>
-  </si>
-  <si>
     <t>1070</t>
   </si>
   <si>
-    <t>Relatório de Recusas Santander - 29 e 30/08/2025</t>
-  </si>
-  <si>
-    <t>133979133</t>
-  </si>
-  <si>
-    <t>134050897</t>
-  </si>
-  <si>
-    <t>134058118</t>
-  </si>
-  <si>
-    <t>134057758</t>
-  </si>
-  <si>
-    <t>134049809</t>
-  </si>
-  <si>
-    <t>134140085</t>
-  </si>
-  <si>
-    <t>134157687</t>
-  </si>
-  <si>
-    <t>134150333</t>
-  </si>
-  <si>
-    <t>134147149</t>
-  </si>
-  <si>
-    <t>133976007</t>
-  </si>
-  <si>
-    <t>133955750</t>
-  </si>
-  <si>
-    <t>133990957</t>
-  </si>
-  <si>
-    <t>134073293</t>
-  </si>
-  <si>
-    <t>134048206</t>
-  </si>
-  <si>
-    <t>134048620</t>
-  </si>
-  <si>
-    <t>134050664</t>
-  </si>
-  <si>
-    <t>134053988</t>
-  </si>
-  <si>
-    <t>134009983</t>
-  </si>
-  <si>
-    <t>134078495</t>
-  </si>
-  <si>
-    <t>134078694</t>
-  </si>
-  <si>
-    <t>134195138</t>
-  </si>
-  <si>
-    <t>133981227</t>
-  </si>
-  <si>
-    <t>134080559</t>
-  </si>
-  <si>
-    <t>134067107</t>
+    <t>Relatório de Recusas  01.09.2025 a 07.09.2025</t>
+  </si>
+  <si>
+    <t>Relatório de Recusas Santander - 01/09/2025</t>
+  </si>
+  <si>
+    <t>134099220</t>
+  </si>
+  <si>
+    <t>134133670</t>
+  </si>
+  <si>
+    <t>134122888</t>
+  </si>
+  <si>
+    <t>134159622</t>
+  </si>
+  <si>
+    <t>134150286</t>
+  </si>
+  <si>
+    <t>134207612</t>
+  </si>
+  <si>
+    <t>134208212</t>
+  </si>
+  <si>
+    <t>134169985</t>
+  </si>
+  <si>
+    <t>134188708</t>
+  </si>
+  <si>
+    <t>134102658</t>
+  </si>
+  <si>
+    <t>134175235</t>
+  </si>
+  <si>
+    <t>134128924</t>
+  </si>
+  <si>
+    <t>134084701</t>
+  </si>
+  <si>
+    <t>134130675</t>
+  </si>
+  <si>
+    <t>134077451</t>
+  </si>
+  <si>
+    <t>134013561</t>
   </si>
 </sst>
 </file>
@@ -566,16 +542,16 @@
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A2" s="6">
-        <v>134048500</v>
+        <v>134003210</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C2" s="2" t="s">
         <v>9</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E2" s="2" t="s">
         <v>6</v>
@@ -587,13 +563,13 @@
         <v>10</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C3" s="2" t="s">
         <v>9</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E3" s="2" t="s">
         <v>6</v>
@@ -605,13 +581,13 @@
         <v>11</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C4" s="2" t="s">
         <v>9</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E4" s="2" t="s">
         <v>6</v>
@@ -623,13 +599,13 @@
         <v>12</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C5" s="2" t="s">
         <v>9</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E5" s="2" t="s">
         <v>6</v>
@@ -641,13 +617,13 @@
         <v>13</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C6" s="2" t="s">
         <v>9</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E6" s="2" t="s">
         <v>6</v>
@@ -659,13 +635,13 @@
         <v>14</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C7" s="2" t="s">
         <v>9</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E7" s="2" t="s">
         <v>6</v>
@@ -677,13 +653,13 @@
         <v>15</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C8" s="2" t="s">
         <v>9</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E8" s="2" t="s">
         <v>6</v>
@@ -695,13 +671,13 @@
         <v>16</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C9" s="2" t="s">
         <v>9</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E9" s="2" t="s">
         <v>6</v>
@@ -713,13 +689,13 @@
         <v>17</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C10" s="2" t="s">
         <v>9</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E10" s="2" t="s">
         <v>6</v>
@@ -731,13 +707,13 @@
         <v>18</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C11" s="2" t="s">
         <v>9</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E11" s="2" t="s">
         <v>6</v>
@@ -749,13 +725,13 @@
         <v>19</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C12" s="2" t="s">
         <v>9</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E12" s="2" t="s">
         <v>6</v>
@@ -767,13 +743,13 @@
         <v>20</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C13" s="2" t="s">
         <v>9</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E13" s="2" t="s">
         <v>6</v>
@@ -785,13 +761,13 @@
         <v>21</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C14" s="2" t="s">
         <v>9</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E14" s="2" t="s">
         <v>6</v>
@@ -803,13 +779,13 @@
         <v>22</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C15" s="2" t="s">
         <v>9</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E15" s="2" t="s">
         <v>6</v>
@@ -821,13 +797,13 @@
         <v>23</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C16" s="2" t="s">
         <v>9</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E16" s="2" t="s">
         <v>6</v>
@@ -839,13 +815,13 @@
         <v>24</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C17" s="2" t="s">
         <v>9</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E17" s="2" t="s">
         <v>6</v>
@@ -857,13 +833,13 @@
         <v>25</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C18" s="2" t="s">
         <v>9</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E18" s="2" t="s">
         <v>6</v>
@@ -871,147 +847,27 @@
       <c r="F18"/>
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A19" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="B19" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="C19" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D19" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="E19" s="2" t="s">
-        <v>6</v>
-      </c>
       <c r="F19"/>
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A20" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="B20" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="C20" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D20" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="E20" s="2" t="s">
-        <v>6</v>
-      </c>
       <c r="F20"/>
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A21" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="B21" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="C21" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D21" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="E21" s="2" t="s">
-        <v>6</v>
-      </c>
       <c r="F21"/>
     </row>
     <row r="22" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A22" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="B22" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="C22" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D22" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="E22" s="2" t="s">
-        <v>6</v>
-      </c>
       <c r="F22"/>
     </row>
     <row r="23" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A23" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="B23" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="C23" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D23" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="E23" s="2" t="s">
-        <v>6</v>
-      </c>
       <c r="F23"/>
     </row>
     <row r="24" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A24" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="B24" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="C24" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D24" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="E24" s="2" t="s">
-        <v>6</v>
-      </c>
       <c r="F24"/>
     </row>
     <row r="25" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A25" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="B25" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="C25" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D25" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="E25" s="2" t="s">
-        <v>6</v>
-      </c>
       <c r="F25"/>
     </row>
     <row r="26" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A26" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="B26" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="C26" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D26" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="E26" s="2" t="s">
-        <v>6</v>
-      </c>
       <c r="F26"/>
     </row>
     <row r="27" spans="1:6" x14ac:dyDescent="0.25">

--- a/Data Files/Backoffce/IndexacaoFG/IndexacaoFG_SANTANDER.xlsx
+++ b/Data Files/Backoffce/IndexacaoFG/IndexacaoFG_SANTANDER.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Public\RPA_ALLIANZ_TREINAMENTO\Data Files\Backoffce\IndexacaoFG\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D57BE537-BD82-4EA6-A924-A4FFB7EFE940}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9EA80E60-7EEB-4016-9BAA-D37EE3EA46FE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="90" uniqueCount="26">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="145" uniqueCount="37">
   <si>
     <t xml:space="preserve">status </t>
   </si>
@@ -57,55 +57,88 @@
     <t>Relatório de Recusas  01.09.2025 a 07.09.2025</t>
   </si>
   <si>
-    <t>Relatório de Recusas Santander - 01/09/2025</t>
-  </si>
-  <si>
-    <t>134099220</t>
-  </si>
-  <si>
-    <t>134133670</t>
-  </si>
-  <si>
-    <t>134122888</t>
-  </si>
-  <si>
-    <t>134159622</t>
-  </si>
-  <si>
-    <t>134150286</t>
-  </si>
-  <si>
-    <t>134207612</t>
-  </si>
-  <si>
-    <t>134208212</t>
-  </si>
-  <si>
-    <t>134169985</t>
-  </si>
-  <si>
-    <t>134188708</t>
-  </si>
-  <si>
-    <t>134102658</t>
-  </si>
-  <si>
-    <t>134175235</t>
-  </si>
-  <si>
-    <t>134128924</t>
-  </si>
-  <si>
-    <t>134084701</t>
-  </si>
-  <si>
-    <t>134130675</t>
-  </si>
-  <si>
-    <t>134077451</t>
-  </si>
-  <si>
-    <t>134013561</t>
+    <t>Relatório de Recusas Santander - 02/09/2025</t>
+  </si>
+  <si>
+    <t>134095794</t>
+  </si>
+  <si>
+    <t>134109745</t>
+  </si>
+  <si>
+    <t>134121915</t>
+  </si>
+  <si>
+    <t>134124054</t>
+  </si>
+  <si>
+    <t>134119965</t>
+  </si>
+  <si>
+    <t>134125794</t>
+  </si>
+  <si>
+    <t>134111080</t>
+  </si>
+  <si>
+    <t>134154960</t>
+  </si>
+  <si>
+    <t>134151876</t>
+  </si>
+  <si>
+    <t>134183088</t>
+  </si>
+  <si>
+    <t>134180763</t>
+  </si>
+  <si>
+    <t>134201306</t>
+  </si>
+  <si>
+    <t>134207033</t>
+  </si>
+  <si>
+    <t>134219558</t>
+  </si>
+  <si>
+    <t>134027006</t>
+  </si>
+  <si>
+    <t>134035956</t>
+  </si>
+  <si>
+    <t>134110967</t>
+  </si>
+  <si>
+    <t>134111484</t>
+  </si>
+  <si>
+    <t>134101134</t>
+  </si>
+  <si>
+    <t>134102178</t>
+  </si>
+  <si>
+    <t>134102379</t>
+  </si>
+  <si>
+    <t>134105072</t>
+  </si>
+  <si>
+    <t>134105650</t>
+  </si>
+  <si>
+    <t>134106643</t>
+  </si>
+  <si>
+    <t>134108795</t>
+  </si>
+  <si>
+    <t>134109633</t>
+  </si>
+  <si>
+    <t>134178433</t>
   </si>
 </sst>
 </file>
@@ -542,7 +575,7 @@
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A2" s="6">
-        <v>134003210</v>
+        <v>134037502</v>
       </c>
       <c r="B2" s="1" t="s">
         <v>7</v>
@@ -847,36 +880,201 @@
       <c r="F18"/>
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A19" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="B19" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C19" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D19" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E19" s="2" t="s">
+        <v>6</v>
+      </c>
       <c r="F19"/>
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A20" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="B20" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C20" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D20" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E20" s="2" t="s">
+        <v>6</v>
+      </c>
       <c r="F20"/>
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A21" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="B21" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C21" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D21" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E21" s="2" t="s">
+        <v>6</v>
+      </c>
       <c r="F21"/>
     </row>
     <row r="22" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A22" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="B22" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C22" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D22" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E22" s="2" t="s">
+        <v>6</v>
+      </c>
       <c r="F22"/>
     </row>
     <row r="23" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A23" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="B23" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C23" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D23" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E23" s="2" t="s">
+        <v>6</v>
+      </c>
       <c r="F23"/>
     </row>
     <row r="24" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A24" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="B24" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C24" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D24" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E24" s="2" t="s">
+        <v>6</v>
+      </c>
       <c r="F24"/>
     </row>
     <row r="25" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A25" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="B25" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C25" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D25" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E25" s="2" t="s">
+        <v>6</v>
+      </c>
       <c r="F25"/>
     </row>
     <row r="26" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A26" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="B26" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C26" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D26" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E26" s="2" t="s">
+        <v>6</v>
+      </c>
       <c r="F26"/>
     </row>
     <row r="27" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A27" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="B27" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C27" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D27" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E27" s="2" t="s">
+        <v>6</v>
+      </c>
       <c r="F27"/>
     </row>
     <row r="28" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A28" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="B28" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C28" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D28" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E28" s="2" t="s">
+        <v>6</v>
+      </c>
       <c r="F28"/>
     </row>
     <row r="29" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A29" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="B29" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C29" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D29" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E29" s="2" t="s">
+        <v>6</v>
+      </c>
       <c r="F29"/>
     </row>
     <row r="30" spans="1:6" x14ac:dyDescent="0.25">

--- a/Data Files/Backoffce/IndexacaoFG/IndexacaoFG_SANTANDER.xlsx
+++ b/Data Files/Backoffce/IndexacaoFG/IndexacaoFG_SANTANDER.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Public\RPA_ALLIANZ_TREINAMENTO\Data Files\Backoffce\IndexacaoFG\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9EA80E60-7EEB-4016-9BAA-D37EE3EA46FE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C65CC160-C212-4ED8-B3E2-2BE6578FA450}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="145" uniqueCount="37">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="110" uniqueCount="30">
   <si>
     <t xml:space="preserve">status </t>
   </si>
@@ -57,88 +57,67 @@
     <t>Relatório de Recusas  01.09.2025 a 07.09.2025</t>
   </si>
   <si>
-    <t>Relatório de Recusas Santander - 02/09/2025</t>
-  </si>
-  <si>
-    <t>134095794</t>
-  </si>
-  <si>
-    <t>134109745</t>
-  </si>
-  <si>
-    <t>134121915</t>
-  </si>
-  <si>
-    <t>134124054</t>
-  </si>
-  <si>
-    <t>134119965</t>
-  </si>
-  <si>
-    <t>134125794</t>
-  </si>
-  <si>
-    <t>134111080</t>
-  </si>
-  <si>
-    <t>134154960</t>
-  </si>
-  <si>
-    <t>134151876</t>
-  </si>
-  <si>
-    <t>134183088</t>
-  </si>
-  <si>
-    <t>134180763</t>
-  </si>
-  <si>
-    <t>134201306</t>
-  </si>
-  <si>
-    <t>134207033</t>
-  </si>
-  <si>
-    <t>134219558</t>
-  </si>
-  <si>
-    <t>134027006</t>
-  </si>
-  <si>
-    <t>134035956</t>
-  </si>
-  <si>
-    <t>134110967</t>
-  </si>
-  <si>
-    <t>134111484</t>
-  </si>
-  <si>
-    <t>134101134</t>
-  </si>
-  <si>
-    <t>134102178</t>
-  </si>
-  <si>
-    <t>134102379</t>
-  </si>
-  <si>
-    <t>134105072</t>
-  </si>
-  <si>
-    <t>134105650</t>
-  </si>
-  <si>
-    <t>134106643</t>
-  </si>
-  <si>
-    <t>134108795</t>
-  </si>
-  <si>
-    <t>134109633</t>
-  </si>
-  <si>
-    <t>134178433</t>
+    <t>Relatório de Recusas Santander - 03/09/2025</t>
+  </si>
+  <si>
+    <t>134147122</t>
+  </si>
+  <si>
+    <t>134214197</t>
+  </si>
+  <si>
+    <t>134238726</t>
+  </si>
+  <si>
+    <t>134059342</t>
+  </si>
+  <si>
+    <t>134116242</t>
+  </si>
+  <si>
+    <t>134081030</t>
+  </si>
+  <si>
+    <t>134148746</t>
+  </si>
+  <si>
+    <t>134053193</t>
+  </si>
+  <si>
+    <t>134123155</t>
+  </si>
+  <si>
+    <t>134079280</t>
+  </si>
+  <si>
+    <t>134263582</t>
+  </si>
+  <si>
+    <t>134242353</t>
+  </si>
+  <si>
+    <t>134064264</t>
+  </si>
+  <si>
+    <t>134068199</t>
+  </si>
+  <si>
+    <t>134073616</t>
+  </si>
+  <si>
+    <t>134074618</t>
+  </si>
+  <si>
+    <t>134075021</t>
+  </si>
+  <si>
+    <t>134076325</t>
+  </si>
+  <si>
+    <t>134179739</t>
+  </si>
+  <si>
+    <t>134177114</t>
   </si>
 </sst>
 </file>
@@ -543,7 +522,7 @@
   <sheetPr>
     <pageSetUpPr autoPageBreaks="0"/>
   </sheetPr>
-  <dimension ref="A1:F31"/>
+  <dimension ref="A1:F22"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="2" width="16.7109375" style="1" customWidth="1" collapsed="1"/>
@@ -575,7 +554,7 @@
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A2" s="6">
-        <v>134037502</v>
+        <v>134179873</v>
       </c>
       <c r="B2" s="1" t="s">
         <v>7</v>
@@ -950,138 +929,6 @@
         <v>6</v>
       </c>
       <c r="F22"/>
-    </row>
-    <row r="23" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A23" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="B23" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C23" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D23" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="E23" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="F23"/>
-    </row>
-    <row r="24" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A24" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="B24" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C24" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D24" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="E24" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="F24"/>
-    </row>
-    <row r="25" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A25" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="B25" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C25" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D25" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="E25" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="F25"/>
-    </row>
-    <row r="26" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A26" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="B26" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C26" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D26" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="E26" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="F26"/>
-    </row>
-    <row r="27" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A27" s="1" t="s">
-        <v>34</v>
-      </c>
-      <c r="B27" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C27" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D27" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="E27" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="F27"/>
-    </row>
-    <row r="28" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A28" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="B28" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C28" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D28" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="E28" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="F28"/>
-    </row>
-    <row r="29" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A29" s="1" t="s">
-        <v>36</v>
-      </c>
-      <c r="B29" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C29" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D29" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="E29" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="F29"/>
-    </row>
-    <row r="30" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="F30"/>
-    </row>
-    <row r="31" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="F31"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:F1" xr:uid="{00000000-0001-0000-0000-000000000000}"/>

--- a/Data Files/Backoffce/IndexacaoFG/IndexacaoFG_SANTANDER.xlsx
+++ b/Data Files/Backoffce/IndexacaoFG/IndexacaoFG_SANTANDER.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Public\RPA_ALLIANZ_TREINAMENTO\Data Files\Backoffce\IndexacaoFG\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C65CC160-C212-4ED8-B3E2-2BE6578FA450}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9313B84B-4A60-40A5-95C3-64D7CDE450A7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="110" uniqueCount="30">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="270" uniqueCount="62">
   <si>
     <t xml:space="preserve">status </t>
   </si>
@@ -57,67 +57,163 @@
     <t>Relatório de Recusas  01.09.2025 a 07.09.2025</t>
   </si>
   <si>
-    <t>Relatório de Recusas Santander - 03/09/2025</t>
-  </si>
-  <si>
-    <t>134147122</t>
-  </si>
-  <si>
-    <t>134214197</t>
-  </si>
-  <si>
-    <t>134238726</t>
-  </si>
-  <si>
-    <t>134059342</t>
-  </si>
-  <si>
-    <t>134116242</t>
-  </si>
-  <si>
-    <t>134081030</t>
-  </si>
-  <si>
-    <t>134148746</t>
-  </si>
-  <si>
-    <t>134053193</t>
-  </si>
-  <si>
-    <t>134123155</t>
-  </si>
-  <si>
-    <t>134079280</t>
-  </si>
-  <si>
-    <t>134263582</t>
-  </si>
-  <si>
-    <t>134242353</t>
-  </si>
-  <si>
-    <t>134064264</t>
-  </si>
-  <si>
-    <t>134068199</t>
-  </si>
-  <si>
-    <t>134073616</t>
-  </si>
-  <si>
-    <t>134074618</t>
-  </si>
-  <si>
-    <t>134075021</t>
-  </si>
-  <si>
-    <t>134076325</t>
-  </si>
-  <si>
-    <t>134179739</t>
-  </si>
-  <si>
-    <t>134177114</t>
+    <t>Relatório de Recusas Santander - 04/09/2025</t>
+  </si>
+  <si>
+    <t>134117963</t>
+  </si>
+  <si>
+    <t>134129842</t>
+  </si>
+  <si>
+    <t>134159242</t>
+  </si>
+  <si>
+    <t>134122740</t>
+  </si>
+  <si>
+    <t>134159592</t>
+  </si>
+  <si>
+    <t>134151508</t>
+  </si>
+  <si>
+    <t>134151675</t>
+  </si>
+  <si>
+    <t>134156726</t>
+  </si>
+  <si>
+    <t>134151502</t>
+  </si>
+  <si>
+    <t>134160229</t>
+  </si>
+  <si>
+    <t>134142314</t>
+  </si>
+  <si>
+    <t>134160191</t>
+  </si>
+  <si>
+    <t>134160582</t>
+  </si>
+  <si>
+    <t>134158678</t>
+  </si>
+  <si>
+    <t>134159195</t>
+  </si>
+  <si>
+    <t>134195795</t>
+  </si>
+  <si>
+    <t>134131938</t>
+  </si>
+  <si>
+    <t>134151203</t>
+  </si>
+  <si>
+    <t>134181258</t>
+  </si>
+  <si>
+    <t>134158894</t>
+  </si>
+  <si>
+    <t>134272282</t>
+  </si>
+  <si>
+    <t>134073511</t>
+  </si>
+  <si>
+    <t>134117765</t>
+  </si>
+  <si>
+    <t>134119034</t>
+  </si>
+  <si>
+    <t>134119881</t>
+  </si>
+  <si>
+    <t>134123847</t>
+  </si>
+  <si>
+    <t>134125124</t>
+  </si>
+  <si>
+    <t>134125486</t>
+  </si>
+  <si>
+    <t>134130794</t>
+  </si>
+  <si>
+    <t>134131237</t>
+  </si>
+  <si>
+    <t>134133609</t>
+  </si>
+  <si>
+    <t>134134215</t>
+  </si>
+  <si>
+    <t>134134268</t>
+  </si>
+  <si>
+    <t>134071048</t>
+  </si>
+  <si>
+    <t>134077361</t>
+  </si>
+  <si>
+    <t>134077137</t>
+  </si>
+  <si>
+    <t>134285315</t>
+  </si>
+  <si>
+    <t>134139465</t>
+  </si>
+  <si>
+    <t>134144563</t>
+  </si>
+  <si>
+    <t>134146490</t>
+  </si>
+  <si>
+    <t>134146948</t>
+  </si>
+  <si>
+    <t>134151477</t>
+  </si>
+  <si>
+    <t>134151955</t>
+  </si>
+  <si>
+    <t>134154522</t>
+  </si>
+  <si>
+    <t>134084614</t>
+  </si>
+  <si>
+    <t>134156516</t>
+  </si>
+  <si>
+    <t>134156704</t>
+  </si>
+  <si>
+    <t>134157147</t>
+  </si>
+  <si>
+    <t>134158807</t>
+  </si>
+  <si>
+    <t>134158935</t>
+  </si>
+  <si>
+    <t>134162394</t>
+  </si>
+  <si>
+    <t>134199244</t>
   </si>
 </sst>
 </file>
@@ -522,7 +618,7 @@
   <sheetPr>
     <pageSetUpPr autoPageBreaks="0"/>
   </sheetPr>
-  <dimension ref="A1:F22"/>
+  <dimension ref="A1:F54"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="2" width="16.7109375" style="1" customWidth="1" collapsed="1"/>
@@ -554,7 +650,7 @@
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A2" s="6">
-        <v>134179873</v>
+        <v>134129134</v>
       </c>
       <c r="B2" s="1" t="s">
         <v>7</v>
@@ -929,6 +1025,550 @@
         <v>6</v>
       </c>
       <c r="F22"/>
+    </row>
+    <row r="23" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A23" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="B23" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C23" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D23" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E23" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="24" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A24" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="B24" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C24" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D24" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E24" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="25" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A25" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="B25" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C25" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D25" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E25" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="26" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A26" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="B26" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C26" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D26" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E26" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="27" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A27" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="B27" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C27" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D27" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E27" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="28" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A28" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="B28" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C28" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D28" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E28" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="29" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A29" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="B29" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C29" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D29" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E29" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="30" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A30" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="B30" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C30" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D30" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E30" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="31" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A31" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="B31" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C31" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D31" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E31" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="32" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A32" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="B32" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C32" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D32" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E32" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="33" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A33" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="B33" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C33" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D33" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E33" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="34" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A34" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="B34" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C34" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D34" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E34" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="35" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A35" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="B35" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C35" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D35" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E35" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="36" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A36" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="B36" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C36" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D36" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E36" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="37" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A37" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="B37" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C37" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D37" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E37" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="38" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A38" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="B38" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C38" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D38" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E38" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="39" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A39" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="B39" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C39" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D39" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E39" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="40" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A40" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="B40" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C40" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D40" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E40" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="41" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A41" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="B41" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C41" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D41" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E41" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="42" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A42" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="B42" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C42" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D42" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E42" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="43" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A43" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="B43" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C43" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D43" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E43" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="44" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A44" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="B44" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C44" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D44" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E44" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="45" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A45" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="B45" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C45" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D45" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E45" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="46" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A46" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="B46" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C46" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D46" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E46" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="47" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A47" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="B47" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C47" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D47" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E47" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="48" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A48" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="B48" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C48" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D48" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E48" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="49" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A49" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="B49" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C49" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D49" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E49" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="50" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A50" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="B50" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C50" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D50" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E50" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="51" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A51" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="B51" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C51" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D51" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E51" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="52" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A52" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="B52" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C52" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D52" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E52" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="53" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A53" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="B53" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C53" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D53" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E53" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="54" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A54" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="B54" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C54" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D54" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E54" s="2" t="s">
+        <v>6</v>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:F1" xr:uid="{00000000-0001-0000-0000-000000000000}"/>

--- a/Data Files/Backoffce/IndexacaoFG/IndexacaoFG_SANTANDER.xlsx
+++ b/Data Files/Backoffce/IndexacaoFG/IndexacaoFG_SANTANDER.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Public\RPA_ALLIANZ_TREINAMENTO\Data Files\Backoffce\IndexacaoFG\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9313B84B-4A60-40A5-95C3-64D7CDE450A7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3F5D0763-1310-4E3B-9E25-1FD211935006}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="270" uniqueCount="62">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="185" uniqueCount="45">
   <si>
     <t xml:space="preserve">status </t>
   </si>
@@ -57,163 +57,112 @@
     <t>Relatório de Recusas  01.09.2025 a 07.09.2025</t>
   </si>
   <si>
-    <t>Relatório de Recusas Santander - 04/09/2025</t>
-  </si>
-  <si>
-    <t>134117963</t>
-  </si>
-  <si>
-    <t>134129842</t>
-  </si>
-  <si>
-    <t>134159242</t>
-  </si>
-  <si>
-    <t>134122740</t>
-  </si>
-  <si>
-    <t>134159592</t>
-  </si>
-  <si>
-    <t>134151508</t>
-  </si>
-  <si>
-    <t>134151675</t>
-  </si>
-  <si>
-    <t>134156726</t>
-  </si>
-  <si>
-    <t>134151502</t>
-  </si>
-  <si>
-    <t>134160229</t>
-  </si>
-  <si>
-    <t>134142314</t>
-  </si>
-  <si>
-    <t>134160191</t>
-  </si>
-  <si>
-    <t>134160582</t>
-  </si>
-  <si>
-    <t>134158678</t>
-  </si>
-  <si>
-    <t>134159195</t>
-  </si>
-  <si>
-    <t>134195795</t>
-  </si>
-  <si>
-    <t>134131938</t>
-  </si>
-  <si>
-    <t>134151203</t>
-  </si>
-  <si>
-    <t>134181258</t>
-  </si>
-  <si>
-    <t>134158894</t>
-  </si>
-  <si>
-    <t>134272282</t>
-  </si>
-  <si>
-    <t>134073511</t>
-  </si>
-  <si>
-    <t>134117765</t>
-  </si>
-  <si>
-    <t>134119034</t>
-  </si>
-  <si>
-    <t>134119881</t>
-  </si>
-  <si>
-    <t>134123847</t>
-  </si>
-  <si>
-    <t>134125124</t>
-  </si>
-  <si>
-    <t>134125486</t>
-  </si>
-  <si>
-    <t>134130794</t>
-  </si>
-  <si>
-    <t>134131237</t>
-  </si>
-  <si>
-    <t>134133609</t>
-  </si>
-  <si>
-    <t>134134215</t>
-  </si>
-  <si>
-    <t>134134268</t>
-  </si>
-  <si>
-    <t>134071048</t>
-  </si>
-  <si>
-    <t>134077361</t>
-  </si>
-  <si>
-    <t>134077137</t>
-  </si>
-  <si>
-    <t>134285315</t>
-  </si>
-  <si>
-    <t>134139465</t>
-  </si>
-  <si>
-    <t>134144563</t>
-  </si>
-  <si>
-    <t>134146490</t>
-  </si>
-  <si>
-    <t>134146948</t>
-  </si>
-  <si>
-    <t>134151477</t>
-  </si>
-  <si>
-    <t>134151955</t>
-  </si>
-  <si>
-    <t>134154522</t>
-  </si>
-  <si>
-    <t>134084614</t>
-  </si>
-  <si>
-    <t>134156516</t>
-  </si>
-  <si>
-    <t>134156704</t>
-  </si>
-  <si>
-    <t>134157147</t>
-  </si>
-  <si>
-    <t>134158807</t>
-  </si>
-  <si>
-    <t>134158935</t>
-  </si>
-  <si>
-    <t>134162394</t>
-  </si>
-  <si>
-    <t>134199244</t>
+    <t>Relatório de Recusas Santander - 05 e 06/09/2025</t>
+  </si>
+  <si>
+    <t>134170741</t>
+  </si>
+  <si>
+    <t>134161553</t>
+  </si>
+  <si>
+    <t>134171037</t>
+  </si>
+  <si>
+    <t>134180317</t>
+  </si>
+  <si>
+    <t>134184079</t>
+  </si>
+  <si>
+    <t>134178123</t>
+  </si>
+  <si>
+    <t>134165952</t>
+  </si>
+  <si>
+    <t>134167202</t>
+  </si>
+  <si>
+    <t>134213558</t>
+  </si>
+  <si>
+    <t>134230438</t>
+  </si>
+  <si>
+    <t>134247248</t>
+  </si>
+  <si>
+    <t>134270150</t>
+  </si>
+  <si>
+    <t>134264217</t>
+  </si>
+  <si>
+    <t>134288985</t>
+  </si>
+  <si>
+    <t>134184515</t>
+  </si>
+  <si>
+    <t>134133617</t>
+  </si>
+  <si>
+    <t>134169949</t>
+  </si>
+  <si>
+    <t>134161572</t>
+  </si>
+  <si>
+    <t>134169958</t>
+  </si>
+  <si>
+    <t>134161577</t>
+  </si>
+  <si>
+    <t>134169561</t>
+  </si>
+  <si>
+    <t>134165135</t>
+  </si>
+  <si>
+    <t>134167349</t>
+  </si>
+  <si>
+    <t>134171657</t>
+  </si>
+  <si>
+    <t>134173263</t>
+  </si>
+  <si>
+    <t>134175866</t>
+  </si>
+  <si>
+    <t>134178173</t>
+  </si>
+  <si>
+    <t>134178347</t>
+  </si>
+  <si>
+    <t>134179577</t>
+  </si>
+  <si>
+    <t>134181932</t>
+  </si>
+  <si>
+    <t>134120789</t>
+  </si>
+  <si>
+    <t>134258691</t>
+  </si>
+  <si>
+    <t>134127370</t>
+  </si>
+  <si>
+    <t>134134592</t>
+  </si>
+  <si>
+    <t>134192707</t>
   </si>
 </sst>
 </file>
@@ -618,7 +567,7 @@
   <sheetPr>
     <pageSetUpPr autoPageBreaks="0"/>
   </sheetPr>
-  <dimension ref="A1:F54"/>
+  <dimension ref="A1:F37"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="2" width="16.7109375" style="1" customWidth="1" collapsed="1"/>
@@ -650,7 +599,7 @@
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A2" s="6">
-        <v>134129134</v>
+        <v>134091381</v>
       </c>
       <c r="B2" s="1" t="s">
         <v>7</v>
@@ -1278,295 +1227,6 @@
         <v>8</v>
       </c>
       <c r="E37" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="38" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A38" s="1" t="s">
-        <v>45</v>
-      </c>
-      <c r="B38" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C38" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D38" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="E38" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="39" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A39" s="1" t="s">
-        <v>46</v>
-      </c>
-      <c r="B39" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C39" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D39" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="E39" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="40" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A40" s="1" t="s">
-        <v>47</v>
-      </c>
-      <c r="B40" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C40" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D40" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="E40" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="41" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A41" s="1" t="s">
-        <v>48</v>
-      </c>
-      <c r="B41" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C41" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D41" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="E41" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="42" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A42" s="1" t="s">
-        <v>49</v>
-      </c>
-      <c r="B42" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C42" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D42" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="E42" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="43" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A43" s="1" t="s">
-        <v>50</v>
-      </c>
-      <c r="B43" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C43" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D43" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="E43" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="44" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A44" s="1" t="s">
-        <v>51</v>
-      </c>
-      <c r="B44" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C44" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D44" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="E44" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="45" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A45" s="1" t="s">
-        <v>52</v>
-      </c>
-      <c r="B45" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C45" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D45" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="E45" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="46" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A46" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="B46" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C46" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D46" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="E46" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="47" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A47" s="1" t="s">
-        <v>54</v>
-      </c>
-      <c r="B47" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C47" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D47" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="E47" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="48" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A48" s="1" t="s">
-        <v>55</v>
-      </c>
-      <c r="B48" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C48" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D48" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="E48" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="49" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A49" s="1" t="s">
-        <v>56</v>
-      </c>
-      <c r="B49" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C49" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D49" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="E49" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="50" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A50" s="1" t="s">
-        <v>57</v>
-      </c>
-      <c r="B50" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C50" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D50" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="E50" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="51" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A51" s="1" t="s">
-        <v>58</v>
-      </c>
-      <c r="B51" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C51" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D51" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="E51" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="52" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A52" s="1" t="s">
-        <v>59</v>
-      </c>
-      <c r="B52" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C52" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D52" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="E52" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="53" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A53" s="1" t="s">
-        <v>60</v>
-      </c>
-      <c r="B53" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C53" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D53" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="E53" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="54" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A54" s="1" t="s">
-        <v>61</v>
-      </c>
-      <c r="B54" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C54" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D54" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="E54" s="2" t="s">
         <v>6</v>
       </c>
     </row>

--- a/Data Files/Backoffce/IndexacaoFG/IndexacaoFG_SANTANDER.xlsx
+++ b/Data Files/Backoffce/IndexacaoFG/IndexacaoFG_SANTANDER.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Public\RPA_ALLIANZ_TREINAMENTO\Data Files\Backoffce\IndexacaoFG\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3F5D0763-1310-4E3B-9E25-1FD211935006}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{90D14C84-774E-4685-A226-D083B3F6826D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>

--- a/Data Files/Backoffce/IndexacaoFG/IndexacaoFG_SANTANDER.xlsx
+++ b/Data Files/Backoffce/IndexacaoFG/IndexacaoFG_SANTANDER.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Public\RPA_ALLIANZ_TREINAMENTO\Data Files\Backoffce\IndexacaoFG\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{90D14C84-774E-4685-A226-D083B3F6826D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0F058226-9E2D-4458-8787-847C2CA44E1C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="20370" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="IndexacaoFG" sheetId="2" r:id="rId1"/>

--- a/Data Files/Backoffce/IndexacaoFG/IndexacaoFG_SANTANDER.xlsx
+++ b/Data Files/Backoffce/IndexacaoFG/IndexacaoFG_SANTANDER.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Public\RPA_ALLIANZ_TREINAMENTO\Data Files\Backoffce\IndexacaoFG\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0F058226-9E2D-4458-8787-847C2CA44E1C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{21803A4F-7F9C-4E5E-B488-F7F34EDE6C1C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="20370" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="185" uniqueCount="45">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="175" uniqueCount="43">
   <si>
     <t xml:space="preserve">status </t>
   </si>
@@ -54,115 +54,109 @@
     <t>1070</t>
   </si>
   <si>
-    <t>Relatório de Recusas  01.09.2025 a 07.09.2025</t>
-  </si>
-  <si>
-    <t>Relatório de Recusas Santander - 05 e 06/09/2025</t>
-  </si>
-  <si>
-    <t>134170741</t>
-  </si>
-  <si>
-    <t>134161553</t>
-  </si>
-  <si>
-    <t>134171037</t>
-  </si>
-  <si>
-    <t>134180317</t>
-  </si>
-  <si>
-    <t>134184079</t>
-  </si>
-  <si>
-    <t>134178123</t>
-  </si>
-  <si>
-    <t>134165952</t>
-  </si>
-  <si>
-    <t>134167202</t>
-  </si>
-  <si>
-    <t>134213558</t>
-  </si>
-  <si>
-    <t>134230438</t>
-  </si>
-  <si>
-    <t>134247248</t>
-  </si>
-  <si>
-    <t>134270150</t>
-  </si>
-  <si>
-    <t>134264217</t>
-  </si>
-  <si>
-    <t>134288985</t>
-  </si>
-  <si>
-    <t>134184515</t>
-  </si>
-  <si>
-    <t>134133617</t>
-  </si>
-  <si>
-    <t>134169949</t>
-  </si>
-  <si>
-    <t>134161572</t>
-  </si>
-  <si>
-    <t>134169958</t>
-  </si>
-  <si>
-    <t>134161577</t>
-  </si>
-  <si>
-    <t>134169561</t>
-  </si>
-  <si>
-    <t>134165135</t>
-  </si>
-  <si>
-    <t>134167349</t>
-  </si>
-  <si>
-    <t>134171657</t>
-  </si>
-  <si>
-    <t>134173263</t>
-  </si>
-  <si>
-    <t>134175866</t>
-  </si>
-  <si>
-    <t>134178173</t>
-  </si>
-  <si>
-    <t>134178347</t>
-  </si>
-  <si>
-    <t>134179577</t>
-  </si>
-  <si>
-    <t>134181932</t>
-  </si>
-  <si>
-    <t>134120789</t>
-  </si>
-  <si>
-    <t>134258691</t>
-  </si>
-  <si>
-    <t>134127370</t>
-  </si>
-  <si>
-    <t>134134592</t>
-  </si>
-  <si>
-    <t>134192707</t>
+    <t>Relatório de Recusas  08.09.2025 a 14.09.2025</t>
+  </si>
+  <si>
+    <t>Relatório de Recusas Santander - 08/09/2025</t>
+  </si>
+  <si>
+    <t>134191040</t>
+  </si>
+  <si>
+    <t>134189799</t>
+  </si>
+  <si>
+    <t>134190893</t>
+  </si>
+  <si>
+    <t>134222045</t>
+  </si>
+  <si>
+    <t>134248576</t>
+  </si>
+  <si>
+    <t>134242792</t>
+  </si>
+  <si>
+    <t>134283389</t>
+  </si>
+  <si>
+    <t>134313099</t>
+  </si>
+  <si>
+    <t>134303403</t>
+  </si>
+  <si>
+    <t>134197036</t>
+  </si>
+  <si>
+    <t>134196299</t>
+  </si>
+  <si>
+    <t>134192439</t>
+  </si>
+  <si>
+    <t>134172329</t>
+  </si>
+  <si>
+    <t>134200564</t>
+  </si>
+  <si>
+    <t>134185921</t>
+  </si>
+  <si>
+    <t>134186694</t>
+  </si>
+  <si>
+    <t>134188321</t>
+  </si>
+  <si>
+    <t>134190841</t>
+  </si>
+  <si>
+    <t>134191494</t>
+  </si>
+  <si>
+    <t>134191741</t>
+  </si>
+  <si>
+    <t>134192757</t>
+  </si>
+  <si>
+    <t>134195357</t>
+  </si>
+  <si>
+    <t>134197529</t>
+  </si>
+  <si>
+    <t>134197979</t>
+  </si>
+  <si>
+    <t>134199689</t>
+  </si>
+  <si>
+    <t>134199896</t>
+  </si>
+  <si>
+    <t>134200360</t>
+  </si>
+  <si>
+    <t>134201161</t>
+  </si>
+  <si>
+    <t>134201314</t>
+  </si>
+  <si>
+    <t>134201496</t>
+  </si>
+  <si>
+    <t>134204824</t>
+  </si>
+  <si>
+    <t>134208669</t>
+  </si>
+  <si>
+    <t>134209125</t>
   </si>
 </sst>
 </file>
@@ -567,7 +561,7 @@
   <sheetPr>
     <pageSetUpPr autoPageBreaks="0"/>
   </sheetPr>
-  <dimension ref="A1:F37"/>
+  <dimension ref="A1:F35"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="2" width="16.7109375" style="1" customWidth="1" collapsed="1"/>
@@ -599,7 +593,7 @@
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A2" s="6">
-        <v>134091381</v>
+        <v>134188990</v>
       </c>
       <c r="B2" s="1" t="s">
         <v>7</v>
@@ -1193,40 +1187,6 @@
         <v>8</v>
       </c>
       <c r="E35" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="36" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A36" s="1" t="s">
-        <v>43</v>
-      </c>
-      <c r="B36" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C36" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D36" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="E36" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="37" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A37" s="1" t="s">
-        <v>44</v>
-      </c>
-      <c r="B37" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C37" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D37" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="E37" s="2" t="s">
         <v>6</v>
       </c>
     </row>

--- a/Data Files/Backoffce/IndexacaoFG/IndexacaoFG_SANTANDER.xlsx
+++ b/Data Files/Backoffce/IndexacaoFG/IndexacaoFG_SANTANDER.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Public\RPA_ALLIANZ_TREINAMENTO\Data Files\Backoffce\IndexacaoFG\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{21803A4F-7F9C-4E5E-B488-F7F34EDE6C1C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A598D68F-A6D8-4043-AA68-C044D8CF9970}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="20370" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="175" uniqueCount="43">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="90" uniqueCount="26">
   <si>
     <t xml:space="preserve">status </t>
   </si>
@@ -57,106 +57,55 @@
     <t>Relatório de Recusas  08.09.2025 a 14.09.2025</t>
   </si>
   <si>
-    <t>Relatório de Recusas Santander - 08/09/2025</t>
-  </si>
-  <si>
-    <t>134191040</t>
-  </si>
-  <si>
-    <t>134189799</t>
-  </si>
-  <si>
-    <t>134190893</t>
-  </si>
-  <si>
-    <t>134222045</t>
-  </si>
-  <si>
-    <t>134248576</t>
-  </si>
-  <si>
-    <t>134242792</t>
-  </si>
-  <si>
-    <t>134283389</t>
-  </si>
-  <si>
-    <t>134313099</t>
-  </si>
-  <si>
-    <t>134303403</t>
-  </si>
-  <si>
-    <t>134197036</t>
-  </si>
-  <si>
-    <t>134196299</t>
-  </si>
-  <si>
-    <t>134192439</t>
-  </si>
-  <si>
-    <t>134172329</t>
-  </si>
-  <si>
-    <t>134200564</t>
-  </si>
-  <si>
-    <t>134185921</t>
-  </si>
-  <si>
-    <t>134186694</t>
-  </si>
-  <si>
-    <t>134188321</t>
-  </si>
-  <si>
-    <t>134190841</t>
-  </si>
-  <si>
-    <t>134191494</t>
-  </si>
-  <si>
-    <t>134191741</t>
-  </si>
-  <si>
-    <t>134192757</t>
-  </si>
-  <si>
-    <t>134195357</t>
-  </si>
-  <si>
-    <t>134197529</t>
-  </si>
-  <si>
-    <t>134197979</t>
-  </si>
-  <si>
-    <t>134199689</t>
-  </si>
-  <si>
-    <t>134199896</t>
-  </si>
-  <si>
-    <t>134200360</t>
-  </si>
-  <si>
-    <t>134201161</t>
-  </si>
-  <si>
-    <t>134201314</t>
-  </si>
-  <si>
-    <t>134201496</t>
-  </si>
-  <si>
-    <t>134204824</t>
-  </si>
-  <si>
-    <t>134208669</t>
-  </si>
-  <si>
-    <t>134209125</t>
+    <t>Relatório de Recusas Santander - 09/09/2025</t>
+  </si>
+  <si>
+    <t>134216628</t>
+  </si>
+  <si>
+    <t>134230678</t>
+  </si>
+  <si>
+    <t>134267077</t>
+  </si>
+  <si>
+    <t>134150028</t>
+  </si>
+  <si>
+    <t>134142970</t>
+  </si>
+  <si>
+    <t>134218656</t>
+  </si>
+  <si>
+    <t>134217366</t>
+  </si>
+  <si>
+    <t>134221682</t>
+  </si>
+  <si>
+    <t>134259586</t>
+  </si>
+  <si>
+    <t>134220631</t>
+  </si>
+  <si>
+    <t>134217300</t>
+  </si>
+  <si>
+    <t>134221526</t>
+  </si>
+  <si>
+    <t>134275478</t>
+  </si>
+  <si>
+    <t>134224096</t>
+  </si>
+  <si>
+    <t>134227978</t>
+  </si>
+  <si>
+    <t>134231864</t>
   </si>
 </sst>
 </file>
@@ -561,7 +510,7 @@
   <sheetPr>
     <pageSetUpPr autoPageBreaks="0"/>
   </sheetPr>
-  <dimension ref="A1:F35"/>
+  <dimension ref="A1:F22"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="2" width="16.7109375" style="1" customWidth="1" collapsed="1"/>
@@ -593,7 +542,7 @@
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A2" s="6">
-        <v>134188990</v>
+        <v>134216123</v>
       </c>
       <c r="B2" s="1" t="s">
         <v>7</v>
@@ -898,297 +847,16 @@
       <c r="F18"/>
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A19" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="B19" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C19" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D19" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="E19" s="2" t="s">
-        <v>6</v>
-      </c>
       <c r="F19"/>
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A20" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="B20" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C20" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D20" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="E20" s="2" t="s">
-        <v>6</v>
-      </c>
       <c r="F20"/>
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A21" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="B21" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C21" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D21" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="E21" s="2" t="s">
-        <v>6</v>
-      </c>
       <c r="F21"/>
     </row>
     <row r="22" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A22" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="B22" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C22" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D22" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="E22" s="2" t="s">
-        <v>6</v>
-      </c>
       <c r="F22"/>
-    </row>
-    <row r="23" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A23" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="B23" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C23" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D23" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="E23" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="24" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A24" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="B24" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C24" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D24" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="E24" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="25" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A25" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="B25" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C25" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D25" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="E25" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="26" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A26" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="B26" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C26" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D26" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="E26" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="27" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A27" s="1" t="s">
-        <v>34</v>
-      </c>
-      <c r="B27" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C27" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D27" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="E27" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="28" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A28" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="B28" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C28" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D28" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="E28" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="29" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A29" s="1" t="s">
-        <v>36</v>
-      </c>
-      <c r="B29" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C29" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D29" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="E29" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="30" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A30" s="1" t="s">
-        <v>37</v>
-      </c>
-      <c r="B30" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C30" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D30" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="E30" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="31" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A31" s="1" t="s">
-        <v>38</v>
-      </c>
-      <c r="B31" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C31" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D31" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="E31" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="32" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A32" s="1" t="s">
-        <v>39</v>
-      </c>
-      <c r="B32" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C32" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D32" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="E32" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="33" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A33" s="1" t="s">
-        <v>40</v>
-      </c>
-      <c r="B33" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C33" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D33" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="E33" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="34" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A34" s="1" t="s">
-        <v>41</v>
-      </c>
-      <c r="B34" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C34" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D34" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="E34" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="35" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A35" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="B35" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C35" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D35" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="E35" s="2" t="s">
-        <v>6</v>
-      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:F1" xr:uid="{00000000-0001-0000-0000-000000000000}"/>

--- a/Data Files/Backoffce/IndexacaoFG/IndexacaoFG_SANTANDER.xlsx
+++ b/Data Files/Backoffce/IndexacaoFG/IndexacaoFG_SANTANDER.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Public\RPA_ALLIANZ_TREINAMENTO\Data Files\Backoffce\IndexacaoFG\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A598D68F-A6D8-4043-AA68-C044D8CF9970}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8D80AF99-0CD9-4B6B-8B42-3A3F5B97CD44}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="20370" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="90" uniqueCount="26">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="65" uniqueCount="21">
   <si>
     <t xml:space="preserve">status </t>
   </si>
@@ -57,55 +57,40 @@
     <t>Relatório de Recusas  08.09.2025 a 14.09.2025</t>
   </si>
   <si>
-    <t>Relatório de Recusas Santander - 09/09/2025</t>
-  </si>
-  <si>
-    <t>134216628</t>
-  </si>
-  <si>
-    <t>134230678</t>
-  </si>
-  <si>
-    <t>134267077</t>
-  </si>
-  <si>
-    <t>134150028</t>
-  </si>
-  <si>
-    <t>134142970</t>
-  </si>
-  <si>
-    <t>134218656</t>
-  </si>
-  <si>
-    <t>134217366</t>
-  </si>
-  <si>
-    <t>134221682</t>
-  </si>
-  <si>
-    <t>134259586</t>
-  </si>
-  <si>
-    <t>134220631</t>
-  </si>
-  <si>
-    <t>134217300</t>
-  </si>
-  <si>
-    <t>134221526</t>
-  </si>
-  <si>
-    <t>134275478</t>
-  </si>
-  <si>
-    <t>134224096</t>
-  </si>
-  <si>
-    <t>134227978</t>
-  </si>
-  <si>
-    <t>134231864</t>
+    <t>Relatório Recusas Santander- 10.09.2025</t>
+  </si>
+  <si>
+    <t>134304975</t>
+  </si>
+  <si>
+    <t>134345251</t>
+  </si>
+  <si>
+    <t>134354096</t>
+  </si>
+  <si>
+    <t>134170423</t>
+  </si>
+  <si>
+    <t>134174713</t>
+  </si>
+  <si>
+    <t>134175439</t>
+  </si>
+  <si>
+    <t>134374124</t>
+  </si>
+  <si>
+    <t>134230537</t>
+  </si>
+  <si>
+    <t>134188240</t>
+  </si>
+  <si>
+    <t>134383118</t>
+  </si>
+  <si>
+    <t>134272786</t>
   </si>
 </sst>
 </file>
@@ -542,7 +527,7 @@
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A2" s="6">
-        <v>134216123</v>
+        <v>134313690</v>
       </c>
       <c r="B2" s="1" t="s">
         <v>7</v>
@@ -757,105 +742,30 @@
       <c r="F13"/>
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A14" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="B14" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C14" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D14" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="E14" s="2" t="s">
-        <v>6</v>
-      </c>
       <c r="F14"/>
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A15" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="B15" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C15" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D15" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="E15" s="2" t="s">
-        <v>6</v>
-      </c>
       <c r="F15"/>
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A16" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="B16" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C16" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D16" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="E16" s="2" t="s">
-        <v>6</v>
-      </c>
       <c r="F16"/>
     </row>
-    <row r="17" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A17" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="B17" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C17" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D17" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="E17" s="2" t="s">
-        <v>6</v>
-      </c>
+    <row r="17" spans="6:6" x14ac:dyDescent="0.25">
       <c r="F17"/>
     </row>
-    <row r="18" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A18" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="B18" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C18" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D18" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="E18" s="2" t="s">
-        <v>6</v>
-      </c>
+    <row r="18" spans="6:6" x14ac:dyDescent="0.25">
       <c r="F18"/>
     </row>
-    <row r="19" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="19" spans="6:6" x14ac:dyDescent="0.25">
       <c r="F19"/>
     </row>
-    <row r="20" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="20" spans="6:6" x14ac:dyDescent="0.25">
       <c r="F20"/>
     </row>
-    <row r="21" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="21" spans="6:6" x14ac:dyDescent="0.25">
       <c r="F21"/>
     </row>
-    <row r="22" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="22" spans="6:6" x14ac:dyDescent="0.25">
       <c r="F22"/>
     </row>
   </sheetData>

--- a/Data Files/Backoffce/IndexacaoFG/IndexacaoFG_SANTANDER.xlsx
+++ b/Data Files/Backoffce/IndexacaoFG/IndexacaoFG_SANTANDER.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Public\RPA_ALLIANZ_TREINAMENTO\Data Files\Backoffce\IndexacaoFG\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8D80AF99-0CD9-4B6B-8B42-3A3F5B97CD44}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5DFFC1ED-FEE9-4C70-9B5F-D394E7589A40}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="20370" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="65" uniqueCount="21">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="160" uniqueCount="40">
   <si>
     <t xml:space="preserve">status </t>
   </si>
@@ -54,43 +54,100 @@
     <t>1070</t>
   </si>
   <si>
+    <t>Relatório de Recusas Santander - 11/09/2025</t>
+  </si>
+  <si>
+    <t>134196293</t>
+  </si>
+  <si>
+    <t>134207349</t>
+  </si>
+  <si>
+    <t>134272705</t>
+  </si>
+  <si>
+    <t>134272529</t>
+  </si>
+  <si>
+    <t>134286685</t>
+  </si>
+  <si>
+    <t>134276082</t>
+  </si>
+  <si>
+    <t>134355910</t>
+  </si>
+  <si>
+    <t>134288666</t>
+  </si>
+  <si>
+    <t>134185969</t>
+  </si>
+  <si>
+    <t>134191506</t>
+  </si>
+  <si>
+    <t>134193208</t>
+  </si>
+  <si>
+    <t>134196102</t>
+  </si>
+  <si>
+    <t>134196146</t>
+  </si>
+  <si>
+    <t>134196348</t>
+  </si>
+  <si>
+    <t>134196592</t>
+  </si>
+  <si>
+    <t>134198312</t>
+  </si>
+  <si>
+    <t>134201215</t>
+  </si>
+  <si>
+    <t>134207354</t>
+  </si>
+  <si>
+    <t>134196164</t>
+  </si>
+  <si>
+    <t>134194278</t>
+  </si>
+  <si>
+    <t>134202624</t>
+  </si>
+  <si>
+    <t>134269504</t>
+  </si>
+  <si>
+    <t>134267441</t>
+  </si>
+  <si>
+    <t>134309150</t>
+  </si>
+  <si>
+    <t>134181065</t>
+  </si>
+  <si>
+    <t>134260322</t>
+  </si>
+  <si>
+    <t>134262306</t>
+  </si>
+  <si>
+    <t>134263367</t>
+  </si>
+  <si>
+    <t>134267833</t>
+  </si>
+  <si>
+    <t>134274558</t>
+  </si>
+  <si>
     <t>Relatório de Recusas  08.09.2025 a 14.09.2025</t>
-  </si>
-  <si>
-    <t>Relatório Recusas Santander- 10.09.2025</t>
-  </si>
-  <si>
-    <t>134304975</t>
-  </si>
-  <si>
-    <t>134345251</t>
-  </si>
-  <si>
-    <t>134354096</t>
-  </si>
-  <si>
-    <t>134170423</t>
-  </si>
-  <si>
-    <t>134174713</t>
-  </si>
-  <si>
-    <t>134175439</t>
-  </si>
-  <si>
-    <t>134374124</t>
-  </si>
-  <si>
-    <t>134230537</t>
-  </si>
-  <si>
-    <t>134188240</t>
-  </si>
-  <si>
-    <t>134383118</t>
-  </si>
-  <si>
-    <t>134272786</t>
   </si>
 </sst>
 </file>
@@ -495,7 +552,7 @@
   <sheetPr>
     <pageSetUpPr autoPageBreaks="0"/>
   </sheetPr>
-  <dimension ref="A1:F22"/>
+  <dimension ref="A1:F32"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="2" width="16.7109375" style="1" customWidth="1" collapsed="1"/>
@@ -527,16 +584,16 @@
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A2" s="6">
-        <v>134313690</v>
+        <v>134202395</v>
       </c>
       <c r="B2" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>8</v>
+        <v>39</v>
       </c>
       <c r="E2" s="2" t="s">
         <v>6</v>
@@ -545,16 +602,16 @@
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B3" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>8</v>
+        <v>39</v>
       </c>
       <c r="E3" s="2" t="s">
         <v>6</v>
@@ -563,16 +620,16 @@
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B4" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>8</v>
+        <v>39</v>
       </c>
       <c r="E4" s="2" t="s">
         <v>6</v>
@@ -581,16 +638,16 @@
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B5" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>8</v>
+        <v>39</v>
       </c>
       <c r="E5" s="2" t="s">
         <v>6</v>
@@ -599,16 +656,16 @@
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" s="1" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B6" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>8</v>
+        <v>39</v>
       </c>
       <c r="E6" s="2" t="s">
         <v>6</v>
@@ -617,16 +674,16 @@
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" s="1" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B7" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>8</v>
+        <v>39</v>
       </c>
       <c r="E7" s="2" t="s">
         <v>6</v>
@@ -635,16 +692,16 @@
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" s="1" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B8" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>8</v>
+        <v>39</v>
       </c>
       <c r="E8" s="2" t="s">
         <v>6</v>
@@ -653,16 +710,16 @@
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" s="1" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B9" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>8</v>
+        <v>39</v>
       </c>
       <c r="E9" s="2" t="s">
         <v>6</v>
@@ -671,16 +728,16 @@
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A10" s="1" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B10" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>8</v>
+        <v>39</v>
       </c>
       <c r="E10" s="2" t="s">
         <v>6</v>
@@ -689,16 +746,16 @@
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A11" s="1" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B11" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>8</v>
+        <v>39</v>
       </c>
       <c r="E11" s="2" t="s">
         <v>6</v>
@@ -707,16 +764,16 @@
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A12" s="1" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B12" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>8</v>
+        <v>39</v>
       </c>
       <c r="E12" s="2" t="s">
         <v>6</v>
@@ -725,48 +782,353 @@
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A13" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="B13" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C13" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D13" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="E13" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="F13"/>
+    </row>
+    <row r="14" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A14" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="B13" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C13" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D13" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="E13" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="F13"/>
-    </row>
-    <row r="14" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="B14" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C14" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D14" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="E14" s="2" t="s">
+        <v>6</v>
+      </c>
       <c r="F14"/>
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A15" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="B15" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C15" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D15" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="E15" s="2" t="s">
+        <v>6</v>
+      </c>
       <c r="F15"/>
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A16" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="B16" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C16" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D16" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="E16" s="2" t="s">
+        <v>6</v>
+      </c>
       <c r="F16"/>
     </row>
-    <row r="17" spans="6:6" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A17" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="B17" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C17" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D17" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="E17" s="2" t="s">
+        <v>6</v>
+      </c>
       <c r="F17"/>
     </row>
-    <row r="18" spans="6:6" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A18" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="B18" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C18" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D18" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="E18" s="2" t="s">
+        <v>6</v>
+      </c>
       <c r="F18"/>
     </row>
-    <row r="19" spans="6:6" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A19" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="B19" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C19" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D19" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="E19" s="2" t="s">
+        <v>6</v>
+      </c>
       <c r="F19"/>
     </row>
-    <row r="20" spans="6:6" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A20" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="B20" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C20" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D20" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="E20" s="2" t="s">
+        <v>6</v>
+      </c>
       <c r="F20"/>
     </row>
-    <row r="21" spans="6:6" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A21" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="B21" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C21" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D21" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="E21" s="2" t="s">
+        <v>6</v>
+      </c>
       <c r="F21"/>
     </row>
-    <row r="22" spans="6:6" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A22" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="B22" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C22" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D22" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="E22" s="2" t="s">
+        <v>6</v>
+      </c>
       <c r="F22"/>
+    </row>
+    <row r="23" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A23" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="B23" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C23" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D23" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="E23" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="24" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A24" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="B24" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C24" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D24" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="E24" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="25" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A25" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="B25" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C25" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D25" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="E25" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="26" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A26" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="B26" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C26" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D26" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="E26" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="27" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A27" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="B27" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C27" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D27" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="E27" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="28" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A28" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="B28" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C28" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D28" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="E28" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="29" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A29" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="B29" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C29" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D29" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="E29" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="30" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A30" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="B30" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C30" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D30" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="E30" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="31" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A31" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="B31" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C31" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D31" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="E31" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="32" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A32" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="B32" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C32" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D32" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="E32" s="2" t="s">
+        <v>6</v>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:F1" xr:uid="{00000000-0001-0000-0000-000000000000}"/>

--- a/Data Files/Backoffce/IndexacaoFG/IndexacaoFG_SANTANDER.xlsx
+++ b/Data Files/Backoffce/IndexacaoFG/IndexacaoFG_SANTANDER.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Public\RPA_ALLIANZ_TREINAMENTO\Data Files\Backoffce\IndexacaoFG\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5DFFC1ED-FEE9-4C70-9B5F-D394E7589A40}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3AC0803F-B7FF-49F5-B730-270A96A10EBC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="20370" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="160" uniqueCount="40">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="175" uniqueCount="43">
   <si>
     <t xml:space="preserve">status </t>
   </si>
@@ -54,100 +54,109 @@
     <t>1070</t>
   </si>
   <si>
-    <t>Relatório de Recusas Santander - 11/09/2025</t>
-  </si>
-  <si>
-    <t>134196293</t>
-  </si>
-  <si>
-    <t>134207349</t>
-  </si>
-  <si>
-    <t>134272705</t>
-  </si>
-  <si>
-    <t>134272529</t>
-  </si>
-  <si>
-    <t>134286685</t>
-  </si>
-  <si>
-    <t>134276082</t>
-  </si>
-  <si>
-    <t>134355910</t>
-  </si>
-  <si>
-    <t>134288666</t>
-  </si>
-  <si>
-    <t>134185969</t>
-  </si>
-  <si>
-    <t>134191506</t>
-  </si>
-  <si>
-    <t>134193208</t>
-  </si>
-  <si>
-    <t>134196102</t>
-  </si>
-  <si>
-    <t>134196146</t>
-  </si>
-  <si>
-    <t>134196348</t>
-  </si>
-  <si>
-    <t>134196592</t>
-  </si>
-  <si>
-    <t>134198312</t>
-  </si>
-  <si>
-    <t>134201215</t>
-  </si>
-  <si>
-    <t>134207354</t>
-  </si>
-  <si>
-    <t>134196164</t>
-  </si>
-  <si>
-    <t>134194278</t>
-  </si>
-  <si>
-    <t>134202624</t>
-  </si>
-  <si>
-    <t>134269504</t>
-  </si>
-  <si>
-    <t>134267441</t>
-  </si>
-  <si>
-    <t>134309150</t>
-  </si>
-  <si>
-    <t>134181065</t>
-  </si>
-  <si>
-    <t>134260322</t>
-  </si>
-  <si>
-    <t>134262306</t>
-  </si>
-  <si>
-    <t>134263367</t>
-  </si>
-  <si>
-    <t>134267833</t>
-  </si>
-  <si>
-    <t>134274558</t>
-  </si>
-  <si>
     <t>Relatório de Recusas  08.09.2025 a 14.09.2025</t>
+  </si>
+  <si>
+    <t>Relatório de Recusas Santander - 12 e 13/09/2025</t>
+  </si>
+  <si>
+    <t>134239779</t>
+  </si>
+  <si>
+    <t>134266788</t>
+  </si>
+  <si>
+    <t>134288429</t>
+  </si>
+  <si>
+    <t>134310686</t>
+  </si>
+  <si>
+    <t>134340978</t>
+  </si>
+  <si>
+    <t>134369214</t>
+  </si>
+  <si>
+    <t>134289918</t>
+  </si>
+  <si>
+    <t>134388724</t>
+  </si>
+  <si>
+    <t>134376954</t>
+  </si>
+  <si>
+    <t>134205403</t>
+  </si>
+  <si>
+    <t>134219039</t>
+  </si>
+  <si>
+    <t>134289481</t>
+  </si>
+  <si>
+    <t>134298444</t>
+  </si>
+  <si>
+    <t>134296242</t>
+  </si>
+  <si>
+    <t>134289627</t>
+  </si>
+  <si>
+    <t>134305449</t>
+  </si>
+  <si>
+    <t>134310587</t>
+  </si>
+  <si>
+    <t>134286913</t>
+  </si>
+  <si>
+    <t>134287772</t>
+  </si>
+  <si>
+    <t>134292594</t>
+  </si>
+  <si>
+    <t>134293418</t>
+  </si>
+  <si>
+    <t>134293663</t>
+  </si>
+  <si>
+    <t>134296888</t>
+  </si>
+  <si>
+    <t>134356575</t>
+  </si>
+  <si>
+    <t>134310021</t>
+  </si>
+  <si>
+    <t>134430847</t>
+  </si>
+  <si>
+    <t>134194304</t>
+  </si>
+  <si>
+    <t>134245553</t>
+  </si>
+  <si>
+    <t>134235821</t>
+  </si>
+  <si>
+    <t>134240693</t>
+  </si>
+  <si>
+    <t>134251883</t>
+  </si>
+  <si>
+    <t>134305707</t>
+  </si>
+  <si>
+    <t>134419878</t>
   </si>
 </sst>
 </file>
@@ -552,7 +561,7 @@
   <sheetPr>
     <pageSetUpPr autoPageBreaks="0"/>
   </sheetPr>
-  <dimension ref="A1:F32"/>
+  <dimension ref="A1:F35"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="2" width="16.7109375" style="1" customWidth="1" collapsed="1"/>
@@ -584,16 +593,16 @@
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A2" s="6">
-        <v>134202395</v>
+        <v>134207460</v>
       </c>
       <c r="B2" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>39</v>
+        <v>8</v>
       </c>
       <c r="E2" s="2" t="s">
         <v>6</v>
@@ -602,16 +611,16 @@
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B3" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>39</v>
+        <v>8</v>
       </c>
       <c r="E3" s="2" t="s">
         <v>6</v>
@@ -620,16 +629,16 @@
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B4" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>39</v>
+        <v>8</v>
       </c>
       <c r="E4" s="2" t="s">
         <v>6</v>
@@ -638,16 +647,16 @@
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B5" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>39</v>
+        <v>8</v>
       </c>
       <c r="E5" s="2" t="s">
         <v>6</v>
@@ -656,16 +665,16 @@
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" s="1" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B6" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>39</v>
+        <v>8</v>
       </c>
       <c r="E6" s="2" t="s">
         <v>6</v>
@@ -674,16 +683,16 @@
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" s="1" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B7" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>39</v>
+        <v>8</v>
       </c>
       <c r="E7" s="2" t="s">
         <v>6</v>
@@ -692,16 +701,16 @@
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" s="1" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="B8" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>39</v>
+        <v>8</v>
       </c>
       <c r="E8" s="2" t="s">
         <v>6</v>
@@ -710,16 +719,16 @@
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B9" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>39</v>
+        <v>8</v>
       </c>
       <c r="E9" s="2" t="s">
         <v>6</v>
@@ -728,16 +737,16 @@
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A10" s="1" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="B10" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>39</v>
+        <v>8</v>
       </c>
       <c r="E10" s="2" t="s">
         <v>6</v>
@@ -746,16 +755,16 @@
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A11" s="1" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="B11" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>39</v>
+        <v>8</v>
       </c>
       <c r="E11" s="2" t="s">
         <v>6</v>
@@ -764,16 +773,16 @@
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A12" s="1" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B12" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>39</v>
+        <v>8</v>
       </c>
       <c r="E12" s="2" t="s">
         <v>6</v>
@@ -782,16 +791,16 @@
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A13" s="1" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B13" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>39</v>
+        <v>8</v>
       </c>
       <c r="E13" s="2" t="s">
         <v>6</v>
@@ -800,16 +809,16 @@
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A14" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B14" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>39</v>
+        <v>8</v>
       </c>
       <c r="E14" s="2" t="s">
         <v>6</v>
@@ -818,16 +827,16 @@
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A15" s="1" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="B15" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>39</v>
+        <v>8</v>
       </c>
       <c r="E15" s="2" t="s">
         <v>6</v>
@@ -836,16 +845,16 @@
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A16" s="1" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B16" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>39</v>
+        <v>8</v>
       </c>
       <c r="E16" s="2" t="s">
         <v>6</v>
@@ -854,16 +863,16 @@
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A17" s="1" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="B17" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>39</v>
+        <v>8</v>
       </c>
       <c r="E17" s="2" t="s">
         <v>6</v>
@@ -872,16 +881,16 @@
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A18" s="1" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="B18" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>39</v>
+        <v>8</v>
       </c>
       <c r="E18" s="2" t="s">
         <v>6</v>
@@ -890,16 +899,16 @@
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A19" s="1" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="B19" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>39</v>
+        <v>8</v>
       </c>
       <c r="E19" s="2" t="s">
         <v>6</v>
@@ -908,16 +917,16 @@
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A20" s="1" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="B20" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>39</v>
+        <v>8</v>
       </c>
       <c r="E20" s="2" t="s">
         <v>6</v>
@@ -926,16 +935,16 @@
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A21" s="1" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="B21" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>39</v>
+        <v>8</v>
       </c>
       <c r="E21" s="2" t="s">
         <v>6</v>
@@ -944,16 +953,16 @@
     </row>
     <row r="22" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A22" s="1" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="B22" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>39</v>
+        <v>8</v>
       </c>
       <c r="E22" s="2" t="s">
         <v>6</v>
@@ -962,16 +971,16 @@
     </row>
     <row r="23" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A23" s="1" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B23" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>39</v>
+        <v>8</v>
       </c>
       <c r="E23" s="2" t="s">
         <v>6</v>
@@ -979,16 +988,16 @@
     </row>
     <row r="24" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A24" s="1" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B24" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C24" s="2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>39</v>
+        <v>8</v>
       </c>
       <c r="E24" s="2" t="s">
         <v>6</v>
@@ -996,16 +1005,16 @@
     </row>
     <row r="25" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A25" s="1" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="B25" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C25" s="2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D25" s="2" t="s">
-        <v>39</v>
+        <v>8</v>
       </c>
       <c r="E25" s="2" t="s">
         <v>6</v>
@@ -1013,16 +1022,16 @@
     </row>
     <row r="26" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A26" s="1" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="B26" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C26" s="2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D26" s="2" t="s">
-        <v>39</v>
+        <v>8</v>
       </c>
       <c r="E26" s="2" t="s">
         <v>6</v>
@@ -1030,16 +1039,16 @@
     </row>
     <row r="27" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A27" s="1" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B27" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C27" s="2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D27" s="2" t="s">
-        <v>39</v>
+        <v>8</v>
       </c>
       <c r="E27" s="2" t="s">
         <v>6</v>
@@ -1047,16 +1056,16 @@
     </row>
     <row r="28" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A28" s="1" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="B28" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C28" s="2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D28" s="2" t="s">
-        <v>39</v>
+        <v>8</v>
       </c>
       <c r="E28" s="2" t="s">
         <v>6</v>
@@ -1064,16 +1073,16 @@
     </row>
     <row r="29" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A29" s="1" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="B29" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C29" s="2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D29" s="2" t="s">
-        <v>39</v>
+        <v>8</v>
       </c>
       <c r="E29" s="2" t="s">
         <v>6</v>
@@ -1081,16 +1090,16 @@
     </row>
     <row r="30" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A30" s="1" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="B30" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C30" s="2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D30" s="2" t="s">
-        <v>39</v>
+        <v>8</v>
       </c>
       <c r="E30" s="2" t="s">
         <v>6</v>
@@ -1098,16 +1107,16 @@
     </row>
     <row r="31" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A31" s="1" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B31" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C31" s="2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D31" s="2" t="s">
-        <v>39</v>
+        <v>8</v>
       </c>
       <c r="E31" s="2" t="s">
         <v>6</v>
@@ -1115,18 +1124,69 @@
     </row>
     <row r="32" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A32" s="1" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B32" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C32" s="2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D32" s="2" t="s">
-        <v>39</v>
+        <v>8</v>
       </c>
       <c r="E32" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="33" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A33" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="B33" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C33" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D33" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E33" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="34" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A34" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="B34" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C34" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D34" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E34" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="35" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A35" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="B35" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C35" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D35" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E35" s="2" t="s">
         <v>6</v>
       </c>
     </row>

--- a/Data Files/Backoffce/IndexacaoFG/IndexacaoFG_SANTANDER.xlsx
+++ b/Data Files/Backoffce/IndexacaoFG/IndexacaoFG_SANTANDER.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Public\RPA_ALLIANZ_TREINAMENTO\Data Files\Backoffce\IndexacaoFG\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3AC0803F-B7FF-49F5-B730-270A96A10EBC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FB07058C-A1FB-4144-B820-5BBDAF799877}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="20370" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="175" uniqueCount="43">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="105" uniqueCount="29">
   <si>
     <t xml:space="preserve">status </t>
   </si>
@@ -54,109 +54,67 @@
     <t>1070</t>
   </si>
   <si>
-    <t>Relatório de Recusas  08.09.2025 a 14.09.2025</t>
-  </si>
-  <si>
-    <t>Relatório de Recusas Santander - 12 e 13/09/2025</t>
-  </si>
-  <si>
-    <t>134239779</t>
-  </si>
-  <si>
-    <t>134266788</t>
-  </si>
-  <si>
-    <t>134288429</t>
-  </si>
-  <si>
-    <t>134310686</t>
-  </si>
-  <si>
-    <t>134340978</t>
-  </si>
-  <si>
-    <t>134369214</t>
-  </si>
-  <si>
-    <t>134289918</t>
-  </si>
-  <si>
-    <t>134388724</t>
-  </si>
-  <si>
-    <t>134376954</t>
-  </si>
-  <si>
-    <t>134205403</t>
-  </si>
-  <si>
-    <t>134219039</t>
-  </si>
-  <si>
-    <t>134289481</t>
-  </si>
-  <si>
-    <t>134298444</t>
-  </si>
-  <si>
-    <t>134296242</t>
-  </si>
-  <si>
-    <t>134289627</t>
-  </si>
-  <si>
-    <t>134305449</t>
-  </si>
-  <si>
-    <t>134310587</t>
-  </si>
-  <si>
-    <t>134286913</t>
-  </si>
-  <si>
-    <t>134287772</t>
-  </si>
-  <si>
-    <t>134292594</t>
-  </si>
-  <si>
-    <t>134293418</t>
-  </si>
-  <si>
-    <t>134293663</t>
-  </si>
-  <si>
-    <t>134296888</t>
-  </si>
-  <si>
-    <t>134356575</t>
-  </si>
-  <si>
-    <t>134310021</t>
-  </si>
-  <si>
-    <t>134430847</t>
-  </si>
-  <si>
-    <t>134194304</t>
-  </si>
-  <si>
-    <t>134245553</t>
-  </si>
-  <si>
-    <t>134235821</t>
-  </si>
-  <si>
-    <t>134240693</t>
-  </si>
-  <si>
-    <t>134251883</t>
-  </si>
-  <si>
-    <t>134305707</t>
-  </si>
-  <si>
-    <t>134419878</t>
+    <t>Relatório de Recusas  15.09.2025 a 21.09.2025</t>
+  </si>
+  <si>
+    <t>Relatório de Recusas Santander - 15/09/2025</t>
+  </si>
+  <si>
+    <t>134323883</t>
+  </si>
+  <si>
+    <t>134352986</t>
+  </si>
+  <si>
+    <t>134372332</t>
+  </si>
+  <si>
+    <t>134390711</t>
+  </si>
+  <si>
+    <t>134391642</t>
+  </si>
+  <si>
+    <t>134311755</t>
+  </si>
+  <si>
+    <t>134376182</t>
+  </si>
+  <si>
+    <t>134398093</t>
+  </si>
+  <si>
+    <t>134442454</t>
+  </si>
+  <si>
+    <t>134366614</t>
+  </si>
+  <si>
+    <t>134305172</t>
+  </si>
+  <si>
+    <t>134293168</t>
+  </si>
+  <si>
+    <t>134357107</t>
+  </si>
+  <si>
+    <t>134304782</t>
+  </si>
+  <si>
+    <t>134308199</t>
+  </si>
+  <si>
+    <t>134310397</t>
+  </si>
+  <si>
+    <t>134311503</t>
+  </si>
+  <si>
+    <t>134357645</t>
+  </si>
+  <si>
+    <t>134221725</t>
   </si>
 </sst>
 </file>
@@ -561,7 +519,7 @@
   <sheetPr>
     <pageSetUpPr autoPageBreaks="0"/>
   </sheetPr>
-  <dimension ref="A1:F35"/>
+  <dimension ref="A1:F22"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="2" width="16.7109375" style="1" customWidth="1" collapsed="1"/>
@@ -593,7 +551,7 @@
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A2" s="6">
-        <v>134207460</v>
+        <v>134310407</v>
       </c>
       <c r="B2" s="1" t="s">
         <v>7</v>
@@ -952,243 +910,7 @@
       <c r="F21"/>
     </row>
     <row r="22" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A22" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="B22" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C22" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D22" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="E22" s="2" t="s">
-        <v>6</v>
-      </c>
       <c r="F22"/>
-    </row>
-    <row r="23" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A23" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="B23" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C23" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D23" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="E23" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="24" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A24" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="B24" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C24" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D24" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="E24" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="25" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A25" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="B25" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C25" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D25" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="E25" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="26" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A26" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="B26" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C26" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D26" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="E26" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="27" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A27" s="1" t="s">
-        <v>34</v>
-      </c>
-      <c r="B27" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C27" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D27" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="E27" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="28" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A28" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="B28" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C28" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D28" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="E28" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="29" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A29" s="1" t="s">
-        <v>36</v>
-      </c>
-      <c r="B29" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C29" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D29" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="E29" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="30" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A30" s="1" t="s">
-        <v>37</v>
-      </c>
-      <c r="B30" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C30" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D30" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="E30" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="31" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A31" s="1" t="s">
-        <v>38</v>
-      </c>
-      <c r="B31" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C31" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D31" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="E31" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="32" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A32" s="1" t="s">
-        <v>39</v>
-      </c>
-      <c r="B32" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C32" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D32" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="E32" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="33" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A33" s="1" t="s">
-        <v>40</v>
-      </c>
-      <c r="B33" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C33" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D33" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="E33" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="34" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A34" s="1" t="s">
-        <v>41</v>
-      </c>
-      <c r="B34" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C34" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D34" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="E34" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="35" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A35" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="B35" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C35" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D35" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="E35" s="2" t="s">
-        <v>6</v>
-      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:F1" xr:uid="{00000000-0001-0000-0000-000000000000}"/>

--- a/Data Files/Backoffce/IndexacaoFG/IndexacaoFG_SANTANDER.xlsx
+++ b/Data Files/Backoffce/IndexacaoFG/IndexacaoFG_SANTANDER.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Public\RPA_ALLIANZ_TREINAMENTO\Data Files\Backoffce\IndexacaoFG\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FB07058C-A1FB-4144-B820-5BBDAF799877}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6FB70553-9500-4C79-8D8D-4570FDD69F69}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="20370" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="105" uniqueCount="29">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="140" uniqueCount="36">
   <si>
     <t xml:space="preserve">status </t>
   </si>
@@ -57,64 +57,85 @@
     <t>Relatório de Recusas  15.09.2025 a 21.09.2025</t>
   </si>
   <si>
-    <t>Relatório de Recusas Santander - 15/09/2025</t>
-  </si>
-  <si>
-    <t>134323883</t>
-  </si>
-  <si>
-    <t>134352986</t>
-  </si>
-  <si>
-    <t>134372332</t>
-  </si>
-  <si>
-    <t>134390711</t>
-  </si>
-  <si>
-    <t>134391642</t>
-  </si>
-  <si>
-    <t>134311755</t>
-  </si>
-  <si>
-    <t>134376182</t>
-  </si>
-  <si>
-    <t>134398093</t>
-  </si>
-  <si>
-    <t>134442454</t>
-  </si>
-  <si>
-    <t>134366614</t>
-  </si>
-  <si>
-    <t>134305172</t>
-  </si>
-  <si>
-    <t>134293168</t>
-  </si>
-  <si>
-    <t>134357107</t>
-  </si>
-  <si>
-    <t>134304782</t>
-  </si>
-  <si>
-    <t>134308199</t>
-  </si>
-  <si>
-    <t>134310397</t>
-  </si>
-  <si>
-    <t>134311503</t>
-  </si>
-  <si>
-    <t>134357645</t>
-  </si>
-  <si>
-    <t>134221725</t>
+    <t>Relatório de Recusas Santander - 16/09/2025</t>
+  </si>
+  <si>
+    <t>134317885</t>
+  </si>
+  <si>
+    <t>134330051</t>
+  </si>
+  <si>
+    <t>134343828</t>
+  </si>
+  <si>
+    <t>134368293</t>
+  </si>
+  <si>
+    <t>134401023</t>
+  </si>
+  <si>
+    <t>134404468</t>
+  </si>
+  <si>
+    <t>134416980</t>
+  </si>
+  <si>
+    <t>134399856</t>
+  </si>
+  <si>
+    <t>134430990</t>
+  </si>
+  <si>
+    <t>134453725</t>
+  </si>
+  <si>
+    <t>134345149</t>
+  </si>
+  <si>
+    <t>134201789</t>
+  </si>
+  <si>
+    <t>134270164</t>
+  </si>
+  <si>
+    <t>134258382</t>
+  </si>
+  <si>
+    <t>134270225</t>
+  </si>
+  <si>
+    <t>134333955</t>
+  </si>
+  <si>
+    <t>134317031</t>
+  </si>
+  <si>
+    <t>134317506</t>
+  </si>
+  <si>
+    <t>134319091</t>
+  </si>
+  <si>
+    <t>134325899</t>
+  </si>
+  <si>
+    <t>134253201</t>
+  </si>
+  <si>
+    <t>134330424</t>
+  </si>
+  <si>
+    <t>134336419</t>
+  </si>
+  <si>
+    <t>134342955</t>
+  </si>
+  <si>
+    <t>134344138</t>
+  </si>
+  <si>
+    <t>134346840</t>
   </si>
 </sst>
 </file>
@@ -519,7 +540,7 @@
   <sheetPr>
     <pageSetUpPr autoPageBreaks="0"/>
   </sheetPr>
-  <dimension ref="A1:F22"/>
+  <dimension ref="A1:F28"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="2" width="16.7109375" style="1" customWidth="1" collapsed="1"/>
@@ -551,7 +572,7 @@
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A2" s="6">
-        <v>134310407</v>
+        <v>134237714</v>
       </c>
       <c r="B2" s="1" t="s">
         <v>7</v>
@@ -910,7 +931,124 @@
       <c r="F21"/>
     </row>
     <row r="22" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A22" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="B22" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C22" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D22" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E22" s="2" t="s">
+        <v>6</v>
+      </c>
       <c r="F22"/>
+    </row>
+    <row r="23" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A23" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="B23" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C23" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D23" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E23" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="24" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A24" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="B24" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C24" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D24" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E24" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="25" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A25" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="B25" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C25" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D25" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E25" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="26" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A26" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="B26" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C26" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D26" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E26" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="27" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A27" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="B27" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C27" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D27" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E27" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="28" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A28" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="B28" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C28" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D28" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E28" s="2" t="s">
+        <v>6</v>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:F1" xr:uid="{00000000-0001-0000-0000-000000000000}"/>

--- a/Data Files/Backoffce/IndexacaoFG/IndexacaoFG_SANTANDER.xlsx
+++ b/Data Files/Backoffce/IndexacaoFG/IndexacaoFG_SANTANDER.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Public\RPA_ALLIANZ_TREINAMENTO\Data Files\Backoffce\IndexacaoFG\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6FB70553-9500-4C79-8D8D-4570FDD69F69}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FF909F00-29AF-4D59-A872-2E63683109ED}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="20370" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="140" uniqueCount="36">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="85" uniqueCount="25">
   <si>
     <t xml:space="preserve">status </t>
   </si>
@@ -57,85 +57,52 @@
     <t>Relatório de Recusas  15.09.2025 a 21.09.2025</t>
   </si>
   <si>
-    <t>Relatório de Recusas Santander - 16/09/2025</t>
-  </si>
-  <si>
-    <t>134317885</t>
-  </si>
-  <si>
-    <t>134330051</t>
-  </si>
-  <si>
-    <t>134343828</t>
-  </si>
-  <si>
-    <t>134368293</t>
-  </si>
-  <si>
-    <t>134401023</t>
-  </si>
-  <si>
-    <t>134404468</t>
-  </si>
-  <si>
-    <t>134416980</t>
-  </si>
-  <si>
-    <t>134399856</t>
-  </si>
-  <si>
-    <t>134430990</t>
-  </si>
-  <si>
-    <t>134453725</t>
-  </si>
-  <si>
-    <t>134345149</t>
-  </si>
-  <si>
-    <t>134201789</t>
-  </si>
-  <si>
-    <t>134270164</t>
-  </si>
-  <si>
-    <t>134258382</t>
-  </si>
-  <si>
-    <t>134270225</t>
-  </si>
-  <si>
-    <t>134333955</t>
-  </si>
-  <si>
-    <t>134317031</t>
-  </si>
-  <si>
-    <t>134317506</t>
-  </si>
-  <si>
-    <t>134319091</t>
-  </si>
-  <si>
-    <t>134325899</t>
-  </si>
-  <si>
-    <t>134253201</t>
-  </si>
-  <si>
-    <t>134330424</t>
-  </si>
-  <si>
-    <t>134336419</t>
-  </si>
-  <si>
-    <t>134342955</t>
-  </si>
-  <si>
-    <t>134344138</t>
-  </si>
-  <si>
-    <t>134346840</t>
+    <t>Relatório de Recusas Santander - 17/09/2025</t>
+  </si>
+  <si>
+    <t>134410569</t>
+  </si>
+  <si>
+    <t>134416448</t>
+  </si>
+  <si>
+    <t>134416827</t>
+  </si>
+  <si>
+    <t>134443930</t>
+  </si>
+  <si>
+    <t>134472466</t>
+  </si>
+  <si>
+    <t>134281070</t>
+  </si>
+  <si>
+    <t>134287555</t>
+  </si>
+  <si>
+    <t>134288001</t>
+  </si>
+  <si>
+    <t>134308384</t>
+  </si>
+  <si>
+    <t>134353962</t>
+  </si>
+  <si>
+    <t>134354255</t>
+  </si>
+  <si>
+    <t>134357895</t>
+  </si>
+  <si>
+    <t>134367117</t>
+  </si>
+  <si>
+    <t>134367628</t>
+  </si>
+  <si>
+    <t>134407560</t>
   </si>
 </sst>
 </file>
@@ -540,7 +507,7 @@
   <sheetPr>
     <pageSetUpPr autoPageBreaks="0"/>
   </sheetPr>
-  <dimension ref="A1:F28"/>
+  <dimension ref="A1:F22"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="2" width="16.7109375" style="1" customWidth="1" collapsed="1"/>
@@ -572,7 +539,7 @@
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A2" s="6">
-        <v>134237714</v>
+        <v>134368647</v>
       </c>
       <c r="B2" s="1" t="s">
         <v>7</v>
@@ -859,196 +826,19 @@
       <c r="F17"/>
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A18" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="B18" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C18" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D18" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="E18" s="2" t="s">
-        <v>6</v>
-      </c>
       <c r="F18"/>
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A19" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="B19" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C19" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D19" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="E19" s="2" t="s">
-        <v>6</v>
-      </c>
       <c r="F19"/>
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A20" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="B20" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C20" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D20" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="E20" s="2" t="s">
-        <v>6</v>
-      </c>
       <c r="F20"/>
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A21" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="B21" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C21" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D21" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="E21" s="2" t="s">
-        <v>6</v>
-      </c>
       <c r="F21"/>
     </row>
     <row r="22" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A22" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="B22" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C22" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D22" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="E22" s="2" t="s">
-        <v>6</v>
-      </c>
       <c r="F22"/>
-    </row>
-    <row r="23" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A23" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="B23" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C23" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D23" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="E23" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="24" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A24" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="B24" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C24" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D24" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="E24" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="25" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A25" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="B25" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C25" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D25" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="E25" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="26" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A26" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="B26" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C26" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D26" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="E26" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="27" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A27" s="1" t="s">
-        <v>34</v>
-      </c>
-      <c r="B27" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C27" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D27" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="E27" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="28" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A28" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="B28" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C28" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D28" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="E28" s="2" t="s">
-        <v>6</v>
-      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:F1" xr:uid="{00000000-0001-0000-0000-000000000000}"/>

--- a/Data Files/Backoffce/IndexacaoFG/IndexacaoFG_SANTANDER.xlsx
+++ b/Data Files/Backoffce/IndexacaoFG/IndexacaoFG_SANTANDER.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Public\RPA_ALLIANZ_TREINAMENTO\Data Files\Backoffce\IndexacaoFG\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FF909F00-29AF-4D59-A872-2E63683109ED}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{92A6DC00-2253-49D8-891D-7884B777F994}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="20370" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="85" uniqueCount="25">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="110" uniqueCount="30">
   <si>
     <t xml:space="preserve">status </t>
   </si>
@@ -57,52 +57,67 @@
     <t>Relatório de Recusas  15.09.2025 a 21.09.2025</t>
   </si>
   <si>
-    <t>Relatório de Recusas Santander - 17/09/2025</t>
-  </si>
-  <si>
-    <t>134410569</t>
-  </si>
-  <si>
-    <t>134416448</t>
-  </si>
-  <si>
-    <t>134416827</t>
-  </si>
-  <si>
-    <t>134443930</t>
-  </si>
-  <si>
-    <t>134472466</t>
-  </si>
-  <si>
-    <t>134281070</t>
-  </si>
-  <si>
-    <t>134287555</t>
-  </si>
-  <si>
-    <t>134288001</t>
-  </si>
-  <si>
-    <t>134308384</t>
-  </si>
-  <si>
-    <t>134353962</t>
-  </si>
-  <si>
-    <t>134354255</t>
-  </si>
-  <si>
-    <t>134357895</t>
-  </si>
-  <si>
-    <t>134367117</t>
-  </si>
-  <si>
-    <t>134367628</t>
-  </si>
-  <si>
-    <t>134407560</t>
+    <t>Relatório de Recusas Santander - 18/09/2025</t>
+  </si>
+  <si>
+    <t>134391349</t>
+  </si>
+  <si>
+    <t>134387165</t>
+  </si>
+  <si>
+    <t>134406609</t>
+  </si>
+  <si>
+    <t>134421442</t>
+  </si>
+  <si>
+    <t>134419744</t>
+  </si>
+  <si>
+    <t>134380281</t>
+  </si>
+  <si>
+    <t>134484052</t>
+  </si>
+  <si>
+    <t>134494307</t>
+  </si>
+  <si>
+    <t>134490512</t>
+  </si>
+  <si>
+    <t>134342644</t>
+  </si>
+  <si>
+    <t>134321378</t>
+  </si>
+  <si>
+    <t>134318246</t>
+  </si>
+  <si>
+    <t>134379626</t>
+  </si>
+  <si>
+    <t>134458947</t>
+  </si>
+  <si>
+    <t>134306197</t>
+  </si>
+  <si>
+    <t>134378477</t>
+  </si>
+  <si>
+    <t>134376163</t>
+  </si>
+  <si>
+    <t>134377562</t>
+  </si>
+  <si>
+    <t>134382820</t>
+  </si>
+  <si>
+    <t>134384068</t>
   </si>
 </sst>
 </file>
@@ -539,7 +554,7 @@
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A2" s="6">
-        <v>134368647</v>
+        <v>134306265</v>
       </c>
       <c r="B2" s="1" t="s">
         <v>7</v>
@@ -826,18 +841,93 @@
       <c r="F17"/>
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A18" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="B18" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C18" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D18" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E18" s="2" t="s">
+        <v>6</v>
+      </c>
       <c r="F18"/>
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A19" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="B19" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C19" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D19" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E19" s="2" t="s">
+        <v>6</v>
+      </c>
       <c r="F19"/>
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A20" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="B20" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C20" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D20" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E20" s="2" t="s">
+        <v>6</v>
+      </c>
       <c r="F20"/>
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A21" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="B21" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C21" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D21" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E21" s="2" t="s">
+        <v>6</v>
+      </c>
       <c r="F21"/>
     </row>
     <row r="22" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A22" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="B22" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C22" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D22" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E22" s="2" t="s">
+        <v>6</v>
+      </c>
       <c r="F22"/>
     </row>
   </sheetData>

--- a/Data Files/Backoffce/IndexacaoFG/IndexacaoFG_SANTANDER.xlsx
+++ b/Data Files/Backoffce/IndexacaoFG/IndexacaoFG_SANTANDER.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Public\RPA_ALLIANZ_TREINAMENTO\Data Files\Backoffce\IndexacaoFG\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{92A6DC00-2253-49D8-891D-7884B777F994}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{14A2C1F1-0727-4CBE-AC8F-F3F99DF0CD59}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="20370" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="110" uniqueCount="30">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="145" uniqueCount="37">
   <si>
     <t xml:space="preserve">status </t>
   </si>
@@ -57,67 +57,88 @@
     <t>Relatório de Recusas  15.09.2025 a 21.09.2025</t>
   </si>
   <si>
-    <t>Relatório de Recusas Santander - 18/09/2025</t>
-  </si>
-  <si>
-    <t>134391349</t>
-  </si>
-  <si>
-    <t>134387165</t>
-  </si>
-  <si>
-    <t>134406609</t>
-  </si>
-  <si>
-    <t>134421442</t>
-  </si>
-  <si>
-    <t>134419744</t>
-  </si>
-  <si>
-    <t>134380281</t>
-  </si>
-  <si>
-    <t>134484052</t>
-  </si>
-  <si>
-    <t>134494307</t>
-  </si>
-  <si>
-    <t>134490512</t>
-  </si>
-  <si>
-    <t>134342644</t>
-  </si>
-  <si>
-    <t>134321378</t>
-  </si>
-  <si>
-    <t>134318246</t>
-  </si>
-  <si>
-    <t>134379626</t>
-  </si>
-  <si>
-    <t>134458947</t>
-  </si>
-  <si>
-    <t>134306197</t>
-  </si>
-  <si>
-    <t>134378477</t>
-  </si>
-  <si>
-    <t>134376163</t>
-  </si>
-  <si>
-    <t>134377562</t>
-  </si>
-  <si>
-    <t>134382820</t>
-  </si>
-  <si>
-    <t>134384068</t>
+    <t>Relatório de Recusas Santander - 19 e 20/09/2025</t>
+  </si>
+  <si>
+    <t>134396527</t>
+  </si>
+  <si>
+    <t>134409337</t>
+  </si>
+  <si>
+    <t>134400509</t>
+  </si>
+  <si>
+    <t>134450150</t>
+  </si>
+  <si>
+    <t>134482319</t>
+  </si>
+  <si>
+    <t>134470164</t>
+  </si>
+  <si>
+    <t>134480090</t>
+  </si>
+  <si>
+    <t>134399147</t>
+  </si>
+  <si>
+    <t>134495839</t>
+  </si>
+  <si>
+    <t>134500324</t>
+  </si>
+  <si>
+    <t>134496427</t>
+  </si>
+  <si>
+    <t>134526103</t>
+  </si>
+  <si>
+    <t>134529085</t>
+  </si>
+  <si>
+    <t>134383363</t>
+  </si>
+  <si>
+    <t>134411762</t>
+  </si>
+  <si>
+    <t>134401780</t>
+  </si>
+  <si>
+    <t>134400266</t>
+  </si>
+  <si>
+    <t>134401659</t>
+  </si>
+  <si>
+    <t>134399294</t>
+  </si>
+  <si>
+    <t>134400810</t>
+  </si>
+  <si>
+    <t>134398173</t>
+  </si>
+  <si>
+    <t>134399918</t>
+  </si>
+  <si>
+    <t>134402138</t>
+  </si>
+  <si>
+    <t>134402967</t>
+  </si>
+  <si>
+    <t>134405801</t>
+  </si>
+  <si>
+    <t>134322914</t>
+  </si>
+  <si>
+    <t>134413536</t>
   </si>
 </sst>
 </file>
@@ -522,7 +543,7 @@
   <sheetPr>
     <pageSetUpPr autoPageBreaks="0"/>
   </sheetPr>
-  <dimension ref="A1:F22"/>
+  <dimension ref="A1:F29"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="2" width="16.7109375" style="1" customWidth="1" collapsed="1"/>
@@ -554,7 +575,7 @@
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A2" s="6">
-        <v>134306265</v>
+        <v>134391362</v>
       </c>
       <c r="B2" s="1" t="s">
         <v>7</v>
@@ -929,6 +950,125 @@
         <v>6</v>
       </c>
       <c r="F22"/>
+    </row>
+    <row r="23" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A23" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="B23" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C23" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D23" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E23" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="24" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A24" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="B24" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C24" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D24" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E24" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="25" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A25" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="B25" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C25" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D25" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E25" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="26" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A26" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="B26" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C26" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D26" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E26" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="27" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A27" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="B27" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C27" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D27" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E27" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="28" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A28" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="B28" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C28" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D28" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E28" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="29" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A29" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="B29" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C29" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D29" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E29" s="2" t="s">
+        <v>6</v>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:F1" xr:uid="{00000000-0001-0000-0000-000000000000}"/>

--- a/Data Files/Backoffce/IndexacaoFG/IndexacaoFG_SANTANDER.xlsx
+++ b/Data Files/Backoffce/IndexacaoFG/IndexacaoFG_SANTANDER.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Public\RPA_ALLIANZ_TREINAMENTO\Data Files\Backoffce\IndexacaoFG\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{14A2C1F1-0727-4CBE-AC8F-F3F99DF0CD59}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2E6F8264-574D-4D25-9EA8-2744616FBFD2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="20370" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="145" uniqueCount="37">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="95" uniqueCount="27">
   <si>
     <t xml:space="preserve">status </t>
   </si>
@@ -54,91 +54,61 @@
     <t>1070</t>
   </si>
   <si>
-    <t>Relatório de Recusas  15.09.2025 a 21.09.2025</t>
-  </si>
-  <si>
-    <t>Relatório de Recusas Santander - 19 e 20/09/2025</t>
-  </si>
-  <si>
-    <t>134396527</t>
-  </si>
-  <si>
-    <t>134409337</t>
-  </si>
-  <si>
-    <t>134400509</t>
-  </si>
-  <si>
-    <t>134450150</t>
-  </si>
-  <si>
-    <t>134482319</t>
-  </si>
-  <si>
-    <t>134470164</t>
-  </si>
-  <si>
-    <t>134480090</t>
-  </si>
-  <si>
-    <t>134399147</t>
-  </si>
-  <si>
-    <t>134495839</t>
-  </si>
-  <si>
-    <t>134500324</t>
-  </si>
-  <si>
-    <t>134496427</t>
-  </si>
-  <si>
-    <t>134526103</t>
-  </si>
-  <si>
-    <t>134529085</t>
-  </si>
-  <si>
-    <t>134383363</t>
-  </si>
-  <si>
-    <t>134411762</t>
-  </si>
-  <si>
-    <t>134401780</t>
-  </si>
-  <si>
-    <t>134400266</t>
-  </si>
-  <si>
-    <t>134401659</t>
-  </si>
-  <si>
-    <t>134399294</t>
-  </si>
-  <si>
-    <t>134400810</t>
-  </si>
-  <si>
-    <t>134398173</t>
-  </si>
-  <si>
-    <t>134399918</t>
-  </si>
-  <si>
-    <t>134402138</t>
-  </si>
-  <si>
-    <t>134402967</t>
-  </si>
-  <si>
-    <t>134405801</t>
-  </si>
-  <si>
-    <t>134322914</t>
-  </si>
-  <si>
-    <t>134413536</t>
+    <t>Relatório de Recusas  22.09.2025 a 28.09.2025</t>
+  </si>
+  <si>
+    <t>Relatório de Recusas Santander - 22/09/2025</t>
+  </si>
+  <si>
+    <t>134441915</t>
+  </si>
+  <si>
+    <t>134468232</t>
+  </si>
+  <si>
+    <t>134496238</t>
+  </si>
+  <si>
+    <t>134500969</t>
+  </si>
+  <si>
+    <t>134493095</t>
+  </si>
+  <si>
+    <t>134517081</t>
+  </si>
+  <si>
+    <t>134521309</t>
+  </si>
+  <si>
+    <t>134519081</t>
+  </si>
+  <si>
+    <t>134553838</t>
+  </si>
+  <si>
+    <t>134419085</t>
+  </si>
+  <si>
+    <t>134450713</t>
+  </si>
+  <si>
+    <t>134420215</t>
+  </si>
+  <si>
+    <t>134421253</t>
+  </si>
+  <si>
+    <t>134430120</t>
+  </si>
+  <si>
+    <t>134380262</t>
+  </si>
+  <si>
+    <t>134438763</t>
+  </si>
+  <si>
+    <t>134454618</t>
   </si>
 </sst>
 </file>
@@ -543,7 +513,7 @@
   <sheetPr>
     <pageSetUpPr autoPageBreaks="0"/>
   </sheetPr>
-  <dimension ref="A1:F29"/>
+  <dimension ref="A1:F22"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="2" width="16.7109375" style="1" customWidth="1" collapsed="1"/>
@@ -575,7 +545,7 @@
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A2" s="6">
-        <v>134391362</v>
+        <v>134355005</v>
       </c>
       <c r="B2" s="1" t="s">
         <v>7</v>
@@ -898,177 +868,13 @@
       <c r="F19"/>
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A20" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="B20" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C20" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D20" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="E20" s="2" t="s">
-        <v>6</v>
-      </c>
       <c r="F20"/>
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A21" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="B21" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C21" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D21" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="E21" s="2" t="s">
-        <v>6</v>
-      </c>
       <c r="F21"/>
     </row>
     <row r="22" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A22" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="B22" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C22" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D22" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="E22" s="2" t="s">
-        <v>6</v>
-      </c>
       <c r="F22"/>
-    </row>
-    <row r="23" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A23" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="B23" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C23" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D23" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="E23" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="24" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A24" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="B24" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C24" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D24" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="E24" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="25" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A25" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="B25" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C25" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D25" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="E25" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="26" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A26" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="B26" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C26" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D26" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="E26" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="27" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A27" s="1" t="s">
-        <v>34</v>
-      </c>
-      <c r="B27" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C27" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D27" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="E27" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="28" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A28" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="B28" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C28" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D28" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="E28" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="29" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A29" s="1" t="s">
-        <v>36</v>
-      </c>
-      <c r="B29" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C29" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D29" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="E29" s="2" t="s">
-        <v>6</v>
-      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:F1" xr:uid="{00000000-0001-0000-0000-000000000000}"/>

--- a/Data Files/Backoffce/IndexacaoFG/IndexacaoFG_SANTANDER.xlsx
+++ b/Data Files/Backoffce/IndexacaoFG/IndexacaoFG_SANTANDER.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Public\RPA_ALLIANZ_TREINAMENTO\Data Files\Backoffce\IndexacaoFG\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2E6F8264-574D-4D25-9EA8-2744616FBFD2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3B65BA79-88D6-4203-B9B0-B8FB3341BE17}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="20370" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="95" uniqueCount="27">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="85" uniqueCount="25">
   <si>
     <t xml:space="preserve">status </t>
   </si>
@@ -57,58 +57,52 @@
     <t>Relatório de Recusas  22.09.2025 a 28.09.2025</t>
   </si>
   <si>
-    <t>Relatório de Recusas Santander - 22/09/2025</t>
-  </si>
-  <si>
-    <t>134441915</t>
-  </si>
-  <si>
-    <t>134468232</t>
-  </si>
-  <si>
-    <t>134496238</t>
-  </si>
-  <si>
-    <t>134500969</t>
-  </si>
-  <si>
-    <t>134493095</t>
-  </si>
-  <si>
-    <t>134517081</t>
-  </si>
-  <si>
-    <t>134521309</t>
-  </si>
-  <si>
-    <t>134519081</t>
-  </si>
-  <si>
-    <t>134553838</t>
-  </si>
-  <si>
-    <t>134419085</t>
-  </si>
-  <si>
-    <t>134450713</t>
-  </si>
-  <si>
-    <t>134420215</t>
-  </si>
-  <si>
-    <t>134421253</t>
-  </si>
-  <si>
-    <t>134430120</t>
-  </si>
-  <si>
-    <t>134380262</t>
-  </si>
-  <si>
-    <t>134438763</t>
-  </si>
-  <si>
-    <t>134454618</t>
+    <t>Relatório de Recusas Santander - 23/09/2025</t>
+  </si>
+  <si>
+    <t>134450716</t>
+  </si>
+  <si>
+    <t>134445901</t>
+  </si>
+  <si>
+    <t>134498760</t>
+  </si>
+  <si>
+    <t>134516870</t>
+  </si>
+  <si>
+    <t>134529211</t>
+  </si>
+  <si>
+    <t>134573678</t>
+  </si>
+  <si>
+    <t>134485071</t>
+  </si>
+  <si>
+    <t>134446135</t>
+  </si>
+  <si>
+    <t>134379980</t>
+  </si>
+  <si>
+    <t>134379871</t>
+  </si>
+  <si>
+    <t>134528375</t>
+  </si>
+  <si>
+    <t>134461194</t>
+  </si>
+  <si>
+    <t>134446742</t>
+  </si>
+  <si>
+    <t>134453455</t>
+  </si>
+  <si>
+    <t>134459827</t>
   </si>
 </sst>
 </file>
@@ -545,7 +539,7 @@
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A2" s="6">
-        <v>134355005</v>
+        <v>134379567</v>
       </c>
       <c r="B2" s="1" t="s">
         <v>7</v>
@@ -832,39 +826,9 @@
       <c r="F17"/>
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A18" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="B18" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C18" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D18" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="E18" s="2" t="s">
-        <v>6</v>
-      </c>
       <c r="F18"/>
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A19" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="B19" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C19" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D19" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="E19" s="2" t="s">
-        <v>6</v>
-      </c>
       <c r="F19"/>
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.25">

--- a/Data Files/Backoffce/IndexacaoFG/IndexacaoFG_SANTANDER.xlsx
+++ b/Data Files/Backoffce/IndexacaoFG/IndexacaoFG_SANTANDER.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Public\RPA_ALLIANZ_TREINAMENTO\Data Files\Backoffce\IndexacaoFG\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3B65BA79-88D6-4203-B9B0-B8FB3341BE17}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D5AB89FE-9F6E-4F23-A1A7-362F36C0F678}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="20370" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="85" uniqueCount="25">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="80" uniqueCount="24">
   <si>
     <t xml:space="preserve">status </t>
   </si>
@@ -54,55 +54,52 @@
     <t>1070</t>
   </si>
   <si>
+    <t>Relatório de Recusas Santander - 24/09/2025</t>
+  </si>
+  <si>
+    <t>134468982</t>
+  </si>
+  <si>
+    <t>134483331</t>
+  </si>
+  <si>
+    <t>134484517</t>
+  </si>
+  <si>
+    <t>134494799</t>
+  </si>
+  <si>
+    <t>134524687</t>
+  </si>
+  <si>
+    <t>134399157</t>
+  </si>
+  <si>
+    <t>134408947</t>
+  </si>
+  <si>
+    <t>134395199</t>
+  </si>
+  <si>
+    <t>134396515</t>
+  </si>
+  <si>
+    <t>134485726</t>
+  </si>
+  <si>
+    <t>134471359</t>
+  </si>
+  <si>
+    <t>134482430</t>
+  </si>
+  <si>
+    <t>134514508</t>
+  </si>
+  <si>
+    <t>134521468</t>
+  </si>
+  <si>
     <t>Relatório de Recusas  22.09.2025 a 28.09.2025</t>
-  </si>
-  <si>
-    <t>Relatório de Recusas Santander - 23/09/2025</t>
-  </si>
-  <si>
-    <t>134450716</t>
-  </si>
-  <si>
-    <t>134445901</t>
-  </si>
-  <si>
-    <t>134498760</t>
-  </si>
-  <si>
-    <t>134516870</t>
-  </si>
-  <si>
-    <t>134529211</t>
-  </si>
-  <si>
-    <t>134573678</t>
-  </si>
-  <si>
-    <t>134485071</t>
-  </si>
-  <si>
-    <t>134446135</t>
-  </si>
-  <si>
-    <t>134379980</t>
-  </si>
-  <si>
-    <t>134379871</t>
-  </si>
-  <si>
-    <t>134528375</t>
-  </si>
-  <si>
-    <t>134461194</t>
-  </si>
-  <si>
-    <t>134446742</t>
-  </si>
-  <si>
-    <t>134453455</t>
-  </si>
-  <si>
-    <t>134459827</t>
   </si>
 </sst>
 </file>
@@ -539,16 +536,16 @@
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A2" s="6">
-        <v>134379567</v>
+        <v>134408275</v>
       </c>
       <c r="B2" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>8</v>
+        <v>23</v>
       </c>
       <c r="E2" s="2" t="s">
         <v>6</v>
@@ -557,16 +554,16 @@
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B3" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>8</v>
+        <v>23</v>
       </c>
       <c r="E3" s="2" t="s">
         <v>6</v>
@@ -575,16 +572,16 @@
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B4" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>8</v>
+        <v>23</v>
       </c>
       <c r="E4" s="2" t="s">
         <v>6</v>
@@ -593,16 +590,16 @@
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B5" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>8</v>
+        <v>23</v>
       </c>
       <c r="E5" s="2" t="s">
         <v>6</v>
@@ -611,16 +608,16 @@
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" s="1" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B6" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>8</v>
+        <v>23</v>
       </c>
       <c r="E6" s="2" t="s">
         <v>6</v>
@@ -629,16 +626,16 @@
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" s="1" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B7" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>8</v>
+        <v>23</v>
       </c>
       <c r="E7" s="2" t="s">
         <v>6</v>
@@ -647,16 +644,16 @@
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" s="1" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B8" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>8</v>
+        <v>23</v>
       </c>
       <c r="E8" s="2" t="s">
         <v>6</v>
@@ -665,16 +662,16 @@
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" s="1" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B9" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>8</v>
+        <v>23</v>
       </c>
       <c r="E9" s="2" t="s">
         <v>6</v>
@@ -683,16 +680,16 @@
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A10" s="1" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B10" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>8</v>
+        <v>23</v>
       </c>
       <c r="E10" s="2" t="s">
         <v>6</v>
@@ -701,16 +698,16 @@
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A11" s="1" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B11" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>8</v>
+        <v>23</v>
       </c>
       <c r="E11" s="2" t="s">
         <v>6</v>
@@ -719,16 +716,16 @@
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A12" s="1" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B12" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>8</v>
+        <v>23</v>
       </c>
       <c r="E12" s="2" t="s">
         <v>6</v>
@@ -737,16 +734,16 @@
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A13" s="1" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B13" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>8</v>
+        <v>23</v>
       </c>
       <c r="E13" s="2" t="s">
         <v>6</v>
@@ -755,16 +752,16 @@
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A14" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="B14" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>8</v>
+        <v>23</v>
       </c>
       <c r="E14" s="2" t="s">
         <v>6</v>
@@ -773,16 +770,16 @@
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A15" s="1" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B15" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>8</v>
+        <v>23</v>
       </c>
       <c r="E15" s="2" t="s">
         <v>6</v>
@@ -791,53 +788,38 @@
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A16" s="1" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B16" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>8</v>
+        <v>23</v>
       </c>
       <c r="E16" s="2" t="s">
         <v>6</v>
       </c>
       <c r="F16"/>
     </row>
-    <row r="17" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A17" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="B17" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C17" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D17" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="E17" s="2" t="s">
-        <v>6</v>
-      </c>
+    <row r="17" spans="6:6" x14ac:dyDescent="0.25">
       <c r="F17"/>
     </row>
-    <row r="18" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="18" spans="6:6" x14ac:dyDescent="0.25">
       <c r="F18"/>
     </row>
-    <row r="19" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="19" spans="6:6" x14ac:dyDescent="0.25">
       <c r="F19"/>
     </row>
-    <row r="20" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="20" spans="6:6" x14ac:dyDescent="0.25">
       <c r="F20"/>
     </row>
-    <row r="21" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="21" spans="6:6" x14ac:dyDescent="0.25">
       <c r="F21"/>
     </row>
-    <row r="22" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="22" spans="6:6" x14ac:dyDescent="0.25">
       <c r="F22"/>
     </row>
   </sheetData>

--- a/Data Files/Backoffce/IndexacaoFG/IndexacaoFG_SANTANDER.xlsx
+++ b/Data Files/Backoffce/IndexacaoFG/IndexacaoFG_SANTANDER.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Public\RPA_ALLIANZ_TREINAMENTO\Data Files\Backoffce\IndexacaoFG\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D5AB89FE-9F6E-4F23-A1A7-362F36C0F678}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AA60A01A-D799-4FA4-91C3-53C26D0A25D3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="20370" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>

--- a/Data Files/Backoffce/IndexacaoFG/IndexacaoFG_SANTANDER.xlsx
+++ b/Data Files/Backoffce/IndexacaoFG/IndexacaoFG_SANTANDER.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27928"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28526"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Public\RPA_ALLIANZ_TREINAMENTO\Data Files\Backoffce\IndexacaoFG\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AA60A01A-D799-4FA4-91C3-53C26D0A25D3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4029EF3B-C606-44B7-B7EB-94F0031E58A0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="20370" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="80" uniqueCount="24">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="170" uniqueCount="42">
   <si>
     <t xml:space="preserve">status </t>
   </si>
@@ -54,52 +54,106 @@
     <t>1070</t>
   </si>
   <si>
-    <t>Relatório de Recusas Santander - 24/09/2025</t>
-  </si>
-  <si>
-    <t>134468982</t>
-  </si>
-  <si>
-    <t>134483331</t>
-  </si>
-  <si>
-    <t>134484517</t>
-  </si>
-  <si>
-    <t>134494799</t>
-  </si>
-  <si>
-    <t>134524687</t>
-  </si>
-  <si>
-    <t>134399157</t>
-  </si>
-  <si>
-    <t>134408947</t>
-  </si>
-  <si>
-    <t>134395199</t>
-  </si>
-  <si>
-    <t>134396515</t>
-  </si>
-  <si>
-    <t>134485726</t>
-  </si>
-  <si>
-    <t>134471359</t>
-  </si>
-  <si>
-    <t>134482430</t>
-  </si>
-  <si>
-    <t>134514508</t>
-  </si>
-  <si>
-    <t>134521468</t>
-  </si>
-  <si>
-    <t>Relatório de Recusas  22.09.2025 a 28.09.2025</t>
+    <t>Relatório de Recusas Santander - 06/10/2025</t>
+  </si>
+  <si>
+    <t>134652343</t>
+  </si>
+  <si>
+    <t>134658870</t>
+  </si>
+  <si>
+    <t>134667095</t>
+  </si>
+  <si>
+    <t>134671678</t>
+  </si>
+  <si>
+    <t>134665477</t>
+  </si>
+  <si>
+    <t>134652012</t>
+  </si>
+  <si>
+    <t>134656283</t>
+  </si>
+  <si>
+    <t>134654702</t>
+  </si>
+  <si>
+    <t>134652102</t>
+  </si>
+  <si>
+    <t>134698414</t>
+  </si>
+  <si>
+    <t>134701391</t>
+  </si>
+  <si>
+    <t>134703116</t>
+  </si>
+  <si>
+    <t>134713267</t>
+  </si>
+  <si>
+    <t>134681011</t>
+  </si>
+  <si>
+    <t>134756714</t>
+  </si>
+  <si>
+    <t>134770404</t>
+  </si>
+  <si>
+    <t>134598337</t>
+  </si>
+  <si>
+    <t>134665384</t>
+  </si>
+  <si>
+    <t>134662074</t>
+  </si>
+  <si>
+    <t>134660067</t>
+  </si>
+  <si>
+    <t>134692267</t>
+  </si>
+  <si>
+    <t>134651036</t>
+  </si>
+  <si>
+    <t>134652142</t>
+  </si>
+  <si>
+    <t>134652159</t>
+  </si>
+  <si>
+    <t>134652965</t>
+  </si>
+  <si>
+    <t>134655241</t>
+  </si>
+  <si>
+    <t>134658334</t>
+  </si>
+  <si>
+    <t>134658593</t>
+  </si>
+  <si>
+    <t>134662051</t>
+  </si>
+  <si>
+    <t>134665397</t>
+  </si>
+  <si>
+    <t>134668994</t>
+  </si>
+  <si>
+    <t>134669432</t>
+  </si>
+  <si>
+    <t>Relatório de Recusas 06.10.2025 a 12.10.2025</t>
   </si>
 </sst>
 </file>
@@ -504,7 +558,7 @@
   <sheetPr>
     <pageSetUpPr autoPageBreaks="0"/>
   </sheetPr>
-  <dimension ref="A1:F22"/>
+  <dimension ref="A1:F34"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="2" width="16.7109375" style="1" customWidth="1" collapsed="1"/>
@@ -536,7 +590,7 @@
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A2" s="6">
-        <v>134408275</v>
+        <v>134596935</v>
       </c>
       <c r="B2" s="1" t="s">
         <v>7</v>
@@ -545,7 +599,7 @@
         <v>8</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>23</v>
+        <v>41</v>
       </c>
       <c r="E2" s="2" t="s">
         <v>6</v>
@@ -563,7 +617,7 @@
         <v>8</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>23</v>
+        <v>41</v>
       </c>
       <c r="E3" s="2" t="s">
         <v>6</v>
@@ -581,7 +635,7 @@
         <v>8</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>23</v>
+        <v>41</v>
       </c>
       <c r="E4" s="2" t="s">
         <v>6</v>
@@ -599,7 +653,7 @@
         <v>8</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>23</v>
+        <v>41</v>
       </c>
       <c r="E5" s="2" t="s">
         <v>6</v>
@@ -617,7 +671,7 @@
         <v>8</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>23</v>
+        <v>41</v>
       </c>
       <c r="E6" s="2" t="s">
         <v>6</v>
@@ -635,7 +689,7 @@
         <v>8</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>23</v>
+        <v>41</v>
       </c>
       <c r="E7" s="2" t="s">
         <v>6</v>
@@ -653,7 +707,7 @@
         <v>8</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>23</v>
+        <v>41</v>
       </c>
       <c r="E8" s="2" t="s">
         <v>6</v>
@@ -671,7 +725,7 @@
         <v>8</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>23</v>
+        <v>41</v>
       </c>
       <c r="E9" s="2" t="s">
         <v>6</v>
@@ -689,7 +743,7 @@
         <v>8</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>23</v>
+        <v>41</v>
       </c>
       <c r="E10" s="2" t="s">
         <v>6</v>
@@ -707,7 +761,7 @@
         <v>8</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>23</v>
+        <v>41</v>
       </c>
       <c r="E11" s="2" t="s">
         <v>6</v>
@@ -725,7 +779,7 @@
         <v>8</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>23</v>
+        <v>41</v>
       </c>
       <c r="E12" s="2" t="s">
         <v>6</v>
@@ -743,7 +797,7 @@
         <v>8</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>23</v>
+        <v>41</v>
       </c>
       <c r="E13" s="2" t="s">
         <v>6</v>
@@ -761,7 +815,7 @@
         <v>8</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>23</v>
+        <v>41</v>
       </c>
       <c r="E14" s="2" t="s">
         <v>6</v>
@@ -779,7 +833,7 @@
         <v>8</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>23</v>
+        <v>41</v>
       </c>
       <c r="E15" s="2" t="s">
         <v>6</v>
@@ -797,30 +851,324 @@
         <v>8</v>
       </c>
       <c r="D16" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="E16" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="F16"/>
+    </row>
+    <row r="17" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A17" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="E16" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="F16"/>
-    </row>
-    <row r="17" spans="6:6" x14ac:dyDescent="0.25">
+      <c r="B17" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C17" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D17" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="E17" s="2" t="s">
+        <v>6</v>
+      </c>
       <c r="F17"/>
     </row>
-    <row r="18" spans="6:6" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A18" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="B18" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C18" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D18" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="E18" s="2" t="s">
+        <v>6</v>
+      </c>
       <c r="F18"/>
     </row>
-    <row r="19" spans="6:6" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A19" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="B19" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C19" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D19" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="E19" s="2" t="s">
+        <v>6</v>
+      </c>
       <c r="F19"/>
     </row>
-    <row r="20" spans="6:6" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A20" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="B20" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C20" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D20" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="E20" s="2" t="s">
+        <v>6</v>
+      </c>
       <c r="F20"/>
     </row>
-    <row r="21" spans="6:6" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A21" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="B21" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C21" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D21" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="E21" s="2" t="s">
+        <v>6</v>
+      </c>
       <c r="F21"/>
     </row>
-    <row r="22" spans="6:6" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A22" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="B22" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C22" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D22" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="E22" s="2" t="s">
+        <v>6</v>
+      </c>
       <c r="F22"/>
+    </row>
+    <row r="23" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A23" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="B23" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C23" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D23" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="E23" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="24" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A24" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="B24" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C24" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D24" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="E24" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="25" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A25" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="B25" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C25" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D25" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="E25" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="26" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A26" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="B26" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C26" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D26" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="E26" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="27" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A27" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="B27" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C27" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D27" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="E27" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="28" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A28" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="B28" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C28" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D28" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="E28" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="29" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A29" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="B29" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C29" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D29" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="E29" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="30" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A30" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="B30" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C30" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D30" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="E30" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="31" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A31" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="B31" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C31" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D31" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="E31" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="32" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A32" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="B32" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C32" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D32" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="E32" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="33" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A33" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="B33" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C33" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D33" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="E33" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="34" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A34" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="B34" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C34" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D34" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="E34" s="2" t="s">
+        <v>6</v>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:F1" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
@@ -836,31 +1184,31 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<sisl xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns="http://www.boldonjames.com/2008/01/sie/internal/label" sislVersion="0" policy="dd20d239-a7e6-4c49-877c-45b7b43359cb" origin="defaultValue">
+  <element uid="5027ba01-e221-4650-87c9-b8eeda1feb2f" value=""/>
+</sisl>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <WrappedLabelHistory xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns="http://www.boldonjames.com/2016/02/Classifier/internal/wrappedLabelHistory">
   <Value>PD94bWwgdmVyc2lvbj0iMS4wIiBlbmNvZGluZz0idXMtYXNjaWkiPz48bGFiZWxIaXN0b3J5IHhtbG5zOnhzZD0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEiIHhtbG5zOnhzaT0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEtaW5zdGFuY2UiIHhtbG5zPSJodHRwOi8vd3d3LmJvbGRvbmphbWVzLmNvbS8yMDE2LzAyL0NsYXNzaWZpZXIvaW50ZXJuYWwvbGFiZWxIaXN0b3J5Ij48aXRlbT48c2lzbCBzaXNsVmVyc2lvbj0iMCIgcG9saWN5PSJkZDIwZDIzOS1hN2U2LTRjNDktODc3Yy00NWI3YjQzMzU5Y2IiIG9yaWdpbj0iZGVmYXVsdFZhbHVlIj48ZWxlbWVudCB1aWQ9IjUwMjdiYTAxLWUyMjEtNDY1MC04N2M5LWI4ZWVkYTFmZWIyZiIgdmFsdWU9IiIgeG1sbnM9Imh0dHA6Ly93d3cuYm9sZG9uamFtZXMuY29tLzIwMDgvMDEvc2llL2ludGVybmFsL2xhYmVsIiAvPjwvc2lzbD48VXNlck5hbWU+QUxMSUFOWlxCRTAwMTUxPC9Vc2VyTmFtZT48RGF0ZVRpbWU+MTcvMDkvMjAxOSAxODoxMjoxMjwvRGF0ZVRpbWU+PExhYmVsU3RyaW5nPiAgICAgICAxNy8wOS8yMDE5ICBJTlRFUk5PICA8L0xhYmVsU3RyaW5nPjwvaXRlbT48L2xhYmVsSGlzdG9yeT4=</Value>
 </WrappedLabelHistory>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<sisl xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns="http://www.boldonjames.com/2008/01/sie/internal/label" sislVersion="0" policy="dd20d239-a7e6-4c49-877c-45b7b43359cb" origin="defaultValue">
-  <element uid="5027ba01-e221-4650-87c9-b8eeda1feb2f" value=""/>
-</sisl>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{758EF150-7616-48C2-9614-E853EDB7BDD0}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
+    <ds:schemaRef ds:uri="http://www.boldonjames.com/2008/01/sie/internal/label"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D7CACE11-ACDB-4C58-86FC-5A54EABF64E3}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
     <ds:schemaRef ds:uri="http://www.boldonjames.com/2016/02/Classifier/internal/wrappedLabelHistory"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{758EF150-7616-48C2-9614-E853EDB7BDD0}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
-    <ds:schemaRef ds:uri="http://www.boldonjames.com/2008/01/sie/internal/label"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>
--- a/Data Files/Backoffce/IndexacaoFG/IndexacaoFG_SANTANDER.xlsx
+++ b/Data Files/Backoffce/IndexacaoFG/IndexacaoFG_SANTANDER.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Public\RPA_ALLIANZ_TREINAMENTO\Data Files\Backoffce\IndexacaoFG\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4029EF3B-C606-44B7-B7EB-94F0031E58A0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8DEA7C5D-8BD3-432A-A37E-2E283D9C291B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="20370" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1184,31 +1184,31 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<WrappedLabelHistory xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns="http://www.boldonjames.com/2016/02/Classifier/internal/wrappedLabelHistory">
+  <Value>PD94bWwgdmVyc2lvbj0iMS4wIiBlbmNvZGluZz0idXMtYXNjaWkiPz48bGFiZWxIaXN0b3J5IHhtbG5zOnhzZD0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEiIHhtbG5zOnhzaT0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEtaW5zdGFuY2UiIHhtbG5zPSJodHRwOi8vd3d3LmJvbGRvbmphbWVzLmNvbS8yMDE2LzAyL0NsYXNzaWZpZXIvaW50ZXJuYWwvbGFiZWxIaXN0b3J5Ij48aXRlbT48c2lzbCBzaXNsVmVyc2lvbj0iMCIgcG9saWN5PSJkZDIwZDIzOS1hN2U2LTRjNDktODc3Yy00NWI3YjQzMzU5Y2IiIG9yaWdpbj0iZGVmYXVsdFZhbHVlIj48ZWxlbWVudCB1aWQ9IjUwMjdiYTAxLWUyMjEtNDY1MC04N2M5LWI4ZWVkYTFmZWIyZiIgdmFsdWU9IiIgeG1sbnM9Imh0dHA6Ly93d3cuYm9sZG9uamFtZXMuY29tLzIwMDgvMDEvc2llL2ludGVybmFsL2xhYmVsIiAvPjwvc2lzbD48VXNlck5hbWU+QUxMSUFOWlxCRTAwMTUxPC9Vc2VyTmFtZT48RGF0ZVRpbWU+MTcvMDkvMjAxOSAxODoxMjoxMjwvRGF0ZVRpbWU+PExhYmVsU3RyaW5nPiAgICAgICAxNy8wOS8yMDE5ICBJTlRFUk5PICA8L0xhYmVsU3RyaW5nPjwvaXRlbT48L2xhYmVsSGlzdG9yeT4=</Value>
+</WrappedLabelHistory>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <sisl xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns="http://www.boldonjames.com/2008/01/sie/internal/label" sislVersion="0" policy="dd20d239-a7e6-4c49-877c-45b7b43359cb" origin="defaultValue">
   <element uid="5027ba01-e221-4650-87c9-b8eeda1feb2f" value=""/>
 </sisl>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<WrappedLabelHistory xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns="http://www.boldonjames.com/2016/02/Classifier/internal/wrappedLabelHistory">
-  <Value>PD94bWwgdmVyc2lvbj0iMS4wIiBlbmNvZGluZz0idXMtYXNjaWkiPz48bGFiZWxIaXN0b3J5IHhtbG5zOnhzZD0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEiIHhtbG5zOnhzaT0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEtaW5zdGFuY2UiIHhtbG5zPSJodHRwOi8vd3d3LmJvbGRvbmphbWVzLmNvbS8yMDE2LzAyL0NsYXNzaWZpZXIvaW50ZXJuYWwvbGFiZWxIaXN0b3J5Ij48aXRlbT48c2lzbCBzaXNsVmVyc2lvbj0iMCIgcG9saWN5PSJkZDIwZDIzOS1hN2U2LTRjNDktODc3Yy00NWI3YjQzMzU5Y2IiIG9yaWdpbj0iZGVmYXVsdFZhbHVlIj48ZWxlbWVudCB1aWQ9IjUwMjdiYTAxLWUyMjEtNDY1MC04N2M5LWI4ZWVkYTFmZWIyZiIgdmFsdWU9IiIgeG1sbnM9Imh0dHA6Ly93d3cuYm9sZG9uamFtZXMuY29tLzIwMDgvMDEvc2llL2ludGVybmFsL2xhYmVsIiAvPjwvc2lzbD48VXNlck5hbWU+QUxMSUFOWlxCRTAwMTUxPC9Vc2VyTmFtZT48RGF0ZVRpbWU+MTcvMDkvMjAxOSAxODoxMjoxMjwvRGF0ZVRpbWU+PExhYmVsU3RyaW5nPiAgICAgICAxNy8wOS8yMDE5ICBJTlRFUk5PICA8L0xhYmVsU3RyaW5nPjwvaXRlbT48L2xhYmVsSGlzdG9yeT4=</Value>
-</WrappedLabelHistory>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D7CACE11-ACDB-4C58-86FC-5A54EABF64E3}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
+    <ds:schemaRef ds:uri="http://www.boldonjames.com/2016/02/Classifier/internal/wrappedLabelHistory"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{758EF150-7616-48C2-9614-E853EDB7BDD0}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
     <ds:schemaRef ds:uri="http://www.boldonjames.com/2008/01/sie/internal/label"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D7CACE11-ACDB-4C58-86FC-5A54EABF64E3}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
-    <ds:schemaRef ds:uri="http://www.boldonjames.com/2016/02/Classifier/internal/wrappedLabelHistory"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>
--- a/Data Files/Backoffce/IndexacaoFG/IndexacaoFG_SANTANDER.xlsx
+++ b/Data Files/Backoffce/IndexacaoFG/IndexacaoFG_SANTANDER.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Public\RPA_ALLIANZ_TREINAMENTO\Data Files\Backoffce\IndexacaoFG\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8DEA7C5D-8BD3-432A-A37E-2E283D9C291B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8B7F936A-9770-48AA-A50F-780B3A133E39}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="20370" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="170" uniqueCount="42">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="140" uniqueCount="36">
   <si>
     <t xml:space="preserve">status </t>
   </si>
@@ -54,106 +54,88 @@
     <t>1070</t>
   </si>
   <si>
-    <t>Relatório de Recusas Santander - 06/10/2025</t>
-  </si>
-  <si>
-    <t>134652343</t>
-  </si>
-  <si>
-    <t>134658870</t>
-  </si>
-  <si>
-    <t>134667095</t>
-  </si>
-  <si>
-    <t>134671678</t>
-  </si>
-  <si>
-    <t>134665477</t>
-  </si>
-  <si>
-    <t>134652012</t>
-  </si>
-  <si>
-    <t>134656283</t>
-  </si>
-  <si>
-    <t>134654702</t>
-  </si>
-  <si>
-    <t>134652102</t>
-  </si>
-  <si>
-    <t>134698414</t>
-  </si>
-  <si>
-    <t>134701391</t>
-  </si>
-  <si>
-    <t>134703116</t>
-  </si>
-  <si>
-    <t>134713267</t>
-  </si>
-  <si>
-    <t>134681011</t>
-  </si>
-  <si>
-    <t>134756714</t>
-  </si>
-  <si>
-    <t>134770404</t>
-  </si>
-  <si>
-    <t>134598337</t>
-  </si>
-  <si>
-    <t>134665384</t>
-  </si>
-  <si>
-    <t>134662074</t>
-  </si>
-  <si>
-    <t>134660067</t>
-  </si>
-  <si>
-    <t>134692267</t>
-  </si>
-  <si>
-    <t>134651036</t>
-  </si>
-  <si>
-    <t>134652142</t>
-  </si>
-  <si>
-    <t>134652159</t>
-  </si>
-  <si>
-    <t>134652965</t>
-  </si>
-  <si>
-    <t>134655241</t>
-  </si>
-  <si>
-    <t>134658334</t>
-  </si>
-  <si>
-    <t>134658593</t>
-  </si>
-  <si>
-    <t>134662051</t>
-  </si>
-  <si>
-    <t>134665397</t>
-  </si>
-  <si>
-    <t>134668994</t>
-  </si>
-  <si>
-    <t>134669432</t>
-  </si>
-  <si>
     <t>Relatório de Recusas 06.10.2025 a 12.10.2025</t>
+  </si>
+  <si>
+    <t>Relatório de Recusas Santander - 07/10/2025</t>
+  </si>
+  <si>
+    <t>134683357</t>
+  </si>
+  <si>
+    <t>134689189</t>
+  </si>
+  <si>
+    <t>134691356</t>
+  </si>
+  <si>
+    <t>134691773</t>
+  </si>
+  <si>
+    <t>134680144</t>
+  </si>
+  <si>
+    <t>134711738</t>
+  </si>
+  <si>
+    <t>134720385</t>
+  </si>
+  <si>
+    <t>134755230</t>
+  </si>
+  <si>
+    <t>134775095</t>
+  </si>
+  <si>
+    <t>134772972</t>
+  </si>
+  <si>
+    <t>134770331</t>
+  </si>
+  <si>
+    <t>134757544</t>
+  </si>
+  <si>
+    <t>134623063</t>
+  </si>
+  <si>
+    <t>134680848</t>
+  </si>
+  <si>
+    <t>134681098</t>
+  </si>
+  <si>
+    <t>134683463</t>
+  </si>
+  <si>
+    <t>134684719</t>
+  </si>
+  <si>
+    <t>134679649</t>
+  </si>
+  <si>
+    <t>134687908</t>
+  </si>
+  <si>
+    <t>134688236</t>
+  </si>
+  <si>
+    <t>134688982</t>
+  </si>
+  <si>
+    <t>134689719</t>
+  </si>
+  <si>
+    <t>134689748</t>
+  </si>
+  <si>
+    <t>134692186</t>
+  </si>
+  <si>
+    <t>134694208</t>
+  </si>
+  <si>
+    <t>134621154</t>
   </si>
 </sst>
 </file>
@@ -558,7 +540,7 @@
   <sheetPr>
     <pageSetUpPr autoPageBreaks="0"/>
   </sheetPr>
-  <dimension ref="A1:F34"/>
+  <dimension ref="A1:F28"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="2" width="16.7109375" style="1" customWidth="1" collapsed="1"/>
@@ -590,16 +572,16 @@
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A2" s="6">
-        <v>134596935</v>
+        <v>134681507</v>
       </c>
       <c r="B2" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>41</v>
+        <v>8</v>
       </c>
       <c r="E2" s="2" t="s">
         <v>6</v>
@@ -608,16 +590,16 @@
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B3" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>41</v>
+        <v>8</v>
       </c>
       <c r="E3" s="2" t="s">
         <v>6</v>
@@ -626,16 +608,16 @@
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B4" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>41</v>
+        <v>8</v>
       </c>
       <c r="E4" s="2" t="s">
         <v>6</v>
@@ -644,16 +626,16 @@
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B5" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>41</v>
+        <v>8</v>
       </c>
       <c r="E5" s="2" t="s">
         <v>6</v>
@@ -662,16 +644,16 @@
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" s="1" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B6" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>41</v>
+        <v>8</v>
       </c>
       <c r="E6" s="2" t="s">
         <v>6</v>
@@ -680,16 +662,16 @@
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" s="1" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B7" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>41</v>
+        <v>8</v>
       </c>
       <c r="E7" s="2" t="s">
         <v>6</v>
@@ -698,16 +680,16 @@
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" s="1" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="B8" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>41</v>
+        <v>8</v>
       </c>
       <c r="E8" s="2" t="s">
         <v>6</v>
@@ -716,16 +698,16 @@
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B9" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>41</v>
+        <v>8</v>
       </c>
       <c r="E9" s="2" t="s">
         <v>6</v>
@@ -734,16 +716,16 @@
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A10" s="1" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="B10" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>41</v>
+        <v>8</v>
       </c>
       <c r="E10" s="2" t="s">
         <v>6</v>
@@ -752,16 +734,16 @@
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A11" s="1" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="B11" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>41</v>
+        <v>8</v>
       </c>
       <c r="E11" s="2" t="s">
         <v>6</v>
@@ -770,16 +752,16 @@
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A12" s="1" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B12" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>41</v>
+        <v>8</v>
       </c>
       <c r="E12" s="2" t="s">
         <v>6</v>
@@ -788,16 +770,16 @@
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A13" s="1" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B13" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>41</v>
+        <v>8</v>
       </c>
       <c r="E13" s="2" t="s">
         <v>6</v>
@@ -806,16 +788,16 @@
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A14" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B14" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>41</v>
+        <v>8</v>
       </c>
       <c r="E14" s="2" t="s">
         <v>6</v>
@@ -824,16 +806,16 @@
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A15" s="1" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="B15" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>41</v>
+        <v>8</v>
       </c>
       <c r="E15" s="2" t="s">
         <v>6</v>
@@ -842,16 +824,16 @@
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A16" s="1" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B16" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>41</v>
+        <v>8</v>
       </c>
       <c r="E16" s="2" t="s">
         <v>6</v>
@@ -860,16 +842,16 @@
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A17" s="1" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="B17" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>41</v>
+        <v>8</v>
       </c>
       <c r="E17" s="2" t="s">
         <v>6</v>
@@ -878,16 +860,16 @@
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A18" s="1" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="B18" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>41</v>
+        <v>8</v>
       </c>
       <c r="E18" s="2" t="s">
         <v>6</v>
@@ -896,16 +878,16 @@
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A19" s="1" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="B19" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>41</v>
+        <v>8</v>
       </c>
       <c r="E19" s="2" t="s">
         <v>6</v>
@@ -914,16 +896,16 @@
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A20" s="1" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="B20" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>41</v>
+        <v>8</v>
       </c>
       <c r="E20" s="2" t="s">
         <v>6</v>
@@ -932,16 +914,16 @@
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A21" s="1" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="B21" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>41</v>
+        <v>8</v>
       </c>
       <c r="E21" s="2" t="s">
         <v>6</v>
@@ -950,16 +932,16 @@
     </row>
     <row r="22" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A22" s="1" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="B22" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>41</v>
+        <v>8</v>
       </c>
       <c r="E22" s="2" t="s">
         <v>6</v>
@@ -968,16 +950,16 @@
     </row>
     <row r="23" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A23" s="1" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B23" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>41</v>
+        <v>8</v>
       </c>
       <c r="E23" s="2" t="s">
         <v>6</v>
@@ -985,16 +967,16 @@
     </row>
     <row r="24" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A24" s="1" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B24" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C24" s="2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>41</v>
+        <v>8</v>
       </c>
       <c r="E24" s="2" t="s">
         <v>6</v>
@@ -1002,16 +984,16 @@
     </row>
     <row r="25" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A25" s="1" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="B25" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C25" s="2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D25" s="2" t="s">
-        <v>41</v>
+        <v>8</v>
       </c>
       <c r="E25" s="2" t="s">
         <v>6</v>
@@ -1019,16 +1001,16 @@
     </row>
     <row r="26" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A26" s="1" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="B26" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C26" s="2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D26" s="2" t="s">
-        <v>41</v>
+        <v>8</v>
       </c>
       <c r="E26" s="2" t="s">
         <v>6</v>
@@ -1036,16 +1018,16 @@
     </row>
     <row r="27" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A27" s="1" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B27" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C27" s="2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D27" s="2" t="s">
-        <v>41</v>
+        <v>8</v>
       </c>
       <c r="E27" s="2" t="s">
         <v>6</v>
@@ -1053,120 +1035,18 @@
     </row>
     <row r="28" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A28" s="1" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="B28" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C28" s="2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D28" s="2" t="s">
-        <v>41</v>
+        <v>8</v>
       </c>
       <c r="E28" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="29" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A29" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="B29" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C29" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="D29" s="2" t="s">
-        <v>41</v>
-      </c>
-      <c r="E29" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="30" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A30" s="1" t="s">
-        <v>36</v>
-      </c>
-      <c r="B30" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C30" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="D30" s="2" t="s">
-        <v>41</v>
-      </c>
-      <c r="E30" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="31" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A31" s="1" t="s">
-        <v>37</v>
-      </c>
-      <c r="B31" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C31" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="D31" s="2" t="s">
-        <v>41</v>
-      </c>
-      <c r="E31" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="32" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A32" s="1" t="s">
-        <v>38</v>
-      </c>
-      <c r="B32" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C32" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="D32" s="2" t="s">
-        <v>41</v>
-      </c>
-      <c r="E32" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="33" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A33" s="1" t="s">
-        <v>39</v>
-      </c>
-      <c r="B33" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C33" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="D33" s="2" t="s">
-        <v>41</v>
-      </c>
-      <c r="E33" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="34" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A34" s="1" t="s">
-        <v>40</v>
-      </c>
-      <c r="B34" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C34" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="D34" s="2" t="s">
-        <v>41</v>
-      </c>
-      <c r="E34" s="2" t="s">
         <v>6</v>
       </c>
     </row>
@@ -1184,31 +1064,31 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<sisl xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns="http://www.boldonjames.com/2008/01/sie/internal/label" sislVersion="0" policy="dd20d239-a7e6-4c49-877c-45b7b43359cb" origin="defaultValue">
+  <element uid="5027ba01-e221-4650-87c9-b8eeda1feb2f" value=""/>
+</sisl>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <WrappedLabelHistory xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns="http://www.boldonjames.com/2016/02/Classifier/internal/wrappedLabelHistory">
   <Value>PD94bWwgdmVyc2lvbj0iMS4wIiBlbmNvZGluZz0idXMtYXNjaWkiPz48bGFiZWxIaXN0b3J5IHhtbG5zOnhzZD0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEiIHhtbG5zOnhzaT0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEtaW5zdGFuY2UiIHhtbG5zPSJodHRwOi8vd3d3LmJvbGRvbmphbWVzLmNvbS8yMDE2LzAyL0NsYXNzaWZpZXIvaW50ZXJuYWwvbGFiZWxIaXN0b3J5Ij48aXRlbT48c2lzbCBzaXNsVmVyc2lvbj0iMCIgcG9saWN5PSJkZDIwZDIzOS1hN2U2LTRjNDktODc3Yy00NWI3YjQzMzU5Y2IiIG9yaWdpbj0iZGVmYXVsdFZhbHVlIj48ZWxlbWVudCB1aWQ9IjUwMjdiYTAxLWUyMjEtNDY1MC04N2M5LWI4ZWVkYTFmZWIyZiIgdmFsdWU9IiIgeG1sbnM9Imh0dHA6Ly93d3cuYm9sZG9uamFtZXMuY29tLzIwMDgvMDEvc2llL2ludGVybmFsL2xhYmVsIiAvPjwvc2lzbD48VXNlck5hbWU+QUxMSUFOWlxCRTAwMTUxPC9Vc2VyTmFtZT48RGF0ZVRpbWU+MTcvMDkvMjAxOSAxODoxMjoxMjwvRGF0ZVRpbWU+PExhYmVsU3RyaW5nPiAgICAgICAxNy8wOS8yMDE5ICBJTlRFUk5PICA8L0xhYmVsU3RyaW5nPjwvaXRlbT48L2xhYmVsSGlzdG9yeT4=</Value>
 </WrappedLabelHistory>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<sisl xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns="http://www.boldonjames.com/2008/01/sie/internal/label" sislVersion="0" policy="dd20d239-a7e6-4c49-877c-45b7b43359cb" origin="defaultValue">
-  <element uid="5027ba01-e221-4650-87c9-b8eeda1feb2f" value=""/>
-</sisl>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{758EF150-7616-48C2-9614-E853EDB7BDD0}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
+    <ds:schemaRef ds:uri="http://www.boldonjames.com/2008/01/sie/internal/label"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D7CACE11-ACDB-4C58-86FC-5A54EABF64E3}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
     <ds:schemaRef ds:uri="http://www.boldonjames.com/2016/02/Classifier/internal/wrappedLabelHistory"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{758EF150-7616-48C2-9614-E853EDB7BDD0}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
-    <ds:schemaRef ds:uri="http://www.boldonjames.com/2008/01/sie/internal/label"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>
--- a/Data Files/Backoffce/IndexacaoFG/IndexacaoFG_SANTANDER.xlsx
+++ b/Data Files/Backoffce/IndexacaoFG/IndexacaoFG_SANTANDER.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Public\RPA_ALLIANZ_TREINAMENTO\Data Files\Backoffce\IndexacaoFG\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8B7F936A-9770-48AA-A50F-780B3A133E39}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4DC6A1AF-B0A5-41C3-A3CF-A0D67A9A999F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="20370" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1064,31 +1064,31 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<WrappedLabelHistory xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns="http://www.boldonjames.com/2016/02/Classifier/internal/wrappedLabelHistory">
+  <Value>PD94bWwgdmVyc2lvbj0iMS4wIiBlbmNvZGluZz0idXMtYXNjaWkiPz48bGFiZWxIaXN0b3J5IHhtbG5zOnhzZD0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEiIHhtbG5zOnhzaT0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEtaW5zdGFuY2UiIHhtbG5zPSJodHRwOi8vd3d3LmJvbGRvbmphbWVzLmNvbS8yMDE2LzAyL0NsYXNzaWZpZXIvaW50ZXJuYWwvbGFiZWxIaXN0b3J5Ij48aXRlbT48c2lzbCBzaXNsVmVyc2lvbj0iMCIgcG9saWN5PSJkZDIwZDIzOS1hN2U2LTRjNDktODc3Yy00NWI3YjQzMzU5Y2IiIG9yaWdpbj0iZGVmYXVsdFZhbHVlIj48ZWxlbWVudCB1aWQ9IjUwMjdiYTAxLWUyMjEtNDY1MC04N2M5LWI4ZWVkYTFmZWIyZiIgdmFsdWU9IiIgeG1sbnM9Imh0dHA6Ly93d3cuYm9sZG9uamFtZXMuY29tLzIwMDgvMDEvc2llL2ludGVybmFsL2xhYmVsIiAvPjwvc2lzbD48VXNlck5hbWU+QUxMSUFOWlxCRTAwMTUxPC9Vc2VyTmFtZT48RGF0ZVRpbWU+MTcvMDkvMjAxOSAxODoxMjoxMjwvRGF0ZVRpbWU+PExhYmVsU3RyaW5nPiAgICAgICAxNy8wOS8yMDE5ICBJTlRFUk5PICA8L0xhYmVsU3RyaW5nPjwvaXRlbT48L2xhYmVsSGlzdG9yeT4=</Value>
+</WrappedLabelHistory>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <sisl xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns="http://www.boldonjames.com/2008/01/sie/internal/label" sislVersion="0" policy="dd20d239-a7e6-4c49-877c-45b7b43359cb" origin="defaultValue">
   <element uid="5027ba01-e221-4650-87c9-b8eeda1feb2f" value=""/>
 </sisl>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<WrappedLabelHistory xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns="http://www.boldonjames.com/2016/02/Classifier/internal/wrappedLabelHistory">
-  <Value>PD94bWwgdmVyc2lvbj0iMS4wIiBlbmNvZGluZz0idXMtYXNjaWkiPz48bGFiZWxIaXN0b3J5IHhtbG5zOnhzZD0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEiIHhtbG5zOnhzaT0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEtaW5zdGFuY2UiIHhtbG5zPSJodHRwOi8vd3d3LmJvbGRvbmphbWVzLmNvbS8yMDE2LzAyL0NsYXNzaWZpZXIvaW50ZXJuYWwvbGFiZWxIaXN0b3J5Ij48aXRlbT48c2lzbCBzaXNsVmVyc2lvbj0iMCIgcG9saWN5PSJkZDIwZDIzOS1hN2U2LTRjNDktODc3Yy00NWI3YjQzMzU5Y2IiIG9yaWdpbj0iZGVmYXVsdFZhbHVlIj48ZWxlbWVudCB1aWQ9IjUwMjdiYTAxLWUyMjEtNDY1MC04N2M5LWI4ZWVkYTFmZWIyZiIgdmFsdWU9IiIgeG1sbnM9Imh0dHA6Ly93d3cuYm9sZG9uamFtZXMuY29tLzIwMDgvMDEvc2llL2ludGVybmFsL2xhYmVsIiAvPjwvc2lzbD48VXNlck5hbWU+QUxMSUFOWlxCRTAwMTUxPC9Vc2VyTmFtZT48RGF0ZVRpbWU+MTcvMDkvMjAxOSAxODoxMjoxMjwvRGF0ZVRpbWU+PExhYmVsU3RyaW5nPiAgICAgICAxNy8wOS8yMDE5ICBJTlRFUk5PICA8L0xhYmVsU3RyaW5nPjwvaXRlbT48L2xhYmVsSGlzdG9yeT4=</Value>
-</WrappedLabelHistory>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D7CACE11-ACDB-4C58-86FC-5A54EABF64E3}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
+    <ds:schemaRef ds:uri="http://www.boldonjames.com/2016/02/Classifier/internal/wrappedLabelHistory"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{758EF150-7616-48C2-9614-E853EDB7BDD0}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
     <ds:schemaRef ds:uri="http://www.boldonjames.com/2008/01/sie/internal/label"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D7CACE11-ACDB-4C58-86FC-5A54EABF64E3}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
-    <ds:schemaRef ds:uri="http://www.boldonjames.com/2016/02/Classifier/internal/wrappedLabelHistory"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>
--- a/Data Files/Backoffce/IndexacaoFG/IndexacaoFG_SANTANDER.xlsx
+++ b/Data Files/Backoffce/IndexacaoFG/IndexacaoFG_SANTANDER.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Public\RPA_ALLIANZ_TREINAMENTO\Data Files\Backoffce\IndexacaoFG\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4DC6A1AF-B0A5-41C3-A3CF-A0D67A9A999F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{836B2536-58D8-4C7B-B48A-22807503D795}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="20370" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="140" uniqueCount="36">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="100" uniqueCount="28">
   <si>
     <t xml:space="preserve">status </t>
   </si>
@@ -57,85 +57,61 @@
     <t>Relatório de Recusas 06.10.2025 a 12.10.2025</t>
   </si>
   <si>
-    <t>Relatório de Recusas Santander - 07/10/2025</t>
-  </si>
-  <si>
-    <t>134683357</t>
-  </si>
-  <si>
-    <t>134689189</t>
-  </si>
-  <si>
-    <t>134691356</t>
-  </si>
-  <si>
-    <t>134691773</t>
-  </si>
-  <si>
-    <t>134680144</t>
-  </si>
-  <si>
-    <t>134711738</t>
-  </si>
-  <si>
-    <t>134720385</t>
-  </si>
-  <si>
-    <t>134755230</t>
-  </si>
-  <si>
-    <t>134775095</t>
-  </si>
-  <si>
-    <t>134772972</t>
-  </si>
-  <si>
-    <t>134770331</t>
-  </si>
-  <si>
-    <t>134757544</t>
-  </si>
-  <si>
-    <t>134623063</t>
-  </si>
-  <si>
-    <t>134680848</t>
-  </si>
-  <si>
-    <t>134681098</t>
-  </si>
-  <si>
-    <t>134683463</t>
-  </si>
-  <si>
-    <t>134684719</t>
-  </si>
-  <si>
-    <t>134679649</t>
-  </si>
-  <si>
-    <t>134687908</t>
-  </si>
-  <si>
-    <t>134688236</t>
-  </si>
-  <si>
-    <t>134688982</t>
-  </si>
-  <si>
-    <t>134689719</t>
-  </si>
-  <si>
-    <t>134689748</t>
-  </si>
-  <si>
-    <t>134692186</t>
-  </si>
-  <si>
-    <t>134694208</t>
-  </si>
-  <si>
-    <t>134621154</t>
+    <t>Relatório de Recusas Santander - 08/10/2025</t>
+  </si>
+  <si>
+    <t>134693268</t>
+  </si>
+  <si>
+    <t>134715792</t>
+  </si>
+  <si>
+    <t>134716555</t>
+  </si>
+  <si>
+    <t>134723358</t>
+  </si>
+  <si>
+    <t>134707736</t>
+  </si>
+  <si>
+    <t>134757273</t>
+  </si>
+  <si>
+    <t>134783975</t>
+  </si>
+  <si>
+    <t>134806114</t>
+  </si>
+  <si>
+    <t>134633677</t>
+  </si>
+  <si>
+    <t>134633366</t>
+  </si>
+  <si>
+    <t>134701456</t>
+  </si>
+  <si>
+    <t>134707976</t>
+  </si>
+  <si>
+    <t>134640712</t>
+  </si>
+  <si>
+    <t>134713489</t>
+  </si>
+  <si>
+    <t>134716459</t>
+  </si>
+  <si>
+    <t>134705705</t>
+  </si>
+  <si>
+    <t>134800087</t>
+  </si>
+  <si>
+    <t>134700416</t>
   </si>
 </sst>
 </file>
@@ -540,7 +516,7 @@
   <sheetPr>
     <pageSetUpPr autoPageBreaks="0"/>
   </sheetPr>
-  <dimension ref="A1:F28"/>
+  <dimension ref="A1:F22"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="2" width="16.7109375" style="1" customWidth="1" collapsed="1"/>
@@ -572,7 +548,7 @@
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A2" s="6">
-        <v>134681507</v>
+        <v>134646233</v>
       </c>
       <c r="B2" s="1" t="s">
         <v>7</v>
@@ -913,142 +889,10 @@
       <c r="F20"/>
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A21" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="B21" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C21" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D21" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="E21" s="2" t="s">
-        <v>6</v>
-      </c>
       <c r="F21"/>
     </row>
     <row r="22" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A22" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="B22" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C22" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D22" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="E22" s="2" t="s">
-        <v>6</v>
-      </c>
       <c r="F22"/>
-    </row>
-    <row r="23" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A23" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="B23" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C23" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D23" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="E23" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="24" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A24" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="B24" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C24" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D24" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="E24" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="25" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A25" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="B25" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C25" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D25" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="E25" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="26" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A26" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="B26" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C26" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D26" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="E26" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="27" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A27" s="1" t="s">
-        <v>34</v>
-      </c>
-      <c r="B27" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C27" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D27" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="E27" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="28" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A28" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="B28" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C28" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D28" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="E28" s="2" t="s">
-        <v>6</v>
-      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:F1" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
@@ -1064,31 +908,31 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<sisl xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns="http://www.boldonjames.com/2008/01/sie/internal/label" sislVersion="0" policy="dd20d239-a7e6-4c49-877c-45b7b43359cb" origin="defaultValue">
+  <element uid="5027ba01-e221-4650-87c9-b8eeda1feb2f" value=""/>
+</sisl>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <WrappedLabelHistory xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns="http://www.boldonjames.com/2016/02/Classifier/internal/wrappedLabelHistory">
   <Value>PD94bWwgdmVyc2lvbj0iMS4wIiBlbmNvZGluZz0idXMtYXNjaWkiPz48bGFiZWxIaXN0b3J5IHhtbG5zOnhzZD0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEiIHhtbG5zOnhzaT0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEtaW5zdGFuY2UiIHhtbG5zPSJodHRwOi8vd3d3LmJvbGRvbmphbWVzLmNvbS8yMDE2LzAyL0NsYXNzaWZpZXIvaW50ZXJuYWwvbGFiZWxIaXN0b3J5Ij48aXRlbT48c2lzbCBzaXNsVmVyc2lvbj0iMCIgcG9saWN5PSJkZDIwZDIzOS1hN2U2LTRjNDktODc3Yy00NWI3YjQzMzU5Y2IiIG9yaWdpbj0iZGVmYXVsdFZhbHVlIj48ZWxlbWVudCB1aWQ9IjUwMjdiYTAxLWUyMjEtNDY1MC04N2M5LWI4ZWVkYTFmZWIyZiIgdmFsdWU9IiIgeG1sbnM9Imh0dHA6Ly93d3cuYm9sZG9uamFtZXMuY29tLzIwMDgvMDEvc2llL2ludGVybmFsL2xhYmVsIiAvPjwvc2lzbD48VXNlck5hbWU+QUxMSUFOWlxCRTAwMTUxPC9Vc2VyTmFtZT48RGF0ZVRpbWU+MTcvMDkvMjAxOSAxODoxMjoxMjwvRGF0ZVRpbWU+PExhYmVsU3RyaW5nPiAgICAgICAxNy8wOS8yMDE5ICBJTlRFUk5PICA8L0xhYmVsU3RyaW5nPjwvaXRlbT48L2xhYmVsSGlzdG9yeT4=</Value>
 </WrappedLabelHistory>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<sisl xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns="http://www.boldonjames.com/2008/01/sie/internal/label" sislVersion="0" policy="dd20d239-a7e6-4c49-877c-45b7b43359cb" origin="defaultValue">
-  <element uid="5027ba01-e221-4650-87c9-b8eeda1feb2f" value=""/>
-</sisl>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{758EF150-7616-48C2-9614-E853EDB7BDD0}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
+    <ds:schemaRef ds:uri="http://www.boldonjames.com/2008/01/sie/internal/label"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D7CACE11-ACDB-4C58-86FC-5A54EABF64E3}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
     <ds:schemaRef ds:uri="http://www.boldonjames.com/2016/02/Classifier/internal/wrappedLabelHistory"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{758EF150-7616-48C2-9614-E853EDB7BDD0}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
-    <ds:schemaRef ds:uri="http://www.boldonjames.com/2008/01/sie/internal/label"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>
--- a/Data Files/Backoffce/IndexacaoFG/IndexacaoFG_SANTANDER.xlsx
+++ b/Data Files/Backoffce/IndexacaoFG/IndexacaoFG_SANTANDER.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Public\RPA_ALLIANZ_TREINAMENTO\Data Files\Backoffce\IndexacaoFG\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{836B2536-58D8-4C7B-B48A-22807503D795}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3535EF7C-EC95-4872-AF95-052C8D33405B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="20370" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="100" uniqueCount="28">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="295" uniqueCount="67">
   <si>
     <t xml:space="preserve">status </t>
   </si>
@@ -57,61 +57,178 @@
     <t>Relatório de Recusas 06.10.2025 a 12.10.2025</t>
   </si>
   <si>
-    <t>Relatório de Recusas Santander - 08/10/2025</t>
-  </si>
-  <si>
-    <t>134693268</t>
-  </si>
-  <si>
-    <t>134715792</t>
-  </si>
-  <si>
-    <t>134716555</t>
-  </si>
-  <si>
-    <t>134723358</t>
-  </si>
-  <si>
-    <t>134707736</t>
-  </si>
-  <si>
-    <t>134757273</t>
-  </si>
-  <si>
-    <t>134783975</t>
-  </si>
-  <si>
-    <t>134806114</t>
-  </si>
-  <si>
-    <t>134633677</t>
-  </si>
-  <si>
-    <t>134633366</t>
-  </si>
-  <si>
-    <t>134701456</t>
-  </si>
-  <si>
-    <t>134707976</t>
-  </si>
-  <si>
-    <t>134640712</t>
-  </si>
-  <si>
-    <t>134713489</t>
-  </si>
-  <si>
-    <t>134716459</t>
-  </si>
-  <si>
-    <t>134705705</t>
-  </si>
-  <si>
-    <t>134800087</t>
-  </si>
-  <si>
-    <t>134700416</t>
+    <t>Relatório de Recusas Santander - 09/10/2025</t>
+  </si>
+  <si>
+    <t>134705802</t>
+  </si>
+  <si>
+    <t>134705973</t>
+  </si>
+  <si>
+    <t>134714627</t>
+  </si>
+  <si>
+    <t>134705558</t>
+  </si>
+  <si>
+    <t>134711717</t>
+  </si>
+  <si>
+    <t>134713506</t>
+  </si>
+  <si>
+    <t>134714325</t>
+  </si>
+  <si>
+    <t>134701829</t>
+  </si>
+  <si>
+    <t>134716592</t>
+  </si>
+  <si>
+    <t>134720289</t>
+  </si>
+  <si>
+    <t>134704471</t>
+  </si>
+  <si>
+    <t>134721001</t>
+  </si>
+  <si>
+    <t>134731096</t>
+  </si>
+  <si>
+    <t>134739126</t>
+  </si>
+  <si>
+    <t>134721872</t>
+  </si>
+  <si>
+    <t>134725472</t>
+  </si>
+  <si>
+    <t>134733874</t>
+  </si>
+  <si>
+    <t>134702759</t>
+  </si>
+  <si>
+    <t>134710734</t>
+  </si>
+  <si>
+    <t>134707685</t>
+  </si>
+  <si>
+    <t>134700667</t>
+  </si>
+  <si>
+    <t>134797684</t>
+  </si>
+  <si>
+    <t>134825913</t>
+  </si>
+  <si>
+    <t>134826970</t>
+  </si>
+  <si>
+    <t>134735996</t>
+  </si>
+  <si>
+    <t>134700854</t>
+  </si>
+  <si>
+    <t>134833192</t>
+  </si>
+  <si>
+    <t>134839517</t>
+  </si>
+  <si>
+    <t>134712612</t>
+  </si>
+  <si>
+    <t>134661083</t>
+  </si>
+  <si>
+    <t>134704437</t>
+  </si>
+  <si>
+    <t>134707055</t>
+  </si>
+  <si>
+    <t>134708678</t>
+  </si>
+  <si>
+    <t>134709137</t>
+  </si>
+  <si>
+    <t>134710928</t>
+  </si>
+  <si>
+    <t>134711937</t>
+  </si>
+  <si>
+    <t>134712402</t>
+  </si>
+  <si>
+    <t>134713194</t>
+  </si>
+  <si>
+    <t>134713216</t>
+  </si>
+  <si>
+    <t>134714456</t>
+  </si>
+  <si>
+    <t>134714566</t>
+  </si>
+  <si>
+    <t>134714660</t>
+  </si>
+  <si>
+    <t>134714887</t>
+  </si>
+  <si>
+    <t>134715302</t>
+  </si>
+  <si>
+    <t>134715732</t>
+  </si>
+  <si>
+    <t>134667986</t>
+  </si>
+  <si>
+    <t>134857082</t>
+  </si>
+  <si>
+    <t>134722366</t>
+  </si>
+  <si>
+    <t>134724022</t>
+  </si>
+  <si>
+    <t>134724143</t>
+  </si>
+  <si>
+    <t>134727296</t>
+  </si>
+  <si>
+    <t>134727457</t>
+  </si>
+  <si>
+    <t>134727484</t>
+  </si>
+  <si>
+    <t>134727605</t>
+  </si>
+  <si>
+    <t>134727680</t>
+  </si>
+  <si>
+    <t>134728030</t>
+  </si>
+  <si>
+    <t>134732752</t>
   </si>
 </sst>
 </file>
@@ -516,7 +633,7 @@
   <sheetPr>
     <pageSetUpPr autoPageBreaks="0"/>
   </sheetPr>
-  <dimension ref="A1:F22"/>
+  <dimension ref="A1:F59"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="2" width="16.7109375" style="1" customWidth="1" collapsed="1"/>
@@ -548,7 +665,7 @@
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A2" s="6">
-        <v>134646233</v>
+        <v>134696628</v>
       </c>
       <c r="B2" s="1" t="s">
         <v>7</v>
@@ -889,10 +1006,669 @@
       <c r="F20"/>
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A21" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="B21" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C21" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D21" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E21" s="2" t="s">
+        <v>6</v>
+      </c>
       <c r="F21"/>
     </row>
     <row r="22" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A22" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="B22" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C22" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D22" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E22" s="2" t="s">
+        <v>6</v>
+      </c>
       <c r="F22"/>
+    </row>
+    <row r="23" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A23" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="B23" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C23" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D23" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E23" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="24" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A24" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="B24" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C24" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D24" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E24" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="25" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A25" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="B25" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C25" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D25" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E25" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="26" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A26" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="B26" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C26" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D26" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E26" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="27" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A27" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="B27" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C27" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D27" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E27" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="28" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A28" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="B28" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C28" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D28" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E28" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="29" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A29" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="B29" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C29" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D29" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E29" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="30" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A30" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="B30" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C30" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D30" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E30" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="31" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A31" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="B31" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C31" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D31" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E31" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="32" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A32" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="B32" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C32" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D32" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E32" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="33" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A33" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="B33" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C33" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D33" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E33" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="34" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A34" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="B34" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C34" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D34" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E34" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="35" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A35" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="B35" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C35" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D35" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E35" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="36" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A36" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="B36" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C36" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D36" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E36" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="37" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A37" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="B37" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C37" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D37" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E37" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="38" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A38" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="B38" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C38" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D38" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E38" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="39" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A39" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="B39" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C39" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D39" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E39" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="40" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A40" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="B40" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C40" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D40" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E40" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="41" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A41" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="B41" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C41" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D41" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E41" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="42" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A42" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="B42" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C42" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D42" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E42" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="43" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A43" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="B43" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C43" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D43" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E43" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="44" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A44" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="B44" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C44" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D44" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E44" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="45" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A45" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="B45" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C45" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D45" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E45" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="46" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A46" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="B46" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C46" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D46" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E46" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="47" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A47" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="B47" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C47" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D47" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E47" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="48" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A48" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="B48" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C48" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D48" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E48" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="49" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A49" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="B49" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C49" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D49" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E49" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="50" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A50" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="B50" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C50" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D50" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E50" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="51" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A51" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="B51" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C51" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D51" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E51" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="52" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A52" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="B52" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C52" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D52" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E52" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="53" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A53" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="B53" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C53" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D53" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E53" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="54" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A54" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="B54" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C54" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D54" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E54" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="55" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A55" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="B55" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C55" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D55" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E55" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="56" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A56" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="B56" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C56" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D56" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E56" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="57" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A57" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="B57" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C57" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D57" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E57" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="58" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A58" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="B58" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C58" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D58" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E58" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="59" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A59" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="B59" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C59" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D59" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E59" s="2" t="s">
+        <v>6</v>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:F1" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
@@ -908,31 +1684,31 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<WrappedLabelHistory xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns="http://www.boldonjames.com/2016/02/Classifier/internal/wrappedLabelHistory">
+  <Value>PD94bWwgdmVyc2lvbj0iMS4wIiBlbmNvZGluZz0idXMtYXNjaWkiPz48bGFiZWxIaXN0b3J5IHhtbG5zOnhzZD0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEiIHhtbG5zOnhzaT0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEtaW5zdGFuY2UiIHhtbG5zPSJodHRwOi8vd3d3LmJvbGRvbmphbWVzLmNvbS8yMDE2LzAyL0NsYXNzaWZpZXIvaW50ZXJuYWwvbGFiZWxIaXN0b3J5Ij48aXRlbT48c2lzbCBzaXNsVmVyc2lvbj0iMCIgcG9saWN5PSJkZDIwZDIzOS1hN2U2LTRjNDktODc3Yy00NWI3YjQzMzU5Y2IiIG9yaWdpbj0iZGVmYXVsdFZhbHVlIj48ZWxlbWVudCB1aWQ9IjUwMjdiYTAxLWUyMjEtNDY1MC04N2M5LWI4ZWVkYTFmZWIyZiIgdmFsdWU9IiIgeG1sbnM9Imh0dHA6Ly93d3cuYm9sZG9uamFtZXMuY29tLzIwMDgvMDEvc2llL2ludGVybmFsL2xhYmVsIiAvPjwvc2lzbD48VXNlck5hbWU+QUxMSUFOWlxCRTAwMTUxPC9Vc2VyTmFtZT48RGF0ZVRpbWU+MTcvMDkvMjAxOSAxODoxMjoxMjwvRGF0ZVRpbWU+PExhYmVsU3RyaW5nPiAgICAgICAxNy8wOS8yMDE5ICBJTlRFUk5PICA8L0xhYmVsU3RyaW5nPjwvaXRlbT48L2xhYmVsSGlzdG9yeT4=</Value>
+</WrappedLabelHistory>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <sisl xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns="http://www.boldonjames.com/2008/01/sie/internal/label" sislVersion="0" policy="dd20d239-a7e6-4c49-877c-45b7b43359cb" origin="defaultValue">
   <element uid="5027ba01-e221-4650-87c9-b8eeda1feb2f" value=""/>
 </sisl>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<WrappedLabelHistory xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns="http://www.boldonjames.com/2016/02/Classifier/internal/wrappedLabelHistory">
-  <Value>PD94bWwgdmVyc2lvbj0iMS4wIiBlbmNvZGluZz0idXMtYXNjaWkiPz48bGFiZWxIaXN0b3J5IHhtbG5zOnhzZD0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEiIHhtbG5zOnhzaT0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEtaW5zdGFuY2UiIHhtbG5zPSJodHRwOi8vd3d3LmJvbGRvbmphbWVzLmNvbS8yMDE2LzAyL0NsYXNzaWZpZXIvaW50ZXJuYWwvbGFiZWxIaXN0b3J5Ij48aXRlbT48c2lzbCBzaXNsVmVyc2lvbj0iMCIgcG9saWN5PSJkZDIwZDIzOS1hN2U2LTRjNDktODc3Yy00NWI3YjQzMzU5Y2IiIG9yaWdpbj0iZGVmYXVsdFZhbHVlIj48ZWxlbWVudCB1aWQ9IjUwMjdiYTAxLWUyMjEtNDY1MC04N2M5LWI4ZWVkYTFmZWIyZiIgdmFsdWU9IiIgeG1sbnM9Imh0dHA6Ly93d3cuYm9sZG9uamFtZXMuY29tLzIwMDgvMDEvc2llL2ludGVybmFsL2xhYmVsIiAvPjwvc2lzbD48VXNlck5hbWU+QUxMSUFOWlxCRTAwMTUxPC9Vc2VyTmFtZT48RGF0ZVRpbWU+MTcvMDkvMjAxOSAxODoxMjoxMjwvRGF0ZVRpbWU+PExhYmVsU3RyaW5nPiAgICAgICAxNy8wOS8yMDE5ICBJTlRFUk5PICA8L0xhYmVsU3RyaW5nPjwvaXRlbT48L2xhYmVsSGlzdG9yeT4=</Value>
-</WrappedLabelHistory>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D7CACE11-ACDB-4C58-86FC-5A54EABF64E3}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
+    <ds:schemaRef ds:uri="http://www.boldonjames.com/2016/02/Classifier/internal/wrappedLabelHistory"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{758EF150-7616-48C2-9614-E853EDB7BDD0}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
     <ds:schemaRef ds:uri="http://www.boldonjames.com/2008/01/sie/internal/label"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D7CACE11-ACDB-4C58-86FC-5A54EABF64E3}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
-    <ds:schemaRef ds:uri="http://www.boldonjames.com/2016/02/Classifier/internal/wrappedLabelHistory"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>
--- a/Data Files/Backoffce/IndexacaoFG/IndexacaoFG_SANTANDER.xlsx
+++ b/Data Files/Backoffce/IndexacaoFG/IndexacaoFG_SANTANDER.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Public\RPA_ALLIANZ_TREINAMENTO\Data Files\Backoffce\IndexacaoFG\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3535EF7C-EC95-4872-AF95-052C8D33405B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F84C1EDC-FE90-4237-A091-9140CB6B3E18}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="20370" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="295" uniqueCount="67">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="145" uniqueCount="37">
   <si>
     <t xml:space="preserve">status </t>
   </si>
@@ -57,178 +57,88 @@
     <t>Relatório de Recusas 06.10.2025 a 12.10.2025</t>
   </si>
   <si>
-    <t>Relatório de Recusas Santander - 09/10/2025</t>
-  </si>
-  <si>
-    <t>134705802</t>
-  </si>
-  <si>
-    <t>134705973</t>
-  </si>
-  <si>
-    <t>134714627</t>
-  </si>
-  <si>
-    <t>134705558</t>
-  </si>
-  <si>
-    <t>134711717</t>
-  </si>
-  <si>
-    <t>134713506</t>
-  </si>
-  <si>
-    <t>134714325</t>
-  </si>
-  <si>
-    <t>134701829</t>
-  </si>
-  <si>
-    <t>134716592</t>
-  </si>
-  <si>
-    <t>134720289</t>
-  </si>
-  <si>
-    <t>134704471</t>
-  </si>
-  <si>
-    <t>134721001</t>
-  </si>
-  <si>
-    <t>134731096</t>
-  </si>
-  <si>
-    <t>134739126</t>
-  </si>
-  <si>
-    <t>134721872</t>
-  </si>
-  <si>
-    <t>134725472</t>
-  </si>
-  <si>
-    <t>134733874</t>
-  </si>
-  <si>
-    <t>134702759</t>
-  </si>
-  <si>
-    <t>134710734</t>
-  </si>
-  <si>
-    <t>134707685</t>
-  </si>
-  <si>
-    <t>134700667</t>
-  </si>
-  <si>
-    <t>134797684</t>
-  </si>
-  <si>
-    <t>134825913</t>
-  </si>
-  <si>
-    <t>134826970</t>
-  </si>
-  <si>
-    <t>134735996</t>
-  </si>
-  <si>
-    <t>134700854</t>
-  </si>
-  <si>
-    <t>134833192</t>
-  </si>
-  <si>
-    <t>134839517</t>
-  </si>
-  <si>
-    <t>134712612</t>
-  </si>
-  <si>
-    <t>134661083</t>
-  </si>
-  <si>
-    <t>134704437</t>
-  </si>
-  <si>
-    <t>134707055</t>
-  </si>
-  <si>
-    <t>134708678</t>
-  </si>
-  <si>
-    <t>134709137</t>
-  </si>
-  <si>
-    <t>134710928</t>
-  </si>
-  <si>
-    <t>134711937</t>
-  </si>
-  <si>
-    <t>134712402</t>
-  </si>
-  <si>
-    <t>134713194</t>
-  </si>
-  <si>
-    <t>134713216</t>
-  </si>
-  <si>
-    <t>134714456</t>
-  </si>
-  <si>
-    <t>134714566</t>
-  </si>
-  <si>
-    <t>134714660</t>
-  </si>
-  <si>
-    <t>134714887</t>
-  </si>
-  <si>
-    <t>134715302</t>
-  </si>
-  <si>
-    <t>134715732</t>
-  </si>
-  <si>
-    <t>134667986</t>
-  </si>
-  <si>
-    <t>134857082</t>
-  </si>
-  <si>
-    <t>134722366</t>
-  </si>
-  <si>
-    <t>134724022</t>
-  </si>
-  <si>
-    <t>134724143</t>
-  </si>
-  <si>
-    <t>134727296</t>
-  </si>
-  <si>
-    <t>134727457</t>
-  </si>
-  <si>
-    <t>134727484</t>
-  </si>
-  <si>
-    <t>134727605</t>
-  </si>
-  <si>
-    <t>134727680</t>
-  </si>
-  <si>
-    <t>134728030</t>
-  </si>
-  <si>
-    <t>134732752</t>
+    <t>Relatório de Recusas Santander - 10 e 11/10/2025</t>
+  </si>
+  <si>
+    <t>134741311</t>
+  </si>
+  <si>
+    <t>134758635</t>
+  </si>
+  <si>
+    <t>134754907</t>
+  </si>
+  <si>
+    <t>134756781</t>
+  </si>
+  <si>
+    <t>134758646</t>
+  </si>
+  <si>
+    <t>134772431</t>
+  </si>
+  <si>
+    <t>134772192</t>
+  </si>
+  <si>
+    <t>134834841</t>
+  </si>
+  <si>
+    <t>134847302</t>
+  </si>
+  <si>
+    <t>134772299</t>
+  </si>
+  <si>
+    <t>134860645</t>
+  </si>
+  <si>
+    <t>134745010</t>
+  </si>
+  <si>
+    <t>134683860</t>
+  </si>
+  <si>
+    <t>134659552</t>
+  </si>
+  <si>
+    <t>134751634</t>
+  </si>
+  <si>
+    <t>134747272</t>
+  </si>
+  <si>
+    <t>134744301</t>
+  </si>
+  <si>
+    <t>134744899</t>
+  </si>
+  <si>
+    <t>134747137</t>
+  </si>
+  <si>
+    <t>134747445</t>
+  </si>
+  <si>
+    <t>134787930</t>
+  </si>
+  <si>
+    <t>134771098</t>
+  </si>
+  <si>
+    <t>134801737</t>
+  </si>
+  <si>
+    <t>134715336</t>
+  </si>
+  <si>
+    <t>134687865</t>
+  </si>
+  <si>
+    <t>134675981</t>
+  </si>
+  <si>
+    <t>134714672</t>
   </si>
 </sst>
 </file>
@@ -633,7 +543,7 @@
   <sheetPr>
     <pageSetUpPr autoPageBreaks="0"/>
   </sheetPr>
-  <dimension ref="A1:F59"/>
+  <dimension ref="A1:F29"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="2" width="16.7109375" style="1" customWidth="1" collapsed="1"/>
@@ -665,7 +575,7 @@
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A2" s="6">
-        <v>134696628</v>
+        <v>134673634</v>
       </c>
       <c r="B2" s="1" t="s">
         <v>7</v>
@@ -1157,516 +1067,6 @@
         <v>8</v>
       </c>
       <c r="E29" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="30" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A30" s="1" t="s">
-        <v>37</v>
-      </c>
-      <c r="B30" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C30" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D30" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="E30" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="31" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A31" s="1" t="s">
-        <v>38</v>
-      </c>
-      <c r="B31" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C31" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D31" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="E31" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="32" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A32" s="1" t="s">
-        <v>39</v>
-      </c>
-      <c r="B32" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C32" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D32" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="E32" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="33" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A33" s="1" t="s">
-        <v>40</v>
-      </c>
-      <c r="B33" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C33" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D33" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="E33" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="34" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A34" s="1" t="s">
-        <v>41</v>
-      </c>
-      <c r="B34" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C34" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D34" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="E34" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="35" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A35" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="B35" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C35" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D35" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="E35" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="36" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A36" s="1" t="s">
-        <v>43</v>
-      </c>
-      <c r="B36" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C36" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D36" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="E36" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="37" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A37" s="1" t="s">
-        <v>44</v>
-      </c>
-      <c r="B37" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C37" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D37" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="E37" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="38" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A38" s="1" t="s">
-        <v>45</v>
-      </c>
-      <c r="B38" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C38" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D38" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="E38" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="39" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A39" s="1" t="s">
-        <v>46</v>
-      </c>
-      <c r="B39" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C39" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D39" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="E39" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="40" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A40" s="1" t="s">
-        <v>47</v>
-      </c>
-      <c r="B40" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C40" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D40" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="E40" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="41" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A41" s="1" t="s">
-        <v>48</v>
-      </c>
-      <c r="B41" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C41" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D41" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="E41" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="42" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A42" s="1" t="s">
-        <v>49</v>
-      </c>
-      <c r="B42" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C42" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D42" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="E42" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="43" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A43" s="1" t="s">
-        <v>50</v>
-      </c>
-      <c r="B43" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C43" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D43" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="E43" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="44" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A44" s="1" t="s">
-        <v>51</v>
-      </c>
-      <c r="B44" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C44" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D44" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="E44" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="45" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A45" s="1" t="s">
-        <v>52</v>
-      </c>
-      <c r="B45" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C45" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D45" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="E45" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="46" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A46" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="B46" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C46" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D46" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="E46" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="47" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A47" s="1" t="s">
-        <v>54</v>
-      </c>
-      <c r="B47" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C47" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D47" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="E47" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="48" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A48" s="1" t="s">
-        <v>55</v>
-      </c>
-      <c r="B48" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C48" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D48" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="E48" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="49" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A49" s="1" t="s">
-        <v>56</v>
-      </c>
-      <c r="B49" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C49" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D49" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="E49" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="50" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A50" s="1" t="s">
-        <v>57</v>
-      </c>
-      <c r="B50" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C50" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D50" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="E50" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="51" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A51" s="1" t="s">
-        <v>58</v>
-      </c>
-      <c r="B51" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C51" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D51" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="E51" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="52" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A52" s="1" t="s">
-        <v>59</v>
-      </c>
-      <c r="B52" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C52" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D52" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="E52" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="53" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A53" s="1" t="s">
-        <v>60</v>
-      </c>
-      <c r="B53" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C53" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D53" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="E53" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="54" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A54" s="1" t="s">
-        <v>61</v>
-      </c>
-      <c r="B54" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C54" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D54" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="E54" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="55" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A55" s="1" t="s">
-        <v>62</v>
-      </c>
-      <c r="B55" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C55" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D55" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="E55" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="56" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A56" s="1" t="s">
-        <v>63</v>
-      </c>
-      <c r="B56" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C56" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D56" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="E56" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="57" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A57" s="1" t="s">
-        <v>64</v>
-      </c>
-      <c r="B57" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C57" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D57" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="E57" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="58" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A58" s="1" t="s">
-        <v>65</v>
-      </c>
-      <c r="B58" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C58" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D58" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="E58" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="59" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A59" s="1" t="s">
-        <v>66</v>
-      </c>
-      <c r="B59" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C59" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D59" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="E59" s="2" t="s">
         <v>6</v>
       </c>
     </row>
@@ -1684,31 +1084,31 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<sisl xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns="http://www.boldonjames.com/2008/01/sie/internal/label" sislVersion="0" policy="dd20d239-a7e6-4c49-877c-45b7b43359cb" origin="defaultValue">
+  <element uid="5027ba01-e221-4650-87c9-b8eeda1feb2f" value=""/>
+</sisl>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <WrappedLabelHistory xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns="http://www.boldonjames.com/2016/02/Classifier/internal/wrappedLabelHistory">
   <Value>PD94bWwgdmVyc2lvbj0iMS4wIiBlbmNvZGluZz0idXMtYXNjaWkiPz48bGFiZWxIaXN0b3J5IHhtbG5zOnhzZD0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEiIHhtbG5zOnhzaT0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEtaW5zdGFuY2UiIHhtbG5zPSJodHRwOi8vd3d3LmJvbGRvbmphbWVzLmNvbS8yMDE2LzAyL0NsYXNzaWZpZXIvaW50ZXJuYWwvbGFiZWxIaXN0b3J5Ij48aXRlbT48c2lzbCBzaXNsVmVyc2lvbj0iMCIgcG9saWN5PSJkZDIwZDIzOS1hN2U2LTRjNDktODc3Yy00NWI3YjQzMzU5Y2IiIG9yaWdpbj0iZGVmYXVsdFZhbHVlIj48ZWxlbWVudCB1aWQ9IjUwMjdiYTAxLWUyMjEtNDY1MC04N2M5LWI4ZWVkYTFmZWIyZiIgdmFsdWU9IiIgeG1sbnM9Imh0dHA6Ly93d3cuYm9sZG9uamFtZXMuY29tLzIwMDgvMDEvc2llL2ludGVybmFsL2xhYmVsIiAvPjwvc2lzbD48VXNlck5hbWU+QUxMSUFOWlxCRTAwMTUxPC9Vc2VyTmFtZT48RGF0ZVRpbWU+MTcvMDkvMjAxOSAxODoxMjoxMjwvRGF0ZVRpbWU+PExhYmVsU3RyaW5nPiAgICAgICAxNy8wOS8yMDE5ICBJTlRFUk5PICA8L0xhYmVsU3RyaW5nPjwvaXRlbT48L2xhYmVsSGlzdG9yeT4=</Value>
 </WrappedLabelHistory>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<sisl xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns="http://www.boldonjames.com/2008/01/sie/internal/label" sislVersion="0" policy="dd20d239-a7e6-4c49-877c-45b7b43359cb" origin="defaultValue">
-  <element uid="5027ba01-e221-4650-87c9-b8eeda1feb2f" value=""/>
-</sisl>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{758EF150-7616-48C2-9614-E853EDB7BDD0}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
+    <ds:schemaRef ds:uri="http://www.boldonjames.com/2008/01/sie/internal/label"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D7CACE11-ACDB-4C58-86FC-5A54EABF64E3}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
     <ds:schemaRef ds:uri="http://www.boldonjames.com/2016/02/Classifier/internal/wrappedLabelHistory"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{758EF150-7616-48C2-9614-E853EDB7BDD0}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
-    <ds:schemaRef ds:uri="http://www.boldonjames.com/2008/01/sie/internal/label"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>
--- a/Data Files/Backoffce/IndexacaoFG/IndexacaoFG_SANTANDER.xlsx
+++ b/Data Files/Backoffce/IndexacaoFG/IndexacaoFG_SANTANDER.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Public\RPA_ALLIANZ_TREINAMENTO\Data Files\Backoffce\IndexacaoFG\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F84C1EDC-FE90-4237-A091-9140CB6B3E18}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7BB05310-3A8C-461A-A02B-4754A9D8F35C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="20370" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="145" uniqueCount="37">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="305" uniqueCount="72">
   <si>
     <t xml:space="preserve">status </t>
   </si>
@@ -54,91 +54,196 @@
     <t>1070</t>
   </si>
   <si>
-    <t>Relatório de Recusas 06.10.2025 a 12.10.2025</t>
-  </si>
-  <si>
-    <t>Relatório de Recusas Santander - 10 e 11/10/2025</t>
-  </si>
-  <si>
-    <t>134741311</t>
-  </si>
-  <si>
-    <t>134758635</t>
-  </si>
-  <si>
-    <t>134754907</t>
-  </si>
-  <si>
-    <t>134756781</t>
-  </si>
-  <si>
-    <t>134758646</t>
-  </si>
-  <si>
-    <t>134772431</t>
-  </si>
-  <si>
-    <t>134772192</t>
-  </si>
-  <si>
-    <t>134834841</t>
-  </si>
-  <si>
-    <t>134847302</t>
-  </si>
-  <si>
-    <t>134772299</t>
-  </si>
-  <si>
-    <t>134860645</t>
-  </si>
-  <si>
-    <t>134745010</t>
-  </si>
-  <si>
-    <t>134683860</t>
-  </si>
-  <si>
-    <t>134659552</t>
-  </si>
-  <si>
-    <t>134751634</t>
-  </si>
-  <si>
-    <t>134747272</t>
-  </si>
-  <si>
-    <t>134744301</t>
-  </si>
-  <si>
-    <t>134744899</t>
-  </si>
-  <si>
-    <t>134747137</t>
-  </si>
-  <si>
-    <t>134747445</t>
-  </si>
-  <si>
-    <t>134787930</t>
-  </si>
-  <si>
-    <t>134771098</t>
-  </si>
-  <si>
-    <t>134801737</t>
-  </si>
-  <si>
-    <t>134715336</t>
-  </si>
-  <si>
-    <t>134687865</t>
-  </si>
-  <si>
-    <t>134675981</t>
-  </si>
-  <si>
-    <t>134714672</t>
+    <t>Relatório de Recusas Santander -16/10/2025</t>
+  </si>
+  <si>
+    <t>134921585</t>
+  </si>
+  <si>
+    <t>134919110</t>
+  </si>
+  <si>
+    <t>134921171</t>
+  </si>
+  <si>
+    <t>134944976</t>
+  </si>
+  <si>
+    <t>134873071</t>
+  </si>
+  <si>
+    <t>134953488</t>
+  </si>
+  <si>
+    <t>134831845</t>
+  </si>
+  <si>
+    <t>134747798</t>
+  </si>
+  <si>
+    <t>134762243</t>
+  </si>
+  <si>
+    <t>134840802</t>
+  </si>
+  <si>
+    <t>134845539</t>
+  </si>
+  <si>
+    <t>134835808</t>
+  </si>
+  <si>
+    <t>134927735</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Relatório de Recusas 13.10.2025 a 19.10.2025 </t>
+  </si>
+  <si>
+    <t>134734284</t>
+  </si>
+  <si>
+    <t>Relatório de Recusas Santander -14/10/2025</t>
+  </si>
+  <si>
+    <t>134805081</t>
+  </si>
+  <si>
+    <t>134795918</t>
+  </si>
+  <si>
+    <t>134723692</t>
+  </si>
+  <si>
+    <t>134844875</t>
+  </si>
+  <si>
+    <t>134859553</t>
+  </si>
+  <si>
+    <t>134863856</t>
+  </si>
+  <si>
+    <t>134882456</t>
+  </si>
+  <si>
+    <t>134908363</t>
+  </si>
+  <si>
+    <t>134910576</t>
+  </si>
+  <si>
+    <t>134731932</t>
+  </si>
+  <si>
+    <t>134765346</t>
+  </si>
+  <si>
+    <t>134676156</t>
+  </si>
+  <si>
+    <t>134723777</t>
+  </si>
+  <si>
+    <t>134917403</t>
+  </si>
+  <si>
+    <t>134765510</t>
+  </si>
+  <si>
+    <t>134864443</t>
+  </si>
+  <si>
+    <t>134705316</t>
+  </si>
+  <si>
+    <t>134726860</t>
+  </si>
+  <si>
+    <t>134795689</t>
+  </si>
+  <si>
+    <t>134796301</t>
+  </si>
+  <si>
+    <t>134796722</t>
+  </si>
+  <si>
+    <t>134796877</t>
+  </si>
+  <si>
+    <t>134798453</t>
+  </si>
+  <si>
+    <t>134798705</t>
+  </si>
+  <si>
+    <t>134800611</t>
+  </si>
+  <si>
+    <t>134802251</t>
+  </si>
+  <si>
+    <t>Relatório de Recusas 13.10.2025 a 19.10.2025</t>
+  </si>
+  <si>
+    <t>134811751</t>
+  </si>
+  <si>
+    <t>Relatório de Recusas Santander -15/10/2025</t>
+  </si>
+  <si>
+    <t>134888070</t>
+  </si>
+  <si>
+    <t>134900492</t>
+  </si>
+  <si>
+    <t>134907652</t>
+  </si>
+  <si>
+    <t>134909691</t>
+  </si>
+  <si>
+    <t>134912819</t>
+  </si>
+  <si>
+    <t>134921812</t>
+  </si>
+  <si>
+    <t>134920630</t>
+  </si>
+  <si>
+    <t>134924283</t>
+  </si>
+  <si>
+    <t>134815878</t>
+  </si>
+  <si>
+    <t>134820077</t>
+  </si>
+  <si>
+    <t>134747600</t>
+  </si>
+  <si>
+    <t>134747495</t>
+  </si>
+  <si>
+    <t>134817449</t>
+  </si>
+  <si>
+    <t>134821711</t>
+  </si>
+  <si>
+    <t>134815283</t>
+  </si>
+  <si>
+    <t>134819550</t>
+  </si>
+  <si>
+    <t>134869519</t>
+  </si>
+  <si>
+    <t>134748448</t>
   </si>
 </sst>
 </file>
@@ -543,7 +648,7 @@
   <sheetPr>
     <pageSetUpPr autoPageBreaks="0"/>
   </sheetPr>
-  <dimension ref="A1:F29"/>
+  <dimension ref="A1:F61"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="2" width="16.7109375" style="1" customWidth="1" collapsed="1"/>
@@ -575,16 +680,16 @@
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A2" s="6">
-        <v>134673634</v>
+        <v>134856844</v>
       </c>
       <c r="B2" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>8</v>
+        <v>22</v>
       </c>
       <c r="E2" s="2" t="s">
         <v>6</v>
@@ -593,16 +698,16 @@
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B3" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>8</v>
+        <v>22</v>
       </c>
       <c r="E3" s="2" t="s">
         <v>6</v>
@@ -611,16 +716,16 @@
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B4" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>8</v>
+        <v>22</v>
       </c>
       <c r="E4" s="2" t="s">
         <v>6</v>
@@ -629,16 +734,16 @@
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B5" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>8</v>
+        <v>22</v>
       </c>
       <c r="E5" s="2" t="s">
         <v>6</v>
@@ -647,16 +752,16 @@
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" s="1" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B6" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>8</v>
+        <v>22</v>
       </c>
       <c r="E6" s="2" t="s">
         <v>6</v>
@@ -665,16 +770,16 @@
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" s="1" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B7" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>8</v>
+        <v>22</v>
       </c>
       <c r="E7" s="2" t="s">
         <v>6</v>
@@ -683,16 +788,16 @@
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" s="1" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B8" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>8</v>
+        <v>22</v>
       </c>
       <c r="E8" s="2" t="s">
         <v>6</v>
@@ -701,16 +806,16 @@
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" s="1" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B9" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>8</v>
+        <v>22</v>
       </c>
       <c r="E9" s="2" t="s">
         <v>6</v>
@@ -719,16 +824,16 @@
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A10" s="1" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B10" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>8</v>
+        <v>22</v>
       </c>
       <c r="E10" s="2" t="s">
         <v>6</v>
@@ -737,16 +842,16 @@
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A11" s="1" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B11" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>8</v>
+        <v>22</v>
       </c>
       <c r="E11" s="2" t="s">
         <v>6</v>
@@ -755,16 +860,16 @@
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A12" s="1" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B12" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>8</v>
+        <v>22</v>
       </c>
       <c r="E12" s="2" t="s">
         <v>6</v>
@@ -773,16 +878,16 @@
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A13" s="1" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B13" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>8</v>
+        <v>22</v>
       </c>
       <c r="E13" s="2" t="s">
         <v>6</v>
@@ -791,16 +896,16 @@
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A14" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="B14" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>8</v>
+        <v>22</v>
       </c>
       <c r="E14" s="2" t="s">
         <v>6</v>
@@ -809,16 +914,16 @@
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A15" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="B15" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C15" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D15" s="2" t="s">
         <v>22</v>
-      </c>
-      <c r="B15" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C15" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D15" s="2" t="s">
-        <v>8</v>
       </c>
       <c r="E15" s="2" t="s">
         <v>6</v>
@@ -833,10 +938,10 @@
         <v>7</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>9</v>
+        <v>24</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>8</v>
+        <v>51</v>
       </c>
       <c r="E16" s="2" t="s">
         <v>6</v>
@@ -845,16 +950,16 @@
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A17" s="1" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="B17" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>9</v>
+        <v>24</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>8</v>
+        <v>51</v>
       </c>
       <c r="E17" s="2" t="s">
         <v>6</v>
@@ -863,16 +968,16 @@
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A18" s="1" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="B18" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>9</v>
+        <v>24</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>8</v>
+        <v>51</v>
       </c>
       <c r="E18" s="2" t="s">
         <v>6</v>
@@ -881,16 +986,16 @@
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A19" s="1" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="B19" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>9</v>
+        <v>24</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>8</v>
+        <v>51</v>
       </c>
       <c r="E19" s="2" t="s">
         <v>6</v>
@@ -899,16 +1004,16 @@
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A20" s="1" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="B20" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>9</v>
+        <v>24</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>8</v>
+        <v>51</v>
       </c>
       <c r="E20" s="2" t="s">
         <v>6</v>
@@ -917,16 +1022,16 @@
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A21" s="1" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="B21" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>9</v>
+        <v>24</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>8</v>
+        <v>51</v>
       </c>
       <c r="E21" s="2" t="s">
         <v>6</v>
@@ -935,16 +1040,16 @@
     </row>
     <row r="22" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A22" s="1" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B22" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>9</v>
+        <v>24</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>8</v>
+        <v>51</v>
       </c>
       <c r="E22" s="2" t="s">
         <v>6</v>
@@ -953,16 +1058,16 @@
     </row>
     <row r="23" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A23" s="1" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B23" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>9</v>
+        <v>24</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>8</v>
+        <v>51</v>
       </c>
       <c r="E23" s="2" t="s">
         <v>6</v>
@@ -970,16 +1075,16 @@
     </row>
     <row r="24" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A24" s="1" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="B24" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C24" s="2" t="s">
-        <v>9</v>
+        <v>24</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>8</v>
+        <v>51</v>
       </c>
       <c r="E24" s="2" t="s">
         <v>6</v>
@@ -987,16 +1092,16 @@
     </row>
     <row r="25" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A25" s="1" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="B25" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C25" s="2" t="s">
-        <v>9</v>
+        <v>24</v>
       </c>
       <c r="D25" s="2" t="s">
-        <v>8</v>
+        <v>51</v>
       </c>
       <c r="E25" s="2" t="s">
         <v>6</v>
@@ -1004,16 +1109,16 @@
     </row>
     <row r="26" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A26" s="1" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B26" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C26" s="2" t="s">
-        <v>9</v>
+        <v>24</v>
       </c>
       <c r="D26" s="2" t="s">
-        <v>8</v>
+        <v>51</v>
       </c>
       <c r="E26" s="2" t="s">
         <v>6</v>
@@ -1021,16 +1126,16 @@
     </row>
     <row r="27" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A27" s="1" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="B27" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C27" s="2" t="s">
-        <v>9</v>
+        <v>24</v>
       </c>
       <c r="D27" s="2" t="s">
-        <v>8</v>
+        <v>51</v>
       </c>
       <c r="E27" s="2" t="s">
         <v>6</v>
@@ -1038,16 +1143,16 @@
     </row>
     <row r="28" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A28" s="1" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="B28" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C28" s="2" t="s">
-        <v>9</v>
+        <v>24</v>
       </c>
       <c r="D28" s="2" t="s">
-        <v>8</v>
+        <v>51</v>
       </c>
       <c r="E28" s="2" t="s">
         <v>6</v>
@@ -1055,18 +1160,562 @@
     </row>
     <row r="29" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A29" s="1" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="B29" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C29" s="2" t="s">
-        <v>9</v>
+        <v>24</v>
       </c>
       <c r="D29" s="2" t="s">
-        <v>8</v>
+        <v>51</v>
       </c>
       <c r="E29" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="30" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A30" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="B30" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C30" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="D30" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="E30" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="31" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A31" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="B31" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C31" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="D31" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="E31" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="32" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A32" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="B32" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C32" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="D32" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="E32" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="33" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A33" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="B33" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C33" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="D33" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="E33" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="34" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A34" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="B34" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C34" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="D34" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="E34" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="35" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A35" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="B35" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C35" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="D35" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="E35" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="36" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A36" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="B36" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C36" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="D36" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="E36" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="37" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A37" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="B37" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C37" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="D37" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="E37" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="38" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A38" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="B38" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C38" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="D38" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="E38" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="39" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A39" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="B39" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C39" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="D39" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="E39" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="40" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A40" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="B40" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C40" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="D40" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="E40" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="41" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A41" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="B41" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C41" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="D41" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="E41" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="42" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A42" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="B42" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C42" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="D42" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="E42" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="43" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A43" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="B43" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C43" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="D43" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="E43" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="44" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A44" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="B44" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C44" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="D44" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="E44" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="45" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A45" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="B45" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C45" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="D45" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="E45" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="46" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A46" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="B46" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C46" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="D46" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="E46" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="47" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A47" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="B47" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C47" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="D47" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="E47" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="48" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A48" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="B48" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C48" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="D48" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="E48" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="49" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A49" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="B49" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C49" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="D49" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="E49" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="50" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A50" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="B50" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C50" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="D50" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="E50" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="51" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A51" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="B51" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C51" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="D51" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="E51" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="52" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A52" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="B52" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C52" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="D52" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="E52" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="53" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A53" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="B53" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C53" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="D53" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="E53" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="54" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A54" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="B54" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C54" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="D54" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="E54" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="55" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A55" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="B55" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C55" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="D55" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="E55" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="56" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A56" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="B56" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C56" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="D56" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="E56" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="57" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A57" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="B57" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C57" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="D57" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="E57" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="58" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A58" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="B58" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C58" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="D58" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="E58" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="59" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A59" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="B59" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C59" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="D59" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="E59" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="60" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A60" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="B60" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C60" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="D60" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="E60" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="61" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A61" s="1" t="s">
+        <v>71</v>
+      </c>
+      <c r="B61" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C61" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="D61" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="E61" s="2" t="s">
         <v>6</v>
       </c>
     </row>
@@ -1084,31 +1733,31 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<WrappedLabelHistory xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns="http://www.boldonjames.com/2016/02/Classifier/internal/wrappedLabelHistory">
+  <Value>PD94bWwgdmVyc2lvbj0iMS4wIiBlbmNvZGluZz0idXMtYXNjaWkiPz48bGFiZWxIaXN0b3J5IHhtbG5zOnhzZD0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEiIHhtbG5zOnhzaT0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEtaW5zdGFuY2UiIHhtbG5zPSJodHRwOi8vd3d3LmJvbGRvbmphbWVzLmNvbS8yMDE2LzAyL0NsYXNzaWZpZXIvaW50ZXJuYWwvbGFiZWxIaXN0b3J5Ij48aXRlbT48c2lzbCBzaXNsVmVyc2lvbj0iMCIgcG9saWN5PSJkZDIwZDIzOS1hN2U2LTRjNDktODc3Yy00NWI3YjQzMzU5Y2IiIG9yaWdpbj0iZGVmYXVsdFZhbHVlIj48ZWxlbWVudCB1aWQ9IjUwMjdiYTAxLWUyMjEtNDY1MC04N2M5LWI4ZWVkYTFmZWIyZiIgdmFsdWU9IiIgeG1sbnM9Imh0dHA6Ly93d3cuYm9sZG9uamFtZXMuY29tLzIwMDgvMDEvc2llL2ludGVybmFsL2xhYmVsIiAvPjwvc2lzbD48VXNlck5hbWU+QUxMSUFOWlxCRTAwMTUxPC9Vc2VyTmFtZT48RGF0ZVRpbWU+MTcvMDkvMjAxOSAxODoxMjoxMjwvRGF0ZVRpbWU+PExhYmVsU3RyaW5nPiAgICAgICAxNy8wOS8yMDE5ICBJTlRFUk5PICA8L0xhYmVsU3RyaW5nPjwvaXRlbT48L2xhYmVsSGlzdG9yeT4=</Value>
+</WrappedLabelHistory>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <sisl xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns="http://www.boldonjames.com/2008/01/sie/internal/label" sislVersion="0" policy="dd20d239-a7e6-4c49-877c-45b7b43359cb" origin="defaultValue">
   <element uid="5027ba01-e221-4650-87c9-b8eeda1feb2f" value=""/>
 </sisl>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<WrappedLabelHistory xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns="http://www.boldonjames.com/2016/02/Classifier/internal/wrappedLabelHistory">
-  <Value>PD94bWwgdmVyc2lvbj0iMS4wIiBlbmNvZGluZz0idXMtYXNjaWkiPz48bGFiZWxIaXN0b3J5IHhtbG5zOnhzZD0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEiIHhtbG5zOnhzaT0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEtaW5zdGFuY2UiIHhtbG5zPSJodHRwOi8vd3d3LmJvbGRvbmphbWVzLmNvbS8yMDE2LzAyL0NsYXNzaWZpZXIvaW50ZXJuYWwvbGFiZWxIaXN0b3J5Ij48aXRlbT48c2lzbCBzaXNsVmVyc2lvbj0iMCIgcG9saWN5PSJkZDIwZDIzOS1hN2U2LTRjNDktODc3Yy00NWI3YjQzMzU5Y2IiIG9yaWdpbj0iZGVmYXVsdFZhbHVlIj48ZWxlbWVudCB1aWQ9IjUwMjdiYTAxLWUyMjEtNDY1MC04N2M5LWI4ZWVkYTFmZWIyZiIgdmFsdWU9IiIgeG1sbnM9Imh0dHA6Ly93d3cuYm9sZG9uamFtZXMuY29tLzIwMDgvMDEvc2llL2ludGVybmFsL2xhYmVsIiAvPjwvc2lzbD48VXNlck5hbWU+QUxMSUFOWlxCRTAwMTUxPC9Vc2VyTmFtZT48RGF0ZVRpbWU+MTcvMDkvMjAxOSAxODoxMjoxMjwvRGF0ZVRpbWU+PExhYmVsU3RyaW5nPiAgICAgICAxNy8wOS8yMDE5ICBJTlRFUk5PICA8L0xhYmVsU3RyaW5nPjwvaXRlbT48L2xhYmVsSGlzdG9yeT4=</Value>
-</WrappedLabelHistory>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D7CACE11-ACDB-4C58-86FC-5A54EABF64E3}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
+    <ds:schemaRef ds:uri="http://www.boldonjames.com/2016/02/Classifier/internal/wrappedLabelHistory"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{758EF150-7616-48C2-9614-E853EDB7BDD0}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
     <ds:schemaRef ds:uri="http://www.boldonjames.com/2008/01/sie/internal/label"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D7CACE11-ACDB-4C58-86FC-5A54EABF64E3}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
-    <ds:schemaRef ds:uri="http://www.boldonjames.com/2016/02/Classifier/internal/wrappedLabelHistory"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>
--- a/Data Files/Backoffce/IndexacaoFG/IndexacaoFG_SANTANDER.xlsx
+++ b/Data Files/Backoffce/IndexacaoFG/IndexacaoFG_SANTANDER.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Public\RPA_ALLIANZ_TREINAMENTO\Data Files\Backoffce\IndexacaoFG\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7BB05310-3A8C-461A-A02B-4754A9D8F35C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{978FE16D-F65B-498D-A64E-FB4B0BDEF68F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="20370" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="IndexacaoFG" sheetId="2" r:id="rId1"/>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="305" uniqueCount="72">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="438" uniqueCount="11">
   <si>
     <t xml:space="preserve">status </t>
   </si>
@@ -54,196 +54,13 @@
     <t>1070</t>
   </si>
   <si>
-    <t>Relatório de Recusas Santander -16/10/2025</t>
+    <t>Relatório de Recusas Santander -17, 18 e 20/10/2025</t>
   </si>
   <si>
-    <t>134921585</t>
-  </si>
-  <si>
-    <t>134919110</t>
-  </si>
-  <si>
-    <t>134921171</t>
-  </si>
-  <si>
-    <t>134944976</t>
-  </si>
-  <si>
-    <t>134873071</t>
-  </si>
-  <si>
-    <t>134953488</t>
-  </si>
-  <si>
-    <t>134831845</t>
-  </si>
-  <si>
-    <t>134747798</t>
-  </si>
-  <si>
-    <t>134762243</t>
-  </si>
-  <si>
-    <t>134840802</t>
-  </si>
-  <si>
-    <t>134845539</t>
-  </si>
-  <si>
-    <t>134835808</t>
-  </si>
-  <si>
-    <t>134927735</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Relatório de Recusas 13.10.2025 a 19.10.2025 </t>
-  </si>
-  <si>
-    <t>134734284</t>
-  </si>
-  <si>
-    <t>Relatório de Recusas Santander -14/10/2025</t>
-  </si>
-  <si>
-    <t>134805081</t>
-  </si>
-  <si>
-    <t>134795918</t>
-  </si>
-  <si>
-    <t>134723692</t>
-  </si>
-  <si>
-    <t>134844875</t>
-  </si>
-  <si>
-    <t>134859553</t>
-  </si>
-  <si>
-    <t>134863856</t>
-  </si>
-  <si>
-    <t>134882456</t>
-  </si>
-  <si>
-    <t>134908363</t>
-  </si>
-  <si>
-    <t>134910576</t>
-  </si>
-  <si>
-    <t>134731932</t>
-  </si>
-  <si>
-    <t>134765346</t>
-  </si>
-  <si>
-    <t>134676156</t>
-  </si>
-  <si>
-    <t>134723777</t>
-  </si>
-  <si>
-    <t>134917403</t>
-  </si>
-  <si>
-    <t>134765510</t>
-  </si>
-  <si>
-    <t>134864443</t>
-  </si>
-  <si>
-    <t>134705316</t>
-  </si>
-  <si>
-    <t>134726860</t>
-  </si>
-  <si>
-    <t>134795689</t>
-  </si>
-  <si>
-    <t>134796301</t>
-  </si>
-  <si>
-    <t>134796722</t>
-  </si>
-  <si>
-    <t>134796877</t>
-  </si>
-  <si>
-    <t>134798453</t>
-  </si>
-  <si>
-    <t>134798705</t>
-  </si>
-  <si>
-    <t>134800611</t>
-  </si>
-  <si>
-    <t>134802251</t>
+    <t>Relatório de Recusas 20.10.2025 a 26.10.2025</t>
   </si>
   <si>
     <t>Relatório de Recusas 13.10.2025 a 19.10.2025</t>
-  </si>
-  <si>
-    <t>134811751</t>
-  </si>
-  <si>
-    <t>Relatório de Recusas Santander -15/10/2025</t>
-  </si>
-  <si>
-    <t>134888070</t>
-  </si>
-  <si>
-    <t>134900492</t>
-  </si>
-  <si>
-    <t>134907652</t>
-  </si>
-  <si>
-    <t>134909691</t>
-  </si>
-  <si>
-    <t>134912819</t>
-  </si>
-  <si>
-    <t>134921812</t>
-  </si>
-  <si>
-    <t>134920630</t>
-  </si>
-  <si>
-    <t>134924283</t>
-  </si>
-  <si>
-    <t>134815878</t>
-  </si>
-  <si>
-    <t>134820077</t>
-  </si>
-  <si>
-    <t>134747600</t>
-  </si>
-  <si>
-    <t>134747495</t>
-  </si>
-  <si>
-    <t>134817449</t>
-  </si>
-  <si>
-    <t>134821711</t>
-  </si>
-  <si>
-    <t>134815283</t>
-  </si>
-  <si>
-    <t>134819550</t>
-  </si>
-  <si>
-    <t>134869519</t>
-  </si>
-  <si>
-    <t>134748448</t>
   </si>
 </sst>
 </file>
@@ -273,8 +90,8 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="9"/>
-      <color theme="1"/>
+      <sz val="10"/>
+      <color rgb="FF000000"/>
       <name val="Arial"/>
       <family val="2"/>
     </font>
@@ -299,7 +116,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="3">
     <border>
       <left/>
       <right/>
@@ -307,11 +124,41 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF000000"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF000000"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -328,7 +175,13 @@
     <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -648,7 +501,7 @@
   <sheetPr>
     <pageSetUpPr autoPageBreaks="0"/>
   </sheetPr>
-  <dimension ref="A1:F61"/>
+  <dimension ref="A1:F133"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="2" width="16.7109375" style="1" customWidth="1" collapsed="1"/>
@@ -680,16 +533,16 @@
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A2" s="6">
-        <v>134856844</v>
-      </c>
-      <c r="B2" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C2" s="2" t="s">
+        <v>134826721</v>
+      </c>
+      <c r="B2" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="C2" s="8" t="s">
         <v>8</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>22</v>
+        <v>10</v>
       </c>
       <c r="E2" s="2" t="s">
         <v>6</v>
@@ -697,17 +550,17 @@
       <c r="F2"/>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A3" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="B3" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C3" s="2" t="s">
+      <c r="A3" s="6">
+        <v>134838938</v>
+      </c>
+      <c r="B3" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="C3" s="8" t="s">
         <v>8</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>22</v>
+        <v>10</v>
       </c>
       <c r="E3" s="2" t="s">
         <v>6</v>
@@ -715,17 +568,17 @@
       <c r="F3"/>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A4" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="B4" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C4" s="2" t="s">
+      <c r="A4" s="6">
+        <v>134838645</v>
+      </c>
+      <c r="B4" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="C4" s="8" t="s">
         <v>8</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>22</v>
+        <v>10</v>
       </c>
       <c r="E4" s="2" t="s">
         <v>6</v>
@@ -733,17 +586,17 @@
       <c r="F4"/>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A5" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="B5" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C5" s="2" t="s">
+      <c r="A5" s="6">
+        <v>134869500</v>
+      </c>
+      <c r="B5" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="C5" s="8" t="s">
         <v>8</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>22</v>
+        <v>10</v>
       </c>
       <c r="E5" s="2" t="s">
         <v>6</v>
@@ -751,17 +604,17 @@
       <c r="F5"/>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A6" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="B6" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C6" s="2" t="s">
+      <c r="A6" s="6">
+        <v>134910944</v>
+      </c>
+      <c r="B6" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="C6" s="8" t="s">
         <v>8</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>22</v>
+        <v>10</v>
       </c>
       <c r="E6" s="2" t="s">
         <v>6</v>
@@ -769,17 +622,17 @@
       <c r="F6"/>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A7" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="B7" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C7" s="2" t="s">
+      <c r="A7" s="6">
+        <v>134929230</v>
+      </c>
+      <c r="B7" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="C7" s="8" t="s">
         <v>8</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>22</v>
+        <v>10</v>
       </c>
       <c r="E7" s="2" t="s">
         <v>6</v>
@@ -787,17 +640,17 @@
       <c r="F7"/>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A8" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="B8" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C8" s="2" t="s">
+      <c r="A8" s="6">
+        <v>134933777</v>
+      </c>
+      <c r="B8" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="C8" s="8" t="s">
         <v>8</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>22</v>
+        <v>10</v>
       </c>
       <c r="E8" s="2" t="s">
         <v>6</v>
@@ -805,17 +658,17 @@
       <c r="F8"/>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A9" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="B9" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C9" s="2" t="s">
+      <c r="A9" s="6">
+        <v>134966232</v>
+      </c>
+      <c r="B9" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="C9" s="8" t="s">
         <v>8</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>22</v>
+        <v>10</v>
       </c>
       <c r="E9" s="2" t="s">
         <v>6</v>
@@ -823,17 +676,17 @@
       <c r="F9"/>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A10" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="B10" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C10" s="2" t="s">
+      <c r="A10" s="6">
+        <v>134964144</v>
+      </c>
+      <c r="B10" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="C10" s="8" t="s">
         <v>8</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>22</v>
+        <v>10</v>
       </c>
       <c r="E10" s="2" t="s">
         <v>6</v>
@@ -841,17 +694,17 @@
       <c r="F10"/>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A11" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="B11" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C11" s="2" t="s">
+      <c r="A11" s="6">
+        <v>134860076</v>
+      </c>
+      <c r="B11" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="C11" s="8" t="s">
         <v>8</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>22</v>
+        <v>10</v>
       </c>
       <c r="E11" s="2" t="s">
         <v>6</v>
@@ -859,17 +712,17 @@
       <c r="F11"/>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A12" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="B12" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C12" s="2" t="s">
+      <c r="A12" s="6">
+        <v>134869548</v>
+      </c>
+      <c r="B12" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="C12" s="8" t="s">
         <v>8</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>22</v>
+        <v>10</v>
       </c>
       <c r="E12" s="2" t="s">
         <v>6</v>
@@ -877,17 +730,17 @@
       <c r="F12"/>
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A13" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="B13" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C13" s="2" t="s">
+      <c r="A13" s="6">
+        <v>134988983</v>
+      </c>
+      <c r="B13" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="C13" s="8" t="s">
         <v>8</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>22</v>
+        <v>10</v>
       </c>
       <c r="E13" s="2" t="s">
         <v>6</v>
@@ -895,17 +748,17 @@
       <c r="F13"/>
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A14" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="B14" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C14" s="2" t="s">
+      <c r="A14" s="6">
+        <v>134839437</v>
+      </c>
+      <c r="B14" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="C14" s="8" t="s">
         <v>8</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>22</v>
+        <v>10</v>
       </c>
       <c r="E14" s="2" t="s">
         <v>6</v>
@@ -913,17 +766,17 @@
       <c r="F14"/>
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A15" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="B15" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C15" s="2" t="s">
+      <c r="A15" s="6">
+        <v>134842546</v>
+      </c>
+      <c r="B15" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="C15" s="8" t="s">
         <v>8</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>22</v>
+        <v>10</v>
       </c>
       <c r="E15" s="2" t="s">
         <v>6</v>
@@ -931,17 +784,17 @@
       <c r="F15"/>
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A16" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="B16" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C16" s="2" t="s">
-        <v>24</v>
+      <c r="A16" s="6">
+        <v>134844371</v>
+      </c>
+      <c r="B16" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="C16" s="8" t="s">
+        <v>8</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>51</v>
+        <v>10</v>
       </c>
       <c r="E16" s="2" t="s">
         <v>6</v>
@@ -949,17 +802,17 @@
       <c r="F16"/>
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A17" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="B17" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C17" s="2" t="s">
-        <v>24</v>
+      <c r="A17" s="6">
+        <v>134847539</v>
+      </c>
+      <c r="B17" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="C17" s="8" t="s">
+        <v>8</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>51</v>
+        <v>10</v>
       </c>
       <c r="E17" s="2" t="s">
         <v>6</v>
@@ -967,17 +820,17 @@
       <c r="F17"/>
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A18" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="B18" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C18" s="2" t="s">
-        <v>24</v>
+      <c r="A18" s="6">
+        <v>134847996</v>
+      </c>
+      <c r="B18" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="C18" s="8" t="s">
+        <v>8</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>51</v>
+        <v>10</v>
       </c>
       <c r="E18" s="2" t="s">
         <v>6</v>
@@ -985,17 +838,17 @@
       <c r="F18"/>
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A19" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="B19" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C19" s="2" t="s">
-        <v>24</v>
+      <c r="A19" s="6">
+        <v>134849889</v>
+      </c>
+      <c r="B19" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="C19" s="8" t="s">
+        <v>8</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>51</v>
+        <v>10</v>
       </c>
       <c r="E19" s="2" t="s">
         <v>6</v>
@@ -1003,17 +856,17 @@
       <c r="F19"/>
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A20" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="B20" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C20" s="2" t="s">
-        <v>24</v>
+      <c r="A20" s="6">
+        <v>134852830</v>
+      </c>
+      <c r="B20" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="C20" s="8" t="s">
+        <v>8</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>51</v>
+        <v>10</v>
       </c>
       <c r="E20" s="2" t="s">
         <v>6</v>
@@ -1021,17 +874,17 @@
       <c r="F20"/>
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A21" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="B21" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C21" s="2" t="s">
-        <v>24</v>
+      <c r="A21" s="6">
+        <v>134854093</v>
+      </c>
+      <c r="B21" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="C21" s="8" t="s">
+        <v>8</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>51</v>
+        <v>10</v>
       </c>
       <c r="E21" s="2" t="s">
         <v>6</v>
@@ -1039,17 +892,17 @@
       <c r="F21"/>
     </row>
     <row r="22" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A22" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="B22" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C22" s="2" t="s">
-        <v>24</v>
+      <c r="A22" s="6">
+        <v>134854982</v>
+      </c>
+      <c r="B22" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="C22" s="8" t="s">
+        <v>8</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>51</v>
+        <v>10</v>
       </c>
       <c r="E22" s="2" t="s">
         <v>6</v>
@@ -1057,667 +910,1556 @@
       <c r="F22"/>
     </row>
     <row r="23" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A23" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="B23" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C23" s="2" t="s">
-        <v>24</v>
+      <c r="A23" s="6">
+        <v>134857172</v>
+      </c>
+      <c r="B23" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="C23" s="8" t="s">
+        <v>8</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>51</v>
+        <v>10</v>
       </c>
       <c r="E23" s="2" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="24" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A24" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="B24" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C24" s="2" t="s">
-        <v>24</v>
+      <c r="A24" s="6">
+        <v>134860535</v>
+      </c>
+      <c r="B24" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="C24" s="8" t="s">
+        <v>8</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>51</v>
+        <v>10</v>
       </c>
       <c r="E24" s="2" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="25" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A25" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="B25" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C25" s="2" t="s">
-        <v>24</v>
+      <c r="A25" s="6">
+        <v>134813625</v>
+      </c>
+      <c r="B25" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="C25" s="8" t="s">
+        <v>8</v>
       </c>
       <c r="D25" s="2" t="s">
-        <v>51</v>
+        <v>10</v>
       </c>
       <c r="E25" s="2" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="26" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A26" s="1" t="s">
-        <v>34</v>
-      </c>
-      <c r="B26" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C26" s="2" t="s">
-        <v>24</v>
+      <c r="A26" s="6">
+        <v>134814178</v>
+      </c>
+      <c r="B26" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="C26" s="8" t="s">
+        <v>8</v>
       </c>
       <c r="D26" s="2" t="s">
-        <v>51</v>
+        <v>10</v>
       </c>
       <c r="E26" s="2" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="27" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A27" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="B27" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C27" s="2" t="s">
-        <v>24</v>
+      <c r="A27" s="6">
+        <v>134814240</v>
+      </c>
+      <c r="B27" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="C27" s="8" t="s">
+        <v>8</v>
       </c>
       <c r="D27" s="2" t="s">
-        <v>51</v>
+        <v>10</v>
       </c>
       <c r="E27" s="2" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="28" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A28" s="1" t="s">
-        <v>36</v>
-      </c>
-      <c r="B28" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C28" s="2" t="s">
-        <v>24</v>
+      <c r="A28" s="6">
+        <v>134814818</v>
+      </c>
+      <c r="B28" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="C28" s="8" t="s">
+        <v>8</v>
       </c>
       <c r="D28" s="2" t="s">
-        <v>51</v>
+        <v>10</v>
       </c>
       <c r="E28" s="2" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="29" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A29" s="1" t="s">
-        <v>37</v>
-      </c>
-      <c r="B29" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C29" s="2" t="s">
-        <v>24</v>
+      <c r="A29" s="6">
+        <v>134818587</v>
+      </c>
+      <c r="B29" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="C29" s="8" t="s">
+        <v>8</v>
       </c>
       <c r="D29" s="2" t="s">
-        <v>51</v>
+        <v>10</v>
       </c>
       <c r="E29" s="2" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="30" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A30" s="1" t="s">
-        <v>38</v>
-      </c>
-      <c r="B30" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C30" s="2" t="s">
-        <v>24</v>
+      <c r="A30" s="6">
+        <v>134818815</v>
+      </c>
+      <c r="B30" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="C30" s="8" t="s">
+        <v>8</v>
       </c>
       <c r="D30" s="2" t="s">
-        <v>51</v>
+        <v>10</v>
       </c>
       <c r="E30" s="2" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="31" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A31" s="1" t="s">
-        <v>39</v>
-      </c>
-      <c r="B31" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C31" s="2" t="s">
-        <v>24</v>
+      <c r="A31" s="6">
+        <v>134878294</v>
+      </c>
+      <c r="B31" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="C31" s="8" t="s">
+        <v>8</v>
       </c>
       <c r="D31" s="2" t="s">
-        <v>51</v>
+        <v>10</v>
       </c>
       <c r="E31" s="2" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="32" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A32" s="1" t="s">
-        <v>40</v>
-      </c>
-      <c r="B32" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C32" s="2" t="s">
-        <v>24</v>
+      <c r="A32" s="6">
+        <v>134893359</v>
+      </c>
+      <c r="B32" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="C32" s="8" t="s">
+        <v>8</v>
       </c>
       <c r="D32" s="2" t="s">
-        <v>51</v>
+        <v>10</v>
       </c>
       <c r="E32" s="2" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="33" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A33" s="1" t="s">
-        <v>41</v>
-      </c>
-      <c r="B33" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C33" s="2" t="s">
-        <v>24</v>
+      <c r="A33" s="6">
+        <v>134881062</v>
+      </c>
+      <c r="B33" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="C33" s="8" t="s">
+        <v>8</v>
       </c>
       <c r="D33" s="2" t="s">
-        <v>51</v>
+        <v>10</v>
       </c>
       <c r="E33" s="2" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="34" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A34" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="B34" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C34" s="2" t="s">
-        <v>24</v>
+      <c r="A34" s="6">
+        <v>134874668</v>
+      </c>
+      <c r="B34" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="C34" s="8" t="s">
+        <v>8</v>
       </c>
       <c r="D34" s="2" t="s">
-        <v>51</v>
+        <v>10</v>
       </c>
       <c r="E34" s="2" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="35" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A35" s="1" t="s">
-        <v>43</v>
-      </c>
-      <c r="B35" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C35" s="2" t="s">
-        <v>24</v>
+      <c r="A35" s="6">
+        <v>134891446</v>
+      </c>
+      <c r="B35" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="C35" s="8" t="s">
+        <v>8</v>
       </c>
       <c r="D35" s="2" t="s">
-        <v>51</v>
+        <v>10</v>
       </c>
       <c r="E35" s="2" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="36" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A36" s="1" t="s">
-        <v>44</v>
-      </c>
-      <c r="B36" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C36" s="2" t="s">
-        <v>24</v>
+      <c r="A36" s="6">
+        <v>134826952</v>
+      </c>
+      <c r="B36" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="C36" s="8" t="s">
+        <v>8</v>
       </c>
       <c r="D36" s="2" t="s">
-        <v>51</v>
+        <v>10</v>
       </c>
       <c r="E36" s="2" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="37" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A37" s="1" t="s">
-        <v>45</v>
-      </c>
-      <c r="B37" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C37" s="2" t="s">
-        <v>24</v>
+      <c r="A37" s="6">
+        <v>134876679</v>
+      </c>
+      <c r="B37" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="C37" s="8" t="s">
+        <v>8</v>
       </c>
       <c r="D37" s="2" t="s">
-        <v>51</v>
+        <v>10</v>
       </c>
       <c r="E37" s="2" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="38" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A38" s="1" t="s">
-        <v>46</v>
-      </c>
-      <c r="B38" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C38" s="2" t="s">
-        <v>24</v>
+      <c r="A38" s="6">
+        <v>134920718</v>
+      </c>
+      <c r="B38" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="C38" s="8" t="s">
+        <v>8</v>
       </c>
       <c r="D38" s="2" t="s">
-        <v>51</v>
+        <v>10</v>
       </c>
       <c r="E38" s="2" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="39" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A39" s="1" t="s">
-        <v>47</v>
-      </c>
-      <c r="B39" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C39" s="2" t="s">
-        <v>24</v>
+      <c r="A39" s="6">
+        <v>134926193</v>
+      </c>
+      <c r="B39" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="C39" s="8" t="s">
+        <v>8</v>
       </c>
       <c r="D39" s="2" t="s">
-        <v>51</v>
+        <v>10</v>
       </c>
       <c r="E39" s="2" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="40" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A40" s="1" t="s">
-        <v>48</v>
-      </c>
-      <c r="B40" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C40" s="2" t="s">
-        <v>24</v>
+      <c r="A40" s="6">
+        <v>134927129</v>
+      </c>
+      <c r="B40" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="C40" s="8" t="s">
+        <v>8</v>
       </c>
       <c r="D40" s="2" t="s">
-        <v>51</v>
+        <v>10</v>
       </c>
       <c r="E40" s="2" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="41" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A41" s="1" t="s">
-        <v>49</v>
-      </c>
-      <c r="B41" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C41" s="2" t="s">
-        <v>24</v>
+      <c r="A41" s="6">
+        <v>134924632</v>
+      </c>
+      <c r="B41" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="C41" s="8" t="s">
+        <v>8</v>
       </c>
       <c r="D41" s="2" t="s">
-        <v>51</v>
+        <v>10</v>
       </c>
       <c r="E41" s="2" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="42" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A42" s="1" t="s">
-        <v>50</v>
-      </c>
-      <c r="B42" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C42" s="2" t="s">
-        <v>24</v>
+      <c r="A42" s="6">
+        <v>134943152</v>
+      </c>
+      <c r="B42" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="C42" s="8" t="s">
+        <v>8</v>
       </c>
       <c r="D42" s="2" t="s">
-        <v>51</v>
+        <v>10</v>
       </c>
       <c r="E42" s="2" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="43" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A43" s="1" t="s">
-        <v>52</v>
-      </c>
-      <c r="B43" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C43" s="2" t="s">
-        <v>53</v>
+      <c r="A43" s="6">
+        <v>134946354</v>
+      </c>
+      <c r="B43" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="C43" s="8" t="s">
+        <v>8</v>
       </c>
       <c r="D43" s="2" t="s">
-        <v>51</v>
+        <v>10</v>
       </c>
       <c r="E43" s="2" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="44" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A44" s="1" t="s">
-        <v>54</v>
-      </c>
-      <c r="B44" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C44" s="2" t="s">
-        <v>53</v>
+      <c r="A44" s="6">
+        <v>134948123</v>
+      </c>
+      <c r="B44" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="C44" s="8" t="s">
+        <v>8</v>
       </c>
       <c r="D44" s="2" t="s">
-        <v>51</v>
+        <v>10</v>
       </c>
       <c r="E44" s="2" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="45" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A45" s="1" t="s">
-        <v>55</v>
-      </c>
-      <c r="B45" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C45" s="2" t="s">
-        <v>53</v>
+      <c r="A45" s="6">
+        <v>134946767</v>
+      </c>
+      <c r="B45" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="C45" s="8" t="s">
+        <v>8</v>
       </c>
       <c r="D45" s="2" t="s">
-        <v>51</v>
+        <v>10</v>
       </c>
       <c r="E45" s="2" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="46" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A46" s="1" t="s">
-        <v>56</v>
-      </c>
-      <c r="B46" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C46" s="2" t="s">
-        <v>53</v>
+      <c r="A46" s="6">
+        <v>134954190</v>
+      </c>
+      <c r="B46" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="C46" s="8" t="s">
+        <v>8</v>
       </c>
       <c r="D46" s="2" t="s">
-        <v>51</v>
+        <v>10</v>
       </c>
       <c r="E46" s="2" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="47" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A47" s="1" t="s">
-        <v>57</v>
-      </c>
-      <c r="B47" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C47" s="2" t="s">
-        <v>53</v>
+      <c r="A47" s="6">
+        <v>134948164</v>
+      </c>
+      <c r="B47" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="C47" s="8" t="s">
+        <v>8</v>
       </c>
       <c r="D47" s="2" t="s">
-        <v>51</v>
+        <v>10</v>
       </c>
       <c r="E47" s="2" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="48" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A48" s="1" t="s">
-        <v>58</v>
-      </c>
-      <c r="B48" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C48" s="2" t="s">
-        <v>53</v>
+      <c r="A48" s="6">
+        <v>134899850</v>
+      </c>
+      <c r="B48" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="C48" s="8" t="s">
+        <v>8</v>
       </c>
       <c r="D48" s="2" t="s">
-        <v>51</v>
+        <v>10</v>
       </c>
       <c r="E48" s="2" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="49" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A49" s="1" t="s">
-        <v>59</v>
-      </c>
-      <c r="B49" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C49" s="2" t="s">
-        <v>53</v>
+      <c r="A49" s="6">
+        <v>134980185</v>
+      </c>
+      <c r="B49" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="C49" s="8" t="s">
+        <v>8</v>
       </c>
       <c r="D49" s="2" t="s">
-        <v>51</v>
+        <v>10</v>
       </c>
       <c r="E49" s="2" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="50" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A50" s="1" t="s">
-        <v>60</v>
-      </c>
-      <c r="B50" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C50" s="2" t="s">
-        <v>53</v>
+      <c r="A50" s="6">
+        <v>134926575</v>
+      </c>
+      <c r="B50" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="C50" s="8" t="s">
+        <v>8</v>
       </c>
       <c r="D50" s="2" t="s">
-        <v>51</v>
+        <v>10</v>
       </c>
       <c r="E50" s="2" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="51" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A51" s="1" t="s">
-        <v>61</v>
-      </c>
-      <c r="B51" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C51" s="2" t="s">
-        <v>53</v>
+      <c r="A51" s="6">
+        <v>134912411</v>
+      </c>
+      <c r="B51" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="C51" s="8" t="s">
+        <v>8</v>
       </c>
       <c r="D51" s="2" t="s">
-        <v>51</v>
+        <v>10</v>
       </c>
       <c r="E51" s="2" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="52" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A52" s="1" t="s">
-        <v>62</v>
-      </c>
-      <c r="B52" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C52" s="2" t="s">
-        <v>53</v>
+      <c r="A52" s="6">
+        <v>134933365</v>
+      </c>
+      <c r="B52" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="C52" s="8" t="s">
+        <v>8</v>
       </c>
       <c r="D52" s="2" t="s">
-        <v>51</v>
+        <v>10</v>
       </c>
       <c r="E52" s="2" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="53" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A53" s="1" t="s">
-        <v>63</v>
-      </c>
-      <c r="B53" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C53" s="2" t="s">
-        <v>53</v>
+      <c r="A53" s="6">
+        <v>134923813</v>
+      </c>
+      <c r="B53" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="C53" s="8" t="s">
+        <v>8</v>
       </c>
       <c r="D53" s="2" t="s">
-        <v>51</v>
+        <v>10</v>
       </c>
       <c r="E53" s="2" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="54" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A54" s="1" t="s">
-        <v>64</v>
-      </c>
-      <c r="B54" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C54" s="2" t="s">
-        <v>53</v>
+      <c r="A54" s="6">
+        <v>134873058</v>
+      </c>
+      <c r="B54" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="C54" s="8" t="s">
+        <v>8</v>
       </c>
       <c r="D54" s="2" t="s">
-        <v>51</v>
+        <v>10</v>
       </c>
       <c r="E54" s="2" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="55" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A55" s="1" t="s">
-        <v>65</v>
-      </c>
-      <c r="B55" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C55" s="2" t="s">
-        <v>53</v>
+      <c r="A55" s="6">
+        <v>134934767</v>
+      </c>
+      <c r="B55" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="C55" s="8" t="s">
+        <v>8</v>
       </c>
       <c r="D55" s="2" t="s">
-        <v>51</v>
+        <v>10</v>
       </c>
       <c r="E55" s="2" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="56" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A56" s="1" t="s">
-        <v>66</v>
-      </c>
-      <c r="B56" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C56" s="2" t="s">
-        <v>53</v>
-      </c>
-      <c r="D56" s="2" t="s">
-        <v>51</v>
+      <c r="A56" s="6">
+        <v>134826721</v>
+      </c>
+      <c r="B56" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="C56" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="D56" s="8" t="s">
+        <v>9</v>
       </c>
       <c r="E56" s="2" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="57" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A57" s="1" t="s">
-        <v>67</v>
-      </c>
-      <c r="B57" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C57" s="2" t="s">
-        <v>53</v>
-      </c>
-      <c r="D57" s="2" t="s">
-        <v>51</v>
+      <c r="A57" s="6">
+        <v>134838938</v>
+      </c>
+      <c r="B57" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="C57" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="D57" s="8" t="s">
+        <v>9</v>
       </c>
       <c r="E57" s="2" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="58" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A58" s="1" t="s">
-        <v>68</v>
-      </c>
-      <c r="B58" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C58" s="2" t="s">
-        <v>53</v>
-      </c>
-      <c r="D58" s="2" t="s">
-        <v>51</v>
+      <c r="A58" s="6">
+        <v>134838645</v>
+      </c>
+      <c r="B58" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="C58" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="D58" s="8" t="s">
+        <v>9</v>
       </c>
       <c r="E58" s="2" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="59" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A59" s="1" t="s">
-        <v>69</v>
-      </c>
-      <c r="B59" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C59" s="2" t="s">
-        <v>53</v>
-      </c>
-      <c r="D59" s="2" t="s">
-        <v>51</v>
+      <c r="A59" s="6">
+        <v>134869500</v>
+      </c>
+      <c r="B59" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="C59" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="D59" s="8" t="s">
+        <v>9</v>
       </c>
       <c r="E59" s="2" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="60" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A60" s="1" t="s">
-        <v>70</v>
-      </c>
-      <c r="B60" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C60" s="2" t="s">
-        <v>53</v>
-      </c>
-      <c r="D60" s="2" t="s">
-        <v>51</v>
+      <c r="A60" s="6">
+        <v>134910944</v>
+      </c>
+      <c r="B60" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="C60" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="D60" s="8" t="s">
+        <v>9</v>
       </c>
       <c r="E60" s="2" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="61" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A61" s="1" t="s">
-        <v>71</v>
-      </c>
-      <c r="B61" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C61" s="2" t="s">
-        <v>53</v>
-      </c>
-      <c r="D61" s="2" t="s">
-        <v>51</v>
+      <c r="A61" s="6">
+        <v>134929230</v>
+      </c>
+      <c r="B61" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="C61" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="D61" s="8" t="s">
+        <v>9</v>
       </c>
       <c r="E61" s="2" t="s">
         <v>6</v>
       </c>
+    </row>
+    <row r="62" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A62" s="6">
+        <v>134933777</v>
+      </c>
+      <c r="B62" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="C62" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="D62" s="8" t="s">
+        <v>9</v>
+      </c>
+      <c r="E62" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="63" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A63" s="6">
+        <v>134966232</v>
+      </c>
+      <c r="B63" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="C63" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="D63" s="8" t="s">
+        <v>9</v>
+      </c>
+      <c r="E63" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="64" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A64" s="6">
+        <v>134964144</v>
+      </c>
+      <c r="B64" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="C64" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="D64" s="8" t="s">
+        <v>9</v>
+      </c>
+      <c r="E64" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="65" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A65" s="6">
+        <v>134860076</v>
+      </c>
+      <c r="B65" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="C65" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="D65" s="8" t="s">
+        <v>9</v>
+      </c>
+      <c r="E65" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="66" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A66" s="6">
+        <v>134869548</v>
+      </c>
+      <c r="B66" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="C66" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="D66" s="8" t="s">
+        <v>9</v>
+      </c>
+      <c r="E66" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="67" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A67" s="6">
+        <v>134988983</v>
+      </c>
+      <c r="B67" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="C67" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="D67" s="8" t="s">
+        <v>9</v>
+      </c>
+      <c r="E67" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="68" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A68" s="6">
+        <v>134839437</v>
+      </c>
+      <c r="B68" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="C68" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="D68" s="8" t="s">
+        <v>9</v>
+      </c>
+      <c r="E68" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="69" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A69" s="6">
+        <v>134842546</v>
+      </c>
+      <c r="B69" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="C69" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="D69" s="8" t="s">
+        <v>9</v>
+      </c>
+      <c r="E69" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="70" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A70" s="6">
+        <v>134844371</v>
+      </c>
+      <c r="B70" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="C70" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="D70" s="8" t="s">
+        <v>9</v>
+      </c>
+      <c r="E70" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="71" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A71" s="6">
+        <v>134847539</v>
+      </c>
+      <c r="B71" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="C71" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="D71" s="8" t="s">
+        <v>9</v>
+      </c>
+      <c r="E71" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="72" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A72" s="6">
+        <v>134847996</v>
+      </c>
+      <c r="B72" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="C72" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="D72" s="8" t="s">
+        <v>9</v>
+      </c>
+      <c r="E72" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="73" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A73" s="6">
+        <v>134849889</v>
+      </c>
+      <c r="B73" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="C73" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="D73" s="8" t="s">
+        <v>9</v>
+      </c>
+      <c r="E73" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="74" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A74" s="6">
+        <v>134852830</v>
+      </c>
+      <c r="B74" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="C74" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="D74" s="8" t="s">
+        <v>9</v>
+      </c>
+      <c r="E74" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="75" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A75" s="6">
+        <v>134854093</v>
+      </c>
+      <c r="B75" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="C75" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="D75" s="8" t="s">
+        <v>9</v>
+      </c>
+      <c r="E75" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="76" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A76" s="6">
+        <v>134854982</v>
+      </c>
+      <c r="B76" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="C76" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="D76" s="8" t="s">
+        <v>9</v>
+      </c>
+      <c r="E76" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="77" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A77" s="6">
+        <v>134857172</v>
+      </c>
+      <c r="B77" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="C77" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="D77" s="8" t="s">
+        <v>9</v>
+      </c>
+      <c r="E77" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="78" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A78" s="6">
+        <v>134860535</v>
+      </c>
+      <c r="B78" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="C78" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="D78" s="8" t="s">
+        <v>9</v>
+      </c>
+      <c r="E78" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="79" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A79" s="6">
+        <v>134813625</v>
+      </c>
+      <c r="B79" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="C79" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="D79" s="8" t="s">
+        <v>9</v>
+      </c>
+      <c r="E79" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="80" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A80" s="6">
+        <v>134814178</v>
+      </c>
+      <c r="B80" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="C80" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="D80" s="8" t="s">
+        <v>9</v>
+      </c>
+      <c r="E80" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="81" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A81" s="6">
+        <v>134814240</v>
+      </c>
+      <c r="B81" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="C81" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="D81" s="8" t="s">
+        <v>9</v>
+      </c>
+      <c r="E81" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="82" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A82" s="6">
+        <v>134814818</v>
+      </c>
+      <c r="B82" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="C82" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="D82" s="8" t="s">
+        <v>9</v>
+      </c>
+      <c r="E82" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="83" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A83" s="6">
+        <v>134818587</v>
+      </c>
+      <c r="B83" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="C83" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="D83" s="8" t="s">
+        <v>9</v>
+      </c>
+      <c r="E83" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="84" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A84" s="6">
+        <v>134818815</v>
+      </c>
+      <c r="B84" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="C84" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="D84" s="8" t="s">
+        <v>9</v>
+      </c>
+      <c r="E84" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="85" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A85" s="6">
+        <v>134878294</v>
+      </c>
+      <c r="B85" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="C85" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="D85" s="8" t="s">
+        <v>9</v>
+      </c>
+      <c r="E85" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="86" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A86" s="6">
+        <v>134893359</v>
+      </c>
+      <c r="B86" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="C86" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="D86" s="8" t="s">
+        <v>9</v>
+      </c>
+      <c r="E86" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="87" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A87" s="6">
+        <v>134881062</v>
+      </c>
+      <c r="B87" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="C87" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="D87" s="8" t="s">
+        <v>9</v>
+      </c>
+      <c r="E87" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="88" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A88" s="6">
+        <v>134874668</v>
+      </c>
+      <c r="B88" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="C88" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="D88" s="8" t="s">
+        <v>9</v>
+      </c>
+      <c r="E88" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="89" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A89" s="6">
+        <v>134891446</v>
+      </c>
+      <c r="B89" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="C89" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="D89" s="8" t="s">
+        <v>9</v>
+      </c>
+      <c r="E89" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="90" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A90" s="6">
+        <v>134826952</v>
+      </c>
+      <c r="B90" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="C90" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="D90" s="8" t="s">
+        <v>9</v>
+      </c>
+      <c r="E90" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="91" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A91" s="6">
+        <v>134876679</v>
+      </c>
+      <c r="B91" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="C91" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="D91" s="8" t="s">
+        <v>9</v>
+      </c>
+      <c r="E91" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="92" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A92" s="6">
+        <v>134920718</v>
+      </c>
+      <c r="B92" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="C92" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="D92" s="8" t="s">
+        <v>9</v>
+      </c>
+      <c r="E92" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="93" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A93" s="6">
+        <v>134926193</v>
+      </c>
+      <c r="B93" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="C93" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="D93" s="8" t="s">
+        <v>9</v>
+      </c>
+      <c r="E93" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="94" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A94" s="6">
+        <v>134927129</v>
+      </c>
+      <c r="B94" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="C94" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="D94" s="8" t="s">
+        <v>9</v>
+      </c>
+      <c r="E94" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="95" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A95" s="6">
+        <v>134924632</v>
+      </c>
+      <c r="B95" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="C95" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="D95" s="8" t="s">
+        <v>9</v>
+      </c>
+      <c r="E95" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="96" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A96" s="6">
+        <v>134943152</v>
+      </c>
+      <c r="B96" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="C96" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="D96" s="8" t="s">
+        <v>9</v>
+      </c>
+      <c r="E96" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="97" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A97" s="6">
+        <v>134946354</v>
+      </c>
+      <c r="B97" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="C97" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="D97" s="8" t="s">
+        <v>9</v>
+      </c>
+      <c r="E97" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="98" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A98" s="6">
+        <v>134948123</v>
+      </c>
+      <c r="B98" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="C98" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="D98" s="8" t="s">
+        <v>9</v>
+      </c>
+      <c r="E98" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="99" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A99" s="6">
+        <v>134946767</v>
+      </c>
+      <c r="B99" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="C99" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="D99" s="8" t="s">
+        <v>9</v>
+      </c>
+      <c r="E99" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="100" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A100" s="6">
+        <v>134954190</v>
+      </c>
+      <c r="B100" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="C100" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="D100" s="8" t="s">
+        <v>9</v>
+      </c>
+      <c r="E100" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="101" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A101" s="6">
+        <v>134948164</v>
+      </c>
+      <c r="B101" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="C101" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="D101" s="8" t="s">
+        <v>9</v>
+      </c>
+      <c r="E101" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="102" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A102" s="6">
+        <v>134899850</v>
+      </c>
+      <c r="B102" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="C102" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="D102" s="8" t="s">
+        <v>9</v>
+      </c>
+      <c r="E102" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="103" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A103" s="6">
+        <v>134980185</v>
+      </c>
+      <c r="B103" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="C103" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="D103" s="8" t="s">
+        <v>9</v>
+      </c>
+      <c r="E103" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="104" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A104" s="6">
+        <v>134926575</v>
+      </c>
+      <c r="B104" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="C104" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="D104" s="8" t="s">
+        <v>9</v>
+      </c>
+      <c r="E104" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="105" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A105" s="6">
+        <v>134912411</v>
+      </c>
+      <c r="B105" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="C105" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="D105" s="8" t="s">
+        <v>9</v>
+      </c>
+      <c r="E105" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="106" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A106" s="6">
+        <v>134933365</v>
+      </c>
+      <c r="B106" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="C106" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="D106" s="8" t="s">
+        <v>9</v>
+      </c>
+      <c r="E106" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="107" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A107" s="6">
+        <v>134923813</v>
+      </c>
+      <c r="B107" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="C107" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="D107" s="8" t="s">
+        <v>9</v>
+      </c>
+      <c r="E107" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="108" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A108" s="6">
+        <v>134873058</v>
+      </c>
+      <c r="B108" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="C108" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="D108" s="8" t="s">
+        <v>9</v>
+      </c>
+      <c r="E108" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="109" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A109" s="6">
+        <v>134934767</v>
+      </c>
+      <c r="B109" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="C109" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="D109" s="8" t="s">
+        <v>9</v>
+      </c>
+      <c r="E109" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="110" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="C110" s="8"/>
+      <c r="D110" s="8"/>
+    </row>
+    <row r="111" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="D111" s="8"/>
+    </row>
+    <row r="112" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="D112" s="8"/>
+    </row>
+    <row r="113" spans="4:4" x14ac:dyDescent="0.25">
+      <c r="D113" s="8"/>
+    </row>
+    <row r="114" spans="4:4" x14ac:dyDescent="0.25">
+      <c r="D114" s="8"/>
+    </row>
+    <row r="115" spans="4:4" x14ac:dyDescent="0.25">
+      <c r="D115" s="8"/>
+    </row>
+    <row r="116" spans="4:4" x14ac:dyDescent="0.25">
+      <c r="D116" s="8"/>
+    </row>
+    <row r="117" spans="4:4" x14ac:dyDescent="0.25">
+      <c r="D117" s="8"/>
+    </row>
+    <row r="118" spans="4:4" x14ac:dyDescent="0.25">
+      <c r="D118" s="8"/>
+    </row>
+    <row r="119" spans="4:4" x14ac:dyDescent="0.25">
+      <c r="D119" s="8"/>
+    </row>
+    <row r="120" spans="4:4" x14ac:dyDescent="0.25">
+      <c r="D120" s="8"/>
+    </row>
+    <row r="121" spans="4:4" x14ac:dyDescent="0.25">
+      <c r="D121" s="8"/>
+    </row>
+    <row r="122" spans="4:4" x14ac:dyDescent="0.25">
+      <c r="D122" s="8"/>
+    </row>
+    <row r="123" spans="4:4" x14ac:dyDescent="0.25">
+      <c r="D123" s="8"/>
+    </row>
+    <row r="124" spans="4:4" x14ac:dyDescent="0.25">
+      <c r="D124" s="8"/>
+    </row>
+    <row r="125" spans="4:4" x14ac:dyDescent="0.25">
+      <c r="D125" s="8"/>
+    </row>
+    <row r="126" spans="4:4" x14ac:dyDescent="0.25">
+      <c r="D126" s="8"/>
+    </row>
+    <row r="127" spans="4:4" x14ac:dyDescent="0.25">
+      <c r="D127" s="8"/>
+    </row>
+    <row r="128" spans="4:4" x14ac:dyDescent="0.25">
+      <c r="D128" s="8"/>
+    </row>
+    <row r="129" spans="4:4" x14ac:dyDescent="0.25">
+      <c r="D129" s="8"/>
+    </row>
+    <row r="130" spans="4:4" x14ac:dyDescent="0.25">
+      <c r="D130" s="8"/>
+    </row>
+    <row r="131" spans="4:4" x14ac:dyDescent="0.25">
+      <c r="D131" s="8"/>
+    </row>
+    <row r="132" spans="4:4" x14ac:dyDescent="0.25">
+      <c r="D132" s="8"/>
+    </row>
+    <row r="133" spans="4:4" x14ac:dyDescent="0.25">
+      <c r="D133" s="8"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:F1" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
@@ -1733,31 +2475,31 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<sisl xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns="http://www.boldonjames.com/2008/01/sie/internal/label" sislVersion="0" policy="dd20d239-a7e6-4c49-877c-45b7b43359cb" origin="defaultValue">
+  <element uid="5027ba01-e221-4650-87c9-b8eeda1feb2f" value=""/>
+</sisl>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <WrappedLabelHistory xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns="http://www.boldonjames.com/2016/02/Classifier/internal/wrappedLabelHistory">
   <Value>PD94bWwgdmVyc2lvbj0iMS4wIiBlbmNvZGluZz0idXMtYXNjaWkiPz48bGFiZWxIaXN0b3J5IHhtbG5zOnhzZD0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEiIHhtbG5zOnhzaT0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEtaW5zdGFuY2UiIHhtbG5zPSJodHRwOi8vd3d3LmJvbGRvbmphbWVzLmNvbS8yMDE2LzAyL0NsYXNzaWZpZXIvaW50ZXJuYWwvbGFiZWxIaXN0b3J5Ij48aXRlbT48c2lzbCBzaXNsVmVyc2lvbj0iMCIgcG9saWN5PSJkZDIwZDIzOS1hN2U2LTRjNDktODc3Yy00NWI3YjQzMzU5Y2IiIG9yaWdpbj0iZGVmYXVsdFZhbHVlIj48ZWxlbWVudCB1aWQ9IjUwMjdiYTAxLWUyMjEtNDY1MC04N2M5LWI4ZWVkYTFmZWIyZiIgdmFsdWU9IiIgeG1sbnM9Imh0dHA6Ly93d3cuYm9sZG9uamFtZXMuY29tLzIwMDgvMDEvc2llL2ludGVybmFsL2xhYmVsIiAvPjwvc2lzbD48VXNlck5hbWU+QUxMSUFOWlxCRTAwMTUxPC9Vc2VyTmFtZT48RGF0ZVRpbWU+MTcvMDkvMjAxOSAxODoxMjoxMjwvRGF0ZVRpbWU+PExhYmVsU3RyaW5nPiAgICAgICAxNy8wOS8yMDE5ICBJTlRFUk5PICA8L0xhYmVsU3RyaW5nPjwvaXRlbT48L2xhYmVsSGlzdG9yeT4=</Value>
 </WrappedLabelHistory>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<sisl xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns="http://www.boldonjames.com/2008/01/sie/internal/label" sislVersion="0" policy="dd20d239-a7e6-4c49-877c-45b7b43359cb" origin="defaultValue">
-  <element uid="5027ba01-e221-4650-87c9-b8eeda1feb2f" value=""/>
-</sisl>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{758EF150-7616-48C2-9614-E853EDB7BDD0}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
+    <ds:schemaRef ds:uri="http://www.boldonjames.com/2008/01/sie/internal/label"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D7CACE11-ACDB-4C58-86FC-5A54EABF64E3}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
     <ds:schemaRef ds:uri="http://www.boldonjames.com/2016/02/Classifier/internal/wrappedLabelHistory"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{758EF150-7616-48C2-9614-E853EDB7BDD0}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
-    <ds:schemaRef ds:uri="http://www.boldonjames.com/2008/01/sie/internal/label"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>
--- a/Data Files/Backoffce/IndexacaoFG/IndexacaoFG_SANTANDER.xlsx
+++ b/Data Files/Backoffce/IndexacaoFG/IndexacaoFG_SANTANDER.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Public\RPA_ALLIANZ_TREINAMENTO\Data Files\Backoffce\IndexacaoFG\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C258BEB5-6253-4C07-8D1D-FF63B5199670}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C2C4C91F-E7AA-4705-8AB4-D0AF20FDC9AA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="98" uniqueCount="10">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="128" uniqueCount="16">
   <si>
     <t xml:space="preserve">status </t>
   </si>
@@ -57,7 +57,25 @@
     <t>Relatório de Recusas 20.10.2025 a 26.10.2025</t>
   </si>
   <si>
-    <t>Relatório de Recusas Santander - 21/10/2025</t>
+    <t>Relatório de Recusas Santander - 22/10/2025</t>
+  </si>
+  <si>
+    <t>134917784</t>
+  </si>
+  <si>
+    <t>134923879</t>
+  </si>
+  <si>
+    <t>134924247</t>
+  </si>
+  <si>
+    <t>134928778</t>
+  </si>
+  <si>
+    <t>134932121</t>
+  </si>
+  <si>
+    <t>134934017</t>
   </si>
 </sst>
 </file>
@@ -498,7 +516,7 @@
   <sheetPr>
     <pageSetUpPr autoPageBreaks="0"/>
   </sheetPr>
-  <dimension ref="A1:F24"/>
+  <dimension ref="A1:F30"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="2" width="16.7109375" style="1" customWidth="1" collapsed="1"/>
@@ -530,7 +548,7 @@
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A2" s="6">
-        <v>134893205</v>
+        <v>134849892</v>
       </c>
       <c r="B2" s="7" t="s">
         <v>7</v>
@@ -548,7 +566,7 @@
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A3" s="6">
-        <v>134898334</v>
+        <v>134903636</v>
       </c>
       <c r="B3" s="7" t="s">
         <v>7</v>
@@ -566,7 +584,7 @@
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" s="6">
-        <v>134908821</v>
+        <v>134913758</v>
       </c>
       <c r="B4" s="7" t="s">
         <v>7</v>
@@ -584,7 +602,7 @@
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" s="6">
-        <v>134913987</v>
+        <v>134928422</v>
       </c>
       <c r="B5" s="7" t="s">
         <v>7</v>
@@ -602,7 +620,7 @@
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" s="6">
-        <v>134902221</v>
+        <v>134965026</v>
       </c>
       <c r="B6" s="7" t="s">
         <v>7</v>
@@ -620,7 +638,7 @@
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" s="6">
-        <v>134954244</v>
+        <v>134972980</v>
       </c>
       <c r="B7" s="7" t="s">
         <v>7</v>
@@ -638,7 +656,7 @@
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" s="6">
-        <v>134962076</v>
+        <v>134986262</v>
       </c>
       <c r="B8" s="7" t="s">
         <v>7</v>
@@ -656,7 +674,7 @@
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" s="6">
-        <v>134898688</v>
+        <v>134987136</v>
       </c>
       <c r="B9" s="7" t="s">
         <v>7</v>
@@ -674,7 +692,7 @@
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A10" s="6">
-        <v>134981455</v>
+        <v>134986230</v>
       </c>
       <c r="B10" s="7" t="s">
         <v>7</v>
@@ -692,7 +710,7 @@
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A11" s="6">
-        <v>134885981</v>
+        <v>134988232</v>
       </c>
       <c r="B11" s="7" t="s">
         <v>7</v>
@@ -710,7 +728,7 @@
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A12" s="6">
-        <v>134987089</v>
+        <v>134988419</v>
       </c>
       <c r="B12" s="7" t="s">
         <v>7</v>
@@ -728,7 +746,7 @@
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A13" s="6">
-        <v>134998920</v>
+        <v>134993720</v>
       </c>
       <c r="B13" s="7" t="s">
         <v>7</v>
@@ -746,7 +764,7 @@
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A14" s="6">
-        <v>134886837</v>
+        <v>134996719</v>
       </c>
       <c r="B14" s="7" t="s">
         <v>7</v>
@@ -764,7 +782,7 @@
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A15" s="6">
-        <v>135013874</v>
+        <v>134998645</v>
       </c>
       <c r="B15" s="7" t="s">
         <v>7</v>
@@ -782,7 +800,7 @@
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A16" s="6">
-        <v>134903935</v>
+        <v>134986172</v>
       </c>
       <c r="B16" s="7" t="s">
         <v>7</v>
@@ -800,7 +818,7 @@
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A17" s="6">
-        <v>134966734</v>
+        <v>134990611</v>
       </c>
       <c r="B17" s="7" t="s">
         <v>7</v>
@@ -818,7 +836,7 @@
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A18" s="6">
-        <v>134838338</v>
+        <v>134988396</v>
       </c>
       <c r="B18" s="7" t="s">
         <v>7</v>
@@ -836,7 +854,7 @@
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A19" s="6">
-        <v>134831981</v>
+        <v>135029467</v>
       </c>
       <c r="B19" s="7" t="s">
         <v>7</v>
@@ -854,7 +872,7 @@
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A20" s="6">
-        <v>135033178</v>
+        <v>134861748</v>
       </c>
       <c r="B20" s="7" t="s">
         <v>7</v>
@@ -872,7 +890,7 @@
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A21" s="6">
-        <v>134884688</v>
+        <v>134858457</v>
       </c>
       <c r="B21" s="7" t="s">
         <v>7</v>
@@ -890,7 +908,7 @@
     </row>
     <row r="22" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A22" s="6">
-        <v>134886908</v>
+        <v>134948867</v>
       </c>
       <c r="B22" s="7" t="s">
         <v>7</v>
@@ -908,7 +926,7 @@
     </row>
     <row r="23" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A23" s="6">
-        <v>134909904</v>
+        <v>135049650</v>
       </c>
       <c r="B23" s="7" t="s">
         <v>7</v>
@@ -925,7 +943,7 @@
     </row>
     <row r="24" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A24" s="6">
-        <v>134911954</v>
+        <v>134916937</v>
       </c>
       <c r="B24" s="7" t="s">
         <v>7</v>
@@ -937,6 +955,108 @@
         <v>8</v>
       </c>
       <c r="E24" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="25" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A25" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="B25" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C25" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D25" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E25" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="26" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A26" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="B26" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C26" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D26" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E26" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="27" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A27" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="B27" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C27" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D27" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E27" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="28" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A28" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="B28" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C28" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D28" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E28" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="29" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A29" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="B29" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C29" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D29" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E29" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="30" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A30" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="B30" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C30" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D30" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E30" s="2" t="s">
         <v>6</v>
       </c>
     </row>
@@ -954,31 +1074,31 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<sisl xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns="http://www.boldonjames.com/2008/01/sie/internal/label" sislVersion="0" policy="dd20d239-a7e6-4c49-877c-45b7b43359cb" origin="defaultValue">
+  <element uid="5027ba01-e221-4650-87c9-b8eeda1feb2f" value=""/>
+</sisl>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <WrappedLabelHistory xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns="http://www.boldonjames.com/2016/02/Classifier/internal/wrappedLabelHistory">
   <Value>PD94bWwgdmVyc2lvbj0iMS4wIiBlbmNvZGluZz0idXMtYXNjaWkiPz48bGFiZWxIaXN0b3J5IHhtbG5zOnhzZD0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEiIHhtbG5zOnhzaT0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEtaW5zdGFuY2UiIHhtbG5zPSJodHRwOi8vd3d3LmJvbGRvbmphbWVzLmNvbS8yMDE2LzAyL0NsYXNzaWZpZXIvaW50ZXJuYWwvbGFiZWxIaXN0b3J5Ij48aXRlbT48c2lzbCBzaXNsVmVyc2lvbj0iMCIgcG9saWN5PSJkZDIwZDIzOS1hN2U2LTRjNDktODc3Yy00NWI3YjQzMzU5Y2IiIG9yaWdpbj0iZGVmYXVsdFZhbHVlIj48ZWxlbWVudCB1aWQ9IjUwMjdiYTAxLWUyMjEtNDY1MC04N2M5LWI4ZWVkYTFmZWIyZiIgdmFsdWU9IiIgeG1sbnM9Imh0dHA6Ly93d3cuYm9sZG9uamFtZXMuY29tLzIwMDgvMDEvc2llL2ludGVybmFsL2xhYmVsIiAvPjwvc2lzbD48VXNlck5hbWU+QUxMSUFOWlxCRTAwMTUxPC9Vc2VyTmFtZT48RGF0ZVRpbWU+MTcvMDkvMjAxOSAxODoxMjoxMjwvRGF0ZVRpbWU+PExhYmVsU3RyaW5nPiAgICAgICAxNy8wOS8yMDE5ICBJTlRFUk5PICA8L0xhYmVsU3RyaW5nPjwvaXRlbT48L2xhYmVsSGlzdG9yeT4=</Value>
 </WrappedLabelHistory>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<sisl xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns="http://www.boldonjames.com/2008/01/sie/internal/label" sislVersion="0" policy="dd20d239-a7e6-4c49-877c-45b7b43359cb" origin="defaultValue">
-  <element uid="5027ba01-e221-4650-87c9-b8eeda1feb2f" value=""/>
-</sisl>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{758EF150-7616-48C2-9614-E853EDB7BDD0}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
+    <ds:schemaRef ds:uri="http://www.boldonjames.com/2008/01/sie/internal/label"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D7CACE11-ACDB-4C58-86FC-5A54EABF64E3}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
     <ds:schemaRef ds:uri="http://www.boldonjames.com/2016/02/Classifier/internal/wrappedLabelHistory"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{758EF150-7616-48C2-9614-E853EDB7BDD0}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
-    <ds:schemaRef ds:uri="http://www.boldonjames.com/2008/01/sie/internal/label"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>
--- a/Data Files/Backoffce/IndexacaoFG/IndexacaoFG_SANTANDER.xlsx
+++ b/Data Files/Backoffce/IndexacaoFG/IndexacaoFG_SANTANDER.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Public\RPA_ALLIANZ_TREINAMENTO\Data Files\Backoffce\IndexacaoFG\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C2C4C91F-E7AA-4705-8AB4-D0AF20FDC9AA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6DEFC5A0-A105-40D0-A6CC-F60FA1E8D28F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="128" uniqueCount="16">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="108" uniqueCount="12">
   <si>
     <t xml:space="preserve">status </t>
   </si>
@@ -54,28 +54,16 @@
     <t>1070</t>
   </si>
   <si>
-    <t>Relatório de Recusas 20.10.2025 a 26.10.2025</t>
-  </si>
-  <si>
-    <t>Relatório de Recusas Santander - 22/10/2025</t>
-  </si>
-  <si>
-    <t>134917784</t>
-  </si>
-  <si>
-    <t>134923879</t>
-  </si>
-  <si>
-    <t>134924247</t>
-  </si>
-  <si>
-    <t>134928778</t>
-  </si>
-  <si>
-    <t>134932121</t>
-  </si>
-  <si>
-    <t>134934017</t>
+    <t>Relatório de Recusas Santander - 23/10/2025</t>
+  </si>
+  <si>
+    <t>134952625</t>
+  </si>
+  <si>
+    <t>134953465</t>
+  </si>
+  <si>
+    <t>Relatório Recusa _ SICREDI_23.10.2025</t>
   </si>
 </sst>
 </file>
@@ -516,7 +504,7 @@
   <sheetPr>
     <pageSetUpPr autoPageBreaks="0"/>
   </sheetPr>
-  <dimension ref="A1:F30"/>
+  <dimension ref="A1:F26"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="2" width="16.7109375" style="1" customWidth="1" collapsed="1"/>
@@ -548,16 +536,16 @@
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A2" s="6">
-        <v>134849892</v>
+        <v>134893457</v>
       </c>
       <c r="B2" s="7" t="s">
         <v>7</v>
       </c>
       <c r="C2" s="8" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="E2" s="2" t="s">
         <v>6</v>
@@ -566,16 +554,16 @@
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A3" s="6">
-        <v>134903636</v>
+        <v>134952418</v>
       </c>
       <c r="B3" s="7" t="s">
         <v>7</v>
       </c>
       <c r="C3" s="8" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="E3" s="2" t="s">
         <v>6</v>
@@ -584,16 +572,16 @@
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" s="6">
-        <v>134913758</v>
+        <v>134942055</v>
       </c>
       <c r="B4" s="7" t="s">
         <v>7</v>
       </c>
       <c r="C4" s="8" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="E4" s="2" t="s">
         <v>6</v>
@@ -602,16 +590,16 @@
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" s="6">
-        <v>134928422</v>
+        <v>134995393</v>
       </c>
       <c r="B5" s="7" t="s">
         <v>7</v>
       </c>
       <c r="C5" s="8" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="E5" s="2" t="s">
         <v>6</v>
@@ -620,16 +608,16 @@
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" s="6">
-        <v>134965026</v>
+        <v>134953321</v>
       </c>
       <c r="B6" s="7" t="s">
         <v>7</v>
       </c>
       <c r="C6" s="8" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="E6" s="2" t="s">
         <v>6</v>
@@ -638,16 +626,16 @@
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" s="6">
-        <v>134972980</v>
+        <v>135048354</v>
       </c>
       <c r="B7" s="7" t="s">
         <v>7</v>
       </c>
       <c r="C7" s="8" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="E7" s="2" t="s">
         <v>6</v>
@@ -656,16 +644,16 @@
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" s="6">
-        <v>134986262</v>
+        <v>135059123</v>
       </c>
       <c r="B8" s="7" t="s">
         <v>7</v>
       </c>
       <c r="C8" s="8" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="E8" s="2" t="s">
         <v>6</v>
@@ -674,16 +662,16 @@
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" s="6">
-        <v>134987136</v>
+        <v>134877102</v>
       </c>
       <c r="B9" s="7" t="s">
         <v>7</v>
       </c>
       <c r="C9" s="8" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="E9" s="2" t="s">
         <v>6</v>
@@ -692,16 +680,16 @@
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A10" s="6">
-        <v>134986230</v>
+        <v>134877129</v>
       </c>
       <c r="B10" s="7" t="s">
         <v>7</v>
       </c>
       <c r="C10" s="8" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="E10" s="2" t="s">
         <v>6</v>
@@ -710,16 +698,16 @@
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A11" s="6">
-        <v>134988232</v>
+        <v>134877739</v>
       </c>
       <c r="B11" s="7" t="s">
         <v>7</v>
       </c>
       <c r="C11" s="8" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="E11" s="2" t="s">
         <v>6</v>
@@ -728,16 +716,16 @@
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A12" s="6">
-        <v>134988419</v>
+        <v>134878367</v>
       </c>
       <c r="B12" s="7" t="s">
         <v>7</v>
       </c>
       <c r="C12" s="8" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="E12" s="2" t="s">
         <v>6</v>
@@ -746,16 +734,16 @@
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A13" s="6">
-        <v>134993720</v>
+        <v>134880346</v>
       </c>
       <c r="B13" s="7" t="s">
         <v>7</v>
       </c>
       <c r="C13" s="8" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="E13" s="2" t="s">
         <v>6</v>
@@ -764,16 +752,16 @@
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A14" s="6">
-        <v>134996719</v>
+        <v>134890487</v>
       </c>
       <c r="B14" s="7" t="s">
         <v>7</v>
       </c>
       <c r="C14" s="8" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="E14" s="2" t="s">
         <v>6</v>
@@ -782,16 +770,16 @@
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A15" s="6">
-        <v>134998645</v>
+        <v>135028473</v>
       </c>
       <c r="B15" s="7" t="s">
         <v>7</v>
       </c>
       <c r="C15" s="8" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="E15" s="2" t="s">
         <v>6</v>
@@ -800,16 +788,16 @@
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A16" s="6">
-        <v>134986172</v>
+        <v>134938262</v>
       </c>
       <c r="B16" s="7" t="s">
         <v>7</v>
       </c>
       <c r="C16" s="8" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="E16" s="2" t="s">
         <v>6</v>
@@ -818,16 +806,16 @@
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A17" s="6">
-        <v>134990611</v>
+        <v>134942751</v>
       </c>
       <c r="B17" s="7" t="s">
         <v>7</v>
       </c>
       <c r="C17" s="8" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="E17" s="2" t="s">
         <v>6</v>
@@ -836,16 +824,16 @@
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A18" s="6">
-        <v>134988396</v>
+        <v>134942775</v>
       </c>
       <c r="B18" s="7" t="s">
         <v>7</v>
       </c>
       <c r="C18" s="8" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="E18" s="2" t="s">
         <v>6</v>
@@ -854,16 +842,16 @@
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A19" s="6">
-        <v>135029467</v>
+        <v>134943309</v>
       </c>
       <c r="B19" s="7" t="s">
         <v>7</v>
       </c>
       <c r="C19" s="8" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="E19" s="2" t="s">
         <v>6</v>
@@ -872,16 +860,16 @@
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A20" s="6">
-        <v>134861748</v>
+        <v>134943426</v>
       </c>
       <c r="B20" s="7" t="s">
         <v>7</v>
       </c>
       <c r="C20" s="8" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="E20" s="2" t="s">
         <v>6</v>
@@ -890,16 +878,16 @@
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A21" s="6">
-        <v>134858457</v>
+        <v>134943641</v>
       </c>
       <c r="B21" s="7" t="s">
         <v>7</v>
       </c>
       <c r="C21" s="8" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="E21" s="2" t="s">
         <v>6</v>
@@ -908,16 +896,16 @@
     </row>
     <row r="22" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A22" s="6">
-        <v>134948867</v>
+        <v>134948229</v>
       </c>
       <c r="B22" s="7" t="s">
         <v>7</v>
       </c>
       <c r="C22" s="8" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="E22" s="2" t="s">
         <v>6</v>
@@ -926,16 +914,16 @@
     </row>
     <row r="23" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A23" s="6">
-        <v>135049650</v>
+        <v>134950527</v>
       </c>
       <c r="B23" s="7" t="s">
         <v>7</v>
       </c>
       <c r="C23" s="8" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="E23" s="2" t="s">
         <v>6</v>
@@ -943,16 +931,16 @@
     </row>
     <row r="24" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A24" s="6">
-        <v>134916937</v>
+        <v>134950542</v>
       </c>
       <c r="B24" s="7" t="s">
         <v>7</v>
       </c>
       <c r="C24" s="8" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="E24" s="2" t="s">
         <v>6</v>
@@ -960,16 +948,16 @@
     </row>
     <row r="25" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A25" s="1" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B25" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C25" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D25" s="2" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="E25" s="2" t="s">
         <v>6</v>
@@ -977,86 +965,18 @@
     </row>
     <row r="26" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A26" s="1" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B26" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C26" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D26" s="2" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="E26" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="27" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A27" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="B27" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C27" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D27" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="E27" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="28" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A28" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="B28" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C28" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D28" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="E28" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="29" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A29" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="B29" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C29" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D29" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="E29" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="30" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A30" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="B30" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C30" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D30" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="E30" s="2" t="s">
         <v>6</v>
       </c>
     </row>

--- a/Data Files/Backoffce/IndexacaoFG/IndexacaoFG_SANTANDER.xlsx
+++ b/Data Files/Backoffce/IndexacaoFG/IndexacaoFG_SANTANDER.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Public\RPA_ALLIANZ_TREINAMENTO\Data Files\Backoffce\IndexacaoFG\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6DEFC5A0-A105-40D0-A6CC-F60FA1E8D28F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{45E918EE-F9E5-4C4A-ABB4-315BF675777F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="108" uniqueCount="12">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="138" uniqueCount="18">
   <si>
     <t xml:space="preserve">status </t>
   </si>
@@ -54,16 +54,34 @@
     <t>1070</t>
   </si>
   <si>
-    <t>Relatório de Recusas Santander - 23/10/2025</t>
-  </si>
-  <si>
-    <t>134952625</t>
-  </si>
-  <si>
-    <t>134953465</t>
-  </si>
-  <si>
-    <t>Relatório Recusa _ SICREDI_23.10.2025</t>
+    <t>Relatório de Recusas Santander - 24 e 25/10/2025</t>
+  </si>
+  <si>
+    <t>135055061</t>
+  </si>
+  <si>
+    <t>134885465</t>
+  </si>
+  <si>
+    <t>135045948</t>
+  </si>
+  <si>
+    <t>134876730</t>
+  </si>
+  <si>
+    <t>135085387</t>
+  </si>
+  <si>
+    <t>134879652</t>
+  </si>
+  <si>
+    <t>134880056</t>
+  </si>
+  <si>
+    <t>134887332</t>
+  </si>
+  <si>
+    <t>Relatório de Recusas 20.10.2025 a 26.10.2025</t>
   </si>
 </sst>
 </file>
@@ -504,7 +522,7 @@
   <sheetPr>
     <pageSetUpPr autoPageBreaks="0"/>
   </sheetPr>
-  <dimension ref="A1:F26"/>
+  <dimension ref="A1:F32"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="2" width="16.7109375" style="1" customWidth="1" collapsed="1"/>
@@ -536,7 +554,7 @@
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A2" s="6">
-        <v>134893457</v>
+        <v>134972460</v>
       </c>
       <c r="B2" s="7" t="s">
         <v>7</v>
@@ -545,7 +563,7 @@
         <v>8</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="E2" s="2" t="s">
         <v>6</v>
@@ -554,7 +572,7 @@
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A3" s="6">
-        <v>134952418</v>
+        <v>135004830</v>
       </c>
       <c r="B3" s="7" t="s">
         <v>7</v>
@@ -563,7 +581,7 @@
         <v>8</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="E3" s="2" t="s">
         <v>6</v>
@@ -572,7 +590,7 @@
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" s="6">
-        <v>134942055</v>
+        <v>135038927</v>
       </c>
       <c r="B4" s="7" t="s">
         <v>7</v>
@@ -581,7 +599,7 @@
         <v>8</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="E4" s="2" t="s">
         <v>6</v>
@@ -590,7 +608,7 @@
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" s="6">
-        <v>134995393</v>
+        <v>135049107</v>
       </c>
       <c r="B5" s="7" t="s">
         <v>7</v>
@@ -599,7 +617,7 @@
         <v>8</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="E5" s="2" t="s">
         <v>6</v>
@@ -608,7 +626,7 @@
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" s="6">
-        <v>134953321</v>
+        <v>135049760</v>
       </c>
       <c r="B6" s="7" t="s">
         <v>7</v>
@@ -617,7 +635,7 @@
         <v>8</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="E6" s="2" t="s">
         <v>6</v>
@@ -626,7 +644,7 @@
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" s="6">
-        <v>135048354</v>
+        <v>135061542</v>
       </c>
       <c r="B7" s="7" t="s">
         <v>7</v>
@@ -635,7 +653,7 @@
         <v>8</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="E7" s="2" t="s">
         <v>6</v>
@@ -644,7 +662,7 @@
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" s="6">
-        <v>135059123</v>
+        <v>135044623</v>
       </c>
       <c r="B8" s="7" t="s">
         <v>7</v>
@@ -653,7 +671,7 @@
         <v>8</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="E8" s="2" t="s">
         <v>6</v>
@@ -662,7 +680,7 @@
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" s="6">
-        <v>134877102</v>
+        <v>135077889</v>
       </c>
       <c r="B9" s="7" t="s">
         <v>7</v>
@@ -671,7 +689,7 @@
         <v>8</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="E9" s="2" t="s">
         <v>6</v>
@@ -680,7 +698,7 @@
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A10" s="6">
-        <v>134877129</v>
+        <v>135068531</v>
       </c>
       <c r="B10" s="7" t="s">
         <v>7</v>
@@ -689,7 +707,7 @@
         <v>8</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="E10" s="2" t="s">
         <v>6</v>
@@ -698,7 +716,7 @@
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A11" s="6">
-        <v>134877739</v>
+        <v>134887384</v>
       </c>
       <c r="B11" s="7" t="s">
         <v>7</v>
@@ -707,7 +725,7 @@
         <v>8</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="E11" s="2" t="s">
         <v>6</v>
@@ -716,7 +734,7 @@
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A12" s="6">
-        <v>134878367</v>
+        <v>134943834</v>
       </c>
       <c r="B12" s="7" t="s">
         <v>7</v>
@@ -725,7 +743,7 @@
         <v>8</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="E12" s="2" t="s">
         <v>6</v>
@@ -734,7 +752,7 @@
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A13" s="6">
-        <v>134880346</v>
+        <v>135017663</v>
       </c>
       <c r="B13" s="7" t="s">
         <v>7</v>
@@ -743,7 +761,7 @@
         <v>8</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="E13" s="2" t="s">
         <v>6</v>
@@ -752,7 +770,7 @@
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A14" s="6">
-        <v>134890487</v>
+        <v>134892653</v>
       </c>
       <c r="B14" s="7" t="s">
         <v>7</v>
@@ -761,7 +779,7 @@
         <v>8</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="E14" s="2" t="s">
         <v>6</v>
@@ -770,7 +788,7 @@
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A15" s="6">
-        <v>135028473</v>
+        <v>134921005</v>
       </c>
       <c r="B15" s="7" t="s">
         <v>7</v>
@@ -779,7 +797,7 @@
         <v>8</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="E15" s="2" t="s">
         <v>6</v>
@@ -788,7 +806,7 @@
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A16" s="6">
-        <v>134938262</v>
+        <v>135093130</v>
       </c>
       <c r="B16" s="7" t="s">
         <v>7</v>
@@ -797,7 +815,7 @@
         <v>8</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="E16" s="2" t="s">
         <v>6</v>
@@ -806,7 +824,7 @@
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A17" s="6">
-        <v>134942751</v>
+        <v>134960181</v>
       </c>
       <c r="B17" s="7" t="s">
         <v>7</v>
@@ -815,7 +833,7 @@
         <v>8</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="E17" s="2" t="s">
         <v>6</v>
@@ -824,7 +842,7 @@
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A18" s="6">
-        <v>134942775</v>
+        <v>134962517</v>
       </c>
       <c r="B18" s="7" t="s">
         <v>7</v>
@@ -833,7 +851,7 @@
         <v>8</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="E18" s="2" t="s">
         <v>6</v>
@@ -842,7 +860,7 @@
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A19" s="6">
-        <v>134943309</v>
+        <v>134963068</v>
       </c>
       <c r="B19" s="7" t="s">
         <v>7</v>
@@ -851,7 +869,7 @@
         <v>8</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="E19" s="2" t="s">
         <v>6</v>
@@ -860,7 +878,7 @@
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A20" s="6">
-        <v>134943426</v>
+        <v>134964653</v>
       </c>
       <c r="B20" s="7" t="s">
         <v>7</v>
@@ -869,7 +887,7 @@
         <v>8</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="E20" s="2" t="s">
         <v>6</v>
@@ -878,7 +896,7 @@
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A21" s="6">
-        <v>134943641</v>
+        <v>134972256</v>
       </c>
       <c r="B21" s="7" t="s">
         <v>7</v>
@@ -887,7 +905,7 @@
         <v>8</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="E21" s="2" t="s">
         <v>6</v>
@@ -896,7 +914,7 @@
     </row>
     <row r="22" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A22" s="6">
-        <v>134948229</v>
+        <v>134923009</v>
       </c>
       <c r="B22" s="7" t="s">
         <v>7</v>
@@ -905,7 +923,7 @@
         <v>8</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="E22" s="2" t="s">
         <v>6</v>
@@ -914,7 +932,7 @@
     </row>
     <row r="23" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A23" s="6">
-        <v>134950527</v>
+        <v>135019481</v>
       </c>
       <c r="B23" s="7" t="s">
         <v>7</v>
@@ -923,7 +941,7 @@
         <v>8</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="E23" s="2" t="s">
         <v>6</v>
@@ -931,7 +949,7 @@
     </row>
     <row r="24" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A24" s="6">
-        <v>134950542</v>
+        <v>134923904</v>
       </c>
       <c r="B24" s="7" t="s">
         <v>7</v>
@@ -940,7 +958,7 @@
         <v>8</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="E24" s="2" t="s">
         <v>6</v>
@@ -957,7 +975,7 @@
         <v>8</v>
       </c>
       <c r="D25" s="2" t="s">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="E25" s="2" t="s">
         <v>6</v>
@@ -974,9 +992,111 @@
         <v>8</v>
       </c>
       <c r="D26" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="E26" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="27" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A27" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="E26" s="2" t="s">
+      <c r="B27" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C27" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D27" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="E27" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="28" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A28" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="B28" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C28" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D28" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="E28" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="29" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A29" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="B29" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C29" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D29" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="E29" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="30" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A30" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="B30" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C30" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D30" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="E30" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="31" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A31" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="B31" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C31" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D31" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="E31" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="32" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A32" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="B32" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C32" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D32" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="E32" s="2" t="s">
         <v>6</v>
       </c>
     </row>
@@ -994,31 +1114,31 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<WrappedLabelHistory xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns="http://www.boldonjames.com/2016/02/Classifier/internal/wrappedLabelHistory">
+  <Value>PD94bWwgdmVyc2lvbj0iMS4wIiBlbmNvZGluZz0idXMtYXNjaWkiPz48bGFiZWxIaXN0b3J5IHhtbG5zOnhzZD0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEiIHhtbG5zOnhzaT0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEtaW5zdGFuY2UiIHhtbG5zPSJodHRwOi8vd3d3LmJvbGRvbmphbWVzLmNvbS8yMDE2LzAyL0NsYXNzaWZpZXIvaW50ZXJuYWwvbGFiZWxIaXN0b3J5Ij48aXRlbT48c2lzbCBzaXNsVmVyc2lvbj0iMCIgcG9saWN5PSJkZDIwZDIzOS1hN2U2LTRjNDktODc3Yy00NWI3YjQzMzU5Y2IiIG9yaWdpbj0iZGVmYXVsdFZhbHVlIj48ZWxlbWVudCB1aWQ9IjUwMjdiYTAxLWUyMjEtNDY1MC04N2M5LWI4ZWVkYTFmZWIyZiIgdmFsdWU9IiIgeG1sbnM9Imh0dHA6Ly93d3cuYm9sZG9uamFtZXMuY29tLzIwMDgvMDEvc2llL2ludGVybmFsL2xhYmVsIiAvPjwvc2lzbD48VXNlck5hbWU+QUxMSUFOWlxCRTAwMTUxPC9Vc2VyTmFtZT48RGF0ZVRpbWU+MTcvMDkvMjAxOSAxODoxMjoxMjwvRGF0ZVRpbWU+PExhYmVsU3RyaW5nPiAgICAgICAxNy8wOS8yMDE5ICBJTlRFUk5PICA8L0xhYmVsU3RyaW5nPjwvaXRlbT48L2xhYmVsSGlzdG9yeT4=</Value>
+</WrappedLabelHistory>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <sisl xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns="http://www.boldonjames.com/2008/01/sie/internal/label" sislVersion="0" policy="dd20d239-a7e6-4c49-877c-45b7b43359cb" origin="defaultValue">
   <element uid="5027ba01-e221-4650-87c9-b8eeda1feb2f" value=""/>
 </sisl>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<WrappedLabelHistory xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns="http://www.boldonjames.com/2016/02/Classifier/internal/wrappedLabelHistory">
-  <Value>PD94bWwgdmVyc2lvbj0iMS4wIiBlbmNvZGluZz0idXMtYXNjaWkiPz48bGFiZWxIaXN0b3J5IHhtbG5zOnhzZD0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEiIHhtbG5zOnhzaT0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEtaW5zdGFuY2UiIHhtbG5zPSJodHRwOi8vd3d3LmJvbGRvbmphbWVzLmNvbS8yMDE2LzAyL0NsYXNzaWZpZXIvaW50ZXJuYWwvbGFiZWxIaXN0b3J5Ij48aXRlbT48c2lzbCBzaXNsVmVyc2lvbj0iMCIgcG9saWN5PSJkZDIwZDIzOS1hN2U2LTRjNDktODc3Yy00NWI3YjQzMzU5Y2IiIG9yaWdpbj0iZGVmYXVsdFZhbHVlIj48ZWxlbWVudCB1aWQ9IjUwMjdiYTAxLWUyMjEtNDY1MC04N2M5LWI4ZWVkYTFmZWIyZiIgdmFsdWU9IiIgeG1sbnM9Imh0dHA6Ly93d3cuYm9sZG9uamFtZXMuY29tLzIwMDgvMDEvc2llL2ludGVybmFsL2xhYmVsIiAvPjwvc2lzbD48VXNlck5hbWU+QUxMSUFOWlxCRTAwMTUxPC9Vc2VyTmFtZT48RGF0ZVRpbWU+MTcvMDkvMjAxOSAxODoxMjoxMjwvRGF0ZVRpbWU+PExhYmVsU3RyaW5nPiAgICAgICAxNy8wOS8yMDE5ICBJTlRFUk5PICA8L0xhYmVsU3RyaW5nPjwvaXRlbT48L2xhYmVsSGlzdG9yeT4=</Value>
-</WrappedLabelHistory>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D7CACE11-ACDB-4C58-86FC-5A54EABF64E3}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
+    <ds:schemaRef ds:uri="http://www.boldonjames.com/2016/02/Classifier/internal/wrappedLabelHistory"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{758EF150-7616-48C2-9614-E853EDB7BDD0}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
     <ds:schemaRef ds:uri="http://www.boldonjames.com/2008/01/sie/internal/label"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D7CACE11-ACDB-4C58-86FC-5A54EABF64E3}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
-    <ds:schemaRef ds:uri="http://www.boldonjames.com/2016/02/Classifier/internal/wrappedLabelHistory"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>
--- a/Data Files/Backoffce/IndexacaoFG/IndexacaoFG_SANTANDER.xlsx
+++ b/Data Files/Backoffce/IndexacaoFG/IndexacaoFG_SANTANDER.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Public\RPA_ALLIANZ_TREINAMENTO\Data Files\Backoffce\IndexacaoFG\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{45E918EE-F9E5-4C4A-ABB4-315BF675777F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C4CF2C49-238E-4CD2-8654-75228853F153}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="138" uniqueCount="18">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="183" uniqueCount="28">
   <si>
     <t xml:space="preserve">status </t>
   </si>
@@ -54,34 +54,64 @@
     <t>1070</t>
   </si>
   <si>
-    <t>Relatório de Recusas Santander - 24 e 25/10/2025</t>
-  </si>
-  <si>
-    <t>135055061</t>
-  </si>
-  <si>
-    <t>134885465</t>
-  </si>
-  <si>
-    <t>135045948</t>
-  </si>
-  <si>
-    <t>134876730</t>
-  </si>
-  <si>
-    <t>135085387</t>
-  </si>
-  <si>
-    <t>134879652</t>
-  </si>
-  <si>
-    <t>134880056</t>
-  </si>
-  <si>
-    <t>134887332</t>
-  </si>
-  <si>
-    <t>Relatório de Recusas 20.10.2025 a 26.10.2025</t>
+    <t>Relatório de Recusas Santander - 27/10/2025</t>
+  </si>
+  <si>
+    <t>135054365</t>
+  </si>
+  <si>
+    <t>135028570</t>
+  </si>
+  <si>
+    <t>134932306</t>
+  </si>
+  <si>
+    <t>135050900</t>
+  </si>
+  <si>
+    <t>134963451</t>
+  </si>
+  <si>
+    <t>134994340</t>
+  </si>
+  <si>
+    <t>134988980</t>
+  </si>
+  <si>
+    <t>135033815</t>
+  </si>
+  <si>
+    <t>135054537</t>
+  </si>
+  <si>
+    <t>135055563</t>
+  </si>
+  <si>
+    <t>134983887</t>
+  </si>
+  <si>
+    <t>134986277</t>
+  </si>
+  <si>
+    <t>134995666</t>
+  </si>
+  <si>
+    <t>134996771</t>
+  </si>
+  <si>
+    <t>134999685</t>
+  </si>
+  <si>
+    <t>135051340</t>
+  </si>
+  <si>
+    <t>135073583</t>
+  </si>
+  <si>
+    <t>Relatório de Recusas 27.10.2025 a 02.11.2025</t>
+  </si>
+  <si>
+    <t>vRelatório de Recusas 27.10.2025 a 02.11.2025</t>
   </si>
 </sst>
 </file>
@@ -522,7 +552,7 @@
   <sheetPr>
     <pageSetUpPr autoPageBreaks="0"/>
   </sheetPr>
-  <dimension ref="A1:F32"/>
+  <dimension ref="A1:F41"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="2" width="16.7109375" style="1" customWidth="1" collapsed="1"/>
@@ -554,7 +584,7 @@
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A2" s="6">
-        <v>134972460</v>
+        <v>134971230</v>
       </c>
       <c r="B2" s="7" t="s">
         <v>7</v>
@@ -563,7 +593,7 @@
         <v>8</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>17</v>
+        <v>26</v>
       </c>
       <c r="E2" s="2" t="s">
         <v>6</v>
@@ -572,7 +602,7 @@
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A3" s="6">
-        <v>135004830</v>
+        <v>134988741</v>
       </c>
       <c r="B3" s="7" t="s">
         <v>7</v>
@@ -581,7 +611,7 @@
         <v>8</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>17</v>
+        <v>26</v>
       </c>
       <c r="E3" s="2" t="s">
         <v>6</v>
@@ -590,7 +620,7 @@
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" s="6">
-        <v>135038927</v>
+        <v>134987327</v>
       </c>
       <c r="B4" s="7" t="s">
         <v>7</v>
@@ -599,7 +629,7 @@
         <v>8</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>17</v>
+        <v>26</v>
       </c>
       <c r="E4" s="2" t="s">
         <v>6</v>
@@ -608,7 +638,7 @@
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" s="6">
-        <v>135049107</v>
+        <v>135019736</v>
       </c>
       <c r="B5" s="7" t="s">
         <v>7</v>
@@ -617,7 +647,7 @@
         <v>8</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>17</v>
+        <v>26</v>
       </c>
       <c r="E5" s="2" t="s">
         <v>6</v>
@@ -626,7 +656,7 @@
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" s="6">
-        <v>135049760</v>
+        <v>135015163</v>
       </c>
       <c r="B6" s="7" t="s">
         <v>7</v>
@@ -635,7 +665,7 @@
         <v>8</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>17</v>
+        <v>27</v>
       </c>
       <c r="E6" s="2" t="s">
         <v>6</v>
@@ -644,7 +674,7 @@
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" s="6">
-        <v>135061542</v>
+        <v>135026243</v>
       </c>
       <c r="B7" s="7" t="s">
         <v>7</v>
@@ -653,7 +683,7 @@
         <v>8</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>17</v>
+        <v>26</v>
       </c>
       <c r="E7" s="2" t="s">
         <v>6</v>
@@ -662,7 +692,7 @@
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" s="6">
-        <v>135044623</v>
+        <v>135046529</v>
       </c>
       <c r="B8" s="7" t="s">
         <v>7</v>
@@ -671,7 +701,7 @@
         <v>8</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>17</v>
+        <v>26</v>
       </c>
       <c r="E8" s="2" t="s">
         <v>6</v>
@@ -680,7 +710,7 @@
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" s="6">
-        <v>135077889</v>
+        <v>135048698</v>
       </c>
       <c r="B9" s="7" t="s">
         <v>7</v>
@@ -689,7 +719,7 @@
         <v>8</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>17</v>
+        <v>26</v>
       </c>
       <c r="E9" s="2" t="s">
         <v>6</v>
@@ -698,7 +728,7 @@
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A10" s="6">
-        <v>135068531</v>
+        <v>135048914</v>
       </c>
       <c r="B10" s="7" t="s">
         <v>7</v>
@@ -707,7 +737,7 @@
         <v>8</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>17</v>
+        <v>26</v>
       </c>
       <c r="E10" s="2" t="s">
         <v>6</v>
@@ -716,7 +746,7 @@
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A11" s="6">
-        <v>134887384</v>
+        <v>135050384</v>
       </c>
       <c r="B11" s="7" t="s">
         <v>7</v>
@@ -725,7 +755,7 @@
         <v>8</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>17</v>
+        <v>26</v>
       </c>
       <c r="E11" s="2" t="s">
         <v>6</v>
@@ -734,7 +764,7 @@
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A12" s="6">
-        <v>134943834</v>
+        <v>135049543</v>
       </c>
       <c r="B12" s="7" t="s">
         <v>7</v>
@@ -743,7 +773,7 @@
         <v>8</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>17</v>
+        <v>26</v>
       </c>
       <c r="E12" s="2" t="s">
         <v>6</v>
@@ -752,7 +782,7 @@
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A13" s="6">
-        <v>135017663</v>
+        <v>135050051</v>
       </c>
       <c r="B13" s="7" t="s">
         <v>7</v>
@@ -761,7 +791,7 @@
         <v>8</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>17</v>
+        <v>26</v>
       </c>
       <c r="E13" s="2" t="s">
         <v>6</v>
@@ -770,7 +800,7 @@
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A14" s="6">
-        <v>134892653</v>
+        <v>135044777</v>
       </c>
       <c r="B14" s="7" t="s">
         <v>7</v>
@@ -779,7 +809,7 @@
         <v>8</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>17</v>
+        <v>27</v>
       </c>
       <c r="E14" s="2" t="s">
         <v>6</v>
@@ -788,7 +818,7 @@
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A15" s="6">
-        <v>134921005</v>
+        <v>135052121</v>
       </c>
       <c r="B15" s="7" t="s">
         <v>7</v>
@@ -797,7 +827,7 @@
         <v>8</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>17</v>
+        <v>26</v>
       </c>
       <c r="E15" s="2" t="s">
         <v>6</v>
@@ -806,7 +836,7 @@
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A16" s="6">
-        <v>135093130</v>
+        <v>135060115</v>
       </c>
       <c r="B16" s="7" t="s">
         <v>7</v>
@@ -815,7 +845,7 @@
         <v>8</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>17</v>
+        <v>26</v>
       </c>
       <c r="E16" s="2" t="s">
         <v>6</v>
@@ -824,7 +854,7 @@
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A17" s="6">
-        <v>134960181</v>
+        <v>135048549</v>
       </c>
       <c r="B17" s="7" t="s">
         <v>7</v>
@@ -833,7 +863,7 @@
         <v>8</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>17</v>
+        <v>26</v>
       </c>
       <c r="E17" s="2" t="s">
         <v>6</v>
@@ -842,7 +872,7 @@
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A18" s="6">
-        <v>134962517</v>
+        <v>135056897</v>
       </c>
       <c r="B18" s="7" t="s">
         <v>7</v>
@@ -851,7 +881,7 @@
         <v>8</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>17</v>
+        <v>26</v>
       </c>
       <c r="E18" s="2" t="s">
         <v>6</v>
@@ -860,7 +890,7 @@
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A19" s="6">
-        <v>134963068</v>
+        <v>135083023</v>
       </c>
       <c r="B19" s="7" t="s">
         <v>7</v>
@@ -869,7 +899,7 @@
         <v>8</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>17</v>
+        <v>26</v>
       </c>
       <c r="E19" s="2" t="s">
         <v>6</v>
@@ -878,7 +908,7 @@
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A20" s="6">
-        <v>134964653</v>
+        <v>135058343</v>
       </c>
       <c r="B20" s="7" t="s">
         <v>7</v>
@@ -887,7 +917,7 @@
         <v>8</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>17</v>
+        <v>26</v>
       </c>
       <c r="E20" s="2" t="s">
         <v>6</v>
@@ -896,7 +926,7 @@
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A21" s="6">
-        <v>134972256</v>
+        <v>135090745</v>
       </c>
       <c r="B21" s="7" t="s">
         <v>7</v>
@@ -905,7 +935,7 @@
         <v>8</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>17</v>
+        <v>26</v>
       </c>
       <c r="E21" s="2" t="s">
         <v>6</v>
@@ -914,7 +944,7 @@
     </row>
     <row r="22" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A22" s="6">
-        <v>134923009</v>
+        <v>135052917</v>
       </c>
       <c r="B22" s="7" t="s">
         <v>7</v>
@@ -923,7 +953,7 @@
         <v>8</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>17</v>
+        <v>27</v>
       </c>
       <c r="E22" s="2" t="s">
         <v>6</v>
@@ -932,7 +962,7 @@
     </row>
     <row r="23" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A23" s="6">
-        <v>135019481</v>
+        <v>135094626</v>
       </c>
       <c r="B23" s="7" t="s">
         <v>7</v>
@@ -941,7 +971,7 @@
         <v>8</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>17</v>
+        <v>26</v>
       </c>
       <c r="E23" s="2" t="s">
         <v>6</v>
@@ -949,7 +979,7 @@
     </row>
     <row r="24" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A24" s="6">
-        <v>134923904</v>
+        <v>134918888</v>
       </c>
       <c r="B24" s="7" t="s">
         <v>7</v>
@@ -958,7 +988,7 @@
         <v>8</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>17</v>
+        <v>26</v>
       </c>
       <c r="E24" s="2" t="s">
         <v>6</v>
@@ -975,7 +1005,7 @@
         <v>8</v>
       </c>
       <c r="D25" s="2" t="s">
-        <v>17</v>
+        <v>26</v>
       </c>
       <c r="E25" s="2" t="s">
         <v>6</v>
@@ -992,7 +1022,7 @@
         <v>8</v>
       </c>
       <c r="D26" s="2" t="s">
-        <v>17</v>
+        <v>26</v>
       </c>
       <c r="E26" s="2" t="s">
         <v>6</v>
@@ -1009,7 +1039,7 @@
         <v>8</v>
       </c>
       <c r="D27" s="2" t="s">
-        <v>17</v>
+        <v>26</v>
       </c>
       <c r="E27" s="2" t="s">
         <v>6</v>
@@ -1026,7 +1056,7 @@
         <v>8</v>
       </c>
       <c r="D28" s="2" t="s">
-        <v>17</v>
+        <v>26</v>
       </c>
       <c r="E28" s="2" t="s">
         <v>6</v>
@@ -1043,7 +1073,7 @@
         <v>8</v>
       </c>
       <c r="D29" s="2" t="s">
-        <v>17</v>
+        <v>26</v>
       </c>
       <c r="E29" s="2" t="s">
         <v>6</v>
@@ -1060,7 +1090,7 @@
         <v>8</v>
       </c>
       <c r="D30" s="2" t="s">
-        <v>17</v>
+        <v>27</v>
       </c>
       <c r="E30" s="2" t="s">
         <v>6</v>
@@ -1077,7 +1107,7 @@
         <v>8</v>
       </c>
       <c r="D31" s="2" t="s">
-        <v>17</v>
+        <v>26</v>
       </c>
       <c r="E31" s="2" t="s">
         <v>6</v>
@@ -1094,9 +1124,162 @@
         <v>8</v>
       </c>
       <c r="D32" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="E32" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="33" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A33" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="E32" s="2" t="s">
+      <c r="B33" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C33" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D33" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="E33" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="34" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A34" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="B34" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C34" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D34" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="E34" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="35" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A35" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="B35" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C35" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D35" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="E35" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="36" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A36" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="B36" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C36" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D36" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="E36" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="37" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A37" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="B37" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C37" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D37" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="E37" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="38" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A38" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="B38" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C38" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D38" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="E38" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="39" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A39" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="B39" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C39" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D39" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="E39" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="40" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A40" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="B40" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C40" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D40" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="E40" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="41" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A41" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="B41" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C41" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D41" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="E41" s="2" t="s">
         <v>6</v>
       </c>
     </row>
@@ -1114,31 +1297,31 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<sisl xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns="http://www.boldonjames.com/2008/01/sie/internal/label" sislVersion="0" policy="dd20d239-a7e6-4c49-877c-45b7b43359cb" origin="defaultValue">
+  <element uid="5027ba01-e221-4650-87c9-b8eeda1feb2f" value=""/>
+</sisl>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <WrappedLabelHistory xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns="http://www.boldonjames.com/2016/02/Classifier/internal/wrappedLabelHistory">
   <Value>PD94bWwgdmVyc2lvbj0iMS4wIiBlbmNvZGluZz0idXMtYXNjaWkiPz48bGFiZWxIaXN0b3J5IHhtbG5zOnhzZD0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEiIHhtbG5zOnhzaT0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEtaW5zdGFuY2UiIHhtbG5zPSJodHRwOi8vd3d3LmJvbGRvbmphbWVzLmNvbS8yMDE2LzAyL0NsYXNzaWZpZXIvaW50ZXJuYWwvbGFiZWxIaXN0b3J5Ij48aXRlbT48c2lzbCBzaXNsVmVyc2lvbj0iMCIgcG9saWN5PSJkZDIwZDIzOS1hN2U2LTRjNDktODc3Yy00NWI3YjQzMzU5Y2IiIG9yaWdpbj0iZGVmYXVsdFZhbHVlIj48ZWxlbWVudCB1aWQ9IjUwMjdiYTAxLWUyMjEtNDY1MC04N2M5LWI4ZWVkYTFmZWIyZiIgdmFsdWU9IiIgeG1sbnM9Imh0dHA6Ly93d3cuYm9sZG9uamFtZXMuY29tLzIwMDgvMDEvc2llL2ludGVybmFsL2xhYmVsIiAvPjwvc2lzbD48VXNlck5hbWU+QUxMSUFOWlxCRTAwMTUxPC9Vc2VyTmFtZT48RGF0ZVRpbWU+MTcvMDkvMjAxOSAxODoxMjoxMjwvRGF0ZVRpbWU+PExhYmVsU3RyaW5nPiAgICAgICAxNy8wOS8yMDE5ICBJTlRFUk5PICA8L0xhYmVsU3RyaW5nPjwvaXRlbT48L2xhYmVsSGlzdG9yeT4=</Value>
 </WrappedLabelHistory>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<sisl xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns="http://www.boldonjames.com/2008/01/sie/internal/label" sislVersion="0" policy="dd20d239-a7e6-4c49-877c-45b7b43359cb" origin="defaultValue">
-  <element uid="5027ba01-e221-4650-87c9-b8eeda1feb2f" value=""/>
-</sisl>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{758EF150-7616-48C2-9614-E853EDB7BDD0}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
+    <ds:schemaRef ds:uri="http://www.boldonjames.com/2008/01/sie/internal/label"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D7CACE11-ACDB-4C58-86FC-5A54EABF64E3}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
     <ds:schemaRef ds:uri="http://www.boldonjames.com/2016/02/Classifier/internal/wrappedLabelHistory"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{758EF150-7616-48C2-9614-E853EDB7BDD0}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
-    <ds:schemaRef ds:uri="http://www.boldonjames.com/2008/01/sie/internal/label"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>
--- a/Data Files/Backoffce/IndexacaoFG/IndexacaoFG_SANTANDER.xlsx
+++ b/Data Files/Backoffce/IndexacaoFG/IndexacaoFG_SANTANDER.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Public\RPA_ALLIANZ_TREINAMENTO\Data Files\Backoffce\IndexacaoFG\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C4CF2C49-238E-4CD2-8654-75228853F153}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0E2139C2-87C7-4017-89D5-761E09E05504}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="183" uniqueCount="28">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="183" uniqueCount="27">
   <si>
     <t xml:space="preserve">status </t>
   </si>
@@ -109,9 +109,6 @@
   </si>
   <si>
     <t>Relatório de Recusas 27.10.2025 a 02.11.2025</t>
-  </si>
-  <si>
-    <t>vRelatório de Recusas 27.10.2025 a 02.11.2025</t>
   </si>
 </sst>
 </file>
@@ -665,7 +662,7 @@
         <v>8</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="E6" s="2" t="s">
         <v>6</v>
@@ -809,7 +806,7 @@
         <v>8</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="E14" s="2" t="s">
         <v>6</v>
@@ -953,7 +950,7 @@
         <v>8</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="E22" s="2" t="s">
         <v>6</v>
@@ -1090,7 +1087,7 @@
         <v>8</v>
       </c>
       <c r="D30" s="2" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="E30" s="2" t="s">
         <v>6</v>
@@ -1226,7 +1223,7 @@
         <v>8</v>
       </c>
       <c r="D38" s="2" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="E38" s="2" t="s">
         <v>6</v>
@@ -1297,31 +1294,31 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<WrappedLabelHistory xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns="http://www.boldonjames.com/2016/02/Classifier/internal/wrappedLabelHistory">
+  <Value>PD94bWwgdmVyc2lvbj0iMS4wIiBlbmNvZGluZz0idXMtYXNjaWkiPz48bGFiZWxIaXN0b3J5IHhtbG5zOnhzZD0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEiIHhtbG5zOnhzaT0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEtaW5zdGFuY2UiIHhtbG5zPSJodHRwOi8vd3d3LmJvbGRvbmphbWVzLmNvbS8yMDE2LzAyL0NsYXNzaWZpZXIvaW50ZXJuYWwvbGFiZWxIaXN0b3J5Ij48aXRlbT48c2lzbCBzaXNsVmVyc2lvbj0iMCIgcG9saWN5PSJkZDIwZDIzOS1hN2U2LTRjNDktODc3Yy00NWI3YjQzMzU5Y2IiIG9yaWdpbj0iZGVmYXVsdFZhbHVlIj48ZWxlbWVudCB1aWQ9IjUwMjdiYTAxLWUyMjEtNDY1MC04N2M5LWI4ZWVkYTFmZWIyZiIgdmFsdWU9IiIgeG1sbnM9Imh0dHA6Ly93d3cuYm9sZG9uamFtZXMuY29tLzIwMDgvMDEvc2llL2ludGVybmFsL2xhYmVsIiAvPjwvc2lzbD48VXNlck5hbWU+QUxMSUFOWlxCRTAwMTUxPC9Vc2VyTmFtZT48RGF0ZVRpbWU+MTcvMDkvMjAxOSAxODoxMjoxMjwvRGF0ZVRpbWU+PExhYmVsU3RyaW5nPiAgICAgICAxNy8wOS8yMDE5ICBJTlRFUk5PICA8L0xhYmVsU3RyaW5nPjwvaXRlbT48L2xhYmVsSGlzdG9yeT4=</Value>
+</WrappedLabelHistory>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <sisl xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns="http://www.boldonjames.com/2008/01/sie/internal/label" sislVersion="0" policy="dd20d239-a7e6-4c49-877c-45b7b43359cb" origin="defaultValue">
   <element uid="5027ba01-e221-4650-87c9-b8eeda1feb2f" value=""/>
 </sisl>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<WrappedLabelHistory xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns="http://www.boldonjames.com/2016/02/Classifier/internal/wrappedLabelHistory">
-  <Value>PD94bWwgdmVyc2lvbj0iMS4wIiBlbmNvZGluZz0idXMtYXNjaWkiPz48bGFiZWxIaXN0b3J5IHhtbG5zOnhzZD0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEiIHhtbG5zOnhzaT0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEtaW5zdGFuY2UiIHhtbG5zPSJodHRwOi8vd3d3LmJvbGRvbmphbWVzLmNvbS8yMDE2LzAyL0NsYXNzaWZpZXIvaW50ZXJuYWwvbGFiZWxIaXN0b3J5Ij48aXRlbT48c2lzbCBzaXNsVmVyc2lvbj0iMCIgcG9saWN5PSJkZDIwZDIzOS1hN2U2LTRjNDktODc3Yy00NWI3YjQzMzU5Y2IiIG9yaWdpbj0iZGVmYXVsdFZhbHVlIj48ZWxlbWVudCB1aWQ9IjUwMjdiYTAxLWUyMjEtNDY1MC04N2M5LWI4ZWVkYTFmZWIyZiIgdmFsdWU9IiIgeG1sbnM9Imh0dHA6Ly93d3cuYm9sZG9uamFtZXMuY29tLzIwMDgvMDEvc2llL2ludGVybmFsL2xhYmVsIiAvPjwvc2lzbD48VXNlck5hbWU+QUxMSUFOWlxCRTAwMTUxPC9Vc2VyTmFtZT48RGF0ZVRpbWU+MTcvMDkvMjAxOSAxODoxMjoxMjwvRGF0ZVRpbWU+PExhYmVsU3RyaW5nPiAgICAgICAxNy8wOS8yMDE5ICBJTlRFUk5PICA8L0xhYmVsU3RyaW5nPjwvaXRlbT48L2xhYmVsSGlzdG9yeT4=</Value>
-</WrappedLabelHistory>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D7CACE11-ACDB-4C58-86FC-5A54EABF64E3}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
+    <ds:schemaRef ds:uri="http://www.boldonjames.com/2016/02/Classifier/internal/wrappedLabelHistory"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{758EF150-7616-48C2-9614-E853EDB7BDD0}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
     <ds:schemaRef ds:uri="http://www.boldonjames.com/2008/01/sie/internal/label"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D7CACE11-ACDB-4C58-86FC-5A54EABF64E3}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
-    <ds:schemaRef ds:uri="http://www.boldonjames.com/2016/02/Classifier/internal/wrappedLabelHistory"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>
--- a/Data Files/Backoffce/IndexacaoFG/IndexacaoFG_SANTANDER.xlsx
+++ b/Data Files/Backoffce/IndexacaoFG/IndexacaoFG_SANTANDER.xlsx
@@ -1,26 +1,26 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28526"/>
   <workbookPr/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+  <mc:AlternateContent>
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Public\RPA_ALLIANZ\Data Files\Backoffce\IndexacaoFG\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4887EE85-61A5-47CB-9058-744FBEC34B82}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr documentId="13_ncr:1_{734C95E8-9775-4541-8C9E-C2D9F24124F1}" revIDLastSave="0" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView windowHeight="11040" windowWidth="20730" xWindow="-120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}" yWindow="-120"/>
   </bookViews>
   <sheets>
-    <sheet name="IndexacaoFG" sheetId="2" r:id="rId1"/>
+    <sheet name="IndexacaoFG" r:id="rId1" sheetId="2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">IndexacaoFG!$A$1:$F$1</definedName>
+    <definedName hidden="1" localSheetId="0" name="_xlnm._FilterDatabase">IndexacaoFG!$A$1:$F$1</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
+    <ext uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
     </ext>
   </extLst>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="200" uniqueCount="48">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="287" uniqueCount="57">
   <si>
     <t xml:space="preserve">status </t>
   </si>
@@ -54,130 +54,158 @@
     <t>1070</t>
   </si>
   <si>
-    <t>Relatório de Recusas Santander - 03/10/2025</t>
-  </si>
-  <si>
-    <t>134630588</t>
-  </si>
-  <si>
-    <t>134631642</t>
-  </si>
-  <si>
-    <t>134631902</t>
-  </si>
-  <si>
-    <t>134644776</t>
-  </si>
-  <si>
-    <t>134645078</t>
-  </si>
-  <si>
-    <t>134630168</t>
-  </si>
-  <si>
-    <t>134637870</t>
-  </si>
-  <si>
-    <t>134646160</t>
-  </si>
-  <si>
-    <t>134648203</t>
-  </si>
-  <si>
-    <t>134637222</t>
-  </si>
-  <si>
-    <t>134699927</t>
-  </si>
-  <si>
-    <t>134722689</t>
-  </si>
-  <si>
-    <t>134727905</t>
-  </si>
-  <si>
-    <t>134747801</t>
-  </si>
-  <si>
-    <t>134566818</t>
-  </si>
-  <si>
-    <t>134637978</t>
-  </si>
-  <si>
-    <t>134647433</t>
-  </si>
-  <si>
-    <t>134629910</t>
-  </si>
-  <si>
-    <t>134631070</t>
-  </si>
-  <si>
-    <t>134633551</t>
-  </si>
-  <si>
-    <t>134634707</t>
-  </si>
-  <si>
-    <t>134637895</t>
-  </si>
-  <si>
-    <t>134639039</t>
-  </si>
-  <si>
-    <t>134639101</t>
-  </si>
-  <si>
-    <t>134640911</t>
-  </si>
-  <si>
-    <t>134641271</t>
-  </si>
-  <si>
-    <t>134644302</t>
-  </si>
-  <si>
-    <t>134647847</t>
-  </si>
-  <si>
-    <t>134648345</t>
-  </si>
-  <si>
-    <t>134648372</t>
-  </si>
-  <si>
-    <t>134579478</t>
-  </si>
-  <si>
-    <t>134666219</t>
-  </si>
-  <si>
-    <t>134658516</t>
-  </si>
-  <si>
-    <t>134653593</t>
-  </si>
-  <si>
-    <t>134665969</t>
-  </si>
-  <si>
-    <t>134747373</t>
-  </si>
-  <si>
-    <t>134550866</t>
-  </si>
-  <si>
-    <t>134669267</t>
-  </si>
-  <si>
-    <t>Relatório de Recusas  29.09.2025 a 05.10.2025 (1)</t>
+    <t>Relatório de Recusas 17.12.2025 a 24.12.2025</t>
+  </si>
+  <si>
+    <t>Relatório de Recusas Santander - 18.12.2025</t>
+  </si>
+  <si>
+    <t>135734427</t>
+  </si>
+  <si>
+    <t>135754186</t>
+  </si>
+  <si>
+    <t>135748063</t>
+  </si>
+  <si>
+    <t>135756398</t>
+  </si>
+  <si>
+    <t>135774211</t>
+  </si>
+  <si>
+    <t>135792516</t>
+  </si>
+  <si>
+    <t>135824778</t>
+  </si>
+  <si>
+    <t>135826371</t>
+  </si>
+  <si>
+    <t>135842081</t>
+  </si>
+  <si>
+    <t>135841199</t>
+  </si>
+  <si>
+    <t>135843448</t>
+  </si>
+  <si>
+    <t>135832589</t>
+  </si>
+  <si>
+    <t>135838725</t>
+  </si>
+  <si>
+    <t>135845288</t>
+  </si>
+  <si>
+    <t>135843233</t>
+  </si>
+  <si>
+    <t>135827636</t>
+  </si>
+  <si>
+    <t>135841511</t>
+  </si>
+  <si>
+    <t>135827103</t>
+  </si>
+  <si>
+    <t>135830047</t>
+  </si>
+  <si>
+    <t>135830570</t>
+  </si>
+  <si>
+    <t>135807456</t>
+  </si>
+  <si>
+    <t>135904291</t>
+  </si>
+  <si>
+    <t>135902313</t>
+  </si>
+  <si>
+    <t>135819352</t>
+  </si>
+  <si>
+    <t>135723618</t>
+  </si>
+  <si>
+    <t>135717557</t>
+  </si>
+  <si>
+    <t>135673204</t>
+  </si>
+  <si>
+    <t>135718964</t>
+  </si>
+  <si>
+    <t>135796375</t>
+  </si>
+  <si>
+    <t>135845061</t>
+  </si>
+  <si>
+    <t>135831981</t>
+  </si>
+  <si>
+    <t>135829936</t>
+  </si>
+  <si>
+    <t>135844741</t>
+  </si>
+  <si>
+    <t>135717757</t>
+  </si>
+  <si>
+    <t>135726634</t>
+  </si>
+  <si>
+    <t>135728374</t>
+  </si>
+  <si>
+    <t>135776357</t>
+  </si>
+  <si>
+    <t>135830066</t>
+  </si>
+  <si>
+    <t>135786851</t>
+  </si>
+  <si>
+    <t>135747838</t>
+  </si>
+  <si>
+    <t>135751871</t>
+  </si>
+  <si>
+    <t>135752734</t>
+  </si>
+  <si>
+    <t>135755034</t>
+  </si>
+  <si>
+    <t>135758273</t>
+  </si>
+  <si>
+    <t>Processado</t>
+  </si>
+  <si>
+    <t>&lt;u&gt;Documentos indexados&lt;/u&gt;:1-&gt; Relatório de Recusas 17.12.2025 a 24.12.2025.xlsx.</t>
+  </si>
+  <si>
+    <t>Alerta: Falha ao anexar arquivo. Tela - ANEXAR DOCUMENTOS - LI - Não apresentada</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <numFmts count="0"/>
   <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
@@ -237,34 +265,34 @@
     </border>
   </borders>
   <cellStyleXfs count="1">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf borderId="0" fillId="0" fontId="0" numFmtId="0"/>
   </cellStyleXfs>
   <cellXfs count="7">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+    <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0"/>
+    <xf applyAlignment="1" applyNumberFormat="1" borderId="0" fillId="0" fontId="0" numFmtId="49" xfId="0">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+    <xf applyAlignment="1" borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="49" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf applyAlignment="1" applyFill="1" applyFont="1" applyNumberFormat="1" borderId="0" fillId="2" fontId="1" numFmtId="49" xfId="0">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf applyAlignment="1" applyFill="1" applyFont="1" borderId="0" fillId="2" fontId="1" numFmtId="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf applyAlignment="1" applyFill="1" applyFont="1" borderId="0" fillId="3" fontId="1" numFmtId="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf applyAlignment="1" applyFont="1" borderId="0" fillId="0" fontId="3" numFmtId="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle builtinId="0" name="Normal" xfId="0"/>
   </cellStyles>
   <dxfs count="0"/>
-  <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
+  <tableStyles count="0" defaultPivotStyle="PivotStyleLight16" defaultTableStyle="TableStyleMedium2"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
@@ -281,10 +309,10 @@
   <a:themeElements>
     <a:clrScheme name="Office">
       <a:dk1>
-        <a:sysClr val="windowText" lastClr="000000"/>
+        <a:sysClr lastClr="000000" val="windowText"/>
       </a:dk1>
       <a:lt1>
-        <a:sysClr val="window" lastClr="FFFFFF"/>
+        <a:sysClr lastClr="FFFFFF" val="window"/>
       </a:lt1>
       <a:dk2>
         <a:srgbClr val="44546A"/>
@@ -319,7 +347,7 @@
     </a:clrScheme>
     <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
+        <a:latin panose="020F0302020204030204" typeface="Calibri Light"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="游ゴシック Light"/>
@@ -371,7 +399,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
+        <a:latin panose="020F0502020204030204" typeface="Calibri"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="游ゴシック"/>
@@ -482,21 +510,21 @@
         </a:gradFill>
       </a:fillStyleLst>
       <a:lnStyleLst>
-        <a:ln w="6350" cap="flat" cmpd="sng" algn="ctr">
+        <a:ln algn="ctr" cap="flat" cmpd="sng" w="6350">
           <a:solidFill>
             <a:schemeClr val="phClr"/>
           </a:solidFill>
           <a:prstDash val="solid"/>
           <a:miter lim="800000"/>
         </a:ln>
-        <a:ln w="12700" cap="flat" cmpd="sng" algn="ctr">
+        <a:ln algn="ctr" cap="flat" cmpd="sng" w="12700">
           <a:solidFill>
             <a:schemeClr val="phClr"/>
           </a:solidFill>
           <a:prstDash val="solid"/>
           <a:miter lim="800000"/>
         </a:ln>
-        <a:ln w="19050" cap="flat" cmpd="sng" algn="ctr">
+        <a:ln algn="ctr" cap="flat" cmpd="sng" w="19050">
           <a:solidFill>
             <a:schemeClr val="phClr"/>
           </a:solidFill>
@@ -513,7 +541,7 @@
         </a:effectStyle>
         <a:effectStyle>
           <a:effectLst>
-            <a:outerShdw blurRad="57150" dist="19050" dir="5400000" algn="ctr" rotWithShape="0">
+            <a:outerShdw algn="ctr" blurRad="57150" dir="5400000" dist="19050" rotWithShape="0">
               <a:srgbClr val="000000">
                 <a:alpha val="63000"/>
               </a:srgbClr>
@@ -565,25 +593,25 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" name="Office Theme" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <sheetPr>
     <pageSetUpPr autoPageBreaks="0"/>
   </sheetPr>
-  <dimension ref="A1:F40"/>
+  <dimension ref="A1:G46"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="2" width="16.7109375" style="1" customWidth="1" collapsed="1"/>
-    <col min="3" max="4" width="49.5703125" style="2" customWidth="1" collapsed="1"/>
-    <col min="5" max="5" width="16.42578125" style="2" customWidth="1" collapsed="1"/>
-    <col min="6" max="6" width="84.7109375" style="2" customWidth="1" collapsed="1"/>
-    <col min="7" max="16384" width="9.140625" style="2" collapsed="1"/>
+    <col min="1" max="2" customWidth="true" style="1" width="16.7109375" collapsed="true"/>
+    <col min="3" max="4" customWidth="true" style="2" width="49.5703125" collapsed="true"/>
+    <col min="5" max="5" customWidth="true" style="2" width="16.42578125" collapsed="true"/>
+    <col min="6" max="6" customWidth="true" style="2" width="84.7109375" collapsed="true"/>
+    <col min="7" max="16384" style="2" width="9.140625" collapsed="true"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -608,733 +636,943 @@
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A2" s="6">
-        <v>134572297</v>
+        <v>135746284</v>
       </c>
       <c r="B2" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>47</v>
+        <v>8</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="F2"/>
+        <v>54</v>
+      </c>
+      <c r="F2" t="s">
+        <v>55</v>
+      </c>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B3" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>47</v>
+        <v>8</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="F3"/>
+        <v>54</v>
+      </c>
+      <c r="F3" t="s">
+        <v>55</v>
+      </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B4" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>47</v>
+        <v>8</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="F4"/>
+        <v>54</v>
+      </c>
+      <c r="F4" t="s">
+        <v>55</v>
+      </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B5" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>47</v>
+        <v>8</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="F5"/>
+        <v>54</v>
+      </c>
+      <c r="F5" t="s">
+        <v>55</v>
+      </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" s="1" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B6" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>47</v>
+        <v>8</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="F6"/>
+        <v>54</v>
+      </c>
+      <c r="F6" t="s">
+        <v>55</v>
+      </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" s="1" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B7" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>47</v>
+        <v>8</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="F7"/>
+        <v>54</v>
+      </c>
+      <c r="F7" t="s">
+        <v>55</v>
+      </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" s="1" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="B8" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>47</v>
+        <v>8</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="F8"/>
+        <v>54</v>
+      </c>
+      <c r="F8" t="s">
+        <v>55</v>
+      </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B9" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>47</v>
+        <v>8</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="F9"/>
+        <v>54</v>
+      </c>
+      <c r="F9" t="s">
+        <v>55</v>
+      </c>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A10" s="1" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="B10" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>47</v>
+        <v>8</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="F10"/>
+        <v>54</v>
+      </c>
+      <c r="F10" t="s">
+        <v>55</v>
+      </c>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A11" s="1" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="B11" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>47</v>
+        <v>8</v>
       </c>
       <c r="E11" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="F11"/>
+        <v>54</v>
+      </c>
+      <c r="F11" t="s">
+        <v>55</v>
+      </c>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A12" s="1" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B12" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>47</v>
+        <v>8</v>
       </c>
       <c r="E12" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="F12"/>
+        <v>54</v>
+      </c>
+      <c r="F12" t="s">
+        <v>55</v>
+      </c>
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A13" s="1" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B13" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>47</v>
+        <v>8</v>
       </c>
       <c r="E13" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="F13"/>
+        <v>54</v>
+      </c>
+      <c r="F13" t="s">
+        <v>55</v>
+      </c>
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A14" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B14" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>47</v>
+        <v>8</v>
       </c>
       <c r="E14" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="F14"/>
+        <v>54</v>
+      </c>
+      <c r="F14" t="s">
+        <v>55</v>
+      </c>
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A15" s="1" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="B15" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>47</v>
+        <v>8</v>
       </c>
       <c r="E15" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="F15"/>
+        <v>54</v>
+      </c>
+      <c r="F15" t="s">
+        <v>55</v>
+      </c>
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A16" s="1" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B16" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>47</v>
+        <v>8</v>
       </c>
       <c r="E16" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="F16"/>
+        <v>54</v>
+      </c>
+      <c r="F16" t="s">
+        <v>55</v>
+      </c>
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A17" s="1" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="B17" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>47</v>
+        <v>8</v>
       </c>
       <c r="E17" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="F17"/>
+        <v>54</v>
+      </c>
+      <c r="F17" t="s">
+        <v>55</v>
+      </c>
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A18" s="1" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="B18" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>47</v>
+        <v>8</v>
       </c>
       <c r="E18" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="F18"/>
+        <v>54</v>
+      </c>
+      <c r="F18" t="s">
+        <v>55</v>
+      </c>
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A19" s="1" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="B19" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>47</v>
+        <v>8</v>
       </c>
       <c r="E19" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="F19"/>
+        <v>54</v>
+      </c>
+      <c r="F19" t="s">
+        <v>55</v>
+      </c>
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A20" s="1" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="B20" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>47</v>
+        <v>8</v>
       </c>
       <c r="E20" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="F20"/>
+        <v>54</v>
+      </c>
+      <c r="F20" t="s">
+        <v>55</v>
+      </c>
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A21" s="1" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="B21" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>47</v>
+        <v>8</v>
       </c>
       <c r="E21" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="F21"/>
+        <v>54</v>
+      </c>
+      <c r="F21" t="s">
+        <v>55</v>
+      </c>
     </row>
     <row r="22" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A22" s="1" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="B22" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>47</v>
+        <v>8</v>
       </c>
       <c r="E22" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="F22"/>
+        <v>54</v>
+      </c>
+      <c r="F22" t="s">
+        <v>55</v>
+      </c>
     </row>
     <row r="23" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A23" s="1" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B23" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>47</v>
+        <v>8</v>
       </c>
       <c r="E23" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="F23"/>
+        <v>54</v>
+      </c>
+      <c r="F23" t="s">
+        <v>55</v>
+      </c>
     </row>
     <row r="24" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A24" s="1" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B24" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C24" s="2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>47</v>
+        <v>8</v>
       </c>
       <c r="E24" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="F24"/>
+        <v>54</v>
+      </c>
+      <c r="F24" t="s">
+        <v>55</v>
+      </c>
     </row>
     <row r="25" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A25" s="1" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="B25" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C25" s="2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D25" s="2" t="s">
-        <v>47</v>
+        <v>8</v>
       </c>
       <c r="E25" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="F25"/>
+        <v>54</v>
+      </c>
+      <c r="F25" t="s">
+        <v>55</v>
+      </c>
     </row>
     <row r="26" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A26" s="1" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="B26" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C26" s="2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D26" s="2" t="s">
-        <v>47</v>
+        <v>8</v>
       </c>
       <c r="E26" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="F26"/>
+        <v>54</v>
+      </c>
+      <c r="F26" t="s">
+        <v>55</v>
+      </c>
     </row>
     <row r="27" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A27" s="1" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B27" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C27" s="2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D27" s="2" t="s">
-        <v>47</v>
+        <v>8</v>
       </c>
       <c r="E27" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="F27"/>
+        <v>54</v>
+      </c>
+      <c r="F27" t="s">
+        <v>55</v>
+      </c>
     </row>
     <row r="28" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A28" s="1" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="B28" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C28" s="2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D28" s="2" t="s">
-        <v>47</v>
+        <v>8</v>
       </c>
       <c r="E28" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="F28"/>
+        <v>54</v>
+      </c>
+      <c r="F28" t="s">
+        <v>55</v>
+      </c>
     </row>
     <row r="29" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A29" s="1" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="B29" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C29" s="2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D29" s="2" t="s">
-        <v>47</v>
+        <v>8</v>
       </c>
       <c r="E29" s="2" t="s">
-        <v>6</v>
+        <v>54</v>
+      </c>
+      <c r="F29" t="s">
+        <v>55</v>
       </c>
     </row>
     <row r="30" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A30" s="1" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="B30" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C30" s="2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D30" s="2" t="s">
-        <v>47</v>
+        <v>8</v>
       </c>
       <c r="E30" s="2" t="s">
-        <v>6</v>
+        <v>54</v>
+      </c>
+      <c r="F30" t="s">
+        <v>55</v>
       </c>
     </row>
     <row r="31" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A31" s="1" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B31" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C31" s="2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D31" s="2" t="s">
-        <v>47</v>
+        <v>8</v>
       </c>
       <c r="E31" s="2" t="s">
-        <v>6</v>
+        <v>54</v>
+      </c>
+      <c r="F31" t="s">
+        <v>55</v>
       </c>
     </row>
     <row r="32" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A32" s="1" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B32" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C32" s="2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D32" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E32" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="F32" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="33" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A33" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="B33" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C33" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D33" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E33" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="F33" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="34" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A34" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="B34" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C34" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D34" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E34" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="F34" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="35" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A35" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="B35" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C35" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D35" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E35" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="F35" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="36" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A36" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="B36" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C36" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D36" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E36" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="F36" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="37" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A37" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="B37" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C37" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D37" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E37" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="F37" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="38" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A38" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="B38" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C38" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D38" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E38" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="F38" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="39" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A39" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="B39" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C39" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D39" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E39" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="F39" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="40" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A40" s="1" t="s">
         <v>47</v>
       </c>
-      <c r="E32" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="33" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A33" s="1" t="s">
-        <v>39</v>
-      </c>
-      <c r="B33" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C33" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="D33" s="2" t="s">
-        <v>47</v>
-      </c>
-      <c r="E33" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="34" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A34" s="1" t="s">
-        <v>40</v>
-      </c>
-      <c r="B34" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C34" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="D34" s="2" t="s">
-        <v>47</v>
-      </c>
-      <c r="E34" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="35" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A35" s="1" t="s">
-        <v>41</v>
-      </c>
-      <c r="B35" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C35" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="D35" s="2" t="s">
-        <v>47</v>
-      </c>
-      <c r="E35" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="36" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A36" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="B36" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C36" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="D36" s="2" t="s">
-        <v>47</v>
-      </c>
-      <c r="E36" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="37" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A37" s="1" t="s">
-        <v>43</v>
-      </c>
-      <c r="B37" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C37" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="D37" s="2" t="s">
-        <v>47</v>
-      </c>
-      <c r="E37" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="38" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A38" s="1" t="s">
-        <v>44</v>
-      </c>
-      <c r="B38" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C38" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="D38" s="2" t="s">
-        <v>47</v>
-      </c>
-      <c r="E38" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="39" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A39" s="1" t="s">
-        <v>45</v>
-      </c>
-      <c r="B39" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C39" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="D39" s="2" t="s">
-        <v>47</v>
-      </c>
-      <c r="E39" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="40" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A40" s="1" t="s">
-        <v>46</v>
-      </c>
       <c r="B40" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C40" s="2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D40" s="2" t="s">
-        <v>47</v>
+        <v>8</v>
       </c>
       <c r="E40" s="2" t="s">
-        <v>6</v>
+        <v>54</v>
+      </c>
+      <c r="F40" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="41" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A41" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="B41" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C41" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D41" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E41" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="F41" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="42" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A42" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="B42" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C42" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D42" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E42" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="F42" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="43" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A43" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="B43" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C43" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D43" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E43" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="F43" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="44" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A44" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="B44" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C44" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D44" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E44" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="F44" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="45" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A45" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="B45" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C45" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D45" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E45" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="F45" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="46" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A46" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="B46" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C46" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D46" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E46" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="F46" t="s">
+        <v>55</v>
       </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:F1" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
   <phoneticPr fontId="2" type="noConversion"/>
-  <pageMargins left="0.51181102362204722" right="0.51181102362204722" top="0.78740157480314965" bottom="0.78740157480314965" header="0.31496062992125984" footer="0.31496062992125984"/>
-  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+  <pageMargins bottom="0.78740157480314965" footer="0.31496062992125984" header="0.31496062992125984" left="0.51181102362204722" right="0.51181102362204722" top="0.78740157480314965"/>
+  <pageSetup orientation="portrait" paperSize="9" r:id="rId1"/>
   <headerFooter>
-    <oddFooter>&amp;L&amp;"Calibri,Regular"&amp;08&amp;B&amp;K7F7F7FClassificação Allianz:&amp;K595959 &amp;K7F7F7FINTERNO</oddFooter>
-    <evenFooter>&amp;L&amp;"Calibri,Regular"&amp;08&amp;B&amp;K7F7F7FClassificação Allianz:&amp;K595959 &amp;K7F7F7FINTERNO</evenFooter>
-    <firstFooter>&amp;L&amp;"Calibri,Regular"&amp;08&amp;B&amp;K7F7F7FClassificação Allianz:&amp;K595959 &amp;K7F7F7FINTERNO</firstFooter>
+    <oddFooter><![CDATA[&L&"Calibri,Regular"&08&B&K7F7F7FClassificação Allianz:&K595959 &K7F7F7FINTERNO]]></oddFooter>
+    <evenFooter><![CDATA[&L&"Calibri,Regular"&08&B&K7F7F7FClassificação Allianz:&K595959 &K7F7F7FINTERNO]]></evenFooter>
+    <firstFooter><![CDATA[&L&"Calibri,Regular"&08&B&K7F7F7FClassificação Allianz:&K595959 &K7F7F7FINTERNO]]></firstFooter>
   </headerFooter>
 </worksheet>
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<WrappedLabelHistory xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns="http://www.boldonjames.com/2016/02/Classifier/internal/wrappedLabelHistory">
+  <Value>PD94bWwgdmVyc2lvbj0iMS4wIiBlbmNvZGluZz0idXMtYXNjaWkiPz48bGFiZWxIaXN0b3J5IHhtbG5zOnhzZD0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEiIHhtbG5zOnhzaT0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEtaW5zdGFuY2UiIHhtbG5zPSJodHRwOi8vd3d3LmJvbGRvbmphbWVzLmNvbS8yMDE2LzAyL0NsYXNzaWZpZXIvaW50ZXJuYWwvbGFiZWxIaXN0b3J5Ij48aXRlbT48c2lzbCBzaXNsVmVyc2lvbj0iMCIgcG9saWN5PSJkZDIwZDIzOS1hN2U2LTRjNDktODc3Yy00NWI3YjQzMzU5Y2IiIG9yaWdpbj0iZGVmYXVsdFZhbHVlIj48ZWxlbWVudCB1aWQ9IjUwMjdiYTAxLWUyMjEtNDY1MC04N2M5LWI4ZWVkYTFmZWIyZiIgdmFsdWU9IiIgeG1sbnM9Imh0dHA6Ly93d3cuYm9sZG9uamFtZXMuY29tLzIwMDgvMDEvc2llL2ludGVybmFsL2xhYmVsIiAvPjwvc2lzbD48VXNlck5hbWU+QUxMSUFOWlxCRTAwMTUxPC9Vc2VyTmFtZT48RGF0ZVRpbWU+MTcvMDkvMjAxOSAxODoxMjoxMjwvRGF0ZVRpbWU+PExhYmVsU3RyaW5nPiAgICAgICAxNy8wOS8yMDE5ICBJTlRFUk5PICA8L0xhYmVsU3RyaW5nPjwvaXRlbT48L2xhYmVsSGlzdG9yeT4=</Value>
+</WrappedLabelHistory>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <sisl xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns="http://www.boldonjames.com/2008/01/sie/internal/label" sislVersion="0" policy="dd20d239-a7e6-4c49-877c-45b7b43359cb" origin="defaultValue">
   <element uid="5027ba01-e221-4650-87c9-b8eeda1feb2f" value=""/>
 </sisl>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<WrappedLabelHistory xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns="http://www.boldonjames.com/2016/02/Classifier/internal/wrappedLabelHistory">
-  <Value>PD94bWwgdmVyc2lvbj0iMS4wIiBlbmNvZGluZz0idXMtYXNjaWkiPz48bGFiZWxIaXN0b3J5IHhtbG5zOnhzZD0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEiIHhtbG5zOnhzaT0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEtaW5zdGFuY2UiIHhtbG5zPSJodHRwOi8vd3d3LmJvbGRvbmphbWVzLmNvbS8yMDE2LzAyL0NsYXNzaWZpZXIvaW50ZXJuYWwvbGFiZWxIaXN0b3J5Ij48aXRlbT48c2lzbCBzaXNsVmVyc2lvbj0iMCIgcG9saWN5PSJkZDIwZDIzOS1hN2U2LTRjNDktODc3Yy00NWI3YjQzMzU5Y2IiIG9yaWdpbj0iZGVmYXVsdFZhbHVlIj48ZWxlbWVudCB1aWQ9IjUwMjdiYTAxLWUyMjEtNDY1MC04N2M5LWI4ZWVkYTFmZWIyZiIgdmFsdWU9IiIgeG1sbnM9Imh0dHA6Ly93d3cuYm9sZG9uamFtZXMuY29tLzIwMDgvMDEvc2llL2ludGVybmFsL2xhYmVsIiAvPjwvc2lzbD48VXNlck5hbWU+QUxMSUFOWlxCRTAwMTUxPC9Vc2VyTmFtZT48RGF0ZVRpbWU+MTcvMDkvMjAxOSAxODoxMjoxMjwvRGF0ZVRpbWU+PExhYmVsU3RyaW5nPiAgICAgICAxNy8wOS8yMDE5ICBJTlRFUk5PICA8L0xhYmVsU3RyaW5nPjwvaXRlbT48L2xhYmVsSGlzdG9yeT4=</Value>
-</WrappedLabelHistory>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D7CACE11-ACDB-4C58-86FC-5A54EABF64E3}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
+    <ds:schemaRef ds:uri="http://www.boldonjames.com/2016/02/Classifier/internal/wrappedLabelHistory"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{758EF150-7616-48C2-9614-E853EDB7BDD0}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
     <ds:schemaRef ds:uri="http://www.boldonjames.com/2008/01/sie/internal/label"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D7CACE11-ACDB-4C58-86FC-5A54EABF64E3}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
-    <ds:schemaRef ds:uri="http://www.boldonjames.com/2016/02/Classifier/internal/wrappedLabelHistory"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>